--- a/다과_구매목록.xlsx
+++ b/다과_구매목록.xlsx
@@ -577,7 +577,7 @@
         <v>3580</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F5" s="6">
         <f>D5*E5</f>
@@ -609,14 +609,14 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>[오뗄두스] 사브레 쿠키 4종 (택1)</t>
+          <t>[모리나가] 밀크, 소금 카라멜 2종 (택1)</t>
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>6500</v>
+        <v>3400</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F6" s="6">
         <f>D6*E6</f>
@@ -626,53 +626,53 @@
         <v>0</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>9999</v>
+        <v>999</v>
       </c>
       <c r="I6" s="7" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5003504</t>
+          <t>https://www.kurly.com/goods/1000490151</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>필수</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>필수</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>[모리나가] 밀크, 소금 카라멜 2종 (택1)</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>3400</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="F7" s="6">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>추천</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>견과/건과일</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[KF365] 기본에 충실한 하루견과(20g*14봉)</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>13900</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2">
         <f>D7*E7</f>
         <v/>
       </c>
-      <c r="G7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="5" t="n">
-        <v>999</v>
-      </c>
-      <c r="I7" s="7" t="inlineStr">
-        <is>
-          <t>https://www.kurly.com/goods/1000490151</t>
-        </is>
-      </c>
-      <c r="J7" s="5" t="inlineStr"/>
+      <c r="G7" t="n">
+        <v>22</v>
+      </c>
+      <c r="H7" t="n">
+        <v>9999</v>
+      </c>
+      <c r="I7" s="8" t="inlineStr">
+        <is>
+          <t>https://www.kurly.com/goods/1000973922</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -687,11 +687,11 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>[KF365] 기본에 충실한 하루견과(20g*14봉)</t>
+          <t>호두 500g</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>13900</v>
+        <v>12900</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
@@ -701,14 +701,14 @@
         <v/>
       </c>
       <c r="G8" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="H8" t="n">
         <v>9999</v>
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000973922</t>
+          <t>https://www.kurly.com/goods/5051673</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -726,28 +726,28 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>호두 500g</t>
+          <t>[원더풀] 구운 아몬드 무염 &amp; 가염 (택1)</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>12900</v>
+        <v>7990</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" s="2">
         <f>D9*E9</f>
         <v/>
       </c>
       <c r="G9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H9" t="n">
         <v>9999</v>
       </c>
       <c r="I9" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5051673</t>
+          <t>https://www.kurly.com/goods/5027971</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -760,33 +760,33 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>견과/건과일</t>
+          <t>빵/케이크류</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>[원더풀] 구운 아몬드 무염 &amp; 가염 (택1)</t>
+          <t>[메종엠오] 마들렌 3종 (택1)</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>7990</v>
+        <v>3500</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F10" s="2">
         <f>D10*E10</f>
         <v/>
       </c>
       <c r="G10" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>9999</v>
       </c>
       <c r="I10" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5027971</t>
+          <t>https://www.kurly.com/goods/5009371</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -804,14 +804,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>[메종엠오] 마들렌 3종 (택1)</t>
+          <t>[브레댄코] 봉주르 카스테라 2종 (택1)</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>3500</v>
+        <v>11500</v>
       </c>
       <c r="E11" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F11" s="2">
         <f>D11*E11</f>
@@ -825,7 +825,7 @@
       </c>
       <c r="I11" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5009371</t>
+          <t>https://www.kurly.com/goods/5074339</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
@@ -838,16 +838,16 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>빵/케이크류</t>
+          <t>스낵/과자</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>[브레댄코] 봉주르 카스테라 2종 (택1)</t>
+          <t>[CJ] 맛밤 4개입</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>11500</v>
+        <v>7280</v>
       </c>
       <c r="E12" t="n">
         <v>3</v>
@@ -857,14 +857,14 @@
         <v/>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H12" t="n">
         <v>9999</v>
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5074339</t>
+          <t>https://www.kurly.com/goods/5077640</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
@@ -882,28 +882,28 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>[CJ] 맛밤 4개입</t>
+          <t xml:space="preserve">[Lay's] 감자칩 7종 (택1) </t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>7280</v>
+        <v>4780</v>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F13" s="2">
         <f>D13*E13</f>
         <v/>
       </c>
       <c r="G13" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H13" t="n">
         <v>9999</v>
       </c>
       <c r="I13" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5077640</t>
+          <t>https://www.kurly.com/goods/5013230</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -921,28 +921,28 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Lay's] 감자칩 7종 (택1) </t>
+          <t>[크라운] 참쌀선과 253g (44봉)</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>4780</v>
+        <v>4150</v>
       </c>
       <c r="E14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F14" s="2">
         <f>D14*E14</f>
         <v/>
       </c>
       <c r="G14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H14" t="n">
         <v>9999</v>
       </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5013230</t>
+          <t>https://www.kurly.com/goods/1000178191</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -955,16 +955,16 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>스낵/과자</t>
+          <t>에너지바/단백질</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>[크라운] 참쌀선과 253g (44봉)</t>
+          <t>[네이처밸리] 그래놀라 바 3종 ,택1</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>4150</v>
+        <v>3980</v>
       </c>
       <c r="E15" t="n">
         <v>6</v>
@@ -974,14 +974,14 @@
         <v/>
       </c>
       <c r="G15" t="n">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="H15" t="n">
         <v>9999</v>
       </c>
       <c r="I15" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000178191</t>
+          <t>https://www.kurly.com/goods/5007664</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -999,28 +999,28 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>[네이처밸리] 그래놀라 바 3종 ,택1</t>
+          <t>[닥터넛츠] 저당 다크초콜릿 견과 3종</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>3980</v>
+        <v>9970</v>
       </c>
       <c r="E16" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F16" s="2">
         <f>D16*E16</f>
         <v/>
       </c>
       <c r="G16" t="n">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="H16" t="n">
         <v>9999</v>
       </c>
       <c r="I16" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5007664</t>
+          <t>https://www.kurly.com/goods/5055529</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
@@ -1033,33 +1033,33 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>에너지바/단백질</t>
+          <t>일본 과자</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>[닥터넛츠] 저당 다크초콜릿 견과 3종</t>
+          <t>[사토제과] 아주끼 모나카</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>9970</v>
+        <v>7380</v>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F17" s="2">
         <f>D17*E17</f>
         <v/>
       </c>
       <c r="G17" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>9999</v>
+        <v>999</v>
       </c>
       <c r="I17" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5055529</t>
+          <t>https://www.kurly.com/goods/5081428</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -1084,7 +1084,7 @@
         <v>5280</v>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F18" s="2">
         <f>D18*E18</f>

--- a/다과_구매목록.xlsx
+++ b/다과_구매목록.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -492,7 +492,7 @@
         </is>
       </c>
       <c r="D2" s="3">
-        <f>SUM(F5:F37)</f>
+        <f>SUM(F5:F38)</f>
         <v/>
       </c>
       <c r="E2" t="inlineStr">
@@ -889,7 +889,7 @@
         <v>3980</v>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F13" s="2">
         <f>D13*E13</f>
@@ -1311,28 +1311,28 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>[해태] 오예스 미니 크림소다맛 192g</t>
+          <t>[크라운] 쿠크다스 2종 (택1)</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>2506</v>
+        <v>4380</v>
       </c>
       <c r="E24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F24" s="2">
         <f>D24*E24</f>
         <v/>
       </c>
       <c r="G24" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>187</v>
+        <v>999</v>
       </c>
       <c r="I24" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1002225099</t>
+          <t>https://www.kurly.com/goods/5121160</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
@@ -1350,14 +1350,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>[크라운] 쿠크다스 2종 (택1)</t>
+          <t>[롯데] 마가렛트 오리지널 352g</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>4380</v>
+        <v>5440</v>
       </c>
       <c r="E25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F25" s="2">
         <f>D25*E25</f>
@@ -1367,11 +1367,11 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>999</v>
+        <v>956</v>
       </c>
       <c r="I25" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5121160</t>
+          <t>https://www.kurly.com/goods/1000339526</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
@@ -1389,14 +1389,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>[롯데] 마가렛트 오리지널 352g</t>
+          <t>[브레댄코] 리얼 브라우니 쿠키 2종 (택1)</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>5440</v>
+        <v>3690</v>
       </c>
       <c r="E26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F26" s="2">
         <f>D26*E26</f>
@@ -1406,11 +1406,11 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>956</v>
+        <v>9999</v>
       </c>
       <c r="I26" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000339526</t>
+          <t>https://www.kurly.com/goods/5061562</t>
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
@@ -1428,11 +1428,11 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>[브레댄코] 리얼 브라우니 쿠키 2종 (택1)</t>
+          <t>[오리온] 예감 치즈 그라탕 204g</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>3690</v>
+        <v>3580</v>
       </c>
       <c r="E27" t="n">
         <v>3</v>
@@ -1445,11 +1445,11 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>9999</v>
+        <v>999</v>
       </c>
       <c r="I27" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5061562</t>
+          <t>https://www.kurly.com/goods/5095164</t>
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
@@ -1467,11 +1467,11 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>[오리온] 예감 치즈 그라탕 204g</t>
+          <t>[밀카] 베스트 초코쿠키 &amp; 웨하스 4종 (택1)</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>3580</v>
+        <v>4070</v>
       </c>
       <c r="E28" t="n">
         <v>3</v>
@@ -1481,14 +1481,14 @@
         <v/>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H28" t="n">
-        <v>999</v>
+        <v>9999</v>
       </c>
       <c r="I28" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5095164</t>
+          <t>https://www.kurly.com/goods/5067558</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
@@ -1501,33 +1501,33 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>티/커피 스틱</t>
+          <t>쿠키/비스킷(개별포장)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>[이디야] 라떼 30개입 3종 (택1)</t>
+          <t>[오리온] 예감 오리지널 192g</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>10640</v>
+        <v>3580</v>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F29" s="2">
         <f>D29*E29</f>
         <v/>
       </c>
       <c r="G29" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
         <v>999</v>
       </c>
       <c r="I29" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000492705</t>
+          <t>https://www.kurly.com/goods/5095165</t>
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
@@ -1540,16 +1540,16 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>티/커피 스틱</t>
+          <t>쿠키/비스킷(개별포장)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>[샘표] 순작 유기농보리차 (10g X 30개)</t>
+          <t>[롯데] 제로 초코파이 336g</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>3180</v>
+        <v>5100</v>
       </c>
       <c r="E30" t="n">
         <v>2</v>
@@ -1562,11 +1562,11 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>999</v>
+        <v>729</v>
       </c>
       <c r="I30" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1001032586</t>
+          <t>https://www.kurly.com/goods/1000958611</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
@@ -1843,6 +1843,45 @@
         </is>
       </c>
       <c r="J37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>추천</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>파이/케이크(개별포장)</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>[해태] 오예스 미니 크림소다맛 192g</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>2506</v>
+      </c>
+      <c r="E38" t="n">
+        <v>5</v>
+      </c>
+      <c r="F38" s="2">
+        <f>D38*E38</f>
+        <v/>
+      </c>
+      <c r="G38" t="n">
+        <v>30</v>
+      </c>
+      <c r="H38" t="n">
+        <v>187</v>
+      </c>
+      <c r="I38" s="8" t="inlineStr">
+        <is>
+          <t>https://www.kurly.com/goods/1002225099</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1879,6 +1918,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I36" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="rId34"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1890,7 +1930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1928,15 +1968,15 @@
         </is>
       </c>
       <c r="B2">
-        <f>COUNTIF(구매목록!B5:B37,A2)</f>
+        <f>COUNTIF(구매목록!B5:B38,A2)</f>
         <v/>
       </c>
       <c r="C2" s="2">
-        <f>SUMIF(구매목록!B5:B37,A2,구매목록!F5:F37)</f>
+        <f>SUMIF(구매목록!B5:B38,A2,구매목록!F5:F38)</f>
         <v/>
       </c>
       <c r="D2" s="9">
-        <f>C2/SUM($C$2:$C$9)</f>
+        <f>C2/SUM($C$2:$C$8)</f>
         <v/>
       </c>
     </row>
@@ -1947,15 +1987,15 @@
         </is>
       </c>
       <c r="B3">
-        <f>COUNTIF(구매목록!B5:B37,A3)</f>
+        <f>COUNTIF(구매목록!B5:B38,A3)</f>
         <v/>
       </c>
       <c r="C3" s="2">
-        <f>SUMIF(구매목록!B5:B37,A3,구매목록!F5:F37)</f>
+        <f>SUMIF(구매목록!B5:B38,A3,구매목록!F5:F38)</f>
         <v/>
       </c>
       <c r="D3" s="9">
-        <f>C3/SUM($C$2:$C$9)</f>
+        <f>C3/SUM($C$2:$C$8)</f>
         <v/>
       </c>
     </row>
@@ -1966,15 +2006,15 @@
         </is>
       </c>
       <c r="B4">
-        <f>COUNTIF(구매목록!B5:B37,A4)</f>
+        <f>COUNTIF(구매목록!B5:B38,A4)</f>
         <v/>
       </c>
       <c r="C4" s="2">
-        <f>SUMIF(구매목록!B5:B37,A4,구매목록!F5:F37)</f>
+        <f>SUMIF(구매목록!B5:B38,A4,구매목록!F5:F38)</f>
         <v/>
       </c>
       <c r="D4" s="9">
-        <f>C4/SUM($C$2:$C$9)</f>
+        <f>C4/SUM($C$2:$C$8)</f>
         <v/>
       </c>
     </row>
@@ -1985,15 +2025,15 @@
         </is>
       </c>
       <c r="B5">
-        <f>COUNTIF(구매목록!B5:B37,A5)</f>
+        <f>COUNTIF(구매목록!B5:B38,A5)</f>
         <v/>
       </c>
       <c r="C5" s="2">
-        <f>SUMIF(구매목록!B5:B37,A5,구매목록!F5:F37)</f>
+        <f>SUMIF(구매목록!B5:B38,A5,구매목록!F5:F38)</f>
         <v/>
       </c>
       <c r="D5" s="9">
-        <f>C5/SUM($C$2:$C$9)</f>
+        <f>C5/SUM($C$2:$C$8)</f>
         <v/>
       </c>
     </row>
@@ -2004,15 +2044,15 @@
         </is>
       </c>
       <c r="B6">
-        <f>COUNTIF(구매목록!B5:B37,A6)</f>
+        <f>COUNTIF(구매목록!B5:B38,A6)</f>
         <v/>
       </c>
       <c r="C6" s="2">
-        <f>SUMIF(구매목록!B5:B37,A6,구매목록!F5:F37)</f>
+        <f>SUMIF(구매목록!B5:B38,A6,구매목록!F5:F38)</f>
         <v/>
       </c>
       <c r="D6" s="9">
-        <f>C6/SUM($C$2:$C$9)</f>
+        <f>C6/SUM($C$2:$C$8)</f>
         <v/>
       </c>
     </row>
@@ -2023,15 +2063,15 @@
         </is>
       </c>
       <c r="B7">
-        <f>COUNTIF(구매목록!B5:B37,A7)</f>
+        <f>COUNTIF(구매목록!B5:B38,A7)</f>
         <v/>
       </c>
       <c r="C7" s="2">
-        <f>SUMIF(구매목록!B5:B37,A7,구매목록!F5:F37)</f>
+        <f>SUMIF(구매목록!B5:B38,A7,구매목록!F5:F38)</f>
         <v/>
       </c>
       <c r="D7" s="9">
-        <f>C7/SUM($C$2:$C$9)</f>
+        <f>C7/SUM($C$2:$C$8)</f>
         <v/>
       </c>
     </row>
@@ -2042,34 +2082,15 @@
         </is>
       </c>
       <c r="B8">
-        <f>COUNTIF(구매목록!B5:B37,A8)</f>
+        <f>COUNTIF(구매목록!B5:B38,A8)</f>
         <v/>
       </c>
       <c r="C8" s="2">
-        <f>SUMIF(구매목록!B5:B37,A8,구매목록!F5:F37)</f>
+        <f>SUMIF(구매목록!B5:B38,A8,구매목록!F5:F38)</f>
         <v/>
       </c>
       <c r="D8" s="9">
-        <f>C8/SUM($C$2:$C$9)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>티/커피 스틱</t>
-        </is>
-      </c>
-      <c r="B9">
-        <f>COUNTIF(구매목록!B5:B37,A9)</f>
-        <v/>
-      </c>
-      <c r="C9" s="2">
-        <f>SUMIF(구매목록!B5:B37,A9,구매목록!F5:F37)</f>
-        <v/>
-      </c>
-      <c r="D9" s="9">
-        <f>C9/SUM($C$2:$C$9)</f>
+        <f>C8/SUM($C$2:$C$8)</f>
         <v/>
       </c>
     </row>

--- a/다과_구매목록.xlsx
+++ b/다과_구매목록.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -492,7 +492,7 @@
         </is>
       </c>
       <c r="D2" s="3">
-        <f>SUM(F5:F38)</f>
+        <f>SUM(F5:F40)</f>
         <v/>
       </c>
       <c r="E2" t="inlineStr">
@@ -850,7 +850,7 @@
         <v>7380</v>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F12" s="2">
         <f>D12*E12</f>
@@ -921,11 +921,11 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>[댄케이크] 싱글서브 초콜릿칩 쿠키 18입</t>
+          <t>[하리보] 미니스 젤리 7종, 택1</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>13500</v>
+        <v>6980</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -942,7 +942,7 @@
       </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5043922</t>
+          <t>https://www.kurly.com/goods/5044322</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -960,28 +960,28 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>[동원] Dole 컵젤리 200g 7종</t>
+          <t>[하리보] 폭신한 과일맛 젤리 3종, 택1</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>1980</v>
+        <v>2180</v>
       </c>
       <c r="E15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F15" s="2">
         <f>D15*E15</f>
         <v/>
       </c>
       <c r="G15" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>481</v>
+        <v>835</v>
       </c>
       <c r="I15" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1001084575</t>
+          <t>https://www.kurly.com/goods/1001069960</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -999,14 +999,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>[삼립] 온가족이 함께 즐기는 4가지맛 젤리뽀 10입 600g</t>
+          <t xml:space="preserve">[하리보] 요즘 트렌드 얼먹 젤리 3종 (택1) </t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>5980</v>
+        <v>2180</v>
       </c>
       <c r="E16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F16" s="2">
         <f>D16*E16</f>
@@ -1016,11 +1016,11 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>397</v>
+        <v>741</v>
       </c>
       <c r="I16" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000495453</t>
+          <t>https://www.kurly.com/goods/1002033102</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
@@ -1033,19 +1033,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>쿠키/비스킷(개별포장)</t>
+          <t>초콜릿/캔디/젤리</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>[해태] 에이스 364g (24g x 15봉지)</t>
+          <t>[하리보] 핑크빛 젤리 2종, 택1</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>3980</v>
+        <v>2180</v>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F17" s="2">
         <f>D17*E17</f>
@@ -1055,11 +1055,11 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>999</v>
+        <v>520</v>
       </c>
       <c r="I17" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5077465</t>
+          <t>https://www.kurly.com/goods/1000548776</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -1072,19 +1072,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>쿠키/비스킷(개별포장)</t>
+          <t>초콜릿/캔디/젤리</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>[오리온] 다이제 오리지널 351g</t>
+          <t>[롯데] 제로 후르츠 젤리 238g (14g x 17입)</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>3280</v>
+        <v>5580</v>
       </c>
       <c r="E18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F18" s="2">
         <f>D18*E18</f>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="I18" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000033205</t>
+          <t>https://www.kurly.com/goods/5138785</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>[해태] 에이스 바스크 치즈 케이크 364g</t>
+          <t>[해태] 에이스 364g (24g x 15봉지)</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="I19" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000490099</t>
+          <t>https://www.kurly.com/goods/5077465</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
@@ -1155,11 +1155,11 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>[맥비티] 다이제스티브 비스킷 2종 (택1)</t>
+          <t>[오리온] 다이제 오리지널 351g</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>2990</v>
+        <v>3280</v>
       </c>
       <c r="E20" t="n">
         <v>4</v>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="I20" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000975389</t>
+          <t>https://www.kurly.com/goods/1000033205</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
@@ -1194,14 +1194,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>[오리온] 다이제 쏙쏙포장 5종 (택1)</t>
+          <t>[해태] 에이스 바스크 치즈 케이크 364g</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>3200</v>
+        <v>3980</v>
       </c>
       <c r="E21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F21" s="2">
         <f>D21*E21</f>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="I21" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000198198</t>
+          <t>https://www.kurly.com/goods/1000490099</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
@@ -1233,14 +1233,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>[해태] 에이스 씬 에스프레소 291g</t>
+          <t>[맥비티] 다이제스티브 비스킷 2종 (택1)</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>3980</v>
+        <v>2990</v>
       </c>
       <c r="E22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F22" s="2">
         <f>D22*E22</f>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="I22" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000528989</t>
+          <t>https://www.kurly.com/goods/1000975389</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
@@ -1272,14 +1272,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>[오리온] 촉촉한초코칩 320g</t>
+          <t>[오리온] 다이제 쏙쏙포장 5종 (택1)</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>4480</v>
+        <v>3200</v>
       </c>
       <c r="E23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F23" s="2">
         <f>D23*E23</f>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="I23" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5067311</t>
+          <t>https://www.kurly.com/goods/1000198198</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
@@ -1311,11 +1311,11 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>[크라운] 쿠크다스 2종 (택1)</t>
+          <t>[해태] 에이스 씬 에스프레소 291g</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>4380</v>
+        <v>3980</v>
       </c>
       <c r="E24" t="n">
         <v>3</v>
@@ -1332,7 +1332,7 @@
       </c>
       <c r="I24" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5121160</t>
+          <t>https://www.kurly.com/goods/1000528989</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
@@ -1350,14 +1350,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>[롯데] 마가렛트 오리지널 352g</t>
+          <t>[오리온] 촉촉한초코칩 320g</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>5440</v>
+        <v>4480</v>
       </c>
       <c r="E25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F25" s="2">
         <f>D25*E25</f>
@@ -1367,11 +1367,11 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>956</v>
+        <v>999</v>
       </c>
       <c r="I25" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000339526</t>
+          <t>https://www.kurly.com/goods/5067311</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
@@ -1389,11 +1389,11 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>[브레댄코] 리얼 브라우니 쿠키 2종 (택1)</t>
+          <t>[하리보] 이색 젤리 4종, 택1</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>3690</v>
+        <v>4380</v>
       </c>
       <c r="E26" t="n">
         <v>3</v>
@@ -1406,11 +1406,11 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>9999</v>
+        <v>999</v>
       </c>
       <c r="I26" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5061562</t>
+          <t>https://www.kurly.com/goods/1000548850</t>
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
@@ -1428,11 +1428,11 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>[오리온] 예감 치즈 그라탕 204g</t>
+          <t>[크라운] 쿠크다스 2종 (택1)</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>3580</v>
+        <v>4380</v>
       </c>
       <c r="E27" t="n">
         <v>3</v>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="I27" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5095164</t>
+          <t>https://www.kurly.com/goods/5121160</t>
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
@@ -1467,28 +1467,28 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>[밀카] 베스트 초코쿠키 &amp; 웨하스 4종 (택1)</t>
+          <t>[롯데] 마가렛트 오리지널 352g</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>4070</v>
+        <v>5440</v>
       </c>
       <c r="E28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F28" s="2">
         <f>D28*E28</f>
         <v/>
       </c>
       <c r="G28" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>9999</v>
+        <v>956</v>
       </c>
       <c r="I28" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5067558</t>
+          <t>https://www.kurly.com/goods/1000339526</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
@@ -1506,11 +1506,11 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>[오리온] 예감 오리지널 192g</t>
+          <t>[브레댄코] 리얼 브라우니 쿠키 2종 (택1)</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>3580</v>
+        <v>3690</v>
       </c>
       <c r="E29" t="n">
         <v>3</v>
@@ -1523,11 +1523,11 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>999</v>
+        <v>9999</v>
       </c>
       <c r="I29" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5095165</t>
+          <t>https://www.kurly.com/goods/5061562</t>
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
@@ -1545,14 +1545,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>[롯데] 제로 초코파이 336g</t>
+          <t>[오리온] 예감 치즈 그라탕 204g</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>5100</v>
+        <v>3580</v>
       </c>
       <c r="E30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F30" s="2">
         <f>D30*E30</f>
@@ -1562,11 +1562,11 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>729</v>
+        <v>999</v>
       </c>
       <c r="I30" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000958611</t>
+          <t>https://www.kurly.com/goods/5095164</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
@@ -1579,16 +1579,16 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>파이/케이크(개별포장)</t>
+          <t>쿠키/비스킷(개별포장)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>[오리온] 초코파이 12입</t>
+          <t>[밀카] 베스트 초코쿠키 &amp; 웨하스 4종 (택1)</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>4320</v>
+        <v>4070</v>
       </c>
       <c r="E31" t="n">
         <v>3</v>
@@ -1598,14 +1598,14 @@
         <v/>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H31" t="n">
         <v>9999</v>
       </c>
       <c r="I31" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5061296</t>
+          <t>https://www.kurly.com/goods/5067558</t>
         </is>
       </c>
       <c r="J31" t="inlineStr"/>
@@ -1618,19 +1618,19 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>파이/케이크(개별포장)</t>
+          <t>쿠키/비스킷(개별포장)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>[해태] 오예스 미니 기획팩 764g (191g x 4팩)</t>
+          <t>[오리온] 예감 오리지널 192g</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>10800</v>
+        <v>3580</v>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F32" s="2">
         <f>D32*E32</f>
@@ -1640,11 +1640,11 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>865</v>
+        <v>999</v>
       </c>
       <c r="I32" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000339499</t>
+          <t>https://www.kurly.com/goods/5095165</t>
         </is>
       </c>
       <c r="J32" t="inlineStr"/>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>[오리온] 카스타드 12개입 276g</t>
+          <t>[오리온] 초코파이 12입</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
@@ -1679,11 +1679,11 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>745</v>
+        <v>9999</v>
       </c>
       <c r="I33" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000875718</t>
+          <t>https://www.kurly.com/goods/5061296</t>
         </is>
       </c>
       <c r="J33" t="inlineStr"/>
@@ -1701,11 +1701,11 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>[해태] 오예스 기획팩 840g (30g X 28봉지)</t>
+          <t>[해태] 오예스 미니 기획팩 764g (191g x 4팩)</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>11900</v>
+        <v>10800</v>
       </c>
       <c r="E34" t="n">
         <v>1</v>
@@ -1718,11 +1718,11 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>607</v>
+        <v>865</v>
       </c>
       <c r="I34" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1001391146</t>
+          <t>https://www.kurly.com/goods/1000339499</t>
         </is>
       </c>
       <c r="J34" t="inlineStr"/>
@@ -1740,11 +1740,11 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>[오리온] 초코파이 말차쇼콜라 408g</t>
+          <t>[오리온] 카스타드 12개입 276g</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>4800</v>
+        <v>4320</v>
       </c>
       <c r="E35" t="n">
         <v>3</v>
@@ -1757,11 +1757,11 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>950</v>
+        <v>745</v>
       </c>
       <c r="I35" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1001382646</t>
+          <t>https://www.kurly.com/goods/1000875718</t>
         </is>
       </c>
       <c r="J35" t="inlineStr"/>
@@ -1779,14 +1779,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>[롯데] 몽쉘 생크림케이크 오리지널 408g</t>
+          <t>[해태] 오예스 기획팩 840g (30g X 28봉지)</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>5600</v>
+        <v>11900</v>
       </c>
       <c r="E36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F36" s="2">
         <f>D36*E36</f>
@@ -1796,11 +1796,11 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>999</v>
+        <v>607</v>
       </c>
       <c r="I36" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000175874</t>
+          <t>https://www.kurly.com/goods/1001391146</t>
         </is>
       </c>
       <c r="J36" t="inlineStr"/>
@@ -1818,14 +1818,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>[롯데] 몽쉘 생크림케이크 카카오 408g</t>
+          <t>[오리온] 초코파이 말차쇼콜라 408g</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>5600</v>
+        <v>4800</v>
       </c>
       <c r="E37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F37" s="2">
         <f>D37*E37</f>
@@ -1835,11 +1835,11 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>999</v>
+        <v>950</v>
       </c>
       <c r="I37" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000175876</t>
+          <t>https://www.kurly.com/goods/1001382646</t>
         </is>
       </c>
       <c r="J37" t="inlineStr"/>
@@ -1857,31 +1857,109 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>[해태] 오예스 미니 크림소다맛 192g</t>
+          <t>[롯데] 몽쉘 생크림케이크 오리지널 408g</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>2506</v>
+        <v>5600</v>
       </c>
       <c r="E38" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F38" s="2">
         <f>D38*E38</f>
         <v/>
       </c>
       <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>999</v>
+      </c>
+      <c r="I38" s="8" t="inlineStr">
+        <is>
+          <t>https://www.kurly.com/goods/1000175874</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>추천</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>파이/케이크(개별포장)</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>[롯데] 몽쉘 생크림케이크 카카오 408g</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>5600</v>
+      </c>
+      <c r="E39" t="n">
+        <v>2</v>
+      </c>
+      <c r="F39" s="2">
+        <f>D39*E39</f>
+        <v/>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>999</v>
+      </c>
+      <c r="I39" s="8" t="inlineStr">
+        <is>
+          <t>https://www.kurly.com/goods/1000175876</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>추천</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>파이/케이크(개별포장)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>[해태] 오예스 미니 크림소다맛 192g</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>2506</v>
+      </c>
+      <c r="E40" t="n">
+        <v>5</v>
+      </c>
+      <c r="F40" s="2">
+        <f>D40*E40</f>
+        <v/>
+      </c>
+      <c r="G40" t="n">
         <v>30</v>
       </c>
-      <c r="H38" t="n">
+      <c r="H40" t="n">
         <v>187</v>
       </c>
-      <c r="I38" s="8" t="inlineStr">
+      <c r="I40" s="8" t="inlineStr">
         <is>
           <t>https://www.kurly.com/goods/1002225099</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1919,6 +1997,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I36" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="rId36"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1968,11 +2048,11 @@
         </is>
       </c>
       <c r="B2">
-        <f>COUNTIF(구매목록!B5:B38,A2)</f>
+        <f>COUNTIF(구매목록!B5:B40,A2)</f>
         <v/>
       </c>
       <c r="C2" s="2">
-        <f>SUMIF(구매목록!B5:B38,A2,구매목록!F5:F38)</f>
+        <f>SUMIF(구매목록!B5:B40,A2,구매목록!F5:F40)</f>
         <v/>
       </c>
       <c r="D2" s="9">
@@ -1987,11 +2067,11 @@
         </is>
       </c>
       <c r="B3">
-        <f>COUNTIF(구매목록!B5:B38,A3)</f>
+        <f>COUNTIF(구매목록!B5:B40,A3)</f>
         <v/>
       </c>
       <c r="C3" s="2">
-        <f>SUMIF(구매목록!B5:B38,A3,구매목록!F5:F38)</f>
+        <f>SUMIF(구매목록!B5:B40,A3,구매목록!F5:F40)</f>
         <v/>
       </c>
       <c r="D3" s="9">
@@ -2006,11 +2086,11 @@
         </is>
       </c>
       <c r="B4">
-        <f>COUNTIF(구매목록!B5:B38,A4)</f>
+        <f>COUNTIF(구매목록!B5:B40,A4)</f>
         <v/>
       </c>
       <c r="C4" s="2">
-        <f>SUMIF(구매목록!B5:B38,A4,구매목록!F5:F38)</f>
+        <f>SUMIF(구매목록!B5:B40,A4,구매목록!F5:F40)</f>
         <v/>
       </c>
       <c r="D4" s="9">
@@ -2025,11 +2105,11 @@
         </is>
       </c>
       <c r="B5">
-        <f>COUNTIF(구매목록!B5:B38,A5)</f>
+        <f>COUNTIF(구매목록!B5:B40,A5)</f>
         <v/>
       </c>
       <c r="C5" s="2">
-        <f>SUMIF(구매목록!B5:B38,A5,구매목록!F5:F38)</f>
+        <f>SUMIF(구매목록!B5:B40,A5,구매목록!F5:F40)</f>
         <v/>
       </c>
       <c r="D5" s="9">
@@ -2044,11 +2124,11 @@
         </is>
       </c>
       <c r="B6">
-        <f>COUNTIF(구매목록!B5:B38,A6)</f>
+        <f>COUNTIF(구매목록!B5:B40,A6)</f>
         <v/>
       </c>
       <c r="C6" s="2">
-        <f>SUMIF(구매목록!B5:B38,A6,구매목록!F5:F38)</f>
+        <f>SUMIF(구매목록!B5:B40,A6,구매목록!F5:F40)</f>
         <v/>
       </c>
       <c r="D6" s="9">
@@ -2063,11 +2143,11 @@
         </is>
       </c>
       <c r="B7">
-        <f>COUNTIF(구매목록!B5:B38,A7)</f>
+        <f>COUNTIF(구매목록!B5:B40,A7)</f>
         <v/>
       </c>
       <c r="C7" s="2">
-        <f>SUMIF(구매목록!B5:B38,A7,구매목록!F5:F38)</f>
+        <f>SUMIF(구매목록!B5:B40,A7,구매목록!F5:F40)</f>
         <v/>
       </c>
       <c r="D7" s="9">
@@ -2082,11 +2162,11 @@
         </is>
       </c>
       <c r="B8">
-        <f>COUNTIF(구매목록!B5:B38,A8)</f>
+        <f>COUNTIF(구매목록!B5:B40,A8)</f>
         <v/>
       </c>
       <c r="C8" s="2">
-        <f>SUMIF(구매목록!B5:B38,A8,구매목록!F5:F38)</f>
+        <f>SUMIF(구매목록!B5:B40,A8,구매목록!F5:F40)</f>
         <v/>
       </c>
       <c r="D8" s="9">

--- a/다과_구매목록.xlsx
+++ b/다과_구매목록.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -492,7 +492,7 @@
         </is>
       </c>
       <c r="D2" s="3">
-        <f>SUM(F5:F40)</f>
+        <f>SUM(F5:F45)</f>
         <v/>
       </c>
       <c r="E2" t="inlineStr">
@@ -643,19 +643,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>베이커리 소포장</t>
+          <t>개별포장 스낵/감자칩</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[메종엠오] 마들렌 3종 (택1)</t>
+          <t>[오리온] 포카칩 4개입 2종 (택1)</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>3500</v>
+        <v>3390</v>
       </c>
       <c r="E7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F7" s="2">
         <f>D7*E7</f>
@@ -669,7 +669,7 @@
       </c>
       <c r="I7" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5009371</t>
+          <t>https://www.kurly.com/goods/1000648498</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -682,16 +682,16 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>베이커리 소포장</t>
+          <t>개별포장 스낵/감자칩</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>[브레댄코] 봉주르 카스테라 2종 (택1)</t>
+          <t>[롯데] 꼬깔콘 스낵(소) 4번들</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>11500</v>
+        <v>3580</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
@@ -704,11 +704,11 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>9999</v>
+        <v>999</v>
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5074339</t>
+          <t>https://www.kurly.com/goods/5079319</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -721,19 +721,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>베이커리 소포장</t>
+          <t>개별포장 스낵/감자칩</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>[오르랔베이커리] 크러핀 4종 (택1)</t>
+          <t>[해태] 허니버터칩 4번들 (40g x 4묶음)</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>5200</v>
+        <v>3980</v>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F9" s="2">
         <f>D9*E9</f>
@@ -743,11 +743,11 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>9999</v>
+        <v>999</v>
       </c>
       <c r="I9" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5093256</t>
+          <t>https://www.kurly.com/goods/1000263120</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -760,33 +760,33 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>에너지바</t>
+          <t>개별포장 스낵/감자칩</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>[네이처밸리] 그래놀라 바 3종 ,택1</t>
+          <t>[해태] 가루비 감자칩 오리지널 40g X 3개입</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>3980</v>
+        <v>2780</v>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F10" s="2">
         <f>D10*E10</f>
         <v/>
       </c>
       <c r="G10" t="n">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="H10" t="n">
-        <v>9999</v>
+        <v>594</v>
       </c>
       <c r="I10" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5007664</t>
+          <t>https://www.kurly.com/goods/1000582944</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -799,19 +799,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>에너지바</t>
+          <t>개별포장 스낵/감자칩</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>[마켓오네이처] 오!그래놀라 다이제 2종 (택1)</t>
+          <t>[오리온] 꼬북칩 캬라멜팝콘 미니 박스 30g x 12개입</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>5980</v>
+        <v>6800</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" s="2">
         <f>D11*E11</f>
@@ -821,11 +821,11 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>999</v>
+        <v>274</v>
       </c>
       <c r="I11" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000593035</t>
+          <t>https://www.kurly.com/goods/1001235091</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
@@ -838,19 +838,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>일본 과자</t>
+          <t>베이커리 소포장</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>[사토제과] 아주끼 모나카</t>
+          <t>[메종엠오] 마들렌 3종 (택1)</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>7380</v>
+        <v>3500</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F12" s="2">
         <f>D12*E12</f>
@@ -860,11 +860,11 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>999</v>
+        <v>9999</v>
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5081428</t>
+          <t>https://www.kurly.com/goods/5009371</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
@@ -877,16 +877,16 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>일본 과자</t>
+          <t>베이커리 소포장</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>[카수가이] 과일 구미 6종 (택1)</t>
+          <t>[브레댄코] 봉주르 카스테라 2종 (택1)</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>3980</v>
+        <v>11500</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
@@ -899,11 +899,11 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>514</v>
+        <v>9999</v>
       </c>
       <c r="I13" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000499709</t>
+          <t>https://www.kurly.com/goods/5074339</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -916,19 +916,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>초콜릿/캔디/젤리</t>
+          <t>베이커리 소포장</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>[하리보] 미니스 젤리 7종, 택1</t>
+          <t>[오르랔베이커리] 크러핀 4종 (택1)</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>6980</v>
+        <v>5200</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F14" s="2">
         <f>D14*E14</f>
@@ -938,11 +938,11 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>999</v>
+        <v>9999</v>
       </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5044322</t>
+          <t>https://www.kurly.com/goods/5093256</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -955,33 +955,33 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>초콜릿/캔디/젤리</t>
+          <t>에너지바</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>[하리보] 폭신한 과일맛 젤리 3종, 택1</t>
+          <t>[네이처밸리] 그래놀라 바 3종 ,택1</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>2180</v>
+        <v>3980</v>
       </c>
       <c r="E15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F15" s="2">
         <f>D15*E15</f>
         <v/>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="H15" t="n">
-        <v>835</v>
+        <v>9999</v>
       </c>
       <c r="I15" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1001069960</t>
+          <t>https://www.kurly.com/goods/5007664</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -994,19 +994,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>초콜릿/캔디/젤리</t>
+          <t>에너지바</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">[하리보] 요즘 트렌드 얼먹 젤리 3종 (택1) </t>
+          <t>[마켓오네이처] 오!그래놀라 다이제 2종 (택1)</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>2180</v>
+        <v>5980</v>
       </c>
       <c r="E16" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F16" s="2">
         <f>D16*E16</f>
@@ -1016,11 +1016,11 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>741</v>
+        <v>999</v>
       </c>
       <c r="I16" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1002033102</t>
+          <t>https://www.kurly.com/goods/1000593035</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
@@ -1033,19 +1033,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>초콜릿/캔디/젤리</t>
+          <t>일본 과자</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>[하리보] 핑크빛 젤리 2종, 택1</t>
+          <t>[사토제과] 아주끼 모나카</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>2180</v>
+        <v>7380</v>
       </c>
       <c r="E17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F17" s="2">
         <f>D17*E17</f>
@@ -1055,11 +1055,11 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>520</v>
+        <v>999</v>
       </c>
       <c r="I17" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000548776</t>
+          <t>https://www.kurly.com/goods/5081428</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -1072,16 +1072,16 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>초콜릿/캔디/젤리</t>
+          <t>일본 과자</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>[롯데] 제로 후르츠 젤리 238g (14g x 17입)</t>
+          <t>[카수가이] 과일 구미 6종 (택1)</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>5580</v>
+        <v>3980</v>
       </c>
       <c r="E18" t="n">
         <v>1</v>
@@ -1094,11 +1094,11 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>999</v>
+        <v>514</v>
       </c>
       <c r="I18" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5138785</t>
+          <t>https://www.kurly.com/goods/1000499709</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
@@ -1111,19 +1111,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>쿠키/비스킷(개별포장)</t>
+          <t>초콜릿/캔디/젤리</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>[해태] 에이스 364g (24g x 15봉지)</t>
+          <t>[하리보] 미니스 젤리 7종, 택1</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>3980</v>
+        <v>6980</v>
       </c>
       <c r="E19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F19" s="2">
         <f>D19*E19</f>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="I19" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5077465</t>
+          <t>https://www.kurly.com/goods/5044322</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
@@ -1150,19 +1150,19 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>쿠키/비스킷(개별포장)</t>
+          <t>초콜릿/캔디/젤리</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>[오리온] 다이제 오리지널 351g</t>
+          <t>[하리보] 폭신한 과일맛 젤리 3종, 택1</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>3280</v>
+        <v>2180</v>
       </c>
       <c r="E20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F20" s="2">
         <f>D20*E20</f>
@@ -1172,11 +1172,11 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>999</v>
+        <v>835</v>
       </c>
       <c r="I20" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000033205</t>
+          <t>https://www.kurly.com/goods/1001069960</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
@@ -1189,19 +1189,19 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>쿠키/비스킷(개별포장)</t>
+          <t>초콜릿/캔디/젤리</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>[해태] 에이스 바스크 치즈 케이크 364g</t>
+          <t xml:space="preserve">[하리보] 요즘 트렌드 얼먹 젤리 3종 (택1) </t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>3980</v>
+        <v>2180</v>
       </c>
       <c r="E21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F21" s="2">
         <f>D21*E21</f>
@@ -1211,11 +1211,11 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>999</v>
+        <v>741</v>
       </c>
       <c r="I21" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000490099</t>
+          <t>https://www.kurly.com/goods/1002033102</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
@@ -1228,19 +1228,19 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>쿠키/비스킷(개별포장)</t>
+          <t>초콜릿/캔디/젤리</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>[맥비티] 다이제스티브 비스킷 2종 (택1)</t>
+          <t>[하리보] 핑크빛 젤리 2종, 택1</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>2990</v>
+        <v>2180</v>
       </c>
       <c r="E22" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F22" s="2">
         <f>D22*E22</f>
@@ -1250,11 +1250,11 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>999</v>
+        <v>520</v>
       </c>
       <c r="I22" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000975389</t>
+          <t>https://www.kurly.com/goods/1000548776</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
@@ -1267,19 +1267,19 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>쿠키/비스킷(개별포장)</t>
+          <t>초콜릿/캔디/젤리</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>[오리온] 다이제 쏙쏙포장 5종 (택1)</t>
+          <t>[오리온] 후르츠 알맹이 젤리 5종</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>3200</v>
+        <v>2980</v>
       </c>
       <c r="E23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F23" s="2">
         <f>D23*E23</f>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="I23" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000198198</t>
+          <t>https://www.kurly.com/goods/1000279292</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>[해태] 에이스 씬 에스프레소 291g</t>
+          <t>[해태] 에이스 364g (24g x 15봉지)</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="I24" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000528989</t>
+          <t>https://www.kurly.com/goods/5077465</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
@@ -1350,14 +1350,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>[오리온] 촉촉한초코칩 320g</t>
+          <t>[오리온] 다이제 오리지널 351g</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>4480</v>
+        <v>3280</v>
       </c>
       <c r="E25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F25" s="2">
         <f>D25*E25</f>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="I25" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5067311</t>
+          <t>https://www.kurly.com/goods/1000033205</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
@@ -1389,11 +1389,11 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>[하리보] 이색 젤리 4종, 택1</t>
+          <t>[해태] 에이스 바스크 치즈 케이크 364g</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>4380</v>
+        <v>3980</v>
       </c>
       <c r="E26" t="n">
         <v>3</v>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="I26" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000548850</t>
+          <t>https://www.kurly.com/goods/1000490099</t>
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
@@ -1428,14 +1428,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>[크라운] 쿠크다스 2종 (택1)</t>
+          <t>[맥비티] 다이제스티브 비스킷 2종 (택1)</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>4380</v>
+        <v>2990</v>
       </c>
       <c r="E27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F27" s="2">
         <f>D27*E27</f>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="I27" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5121160</t>
+          <t>https://www.kurly.com/goods/1000975389</t>
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
@@ -1467,14 +1467,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>[롯데] 마가렛트 오리지널 352g</t>
+          <t>[오리온] 다이제 쏙쏙포장 5종 (택1)</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>5440</v>
+        <v>3200</v>
       </c>
       <c r="E28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F28" s="2">
         <f>D28*E28</f>
@@ -1484,11 +1484,11 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>956</v>
+        <v>999</v>
       </c>
       <c r="I28" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000339526</t>
+          <t>https://www.kurly.com/goods/1000198198</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
@@ -1506,11 +1506,11 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>[브레댄코] 리얼 브라우니 쿠키 2종 (택1)</t>
+          <t>[해태] 에이스 씬 에스프레소 291g</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>3690</v>
+        <v>3980</v>
       </c>
       <c r="E29" t="n">
         <v>3</v>
@@ -1523,11 +1523,11 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>9999</v>
+        <v>999</v>
       </c>
       <c r="I29" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5061562</t>
+          <t>https://www.kurly.com/goods/1000528989</t>
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
@@ -1545,11 +1545,11 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>[오리온] 예감 치즈 그라탕 204g</t>
+          <t>[오리온] 촉촉한초코칩 320g</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>3580</v>
+        <v>4480</v>
       </c>
       <c r="E30" t="n">
         <v>3</v>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="I30" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5095164</t>
+          <t>https://www.kurly.com/goods/5067311</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
@@ -1584,11 +1584,11 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>[밀카] 베스트 초코쿠키 &amp; 웨하스 4종 (택1)</t>
+          <t>[하리보] 이색 젤리 4종, 택1</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>4070</v>
+        <v>4380</v>
       </c>
       <c r="E31" t="n">
         <v>3</v>
@@ -1598,14 +1598,14 @@
         <v/>
       </c>
       <c r="G31" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>9999</v>
+        <v>999</v>
       </c>
       <c r="I31" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5067558</t>
+          <t>https://www.kurly.com/goods/1000548850</t>
         </is>
       </c>
       <c r="J31" t="inlineStr"/>
@@ -1623,11 +1623,11 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>[오리온] 예감 오리지널 192g</t>
+          <t>[크라운] 쿠크다스 2종 (택1)</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>3580</v>
+        <v>4380</v>
       </c>
       <c r="E32" t="n">
         <v>3</v>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="I32" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5095165</t>
+          <t>https://www.kurly.com/goods/5121160</t>
         </is>
       </c>
       <c r="J32" t="inlineStr"/>
@@ -1657,19 +1657,19 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>파이/케이크(개별포장)</t>
+          <t>쿠키/비스킷(개별포장)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>[오리온] 초코파이 12입</t>
+          <t>[롯데] 마가렛트 오리지널 352g</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>4320</v>
+        <v>5440</v>
       </c>
       <c r="E33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F33" s="2">
         <f>D33*E33</f>
@@ -1679,11 +1679,11 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>9999</v>
+        <v>956</v>
       </c>
       <c r="I33" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5061296</t>
+          <t>https://www.kurly.com/goods/1000339526</t>
         </is>
       </c>
       <c r="J33" t="inlineStr"/>
@@ -1696,19 +1696,19 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>파이/케이크(개별포장)</t>
+          <t>쿠키/비스킷(개별포장)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>[해태] 오예스 미니 기획팩 764g (191g x 4팩)</t>
+          <t>[브레댄코] 리얼 브라우니 쿠키 2종 (택1)</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>10800</v>
+        <v>3690</v>
       </c>
       <c r="E34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F34" s="2">
         <f>D34*E34</f>
@@ -1718,11 +1718,11 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>865</v>
+        <v>9999</v>
       </c>
       <c r="I34" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000339499</t>
+          <t>https://www.kurly.com/goods/5061562</t>
         </is>
       </c>
       <c r="J34" t="inlineStr"/>
@@ -1735,16 +1735,16 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>파이/케이크(개별포장)</t>
+          <t>쿠키/비스킷(개별포장)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>[오리온] 카스타드 12개입 276g</t>
+          <t>[오리온] 예감 치즈 그라탕 204g</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>4320</v>
+        <v>3580</v>
       </c>
       <c r="E35" t="n">
         <v>3</v>
@@ -1757,11 +1757,11 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>745</v>
+        <v>999</v>
       </c>
       <c r="I35" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000875718</t>
+          <t>https://www.kurly.com/goods/5095164</t>
         </is>
       </c>
       <c r="J35" t="inlineStr"/>
@@ -1774,19 +1774,19 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>파이/케이크(개별포장)</t>
+          <t>쿠키/비스킷(개별포장)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>[해태] 오예스 기획팩 840g (30g X 28봉지)</t>
+          <t>[오리온] 예감 오리지널 192g</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>11900</v>
+        <v>3580</v>
       </c>
       <c r="E36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F36" s="2">
         <f>D36*E36</f>
@@ -1796,11 +1796,11 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>607</v>
+        <v>999</v>
       </c>
       <c r="I36" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1001391146</t>
+          <t>https://www.kurly.com/goods/5095165</t>
         </is>
       </c>
       <c r="J36" t="inlineStr"/>
@@ -1813,19 +1813,19 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>파이/케이크(개별포장)</t>
+          <t>쿠키/비스킷(개별포장)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>[오리온] 초코파이 말차쇼콜라 408g</t>
+          <t>[반두아] 코코넛 크래커 150g</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>4800</v>
+        <v>2500</v>
       </c>
       <c r="E37" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F37" s="2">
         <f>D37*E37</f>
@@ -1835,11 +1835,11 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>950</v>
+        <v>9999</v>
       </c>
       <c r="I37" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1001382646</t>
+          <t>https://www.kurly.com/goods/5049808</t>
         </is>
       </c>
       <c r="J37" t="inlineStr"/>
@@ -1857,14 +1857,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>[롯데] 몽쉘 생크림케이크 오리지널 408g</t>
+          <t>[오리온] 초코파이 12입</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>5600</v>
+        <v>4320</v>
       </c>
       <c r="E38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F38" s="2">
         <f>D38*E38</f>
@@ -1874,11 +1874,11 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>999</v>
+        <v>9999</v>
       </c>
       <c r="I38" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000175874</t>
+          <t>https://www.kurly.com/goods/5061296</t>
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
@@ -1896,14 +1896,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>[롯데] 몽쉘 생크림케이크 카카오 408g</t>
+          <t>[해태] 오예스 미니 기획팩 764g (191g x 4팩)</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>5600</v>
+        <v>10800</v>
       </c>
       <c r="E39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F39" s="2">
         <f>D39*E39</f>
@@ -1913,11 +1913,11 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>999</v>
+        <v>865</v>
       </c>
       <c r="I39" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000175876</t>
+          <t>https://www.kurly.com/goods/1000339499</t>
         </is>
       </c>
       <c r="J39" t="inlineStr"/>
@@ -1935,31 +1935,226 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>[해태] 오예스 미니 크림소다맛 192g</t>
+          <t>[오리온] 카스타드 12개입 276g</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>2506</v>
+        <v>4320</v>
       </c>
       <c r="E40" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F40" s="2">
         <f>D40*E40</f>
         <v/>
       </c>
       <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>745</v>
+      </c>
+      <c r="I40" s="8" t="inlineStr">
+        <is>
+          <t>https://www.kurly.com/goods/1000875718</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>추천</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>파이/케이크(개별포장)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>[해태] 오예스 기획팩 840g (30g X 28봉지)</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>11900</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="2">
+        <f>D41*E41</f>
+        <v/>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>607</v>
+      </c>
+      <c r="I41" s="8" t="inlineStr">
+        <is>
+          <t>https://www.kurly.com/goods/1001391146</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>추천</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>파이/케이크(개별포장)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>[오리온] 초코파이 말차쇼콜라 408g</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>4800</v>
+      </c>
+      <c r="E42" t="n">
+        <v>3</v>
+      </c>
+      <c r="F42" s="2">
+        <f>D42*E42</f>
+        <v/>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>950</v>
+      </c>
+      <c r="I42" s="8" t="inlineStr">
+        <is>
+          <t>https://www.kurly.com/goods/1001382646</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>추천</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>파이/케이크(개별포장)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>[롯데] 몽쉘 생크림케이크 오리지널 408g</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>5600</v>
+      </c>
+      <c r="E43" t="n">
+        <v>2</v>
+      </c>
+      <c r="F43" s="2">
+        <f>D43*E43</f>
+        <v/>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>999</v>
+      </c>
+      <c r="I43" s="8" t="inlineStr">
+        <is>
+          <t>https://www.kurly.com/goods/1000175874</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>추천</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>파이/케이크(개별포장)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>[롯데] 몽쉘 생크림케이크 카카오 408g</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>5600</v>
+      </c>
+      <c r="E44" t="n">
+        <v>2</v>
+      </c>
+      <c r="F44" s="2">
+        <f>D44*E44</f>
+        <v/>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>999</v>
+      </c>
+      <c r="I44" s="8" t="inlineStr">
+        <is>
+          <t>https://www.kurly.com/goods/1000175876</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>추천</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>파이/케이크(개별포장)</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>[해태] 오예스 미니 크림소다맛 192g</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>2506</v>
+      </c>
+      <c r="E45" t="n">
+        <v>5</v>
+      </c>
+      <c r="F45" s="2">
+        <f>D45*E45</f>
+        <v/>
+      </c>
+      <c r="G45" t="n">
         <v>30</v>
       </c>
-      <c r="H40" t="n">
+      <c r="H45" t="n">
         <v>187</v>
       </c>
-      <c r="I40" s="8" t="inlineStr">
+      <c r="I45" s="8" t="inlineStr">
         <is>
           <t>https://www.kurly.com/goods/1002225099</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1999,6 +2194,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I41" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId41"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2010,7 +2210,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2048,15 +2248,15 @@
         </is>
       </c>
       <c r="B2">
-        <f>COUNTIF(구매목록!B5:B40,A2)</f>
+        <f>COUNTIF(구매목록!B5:B45,A2)</f>
         <v/>
       </c>
       <c r="C2" s="2">
-        <f>SUMIF(구매목록!B5:B40,A2,구매목록!F5:F40)</f>
+        <f>SUMIF(구매목록!B5:B45,A2,구매목록!F5:F45)</f>
         <v/>
       </c>
       <c r="D2" s="9">
-        <f>C2/SUM($C$2:$C$8)</f>
+        <f>C2/SUM($C$2:$C$9)</f>
         <v/>
       </c>
     </row>
@@ -2067,15 +2267,15 @@
         </is>
       </c>
       <c r="B3">
-        <f>COUNTIF(구매목록!B5:B40,A3)</f>
+        <f>COUNTIF(구매목록!B5:B45,A3)</f>
         <v/>
       </c>
       <c r="C3" s="2">
-        <f>SUMIF(구매목록!B5:B40,A3,구매목록!F5:F40)</f>
+        <f>SUMIF(구매목록!B5:B45,A3,구매목록!F5:F45)</f>
         <v/>
       </c>
       <c r="D3" s="9">
-        <f>C3/SUM($C$2:$C$8)</f>
+        <f>C3/SUM($C$2:$C$9)</f>
         <v/>
       </c>
     </row>
@@ -2086,15 +2286,15 @@
         </is>
       </c>
       <c r="B4">
-        <f>COUNTIF(구매목록!B5:B40,A4)</f>
+        <f>COUNTIF(구매목록!B5:B45,A4)</f>
         <v/>
       </c>
       <c r="C4" s="2">
-        <f>SUMIF(구매목록!B5:B40,A4,구매목록!F5:F40)</f>
+        <f>SUMIF(구매목록!B5:B45,A4,구매목록!F5:F45)</f>
         <v/>
       </c>
       <c r="D4" s="9">
-        <f>C4/SUM($C$2:$C$8)</f>
+        <f>C4/SUM($C$2:$C$9)</f>
         <v/>
       </c>
     </row>
@@ -2105,15 +2305,15 @@
         </is>
       </c>
       <c r="B5">
-        <f>COUNTIF(구매목록!B5:B40,A5)</f>
+        <f>COUNTIF(구매목록!B5:B45,A5)</f>
         <v/>
       </c>
       <c r="C5" s="2">
-        <f>SUMIF(구매목록!B5:B40,A5,구매목록!F5:F40)</f>
+        <f>SUMIF(구매목록!B5:B45,A5,구매목록!F5:F45)</f>
         <v/>
       </c>
       <c r="D5" s="9">
-        <f>C5/SUM($C$2:$C$8)</f>
+        <f>C5/SUM($C$2:$C$9)</f>
         <v/>
       </c>
     </row>
@@ -2124,15 +2324,15 @@
         </is>
       </c>
       <c r="B6">
-        <f>COUNTIF(구매목록!B5:B40,A6)</f>
+        <f>COUNTIF(구매목록!B5:B45,A6)</f>
         <v/>
       </c>
       <c r="C6" s="2">
-        <f>SUMIF(구매목록!B5:B40,A6,구매목록!F5:F40)</f>
+        <f>SUMIF(구매목록!B5:B45,A6,구매목록!F5:F45)</f>
         <v/>
       </c>
       <c r="D6" s="9">
-        <f>C6/SUM($C$2:$C$8)</f>
+        <f>C6/SUM($C$2:$C$9)</f>
         <v/>
       </c>
     </row>
@@ -2143,34 +2343,53 @@
         </is>
       </c>
       <c r="B7">
-        <f>COUNTIF(구매목록!B5:B40,A7)</f>
+        <f>COUNTIF(구매목록!B5:B45,A7)</f>
         <v/>
       </c>
       <c r="C7" s="2">
-        <f>SUMIF(구매목록!B5:B40,A7,구매목록!F5:F40)</f>
+        <f>SUMIF(구매목록!B5:B45,A7,구매목록!F5:F45)</f>
         <v/>
       </c>
       <c r="D7" s="9">
-        <f>C7/SUM($C$2:$C$8)</f>
+        <f>C7/SUM($C$2:$C$9)</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>개별포장 스낵/감자칩</t>
+        </is>
+      </c>
+      <c r="B8">
+        <f>COUNTIF(구매목록!B5:B45,A8)</f>
+        <v/>
+      </c>
+      <c r="C8" s="2">
+        <f>SUMIF(구매목록!B5:B45,A8,구매목록!F5:F45)</f>
+        <v/>
+      </c>
+      <c r="D8" s="9">
+        <f>C8/SUM($C$2:$C$9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>에너지바</t>
         </is>
       </c>
-      <c r="B8">
-        <f>COUNTIF(구매목록!B5:B40,A8)</f>
+      <c r="B9">
+        <f>COUNTIF(구매목록!B5:B45,A9)</f>
         <v/>
       </c>
-      <c r="C8" s="2">
-        <f>SUMIF(구매목록!B5:B40,A8,구매목록!F5:F40)</f>
+      <c r="C9" s="2">
+        <f>SUMIF(구매목록!B5:B45,A9,구매목록!F5:F45)</f>
         <v/>
       </c>
-      <c r="D8" s="9">
-        <f>C8/SUM($C$2:$C$8)</f>
+      <c r="D9" s="9">
+        <f>C9/SUM($C$2:$C$9)</f>
         <v/>
       </c>
     </row>

--- a/다과_구매목록.xlsx
+++ b/다과_구매목록.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J45"/>
+  <dimension ref="A1:J44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -492,7 +492,7 @@
         </is>
       </c>
       <c r="D2" s="3">
-        <f>SUM(F5:F45)</f>
+        <f>SUM(F5:F44)</f>
         <v/>
       </c>
       <c r="E2" t="inlineStr">
@@ -850,7 +850,7 @@
         <v>3500</v>
       </c>
       <c r="E12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F12" s="2">
         <f>D12*E12</f>
@@ -928,7 +928,7 @@
         <v>5200</v>
       </c>
       <c r="E14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F14" s="2">
         <f>D14*E14</f>
@@ -1006,7 +1006,7 @@
         <v>5980</v>
       </c>
       <c r="E16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16" s="2">
         <f>D16*E16</f>
@@ -1116,14 +1116,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>[하리보] 미니스 젤리 7종, 택1</t>
+          <t>[하리보] 폭신한 과일맛 젤리 3종, 택1</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>6980</v>
+        <v>2180</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F19" s="2">
         <f>D19*E19</f>
@@ -1133,11 +1133,11 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>999</v>
+        <v>835</v>
       </c>
       <c r="I19" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5044322</t>
+          <t>https://www.kurly.com/goods/1001069960</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
@@ -1155,14 +1155,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>[하리보] 폭신한 과일맛 젤리 3종, 택1</t>
+          <t xml:space="preserve">[하리보] 요즘 트렌드 얼먹 젤리 3종 (택1) </t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
         <v>2180</v>
       </c>
       <c r="E20" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F20" s="2">
         <f>D20*E20</f>
@@ -1172,11 +1172,11 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>835</v>
+        <v>741</v>
       </c>
       <c r="I20" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1001069960</t>
+          <t>https://www.kurly.com/goods/1002033102</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
@@ -1194,14 +1194,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">[하리보] 요즘 트렌드 얼먹 젤리 3종 (택1) </t>
+          <t>[하리보] 핑크빛 젤리 2종, 택1</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
         <v>2180</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F21" s="2">
         <f>D21*E21</f>
@@ -1211,11 +1211,11 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>741</v>
+        <v>520</v>
       </c>
       <c r="I21" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1002033102</t>
+          <t>https://www.kurly.com/goods/1000548776</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
@@ -1233,14 +1233,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>[하리보] 핑크빛 젤리 2종, 택1</t>
+          <t>[하리보] 헬로 제주 젤리 2종, 택1</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
         <v>2180</v>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F22" s="2">
         <f>D22*E22</f>
@@ -1250,11 +1250,11 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>520</v>
+        <v>243</v>
       </c>
       <c r="I22" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000548776</t>
+          <t>https://www.kurly.com/goods/1002378241</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
@@ -1267,19 +1267,19 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>초콜릿/캔디/젤리</t>
+          <t>쿠키/비스킷(개별포장)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>[오리온] 후르츠 알맹이 젤리 5종</t>
+          <t>[해태] 에이스 364g (24g x 15봉지)</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>2980</v>
+        <v>3980</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F23" s="2">
         <f>D23*E23</f>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="I23" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000279292</t>
+          <t>https://www.kurly.com/goods/5077465</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
@@ -1311,14 +1311,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>[해태] 에이스 364g (24g x 15봉지)</t>
+          <t>[오리온] 다이제 오리지널 351g</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>3980</v>
+        <v>3280</v>
       </c>
       <c r="E24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F24" s="2">
         <f>D24*E24</f>
@@ -1332,7 +1332,7 @@
       </c>
       <c r="I24" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5077465</t>
+          <t>https://www.kurly.com/goods/1000033205</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
@@ -1350,14 +1350,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>[오리온] 다이제 오리지널 351g</t>
+          <t>[해태] 에이스 바스크 치즈 케이크 364g</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>3280</v>
+        <v>3980</v>
       </c>
       <c r="E25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F25" s="2">
         <f>D25*E25</f>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="I25" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000033205</t>
+          <t>https://www.kurly.com/goods/1000490099</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
@@ -1389,14 +1389,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>[해태] 에이스 바스크 치즈 케이크 364g</t>
+          <t>[맥비티] 다이제스티브 비스킷 2종 (택1)</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>3980</v>
+        <v>2990</v>
       </c>
       <c r="E26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F26" s="2">
         <f>D26*E26</f>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="I26" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000490099</t>
+          <t>https://www.kurly.com/goods/1000975389</t>
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
@@ -1428,11 +1428,11 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>[맥비티] 다이제스티브 비스킷 2종 (택1)</t>
+          <t>[오리온] 다이제 쏙쏙포장 5종 (택1)</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>2990</v>
+        <v>3200</v>
       </c>
       <c r="E27" t="n">
         <v>4</v>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="I27" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000975389</t>
+          <t>https://www.kurly.com/goods/1000198198</t>
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
@@ -1467,14 +1467,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>[오리온] 다이제 쏙쏙포장 5종 (택1)</t>
+          <t>[해태] 에이스 씬 에스프레소 291g</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>3200</v>
+        <v>3980</v>
       </c>
       <c r="E28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F28" s="2">
         <f>D28*E28</f>
@@ -1488,7 +1488,7 @@
       </c>
       <c r="I28" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000198198</t>
+          <t>https://www.kurly.com/goods/1000528989</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
@@ -1506,11 +1506,11 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>[해태] 에이스 씬 에스프레소 291g</t>
+          <t>[오리온] 촉촉한초코칩 320g</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>3980</v>
+        <v>4480</v>
       </c>
       <c r="E29" t="n">
         <v>3</v>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="I29" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000528989</t>
+          <t>https://www.kurly.com/goods/5067311</t>
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
@@ -1545,11 +1545,11 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>[오리온] 촉촉한초코칩 320g</t>
+          <t>[크라운] 쿠크다스 2종 (택1)</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>4480</v>
+        <v>4380</v>
       </c>
       <c r="E30" t="n">
         <v>3</v>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="I30" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5067311</t>
+          <t>https://www.kurly.com/goods/5121160</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
@@ -1584,14 +1584,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>[하리보] 이색 젤리 4종, 택1</t>
+          <t>[롯데] 마가렛트 오리지널 352g</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>4380</v>
+        <v>5440</v>
       </c>
       <c r="E31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F31" s="2">
         <f>D31*E31</f>
@@ -1601,11 +1601,11 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>999</v>
+        <v>956</v>
       </c>
       <c r="I31" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000548850</t>
+          <t>https://www.kurly.com/goods/1000339526</t>
         </is>
       </c>
       <c r="J31" t="inlineStr"/>
@@ -1623,14 +1623,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>[크라운] 쿠크다스 2종 (택1)</t>
+          <t>[브레댄코] 리얼 브라우니 쿠키 2종 (택1)</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>4380</v>
+        <v>3690</v>
       </c>
       <c r="E32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F32" s="2">
         <f>D32*E32</f>
@@ -1640,11 +1640,11 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>999</v>
+        <v>9999</v>
       </c>
       <c r="I32" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5121160</t>
+          <t>https://www.kurly.com/goods/5061562</t>
         </is>
       </c>
       <c r="J32" t="inlineStr"/>
@@ -1662,14 +1662,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>[롯데] 마가렛트 오리지널 352g</t>
+          <t>[오리온] 예감 치즈 그라탕 204g</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>5440</v>
+        <v>3580</v>
       </c>
       <c r="E33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F33" s="2">
         <f>D33*E33</f>
@@ -1679,11 +1679,11 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>956</v>
+        <v>999</v>
       </c>
       <c r="I33" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000339526</t>
+          <t>https://www.kurly.com/goods/5095164</t>
         </is>
       </c>
       <c r="J33" t="inlineStr"/>
@@ -1701,14 +1701,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>[브레댄코] 리얼 브라우니 쿠키 2종 (택1)</t>
+          <t>[오리온] 예감 오리지널 192g</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>3690</v>
+        <v>3580</v>
       </c>
       <c r="E34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F34" s="2">
         <f>D34*E34</f>
@@ -1718,11 +1718,11 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>9999</v>
+        <v>999</v>
       </c>
       <c r="I34" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5061562</t>
+          <t>https://www.kurly.com/goods/5095165</t>
         </is>
       </c>
       <c r="J34" t="inlineStr"/>
@@ -1740,14 +1740,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>[오리온] 예감 치즈 그라탕 204g</t>
+          <t>[반두아] 코코넛 크래커 150g</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>3580</v>
+        <v>2500</v>
       </c>
       <c r="E35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F35" s="2">
         <f>D35*E35</f>
@@ -1757,11 +1757,11 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>999</v>
+        <v>9999</v>
       </c>
       <c r="I35" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5095164</t>
+          <t>https://www.kurly.com/goods/5049808</t>
         </is>
       </c>
       <c r="J35" t="inlineStr"/>
@@ -1779,14 +1779,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>[오리온] 예감 오리지널 192g</t>
+          <t>[롯데제과] 카스타드 오리지널 230g</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>3580</v>
+        <v>4780</v>
       </c>
       <c r="E36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F36" s="2">
         <f>D36*E36</f>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="I36" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5095165</t>
+          <t>https://www.kurly.com/goods/5061939</t>
         </is>
       </c>
       <c r="J36" t="inlineStr"/>
@@ -1813,19 +1813,19 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>쿠키/비스킷(개별포장)</t>
+          <t>파이/케이크(개별포장)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>[반두아] 코코넛 크래커 150g</t>
+          <t>[오리온] 초코파이 12입</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>2500</v>
+        <v>4320</v>
       </c>
       <c r="E37" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F37" s="2">
         <f>D37*E37</f>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="I37" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5049808</t>
+          <t>https://www.kurly.com/goods/5061296</t>
         </is>
       </c>
       <c r="J37" t="inlineStr"/>
@@ -1857,14 +1857,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>[오리온] 초코파이 12입</t>
+          <t>[해태] 오예스 미니 기획팩 764g (191g x 4팩)</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>4320</v>
+        <v>10800</v>
       </c>
       <c r="E38" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F38" s="2">
         <f>D38*E38</f>
@@ -1874,11 +1874,11 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>9999</v>
+        <v>865</v>
       </c>
       <c r="I38" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5061296</t>
+          <t>https://www.kurly.com/goods/1000339499</t>
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
@@ -1896,14 +1896,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>[해태] 오예스 미니 기획팩 764g (191g x 4팩)</t>
+          <t>[오리온] 카스타드 12개입 276g</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>10800</v>
+        <v>4320</v>
       </c>
       <c r="E39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F39" s="2">
         <f>D39*E39</f>
@@ -1913,11 +1913,11 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>865</v>
+        <v>745</v>
       </c>
       <c r="I39" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000339499</t>
+          <t>https://www.kurly.com/goods/1000875718</t>
         </is>
       </c>
       <c r="J39" t="inlineStr"/>
@@ -1935,14 +1935,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>[오리온] 카스타드 12개입 276g</t>
+          <t>[해태] 오예스 기획팩 840g (30g X 28봉지)</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>4320</v>
+        <v>11900</v>
       </c>
       <c r="E40" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F40" s="2">
         <f>D40*E40</f>
@@ -1952,11 +1952,11 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>745</v>
+        <v>607</v>
       </c>
       <c r="I40" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000875718</t>
+          <t>https://www.kurly.com/goods/1001391146</t>
         </is>
       </c>
       <c r="J40" t="inlineStr"/>
@@ -1974,14 +1974,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>[해태] 오예스 기획팩 840g (30g X 28봉지)</t>
+          <t>[오리온] 초코파이 말차쇼콜라 408g</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>11900</v>
+        <v>4800</v>
       </c>
       <c r="E41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F41" s="2">
         <f>D41*E41</f>
@@ -1991,11 +1991,11 @@
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>607</v>
+        <v>950</v>
       </c>
       <c r="I41" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1001391146</t>
+          <t>https://www.kurly.com/goods/1001382646</t>
         </is>
       </c>
       <c r="J41" t="inlineStr"/>
@@ -2013,14 +2013,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>[오리온] 초코파이 말차쇼콜라 408g</t>
+          <t>[롯데] 몽쉘 생크림케이크 오리지널 408g</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>4800</v>
+        <v>5600</v>
       </c>
       <c r="E42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F42" s="2">
         <f>D42*E42</f>
@@ -2030,11 +2030,11 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>950</v>
+        <v>999</v>
       </c>
       <c r="I42" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1001382646</t>
+          <t>https://www.kurly.com/goods/1000175874</t>
         </is>
       </c>
       <c r="J42" t="inlineStr"/>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>[롯데] 몽쉘 생크림케이크 오리지널 408g</t>
+          <t>[롯데] 몽쉘 생크림케이크 카카오 408g</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="I43" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000175874</t>
+          <t>https://www.kurly.com/goods/1000175876</t>
         </is>
       </c>
       <c r="J43" t="inlineStr"/>
@@ -2091,70 +2091,31 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>[롯데] 몽쉘 생크림케이크 카카오 408g</t>
+          <t>[해태] 오예스 미니 크림소다맛 192g</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>5600</v>
+        <v>2506</v>
       </c>
       <c r="E44" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F44" s="2">
         <f>D44*E44</f>
         <v/>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H44" t="n">
-        <v>999</v>
+        <v>187</v>
       </c>
       <c r="I44" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000175876</t>
+          <t>https://www.kurly.com/goods/1002225099</t>
         </is>
       </c>
       <c r="J44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>추천</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>파이/케이크(개별포장)</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>[해태] 오예스 미니 크림소다맛 192g</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="n">
-        <v>2506</v>
-      </c>
-      <c r="E45" t="n">
-        <v>5</v>
-      </c>
-      <c r="F45" s="2">
-        <f>D45*E45</f>
-        <v/>
-      </c>
-      <c r="G45" t="n">
-        <v>30</v>
-      </c>
-      <c r="H45" t="n">
-        <v>187</v>
-      </c>
-      <c r="I45" s="8" t="inlineStr">
-        <is>
-          <t>https://www.kurly.com/goods/1002225099</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -2198,7 +2159,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId41"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2248,11 +2208,11 @@
         </is>
       </c>
       <c r="B2">
-        <f>COUNTIF(구매목록!B5:B45,A2)</f>
+        <f>COUNTIF(구매목록!B5:B44,A2)</f>
         <v/>
       </c>
       <c r="C2" s="2">
-        <f>SUMIF(구매목록!B5:B45,A2,구매목록!F5:F45)</f>
+        <f>SUMIF(구매목록!B5:B44,A2,구매목록!F5:F44)</f>
         <v/>
       </c>
       <c r="D2" s="9">
@@ -2267,11 +2227,11 @@
         </is>
       </c>
       <c r="B3">
-        <f>COUNTIF(구매목록!B5:B45,A3)</f>
+        <f>COUNTIF(구매목록!B5:B44,A3)</f>
         <v/>
       </c>
       <c r="C3" s="2">
-        <f>SUMIF(구매목록!B5:B45,A3,구매목록!F5:F45)</f>
+        <f>SUMIF(구매목록!B5:B44,A3,구매목록!F5:F44)</f>
         <v/>
       </c>
       <c r="D3" s="9">
@@ -2286,11 +2246,11 @@
         </is>
       </c>
       <c r="B4">
-        <f>COUNTIF(구매목록!B5:B45,A4)</f>
+        <f>COUNTIF(구매목록!B5:B44,A4)</f>
         <v/>
       </c>
       <c r="C4" s="2">
-        <f>SUMIF(구매목록!B5:B45,A4,구매목록!F5:F45)</f>
+        <f>SUMIF(구매목록!B5:B44,A4,구매목록!F5:F44)</f>
         <v/>
       </c>
       <c r="D4" s="9">
@@ -2305,11 +2265,11 @@
         </is>
       </c>
       <c r="B5">
-        <f>COUNTIF(구매목록!B5:B45,A5)</f>
+        <f>COUNTIF(구매목록!B5:B44,A5)</f>
         <v/>
       </c>
       <c r="C5" s="2">
-        <f>SUMIF(구매목록!B5:B45,A5,구매목록!F5:F45)</f>
+        <f>SUMIF(구매목록!B5:B44,A5,구매목록!F5:F44)</f>
         <v/>
       </c>
       <c r="D5" s="9">
@@ -2324,11 +2284,11 @@
         </is>
       </c>
       <c r="B6">
-        <f>COUNTIF(구매목록!B5:B45,A6)</f>
+        <f>COUNTIF(구매목록!B5:B44,A6)</f>
         <v/>
       </c>
       <c r="C6" s="2">
-        <f>SUMIF(구매목록!B5:B45,A6,구매목록!F5:F45)</f>
+        <f>SUMIF(구매목록!B5:B44,A6,구매목록!F5:F44)</f>
         <v/>
       </c>
       <c r="D6" s="9">
@@ -2343,11 +2303,11 @@
         </is>
       </c>
       <c r="B7">
-        <f>COUNTIF(구매목록!B5:B45,A7)</f>
+        <f>COUNTIF(구매목록!B5:B44,A7)</f>
         <v/>
       </c>
       <c r="C7" s="2">
-        <f>SUMIF(구매목록!B5:B45,A7,구매목록!F5:F45)</f>
+        <f>SUMIF(구매목록!B5:B44,A7,구매목록!F5:F44)</f>
         <v/>
       </c>
       <c r="D7" s="9">
@@ -2362,11 +2322,11 @@
         </is>
       </c>
       <c r="B8">
-        <f>COUNTIF(구매목록!B5:B45,A8)</f>
+        <f>COUNTIF(구매목록!B5:B44,A8)</f>
         <v/>
       </c>
       <c r="C8" s="2">
-        <f>SUMIF(구매목록!B5:B45,A8,구매목록!F5:F45)</f>
+        <f>SUMIF(구매목록!B5:B44,A8,구매목록!F5:F44)</f>
         <v/>
       </c>
       <c r="D8" s="9">
@@ -2381,11 +2341,11 @@
         </is>
       </c>
       <c r="B9">
-        <f>COUNTIF(구매목록!B5:B45,A9)</f>
+        <f>COUNTIF(구매목록!B5:B44,A9)</f>
         <v/>
       </c>
       <c r="C9" s="2">
-        <f>SUMIF(구매목록!B5:B45,A9,구매목록!F5:F45)</f>
+        <f>SUMIF(구매목록!B5:B44,A9,구매목록!F5:F44)</f>
         <v/>
       </c>
       <c r="D9" s="9">

--- a/다과_구매목록.xlsx
+++ b/다과_구매목록.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J44"/>
+  <dimension ref="A1:J46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -492,7 +492,7 @@
         </is>
       </c>
       <c r="D2" s="3">
-        <f>SUM(F5:F44)</f>
+        <f>SUM(F5:F46)</f>
         <v/>
       </c>
       <c r="E2" t="inlineStr">
@@ -648,11 +648,11 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[오리온] 포카칩 4개입 2종 (택1)</t>
+          <t>[오리온] 예감 치즈 그라탕 204g</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>3390</v>
+        <v>3580</v>
       </c>
       <c r="E7" t="n">
         <v>3</v>
@@ -665,11 +665,11 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>9999</v>
+        <v>999</v>
       </c>
       <c r="I7" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000648498</t>
+          <t>https://www.kurly.com/goods/5095164</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -687,14 +687,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>[롯데] 꼬깔콘 스낵(소) 4번들</t>
+          <t>[오리온] 예감 오리지널 192g</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
         <v>3580</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F8" s="2">
         <f>D8*E8</f>
@@ -708,7 +708,7 @@
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5079319</t>
+          <t>https://www.kurly.com/goods/5095165</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -726,14 +726,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>[해태] 허니버터칩 4번들 (40g x 4묶음)</t>
+          <t>[오리온] 눈을감자 96g</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>3980</v>
+        <v>2720</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F9" s="2">
         <f>D9*E9</f>
@@ -743,11 +743,11 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>999</v>
+        <v>953</v>
       </c>
       <c r="I9" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000263120</t>
+          <t>https://www.kurly.com/goods/1000640848</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -765,28 +765,28 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>[해태] 가루비 감자칩 오리지널 40g X 3개입</t>
+          <t>[오리온] 썬 핫스파이시 4번들</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>2780</v>
+        <v>3380</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F10" s="2">
         <f>D10*E10</f>
         <v/>
       </c>
       <c r="G10" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>594</v>
+        <v>999</v>
       </c>
       <c r="I10" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000582944</t>
+          <t>https://www.kurly.com/goods/1000365879</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -804,14 +804,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>[오리온] 꼬북칩 캬라멜팝콘 미니 박스 30g x 12개입</t>
+          <t>[오리온] 눈을감자 칠리치즈프라이즈 96g</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>6800</v>
+        <v>2720</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F11" s="2">
         <f>D11*E11</f>
@@ -821,11 +821,11 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>274</v>
+        <v>494</v>
       </c>
       <c r="I11" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1001235091</t>
+          <t>https://www.kurly.com/goods/1001170989</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
@@ -838,19 +838,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>베이커리 소포장</t>
+          <t>개별포장 스낵/감자칩</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>[메종엠오] 마들렌 3종 (택1)</t>
+          <t>[오리온] 고래밥 20g x 10입</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>3500</v>
+        <v>4500</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F12" s="2">
         <f>D12*E12</f>
@@ -860,11 +860,11 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>9999</v>
+        <v>999</v>
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5009371</t>
+          <t>https://www.kurly.com/goods/5081412</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
@@ -877,19 +877,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>베이커리 소포장</t>
+          <t>개별포장 스낵/감자칩</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>[브레댄코] 봉주르 카스테라 2종 (택1)</t>
+          <t>[해태] 자가비 소포장 2종 (택1)</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>11500</v>
+        <v>3580</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F13" s="2">
         <f>D13*E13</f>
@@ -899,11 +899,11 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>9999</v>
+        <v>999</v>
       </c>
       <c r="I13" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5074339</t>
+          <t>https://www.kurly.com/goods/1000343575</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -921,11 +921,11 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>[오르랔베이커리] 크러핀 4종 (택1)</t>
+          <t>[메종엠오] 마들렌 3종 (택1)</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>5200</v>
+        <v>3500</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -942,7 +942,7 @@
       </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5093256</t>
+          <t>https://www.kurly.com/goods/5009371</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -955,33 +955,33 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>에너지바</t>
+          <t>베이커리 소포장</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>[네이처밸리] 그래놀라 바 3종 ,택1</t>
+          <t>[브레댄코] 봉주르 카스테라 2종 (택1)</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>3980</v>
+        <v>11500</v>
       </c>
       <c r="E15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F15" s="2">
         <f>D15*E15</f>
         <v/>
       </c>
       <c r="G15" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>9999</v>
       </c>
       <c r="I15" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5007664</t>
+          <t>https://www.kurly.com/goods/5074339</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -994,16 +994,16 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>에너지바</t>
+          <t>베이커리 소포장</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>[마켓오네이처] 오!그래놀라 다이제 2종 (택1)</t>
+          <t>[오르랔베이커리] 크러핀 4종 (택1)</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>5980</v>
+        <v>5200</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
@@ -1016,11 +1016,11 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>999</v>
+        <v>9999</v>
       </c>
       <c r="I16" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000593035</t>
+          <t>https://www.kurly.com/goods/5093256</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
@@ -1033,33 +1033,33 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>일본 과자</t>
+          <t>에너지바</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>[사토제과] 아주끼 모나카</t>
+          <t>[네이처밸리] 그래놀라 바 3종 ,택1</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>7380</v>
+        <v>3980</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F17" s="2">
         <f>D17*E17</f>
         <v/>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="H17" t="n">
-        <v>999</v>
+        <v>9999</v>
       </c>
       <c r="I17" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5081428</t>
+          <t>https://www.kurly.com/goods/5007664</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -1072,16 +1072,16 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>일본 과자</t>
+          <t>에너지바</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>[카수가이] 과일 구미 6종 (택1)</t>
+          <t>[마켓오네이처] 오!그래놀라 다이제 2종 (택1)</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>3980</v>
+        <v>5980</v>
       </c>
       <c r="E18" t="n">
         <v>1</v>
@@ -1094,11 +1094,11 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>514</v>
+        <v>999</v>
       </c>
       <c r="I18" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000499709</t>
+          <t>https://www.kurly.com/goods/1000593035</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
@@ -1111,19 +1111,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>초콜릿/캔디/젤리</t>
+          <t>일본 과자</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>[하리보] 폭신한 과일맛 젤리 3종, 택1</t>
+          <t>[사토제과] 아주끼 모나카</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>2180</v>
+        <v>7380</v>
       </c>
       <c r="E19" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F19" s="2">
         <f>D19*E19</f>
@@ -1133,11 +1133,11 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>835</v>
+        <v>999</v>
       </c>
       <c r="I19" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1001069960</t>
+          <t>https://www.kurly.com/goods/5081428</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
@@ -1150,19 +1150,19 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>초콜릿/캔디/젤리</t>
+          <t>일본 과자</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">[하리보] 요즘 트렌드 얼먹 젤리 3종 (택1) </t>
+          <t>[카수가이] 과일 구미 6종 (택1)</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>2180</v>
+        <v>3980</v>
       </c>
       <c r="E20" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F20" s="2">
         <f>D20*E20</f>
@@ -1172,11 +1172,11 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>741</v>
+        <v>514</v>
       </c>
       <c r="I20" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1002033102</t>
+          <t>https://www.kurly.com/goods/1000499709</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>[하리보] 핑크빛 젤리 2종, 택1</t>
+          <t>[하리보] 폭신한 과일맛 젤리 3종, 택1</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
@@ -1211,11 +1211,11 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>520</v>
+        <v>835</v>
       </c>
       <c r="I21" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000548776</t>
+          <t>https://www.kurly.com/goods/1001069960</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>[하리보] 헬로 제주 젤리 2종, 택1</t>
+          <t xml:space="preserve">[하리보] 요즘 트렌드 얼먹 젤리 3종 (택1) </t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
@@ -1250,11 +1250,11 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>243</v>
+        <v>741</v>
       </c>
       <c r="I22" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1002378241</t>
+          <t>https://www.kurly.com/goods/1002033102</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
@@ -1267,19 +1267,19 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>쿠키/비스킷(개별포장)</t>
+          <t>초콜릿/캔디/젤리</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>[해태] 에이스 364g (24g x 15봉지)</t>
+          <t>[하리보] 핑크빛 젤리 2종, 택1</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>3980</v>
+        <v>2180</v>
       </c>
       <c r="E23" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F23" s="2">
         <f>D23*E23</f>
@@ -1289,11 +1289,11 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>999</v>
+        <v>520</v>
       </c>
       <c r="I23" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5077465</t>
+          <t>https://www.kurly.com/goods/1000548776</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
@@ -1306,19 +1306,19 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>쿠키/비스킷(개별포장)</t>
+          <t>초콜릿/캔디/젤리</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>[오리온] 다이제 오리지널 351g</t>
+          <t>[하리보] 헬로 제주 젤리 2종, 택1</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>3280</v>
+        <v>2180</v>
       </c>
       <c r="E24" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F24" s="2">
         <f>D24*E24</f>
@@ -1328,11 +1328,11 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>999</v>
+        <v>243</v>
       </c>
       <c r="I24" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000033205</t>
+          <t>https://www.kurly.com/goods/1002378241</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>[해태] 에이스 바스크 치즈 케이크 364g</t>
+          <t>[해태] 에이스 364g (24g x 15봉지)</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="I25" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000490099</t>
+          <t>https://www.kurly.com/goods/5077465</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
@@ -1389,11 +1389,11 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>[맥비티] 다이제스티브 비스킷 2종 (택1)</t>
+          <t>[오리온] 다이제 오리지널 351g</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>2990</v>
+        <v>3280</v>
       </c>
       <c r="E26" t="n">
         <v>4</v>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="I26" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000975389</t>
+          <t>https://www.kurly.com/goods/1000033205</t>
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
@@ -1428,14 +1428,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>[오리온] 다이제 쏙쏙포장 5종 (택1)</t>
+          <t>[해태] 에이스 바스크 치즈 케이크 364g</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>3200</v>
+        <v>3980</v>
       </c>
       <c r="E27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F27" s="2">
         <f>D27*E27</f>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="I27" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000198198</t>
+          <t>https://www.kurly.com/goods/1000490099</t>
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
@@ -1467,14 +1467,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>[해태] 에이스 씬 에스프레소 291g</t>
+          <t>[맥비티] 다이제스티브 비스킷 2종 (택1)</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>3980</v>
+        <v>2990</v>
       </c>
       <c r="E28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F28" s="2">
         <f>D28*E28</f>
@@ -1488,7 +1488,7 @@
       </c>
       <c r="I28" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000528989</t>
+          <t>https://www.kurly.com/goods/1000975389</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
@@ -1506,14 +1506,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>[오리온] 촉촉한초코칩 320g</t>
+          <t>[오리온] 다이제 쏙쏙포장 5종 (택1)</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>4480</v>
+        <v>3200</v>
       </c>
       <c r="E29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F29" s="2">
         <f>D29*E29</f>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="I29" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5067311</t>
+          <t>https://www.kurly.com/goods/1000198198</t>
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
@@ -1545,11 +1545,11 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>[크라운] 쿠크다스 2종 (택1)</t>
+          <t>[해태] 에이스 씬 에스프레소 291g</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>4380</v>
+        <v>3980</v>
       </c>
       <c r="E30" t="n">
         <v>3</v>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="I30" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5121160</t>
+          <t>https://www.kurly.com/goods/1000528989</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
@@ -1584,14 +1584,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>[롯데] 마가렛트 오리지널 352g</t>
+          <t>[오리온] 촉촉한초코칩 320g</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>5440</v>
+        <v>4480</v>
       </c>
       <c r="E31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F31" s="2">
         <f>D31*E31</f>
@@ -1601,11 +1601,11 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>956</v>
+        <v>999</v>
       </c>
       <c r="I31" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000339526</t>
+          <t>https://www.kurly.com/goods/5067311</t>
         </is>
       </c>
       <c r="J31" t="inlineStr"/>
@@ -1623,11 +1623,11 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>[브레댄코] 리얼 브라우니 쿠키 2종 (택1)</t>
+          <t>[크라운] 쿠크다스 2종 (택1)</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>3690</v>
+        <v>4380</v>
       </c>
       <c r="E32" t="n">
         <v>1</v>
@@ -1640,11 +1640,11 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>9999</v>
+        <v>999</v>
       </c>
       <c r="I32" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5061562</t>
+          <t>https://www.kurly.com/goods/5121160</t>
         </is>
       </c>
       <c r="J32" t="inlineStr"/>
@@ -1662,11 +1662,11 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>[오리온] 예감 치즈 그라탕 204g</t>
+          <t>[롯데] 마가렛트 오리지널 352g</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>3580</v>
+        <v>5440</v>
       </c>
       <c r="E33" t="n">
         <v>1</v>
@@ -1679,11 +1679,11 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>999</v>
+        <v>956</v>
       </c>
       <c r="I33" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5095164</t>
+          <t>https://www.kurly.com/goods/1000339526</t>
         </is>
       </c>
       <c r="J33" t="inlineStr"/>
@@ -1701,11 +1701,11 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>[오리온] 예감 오리지널 192g</t>
+          <t>[브레댄코] 리얼 브라우니 쿠키 2종 (택1)</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>3580</v>
+        <v>3690</v>
       </c>
       <c r="E34" t="n">
         <v>1</v>
@@ -1718,11 +1718,11 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>999</v>
+        <v>9999</v>
       </c>
       <c r="I34" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5095165</t>
+          <t>https://www.kurly.com/goods/5061562</t>
         </is>
       </c>
       <c r="J34" t="inlineStr"/>
@@ -1813,19 +1813,19 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>파이/케이크(개별포장)</t>
+          <t>쿠키/비스킷(개별포장)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>[오리온] 초코파이 12입</t>
+          <t>[오리온] 다이제 샌드 우도땅콩 392g</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>4320</v>
+        <v>6000</v>
       </c>
       <c r="E37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F37" s="2">
         <f>D37*E37</f>
@@ -1835,11 +1835,11 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>9999</v>
+        <v>613</v>
       </c>
       <c r="I37" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5061296</t>
+          <t>https://www.kurly.com/goods/1001861625</t>
         </is>
       </c>
       <c r="J37" t="inlineStr"/>
@@ -1852,16 +1852,16 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>파이/케이크(개별포장)</t>
+          <t>쿠키/비스킷(개별포장)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>[해태] 오예스 미니 기획팩 764g (191g x 4팩)</t>
+          <t>[롯데] 칙촉 오리지널 벌크 180g</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>10800</v>
+        <v>4200</v>
       </c>
       <c r="E38" t="n">
         <v>1</v>
@@ -1874,11 +1874,11 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>865</v>
+        <v>999</v>
       </c>
       <c r="I38" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000339499</t>
+          <t>https://www.kurly.com/goods/5132978</t>
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>[오리온] 카스타드 12개입 276g</t>
+          <t>[오리온] 초코파이 12입</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
@@ -1913,11 +1913,11 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>745</v>
+        <v>9999</v>
       </c>
       <c r="I39" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000875718</t>
+          <t>https://www.kurly.com/goods/5061296</t>
         </is>
       </c>
       <c r="J39" t="inlineStr"/>
@@ -1935,11 +1935,11 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>[해태] 오예스 기획팩 840g (30g X 28봉지)</t>
+          <t>[해태] 오예스 미니 기획팩 764g (191g x 4팩)</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>11900</v>
+        <v>10800</v>
       </c>
       <c r="E40" t="n">
         <v>1</v>
@@ -1952,11 +1952,11 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>607</v>
+        <v>865</v>
       </c>
       <c r="I40" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1001391146</t>
+          <t>https://www.kurly.com/goods/1000339499</t>
         </is>
       </c>
       <c r="J40" t="inlineStr"/>
@@ -1974,11 +1974,11 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>[오리온] 초코파이 말차쇼콜라 408g</t>
+          <t>[오리온] 카스타드 12개입 276g</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>4800</v>
+        <v>4320</v>
       </c>
       <c r="E41" t="n">
         <v>3</v>
@@ -1991,11 +1991,11 @@
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>950</v>
+        <v>745</v>
       </c>
       <c r="I41" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1001382646</t>
+          <t>https://www.kurly.com/goods/1000875718</t>
         </is>
       </c>
       <c r="J41" t="inlineStr"/>
@@ -2013,14 +2013,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>[롯데] 몽쉘 생크림케이크 오리지널 408g</t>
+          <t>[해태] 오예스 기획팩 840g (30g X 28봉지)</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>5600</v>
+        <v>11900</v>
       </c>
       <c r="E42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F42" s="2">
         <f>D42*E42</f>
@@ -2030,11 +2030,11 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>999</v>
+        <v>607</v>
       </c>
       <c r="I42" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000175874</t>
+          <t>https://www.kurly.com/goods/1001391146</t>
         </is>
       </c>
       <c r="J42" t="inlineStr"/>
@@ -2052,14 +2052,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>[롯데] 몽쉘 생크림케이크 카카오 408g</t>
+          <t>[오리온] 초코파이 말차쇼콜라 408g</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>5600</v>
+        <v>4800</v>
       </c>
       <c r="E43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F43" s="2">
         <f>D43*E43</f>
@@ -2069,11 +2069,11 @@
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>999</v>
+        <v>950</v>
       </c>
       <c r="I43" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000175876</t>
+          <t>https://www.kurly.com/goods/1001382646</t>
         </is>
       </c>
       <c r="J43" t="inlineStr"/>
@@ -2091,31 +2091,109 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>[해태] 오예스 미니 크림소다맛 192g</t>
+          <t>[롯데] 몽쉘 생크림케이크 오리지널 408g</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>2506</v>
+        <v>5600</v>
       </c>
       <c r="E44" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F44" s="2">
         <f>D44*E44</f>
         <v/>
       </c>
       <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>999</v>
+      </c>
+      <c r="I44" s="8" t="inlineStr">
+        <is>
+          <t>https://www.kurly.com/goods/1000175874</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>추천</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>파이/케이크(개별포장)</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>[롯데] 몽쉘 생크림케이크 카카오 408g</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>5600</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" s="2">
+        <f>D45*E45</f>
+        <v/>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>999</v>
+      </c>
+      <c r="I45" s="8" t="inlineStr">
+        <is>
+          <t>https://www.kurly.com/goods/1000175876</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>추천</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>파이/케이크(개별포장)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>[해태] 오예스 미니 크림소다맛 192g</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>2506</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" s="2">
+        <f>D46*E46</f>
+        <v/>
+      </c>
+      <c r="G46" t="n">
         <v>30</v>
       </c>
-      <c r="H44" t="n">
+      <c r="H46" t="n">
         <v>187</v>
       </c>
-      <c r="I44" s="8" t="inlineStr">
+      <c r="I46" s="8" t="inlineStr">
         <is>
           <t>https://www.kurly.com/goods/1002225099</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -2159,6 +2237,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId42"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2208,11 +2288,11 @@
         </is>
       </c>
       <c r="B2">
-        <f>COUNTIF(구매목록!B5:B44,A2)</f>
+        <f>COUNTIF(구매목록!B5:B46,A2)</f>
         <v/>
       </c>
       <c r="C2" s="2">
-        <f>SUMIF(구매목록!B5:B44,A2,구매목록!F5:F44)</f>
+        <f>SUMIF(구매목록!B5:B46,A2,구매목록!F5:F46)</f>
         <v/>
       </c>
       <c r="D2" s="9">
@@ -2227,11 +2307,11 @@
         </is>
       </c>
       <c r="B3">
-        <f>COUNTIF(구매목록!B5:B44,A3)</f>
+        <f>COUNTIF(구매목록!B5:B46,A3)</f>
         <v/>
       </c>
       <c r="C3" s="2">
-        <f>SUMIF(구매목록!B5:B44,A3,구매목록!F5:F44)</f>
+        <f>SUMIF(구매목록!B5:B46,A3,구매목록!F5:F46)</f>
         <v/>
       </c>
       <c r="D3" s="9">
@@ -2246,11 +2326,11 @@
         </is>
       </c>
       <c r="B4">
-        <f>COUNTIF(구매목록!B5:B44,A4)</f>
+        <f>COUNTIF(구매목록!B5:B46,A4)</f>
         <v/>
       </c>
       <c r="C4" s="2">
-        <f>SUMIF(구매목록!B5:B44,A4,구매목록!F5:F44)</f>
+        <f>SUMIF(구매목록!B5:B46,A4,구매목록!F5:F46)</f>
         <v/>
       </c>
       <c r="D4" s="9">
@@ -2265,11 +2345,11 @@
         </is>
       </c>
       <c r="B5">
-        <f>COUNTIF(구매목록!B5:B44,A5)</f>
+        <f>COUNTIF(구매목록!B5:B46,A5)</f>
         <v/>
       </c>
       <c r="C5" s="2">
-        <f>SUMIF(구매목록!B5:B44,A5,구매목록!F5:F44)</f>
+        <f>SUMIF(구매목록!B5:B46,A5,구매목록!F5:F46)</f>
         <v/>
       </c>
       <c r="D5" s="9">
@@ -2284,11 +2364,11 @@
         </is>
       </c>
       <c r="B6">
-        <f>COUNTIF(구매목록!B5:B44,A6)</f>
+        <f>COUNTIF(구매목록!B5:B46,A6)</f>
         <v/>
       </c>
       <c r="C6" s="2">
-        <f>SUMIF(구매목록!B5:B44,A6,구매목록!F5:F44)</f>
+        <f>SUMIF(구매목록!B5:B46,A6,구매목록!F5:F46)</f>
         <v/>
       </c>
       <c r="D6" s="9">
@@ -2303,11 +2383,11 @@
         </is>
       </c>
       <c r="B7">
-        <f>COUNTIF(구매목록!B5:B44,A7)</f>
+        <f>COUNTIF(구매목록!B5:B46,A7)</f>
         <v/>
       </c>
       <c r="C7" s="2">
-        <f>SUMIF(구매목록!B5:B44,A7,구매목록!F5:F44)</f>
+        <f>SUMIF(구매목록!B5:B46,A7,구매목록!F5:F46)</f>
         <v/>
       </c>
       <c r="D7" s="9">
@@ -2322,11 +2402,11 @@
         </is>
       </c>
       <c r="B8">
-        <f>COUNTIF(구매목록!B5:B44,A8)</f>
+        <f>COUNTIF(구매목록!B5:B46,A8)</f>
         <v/>
       </c>
       <c r="C8" s="2">
-        <f>SUMIF(구매목록!B5:B44,A8,구매목록!F5:F44)</f>
+        <f>SUMIF(구매목록!B5:B46,A8,구매목록!F5:F46)</f>
         <v/>
       </c>
       <c r="D8" s="9">
@@ -2341,11 +2421,11 @@
         </is>
       </c>
       <c r="B9">
-        <f>COUNTIF(구매목록!B5:B44,A9)</f>
+        <f>COUNTIF(구매목록!B5:B46,A9)</f>
         <v/>
       </c>
       <c r="C9" s="2">
-        <f>SUMIF(구매목록!B5:B44,A9,구매목록!F5:F44)</f>
+        <f>SUMIF(구매목록!B5:B46,A9,구매목록!F5:F46)</f>
         <v/>
       </c>
       <c r="D9" s="9">

--- a/다과_구매목록.xlsx
+++ b/다과_구매목록.xlsx
@@ -960,11 +960,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>[브레댄코] 봉주르 카스테라 2종 (택1)</t>
+          <t>[삼립] 보름달 (66g X 3개입)</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>11500</v>
+        <v>4180</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
@@ -977,11 +977,11 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>9999</v>
+        <v>999</v>
       </c>
       <c r="I15" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5074339</t>
+          <t>https://www.kurly.com/goods/5136063</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -999,28 +999,28 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>[오르랔베이커리] 크러핀 4종 (택1)</t>
+          <t>[밀크앤허니] 파운드케이크 4종 (택1)</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>5200</v>
+        <v>11990</v>
       </c>
       <c r="E16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16" s="2">
         <f>D16*E16</f>
         <v/>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H16" t="n">
-        <v>9999</v>
+        <v>999</v>
       </c>
       <c r="I16" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5093256</t>
+          <t>https://www.kurly.com/goods/5043347</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
@@ -1077,11 +1077,11 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>[마켓오네이처] 오!그래놀라 다이제 2종 (택1)</t>
+          <t>[닥터유] 미니 에너지바 &amp; 단백질바 2종</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>5980</v>
+        <v>5120</v>
       </c>
       <c r="E18" t="n">
         <v>1</v>
@@ -1094,11 +1094,11 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>999</v>
+        <v>9999</v>
       </c>
       <c r="I18" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000593035</t>
+          <t>https://www.kurly.com/goods/5055905</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
@@ -1350,14 +1350,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>[해태] 에이스 바스크 치즈 케이크 364g</t>
+          <t>[맥비티] 다이제스티브 비스킷 2종 (택1)</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>3980</v>
+        <v>2990</v>
       </c>
       <c r="E25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F25" s="2">
         <f>D25*E25</f>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="I25" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000490099</t>
+          <t>https://www.kurly.com/goods/1000975389</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
@@ -1389,14 +1389,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>[맥비티] 다이제스티브 비스킷 2종 (택1)</t>
+          <t>[오리온] 다이제 쏙쏙포장 5종 (택1)</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>2990</v>
+        <v>3200</v>
       </c>
       <c r="E26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F26" s="2">
         <f>D26*E26</f>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="I26" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000975389</t>
+          <t>https://www.kurly.com/goods/1000198198</t>
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
@@ -1428,11 +1428,11 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>[오리온] 다이제 쏙쏙포장 5종 (택1)</t>
+          <t>[해태] 에이스 씬 에스프레소 291g</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>3200</v>
+        <v>3980</v>
       </c>
       <c r="E27" t="n">
         <v>3</v>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="I27" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000198198</t>
+          <t>https://www.kurly.com/goods/1000528989</t>
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
@@ -1467,14 +1467,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>[해태] 에이스 씬 에스프레소 291g</t>
+          <t>[롯데] 몽쉘 생크림케이크 카카오 408g</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>3980</v>
+        <v>5600</v>
       </c>
       <c r="E28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F28" s="2">
         <f>D28*E28</f>
@@ -1488,7 +1488,7 @@
       </c>
       <c r="I28" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000528989</t>
+          <t>https://www.kurly.com/goods/1000175876</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
@@ -1506,11 +1506,11 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>[롯데] 몽쉘 생크림케이크 카카오 408g</t>
+          <t>[오리온] 촉촉한초코칩 320g</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>5600</v>
+        <v>4480</v>
       </c>
       <c r="E29" t="n">
         <v>2</v>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="I29" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000175876</t>
+          <t>https://www.kurly.com/goods/5067311</t>
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
@@ -1545,14 +1545,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>[오리온] 촉촉한초코칩 320g</t>
+          <t>[크라운] 쿠크다스 2종 (택1)</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>4480</v>
+        <v>4380</v>
       </c>
       <c r="E30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F30" s="2">
         <f>D30*E30</f>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="I30" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5067311</t>
+          <t>https://www.kurly.com/goods/5121160</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
@@ -1584,14 +1584,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>[크라운] 쿠크다스 2종 (택1)</t>
+          <t>[롯데] 마가렛트 오리지널 352g</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>4380</v>
+        <v>5440</v>
       </c>
       <c r="E31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F31" s="2">
         <f>D31*E31</f>
@@ -1601,11 +1601,11 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>999</v>
+        <v>956</v>
       </c>
       <c r="I31" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5121160</t>
+          <t>https://www.kurly.com/goods/1000339526</t>
         </is>
       </c>
       <c r="J31" t="inlineStr"/>
@@ -1623,14 +1623,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>[롯데] 마가렛트 오리지널 352g</t>
+          <t>[브레댄코] 리얼 브라우니 쿠키 2종 (택1)</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>5440</v>
+        <v>3690</v>
       </c>
       <c r="E32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F32" s="2">
         <f>D32*E32</f>
@@ -1640,11 +1640,11 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>956</v>
+        <v>9999</v>
       </c>
       <c r="I32" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000339526</t>
+          <t>https://www.kurly.com/goods/5061562</t>
         </is>
       </c>
       <c r="J32" t="inlineStr"/>
@@ -1662,14 +1662,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>[브레댄코] 리얼 브라우니 쿠키 2종 (택1)</t>
+          <t>[반두아] 코코넛 크래커 150g</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>3690</v>
+        <v>2500</v>
       </c>
       <c r="E33" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F33" s="2">
         <f>D33*E33</f>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="I33" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5061562</t>
+          <t>https://www.kurly.com/goods/5049808</t>
         </is>
       </c>
       <c r="J33" t="inlineStr"/>
@@ -1701,11 +1701,11 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>[반두아] 코코넛 크래커 150g</t>
+          <t>[롯데제과] 카스타드 오리지널 230g</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>2500</v>
+        <v>4780</v>
       </c>
       <c r="E34" t="n">
         <v>1</v>
@@ -1718,11 +1718,11 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>9999</v>
+        <v>999</v>
       </c>
       <c r="I34" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5049808</t>
+          <t>https://www.kurly.com/goods/5061939</t>
         </is>
       </c>
       <c r="J34" t="inlineStr"/>

--- a/다과_구매목록.xlsx
+++ b/다과_구매목록.xlsx
@@ -999,11 +999,11 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>[밀크앤허니] 파운드케이크 4종 (택1)</t>
+          <t>[마루산] 도쿄바나나의 연인</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>11990</v>
+        <v>12510</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
@@ -1013,14 +1013,14 @@
         <v/>
       </c>
       <c r="G16" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H16" t="n">
-        <v>999</v>
+        <v>713</v>
       </c>
       <c r="I16" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5043347</t>
+          <t>https://www.kurly.com/goods/1000400351</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>

--- a/다과_구매목록.xlsx
+++ b/다과_구매목록.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -492,7 +492,7 @@
         </is>
       </c>
       <c r="D2" s="3">
-        <f>SUM(F5:F40)</f>
+        <f>SUM(F5:F39)</f>
         <v/>
       </c>
       <c r="E2" t="inlineStr">
@@ -726,11 +726,11 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>[오리온] 눈을감자 96g</t>
+          <t>[오리온] 썬 핫스파이시 4번들</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>2720</v>
+        <v>3380</v>
       </c>
       <c r="E9" t="n">
         <v>3</v>
@@ -743,11 +743,11 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>953</v>
+        <v>999</v>
       </c>
       <c r="I9" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000640848</t>
+          <t>https://www.kurly.com/goods/1000365879</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -765,11 +765,11 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>[오리온] 썬 핫스파이시 4번들</t>
+          <t>[오리온] 고래밥 20g x 10입</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>3380</v>
+        <v>4500</v>
       </c>
       <c r="E10" t="n">
         <v>3</v>
@@ -786,7 +786,7 @@
       </c>
       <c r="I10" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000365879</t>
+          <t>https://www.kurly.com/goods/5081412</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -804,11 +804,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>[오리온] 눈을감자 칠리치즈프라이즈 96g</t>
+          <t>[해태] 구운감자 27g x 5입</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>2720</v>
+        <v>3780</v>
       </c>
       <c r="E11" t="n">
         <v>3</v>
@@ -818,14 +818,14 @@
         <v/>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H11" t="n">
-        <v>494</v>
+        <v>999</v>
       </c>
       <c r="I11" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1001170989</t>
+          <t>https://www.kurly.com/goods/5110063</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
@@ -843,11 +843,11 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>[오리온] 고래밥 20g x 10입</t>
+          <t>[해태] 자가비 소포장 2종 (택1)</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>4500</v>
+        <v>3580</v>
       </c>
       <c r="E12" t="n">
         <v>3</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5081412</t>
+          <t>https://www.kurly.com/goods/1000343575</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
@@ -877,16 +877,16 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>개별포장 스낵/감자칩</t>
+          <t>베이커리 소포장</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>[해태] 구운감자 27g x 5입</t>
+          <t>[메종엠오] 마들렌 3종 (택1)</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>3780</v>
+        <v>3500</v>
       </c>
       <c r="E13" t="n">
         <v>3</v>
@@ -896,14 +896,14 @@
         <v/>
       </c>
       <c r="G13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>999</v>
+        <v>9999</v>
       </c>
       <c r="I13" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5110063</t>
+          <t>https://www.kurly.com/goods/5009371</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -921,14 +921,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>[메종엠오] 마들렌 3종 (택1)</t>
+          <t>[삼립] 보름달 (66g X 3개입)</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>3500</v>
+        <v>4180</v>
       </c>
       <c r="E14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F14" s="2">
         <f>D14*E14</f>
@@ -938,11 +938,11 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>9999</v>
+        <v>999</v>
       </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5009371</t>
+          <t>https://www.kurly.com/goods/5136063</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -960,11 +960,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>[삼립] 보름달 (66g X 3개입)</t>
+          <t>[마루산] 도쿄바나나의 연인</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>4180</v>
+        <v>12510</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
@@ -974,14 +974,14 @@
         <v/>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H15" t="n">
-        <v>999</v>
+        <v>713</v>
       </c>
       <c r="I15" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5136063</t>
+          <t>https://www.kurly.com/goods/1000400351</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -994,33 +994,33 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>베이커리 소포장</t>
+          <t>에너지바</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>[마루산] 도쿄바나나의 연인</t>
+          <t>[네이처밸리] 그래놀라 바 3종 ,택1</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>12510</v>
+        <v>3980</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" s="2">
         <f>D16*E16</f>
         <v/>
       </c>
       <c r="G16" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="H16" t="n">
-        <v>713</v>
+        <v>9999</v>
       </c>
       <c r="I16" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000400351</t>
+          <t>https://www.kurly.com/goods/5007664</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
@@ -1038,28 +1038,28 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>[네이처밸리] 그래놀라 바 3종 ,택1</t>
+          <t>[닥터유] 미니 에너지바 &amp; 단백질바 2종</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>3980</v>
+        <v>5120</v>
       </c>
       <c r="E17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F17" s="2">
         <f>D17*E17</f>
         <v/>
       </c>
       <c r="G17" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>9999</v>
       </c>
       <c r="I17" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5007664</t>
+          <t>https://www.kurly.com/goods/5055905</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -1072,16 +1072,16 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>에너지바</t>
+          <t>일본 과자</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>[닥터유] 미니 에너지바 &amp; 단백질바 2종</t>
+          <t>[사토제과] 아주끼 모나카</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>5120</v>
+        <v>7380</v>
       </c>
       <c r="E18" t="n">
         <v>1</v>
@@ -1094,11 +1094,11 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>9999</v>
+        <v>999</v>
       </c>
       <c r="I18" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5055905</t>
+          <t>https://www.kurly.com/goods/5081428</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
@@ -1116,11 +1116,11 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>[사토제과] 아주끼 모나카</t>
+          <t>[마루이치세이카] 밤긴돈(밤만쥬) 300g</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>7380</v>
+        <v>6480</v>
       </c>
       <c r="E19" t="n">
         <v>1</v>
@@ -1133,11 +1133,11 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>999</v>
+        <v>887</v>
       </c>
       <c r="I19" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5081428</t>
+          <t>https://www.kurly.com/goods/1000087294</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
@@ -1150,19 +1150,19 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>일본 과자</t>
+          <t>초콜릿/캔디/젤리</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>[마루이치세이카] 밤긴돈(밤만쥬) 300g</t>
+          <t>[하리보] 폭신한 과일맛 젤리 3종, 택1</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>6480</v>
+        <v>2180</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F20" s="2">
         <f>D20*E20</f>
@@ -1172,11 +1172,11 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>887</v>
+        <v>835</v>
       </c>
       <c r="I20" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000087294</t>
+          <t>https://www.kurly.com/goods/1001069960</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>[하리보] 폭신한 과일맛 젤리 3종, 택1</t>
+          <t xml:space="preserve">[하리보] 요즘 트렌드 얼먹 젤리 3종 (택1) </t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
@@ -1211,11 +1211,11 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>835</v>
+        <v>741</v>
       </c>
       <c r="I21" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1001069960</t>
+          <t>https://www.kurly.com/goods/1002033102</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">[하리보] 요즘 트렌드 얼먹 젤리 3종 (택1) </t>
+          <t>[하리보] 핑크빛 젤리 2종, 택1</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
@@ -1250,11 +1250,11 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>741</v>
+        <v>520</v>
       </c>
       <c r="I22" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1002033102</t>
+          <t>https://www.kurly.com/goods/1000548776</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>[하리보] 핑크빛 젤리 2종, 택1</t>
+          <t>[하리보] 헬로 제주 젤리 2종, 택1</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
@@ -1289,11 +1289,11 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>520</v>
+        <v>243</v>
       </c>
       <c r="I23" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000548776</t>
+          <t>https://www.kurly.com/goods/1002378241</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
@@ -1306,19 +1306,19 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>초콜릿/캔디/젤리</t>
+          <t>쿠키/비스킷(개별포장)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>[하리보] 헬로 제주 젤리 2종, 택1</t>
+          <t>[맥비티] 다이제스티브 비스킷 2종 (택1)</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>2180</v>
+        <v>2990</v>
       </c>
       <c r="E24" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F24" s="2">
         <f>D24*E24</f>
@@ -1328,11 +1328,11 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>243</v>
+        <v>999</v>
       </c>
       <c r="I24" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1002378241</t>
+          <t>https://www.kurly.com/goods/1000975389</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
@@ -1350,14 +1350,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>[맥비티] 다이제스티브 비스킷 2종 (택1)</t>
+          <t>[오리온] 다이제 쏙쏙포장 5종 (택1)</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>2990</v>
+        <v>3200</v>
       </c>
       <c r="E25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F25" s="2">
         <f>D25*E25</f>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="I25" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000975389</t>
+          <t>https://www.kurly.com/goods/1000198198</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
@@ -1389,11 +1389,11 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>[오리온] 다이제 쏙쏙포장 5종 (택1)</t>
+          <t>[해태] 에이스 씬 에스프레소 291g</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>3200</v>
+        <v>3980</v>
       </c>
       <c r="E26" t="n">
         <v>3</v>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="I26" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000198198</t>
+          <t>https://www.kurly.com/goods/1000528989</t>
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
@@ -1428,14 +1428,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>[해태] 에이스 씬 에스프레소 291g</t>
+          <t>[롯데] 몽쉘 생크림케이크 카카오 408g</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>3980</v>
+        <v>5600</v>
       </c>
       <c r="E27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F27" s="2">
         <f>D27*E27</f>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="I27" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000528989</t>
+          <t>https://www.kurly.com/goods/1000175876</t>
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
@@ -1467,11 +1467,11 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>[롯데] 몽쉘 생크림케이크 카카오 408g</t>
+          <t>[오리온] 촉촉한초코칩 320g</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>5600</v>
+        <v>4480</v>
       </c>
       <c r="E28" t="n">
         <v>2</v>
@@ -1488,7 +1488,7 @@
       </c>
       <c r="I28" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000175876</t>
+          <t>https://www.kurly.com/goods/5067311</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
@@ -1506,14 +1506,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>[오리온] 촉촉한초코칩 320g</t>
+          <t>[크라운] 쿠크다스 2종 (택1)</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>4480</v>
+        <v>4380</v>
       </c>
       <c r="E29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F29" s="2">
         <f>D29*E29</f>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="I29" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5067311</t>
+          <t>https://www.kurly.com/goods/5121160</t>
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
@@ -1545,14 +1545,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>[크라운] 쿠크다스 2종 (택1)</t>
+          <t>[롯데] 마가렛트 오리지널 352g</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>4380</v>
+        <v>5440</v>
       </c>
       <c r="E30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F30" s="2">
         <f>D30*E30</f>
@@ -1562,11 +1562,11 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>999</v>
+        <v>956</v>
       </c>
       <c r="I30" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5121160</t>
+          <t>https://www.kurly.com/goods/1000339526</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
@@ -1584,14 +1584,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>[롯데] 마가렛트 오리지널 352g</t>
+          <t>[브레댄코] 리얼 브라우니 쿠키 2종 (택1)</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>5440</v>
+        <v>3690</v>
       </c>
       <c r="E31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F31" s="2">
         <f>D31*E31</f>
@@ -1601,11 +1601,11 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>956</v>
+        <v>9999</v>
       </c>
       <c r="I31" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000339526</t>
+          <t>https://www.kurly.com/goods/5061562</t>
         </is>
       </c>
       <c r="J31" t="inlineStr"/>
@@ -1623,14 +1623,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>[브레댄코] 리얼 브라우니 쿠키 2종 (택1)</t>
+          <t>[반두아] 코코넛 크래커 150g</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>3690</v>
+        <v>2500</v>
       </c>
       <c r="E32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F32" s="2">
         <f>D32*E32</f>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="I32" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5061562</t>
+          <t>https://www.kurly.com/goods/5049808</t>
         </is>
       </c>
       <c r="J32" t="inlineStr"/>
@@ -1662,14 +1662,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>[반두아] 코코넛 크래커 150g</t>
+          <t>[롯데제과] 카스타드 오리지널 230g</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>2500</v>
+        <v>4780</v>
       </c>
       <c r="E33" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F33" s="2">
         <f>D33*E33</f>
@@ -1679,11 +1679,11 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>9999</v>
+        <v>999</v>
       </c>
       <c r="I33" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5049808</t>
+          <t>https://www.kurly.com/goods/5061939</t>
         </is>
       </c>
       <c r="J33" t="inlineStr"/>
@@ -1696,19 +1696,19 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>쿠키/비스킷(개별포장)</t>
+          <t>파이/케이크(개별포장)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>[롯데제과] 카스타드 오리지널 230g</t>
+          <t>[오리온] 초코파이 12입</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>4780</v>
+        <v>4320</v>
       </c>
       <c r="E34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F34" s="2">
         <f>D34*E34</f>
@@ -1718,11 +1718,11 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>999</v>
+        <v>9999</v>
       </c>
       <c r="I34" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5061939</t>
+          <t>https://www.kurly.com/goods/5061296</t>
         </is>
       </c>
       <c r="J34" t="inlineStr"/>
@@ -1740,14 +1740,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>[오리온] 초코파이 12입</t>
+          <t>[해태] 오예스 미니 기획팩 764g (191g x 4팩)</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>4320</v>
+        <v>10800</v>
       </c>
       <c r="E35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F35" s="2">
         <f>D35*E35</f>
@@ -1757,11 +1757,11 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>9999</v>
+        <v>865</v>
       </c>
       <c r="I35" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5061296</t>
+          <t>https://www.kurly.com/goods/1000339499</t>
         </is>
       </c>
       <c r="J35" t="inlineStr"/>
@@ -1779,14 +1779,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>[해태] 오예스 미니 기획팩 764g (191g x 4팩)</t>
+          <t>[오리온] 카스타드 12개입 276g</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>10800</v>
+        <v>4320</v>
       </c>
       <c r="E36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F36" s="2">
         <f>D36*E36</f>
@@ -1796,11 +1796,11 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>865</v>
+        <v>745</v>
       </c>
       <c r="I36" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000339499</t>
+          <t>https://www.kurly.com/goods/1000875718</t>
         </is>
       </c>
       <c r="J36" t="inlineStr"/>
@@ -1818,14 +1818,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>[오리온] 카스타드 12개입 276g</t>
+          <t>[해태] 오예스 기획팩 840g (30g X 28봉지)</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>4320</v>
+        <v>11900</v>
       </c>
       <c r="E37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F37" s="2">
         <f>D37*E37</f>
@@ -1835,11 +1835,11 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>745</v>
+        <v>607</v>
       </c>
       <c r="I37" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000875718</t>
+          <t>https://www.kurly.com/goods/1001391146</t>
         </is>
       </c>
       <c r="J37" t="inlineStr"/>
@@ -1857,14 +1857,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>[해태] 오예스 기획팩 840g (30g X 28봉지)</t>
+          <t>[오리온] 초코파이 말차쇼콜라 408g</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>11900</v>
+        <v>4800</v>
       </c>
       <c r="E38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F38" s="2">
         <f>D38*E38</f>
@@ -1874,11 +1874,11 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>607</v>
+        <v>950</v>
       </c>
       <c r="I38" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1001391146</t>
+          <t>https://www.kurly.com/goods/1001382646</t>
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
@@ -1896,14 +1896,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>[오리온] 초코파이 말차쇼콜라 408g</t>
+          <t>[롯데] 몽쉘 생크림케이크 오리지널 408g</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>4800</v>
+        <v>5600</v>
       </c>
       <c r="E39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F39" s="2">
         <f>D39*E39</f>
@@ -1913,53 +1913,14 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>950</v>
+        <v>999</v>
       </c>
       <c r="I39" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1001382646</t>
+          <t>https://www.kurly.com/goods/1000175874</t>
         </is>
       </c>
       <c r="J39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>추천</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>파이/케이크(개별포장)</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>[롯데] 몽쉘 생크림케이크 오리지널 408g</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="n">
-        <v>5600</v>
-      </c>
-      <c r="E40" t="n">
-        <v>2</v>
-      </c>
-      <c r="F40" s="2">
-        <f>D40*E40</f>
-        <v/>
-      </c>
-      <c r="G40" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" t="n">
-        <v>999</v>
-      </c>
-      <c r="I40" s="8" t="inlineStr">
-        <is>
-          <t>https://www.kurly.com/goods/1000175874</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1998,7 +1959,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="rId36"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2048,11 +2008,11 @@
         </is>
       </c>
       <c r="B2">
-        <f>COUNTIF(구매목록!B5:B40,A2)</f>
+        <f>COUNTIF(구매목록!B5:B39,A2)</f>
         <v/>
       </c>
       <c r="C2" s="2">
-        <f>SUMIF(구매목록!B5:B40,A2,구매목록!F5:F40)</f>
+        <f>SUMIF(구매목록!B5:B39,A2,구매목록!F5:F39)</f>
         <v/>
       </c>
       <c r="D2" s="9">
@@ -2067,11 +2027,11 @@
         </is>
       </c>
       <c r="B3">
-        <f>COUNTIF(구매목록!B5:B40,A3)</f>
+        <f>COUNTIF(구매목록!B5:B39,A3)</f>
         <v/>
       </c>
       <c r="C3" s="2">
-        <f>SUMIF(구매목록!B5:B40,A3,구매목록!F5:F40)</f>
+        <f>SUMIF(구매목록!B5:B39,A3,구매목록!F5:F39)</f>
         <v/>
       </c>
       <c r="D3" s="9">
@@ -2086,11 +2046,11 @@
         </is>
       </c>
       <c r="B4">
-        <f>COUNTIF(구매목록!B5:B40,A4)</f>
+        <f>COUNTIF(구매목록!B5:B39,A4)</f>
         <v/>
       </c>
       <c r="C4" s="2">
-        <f>SUMIF(구매목록!B5:B40,A4,구매목록!F5:F40)</f>
+        <f>SUMIF(구매목록!B5:B39,A4,구매목록!F5:F39)</f>
         <v/>
       </c>
       <c r="D4" s="9">
@@ -2105,11 +2065,11 @@
         </is>
       </c>
       <c r="B5">
-        <f>COUNTIF(구매목록!B5:B40,A5)</f>
+        <f>COUNTIF(구매목록!B5:B39,A5)</f>
         <v/>
       </c>
       <c r="C5" s="2">
-        <f>SUMIF(구매목록!B5:B40,A5,구매목록!F5:F40)</f>
+        <f>SUMIF(구매목록!B5:B39,A5,구매목록!F5:F39)</f>
         <v/>
       </c>
       <c r="D5" s="9">
@@ -2124,11 +2084,11 @@
         </is>
       </c>
       <c r="B6">
-        <f>COUNTIF(구매목록!B5:B40,A6)</f>
+        <f>COUNTIF(구매목록!B5:B39,A6)</f>
         <v/>
       </c>
       <c r="C6" s="2">
-        <f>SUMIF(구매목록!B5:B40,A6,구매목록!F5:F40)</f>
+        <f>SUMIF(구매목록!B5:B39,A6,구매목록!F5:F39)</f>
         <v/>
       </c>
       <c r="D6" s="9">
@@ -2143,11 +2103,11 @@
         </is>
       </c>
       <c r="B7">
-        <f>COUNTIF(구매목록!B5:B40,A7)</f>
+        <f>COUNTIF(구매목록!B5:B39,A7)</f>
         <v/>
       </c>
       <c r="C7" s="2">
-        <f>SUMIF(구매목록!B5:B40,A7,구매목록!F5:F40)</f>
+        <f>SUMIF(구매목록!B5:B39,A7,구매목록!F5:F39)</f>
         <v/>
       </c>
       <c r="D7" s="9">
@@ -2162,11 +2122,11 @@
         </is>
       </c>
       <c r="B8">
-        <f>COUNTIF(구매목록!B5:B40,A8)</f>
+        <f>COUNTIF(구매목록!B5:B39,A8)</f>
         <v/>
       </c>
       <c r="C8" s="2">
-        <f>SUMIF(구매목록!B5:B40,A8,구매목록!F5:F40)</f>
+        <f>SUMIF(구매목록!B5:B39,A8,구매목록!F5:F39)</f>
         <v/>
       </c>
       <c r="D8" s="9">
@@ -2181,11 +2141,11 @@
         </is>
       </c>
       <c r="B9">
-        <f>COUNTIF(구매목록!B5:B40,A9)</f>
+        <f>COUNTIF(구매목록!B5:B39,A9)</f>
         <v/>
       </c>
       <c r="C9" s="2">
-        <f>SUMIF(구매목록!B5:B40,A9,구매목록!F5:F40)</f>
+        <f>SUMIF(구매목록!B5:B39,A9,구매목록!F5:F39)</f>
         <v/>
       </c>
       <c r="D9" s="9">

--- a/다과_구매목록.xlsx
+++ b/다과_구매목록.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -492,7 +492,7 @@
         </is>
       </c>
       <c r="D2" s="3">
-        <f>SUM(F5:F39)</f>
+        <f>SUM(F5:F38)</f>
         <v/>
       </c>
       <c r="E2" t="inlineStr">
@@ -877,33 +877,33 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>베이커리 소포장</t>
+          <t>에너지바</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>[메종엠오] 마들렌 3종 (택1)</t>
+          <t>[네이처밸리] 그래놀라 바 3종 ,택1</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>3500</v>
+        <v>3980</v>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F13" s="2">
         <f>D13*E13</f>
         <v/>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="H13" t="n">
         <v>9999</v>
       </c>
       <c r="I13" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5009371</t>
+          <t>https://www.kurly.com/goods/5007664</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -916,19 +916,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>베이커리 소포장</t>
+          <t>에너지바</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>[삼립] 보름달 (66g X 3개입)</t>
+          <t>[닥터유] 미니 에너지바 &amp; 단백질바 2종</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>4180</v>
+        <v>5120</v>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F14" s="2">
         <f>D14*E14</f>
@@ -938,11 +938,11 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>999</v>
+        <v>9999</v>
       </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5136063</t>
+          <t>https://www.kurly.com/goods/5055905</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -955,16 +955,16 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>베이커리 소포장</t>
+          <t>일본 과자</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>[마루산] 도쿄바나나의 연인</t>
+          <t>[마루이치세이카] 밤긴돈(밤만쥬) 300g</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>12510</v>
+        <v>6480</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
@@ -974,14 +974,14 @@
         <v/>
       </c>
       <c r="G15" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>713</v>
+        <v>887</v>
       </c>
       <c r="I15" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000400351</t>
+          <t>https://www.kurly.com/goods/1000087294</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -994,33 +994,33 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>에너지바</t>
+          <t>일본 과자</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>[네이처밸리] 그래놀라 바 3종 ,택1</t>
+          <t>[일본디저트여행] 쿠리 미니 밤만쥬 15g*6개입</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>3980</v>
+        <v>6000</v>
       </c>
       <c r="E16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16" s="2">
         <f>D16*E16</f>
         <v/>
       </c>
       <c r="G16" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>9999</v>
+        <v>363</v>
       </c>
       <c r="I16" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5007664</t>
+          <t>https://www.kurly.com/goods/1001899499</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
@@ -1033,19 +1033,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>에너지바</t>
+          <t>초콜릿/캔디/젤리</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>[닥터유] 미니 에너지바 &amp; 단백질바 2종</t>
+          <t>[하리보] 폭신한 과일맛 젤리 3종, 택1</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>5120</v>
+        <v>2180</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F17" s="2">
         <f>D17*E17</f>
@@ -1055,11 +1055,11 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>9999</v>
+        <v>835</v>
       </c>
       <c r="I17" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5055905</t>
+          <t>https://www.kurly.com/goods/1001069960</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -1072,19 +1072,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>일본 과자</t>
+          <t>초콜릿/캔디/젤리</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>[사토제과] 아주끼 모나카</t>
+          <t xml:space="preserve">[하리보] 요즘 트렌드 얼먹 젤리 3종 (택1) </t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>7380</v>
+        <v>2180</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F18" s="2">
         <f>D18*E18</f>
@@ -1094,11 +1094,11 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>999</v>
+        <v>741</v>
       </c>
       <c r="I18" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5081428</t>
+          <t>https://www.kurly.com/goods/1002033102</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
@@ -1111,19 +1111,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>일본 과자</t>
+          <t>초콜릿/캔디/젤리</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>[마루이치세이카] 밤긴돈(밤만쥬) 300g</t>
+          <t>[하리보] 핑크빛 젤리 2종, 택1</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>6480</v>
+        <v>2180</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F19" s="2">
         <f>D19*E19</f>
@@ -1133,11 +1133,11 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>887</v>
+        <v>520</v>
       </c>
       <c r="I19" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000087294</t>
+          <t>https://www.kurly.com/goods/1000548776</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
@@ -1155,7 +1155,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>[하리보] 폭신한 과일맛 젤리 3종, 택1</t>
+          <t>[하리보] 헬로 제주 젤리 2종, 택1</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
@@ -1172,11 +1172,11 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>835</v>
+        <v>243</v>
       </c>
       <c r="I20" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1001069960</t>
+          <t>https://www.kurly.com/goods/1002378241</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
@@ -1189,19 +1189,19 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>초콜릿/캔디/젤리</t>
+          <t>쿠키/비스킷(개별포장)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">[하리보] 요즘 트렌드 얼먹 젤리 3종 (택1) </t>
+          <t>[맥비티] 다이제스티브 비스킷 2종 (택1)</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>2180</v>
+        <v>2990</v>
       </c>
       <c r="E21" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F21" s="2">
         <f>D21*E21</f>
@@ -1211,11 +1211,11 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>741</v>
+        <v>999</v>
       </c>
       <c r="I21" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1002033102</t>
+          <t>https://www.kurly.com/goods/1000975389</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
@@ -1228,19 +1228,19 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>초콜릿/캔디/젤리</t>
+          <t>쿠키/비스킷(개별포장)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>[하리보] 핑크빛 젤리 2종, 택1</t>
+          <t>[오리온] 다이제 쏙쏙포장 5종 (택1)</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>2180</v>
+        <v>3200</v>
       </c>
       <c r="E22" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F22" s="2">
         <f>D22*E22</f>
@@ -1250,11 +1250,11 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>520</v>
+        <v>999</v>
       </c>
       <c r="I22" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000548776</t>
+          <t>https://www.kurly.com/goods/1000198198</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
@@ -1267,19 +1267,19 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>초콜릿/캔디/젤리</t>
+          <t>쿠키/비스킷(개별포장)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>[하리보] 헬로 제주 젤리 2종, 택1</t>
+          <t>[해태] 에이스 씬 에스프레소 291g</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>2180</v>
+        <v>3980</v>
       </c>
       <c r="E23" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F23" s="2">
         <f>D23*E23</f>
@@ -1289,11 +1289,11 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>243</v>
+        <v>999</v>
       </c>
       <c r="I23" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1002378241</t>
+          <t>https://www.kurly.com/goods/1000528989</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
@@ -1311,14 +1311,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>[맥비티] 다이제스티브 비스킷 2종 (택1)</t>
+          <t>[오리온] 촉촉한초코칩 320g</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>2990</v>
+        <v>4480</v>
       </c>
       <c r="E24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F24" s="2">
         <f>D24*E24</f>
@@ -1332,7 +1332,7 @@
       </c>
       <c r="I24" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000975389</t>
+          <t>https://www.kurly.com/goods/5067311</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
@@ -1350,11 +1350,11 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>[오리온] 다이제 쏙쏙포장 5종 (택1)</t>
+          <t>[크라운] 쿠크다스 2종 (택1)</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>3200</v>
+        <v>4380</v>
       </c>
       <c r="E25" t="n">
         <v>3</v>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="I25" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000198198</t>
+          <t>https://www.kurly.com/goods/5121160</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
@@ -1389,14 +1389,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>[해태] 에이스 씬 에스프레소 291g</t>
+          <t>[롯데] 마가렛트 오리지널 352g</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>3980</v>
+        <v>5440</v>
       </c>
       <c r="E26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F26" s="2">
         <f>D26*E26</f>
@@ -1406,11 +1406,11 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>999</v>
+        <v>956</v>
       </c>
       <c r="I26" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000528989</t>
+          <t>https://www.kurly.com/goods/1000339526</t>
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
@@ -1428,14 +1428,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>[롯데] 몽쉘 생크림케이크 카카오 408g</t>
+          <t>[브레댄코] 리얼 브라우니 쿠키 2종 (택1)</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>5600</v>
+        <v>3690</v>
       </c>
       <c r="E27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F27" s="2">
         <f>D27*E27</f>
@@ -1445,11 +1445,11 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>999</v>
+        <v>9999</v>
       </c>
       <c r="I27" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000175876</t>
+          <t>https://www.kurly.com/goods/5061562</t>
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
@@ -1467,14 +1467,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>[오리온] 촉촉한초코칩 320g</t>
+          <t>[반두아] 코코넛 크래커 150g</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>4480</v>
+        <v>2500</v>
       </c>
       <c r="E28" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F28" s="2">
         <f>D28*E28</f>
@@ -1484,11 +1484,11 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>999</v>
+        <v>9999</v>
       </c>
       <c r="I28" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5067311</t>
+          <t>https://www.kurly.com/goods/5049808</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
@@ -1506,11 +1506,11 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>[크라운] 쿠크다스 2종 (택1)</t>
+          <t>[롯데제과] 카스타드 오리지널 230g</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>4380</v>
+        <v>4780</v>
       </c>
       <c r="E29" t="n">
         <v>3</v>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="I29" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5121160</t>
+          <t>https://www.kurly.com/goods/5061939</t>
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
@@ -1545,11 +1545,11 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>[롯데] 마가렛트 오리지널 352g</t>
+          <t>[오리온] 다이제 샌드 우도땅콩 392g</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>5440</v>
+        <v>6000</v>
       </c>
       <c r="E30" t="n">
         <v>2</v>
@@ -1562,11 +1562,11 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>956</v>
+        <v>613</v>
       </c>
       <c r="I30" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000339526</t>
+          <t>https://www.kurly.com/goods/1001861625</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
@@ -1584,14 +1584,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>[브레댄코] 리얼 브라우니 쿠키 2종 (택1)</t>
+          <t>[롯데] 칙촉 오리지널 벌크 180g</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>3690</v>
+        <v>4200</v>
       </c>
       <c r="E31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F31" s="2">
         <f>D31*E31</f>
@@ -1601,11 +1601,11 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>9999</v>
+        <v>999</v>
       </c>
       <c r="I31" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5061562</t>
+          <t>https://www.kurly.com/goods/5132978</t>
         </is>
       </c>
       <c r="J31" t="inlineStr"/>
@@ -1618,19 +1618,19 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>쿠키/비스킷(개별포장)</t>
+          <t>파이/케이크(개별포장)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>[반두아] 코코넛 크래커 150g</t>
+          <t>[오리온] 초코파이 12입</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>2500</v>
+        <v>4320</v>
       </c>
       <c r="E32" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F32" s="2">
         <f>D32*E32</f>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="I32" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5049808</t>
+          <t>https://www.kurly.com/goods/5061296</t>
         </is>
       </c>
       <c r="J32" t="inlineStr"/>
@@ -1657,19 +1657,19 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>쿠키/비스킷(개별포장)</t>
+          <t>파이/케이크(개별포장)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>[롯데제과] 카스타드 오리지널 230g</t>
+          <t>[오리온] 카스타드 12개입 276g</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>4780</v>
+        <v>4320</v>
       </c>
       <c r="E33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F33" s="2">
         <f>D33*E33</f>
@@ -1679,11 +1679,11 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>999</v>
+        <v>745</v>
       </c>
       <c r="I33" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5061939</t>
+          <t>https://www.kurly.com/goods/1000875718</t>
         </is>
       </c>
       <c r="J33" t="inlineStr"/>
@@ -1701,11 +1701,11 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>[오리온] 초코파이 12입</t>
+          <t>[오리온] 초코파이 말차쇼콜라 408g</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>4320</v>
+        <v>4800</v>
       </c>
       <c r="E34" t="n">
         <v>3</v>
@@ -1718,11 +1718,11 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>9999</v>
+        <v>950</v>
       </c>
       <c r="I34" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/5061296</t>
+          <t>https://www.kurly.com/goods/1001382646</t>
         </is>
       </c>
       <c r="J34" t="inlineStr"/>
@@ -1740,14 +1740,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>[해태] 오예스 미니 기획팩 764g (191g x 4팩)</t>
+          <t>[롯데] 몽쉘 생크림케이크 오리지널 408g</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>10800</v>
+        <v>5600</v>
       </c>
       <c r="E35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F35" s="2">
         <f>D35*E35</f>
@@ -1757,11 +1757,11 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>865</v>
+        <v>999</v>
       </c>
       <c r="I35" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000339499</t>
+          <t>https://www.kurly.com/goods/1000175874</t>
         </is>
       </c>
       <c r="J35" t="inlineStr"/>
@@ -1779,14 +1779,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>[오리온] 카스타드 12개입 276g</t>
+          <t>[롯데] 몽쉘 생크림케이크 카카오 408g</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>4320</v>
+        <v>5600</v>
       </c>
       <c r="E36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F36" s="2">
         <f>D36*E36</f>
@@ -1796,11 +1796,11 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>745</v>
+        <v>999</v>
       </c>
       <c r="I36" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1000875718</t>
+          <t>https://www.kurly.com/goods/1000175876</t>
         </is>
       </c>
       <c r="J36" t="inlineStr"/>
@@ -1818,28 +1818,28 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>[해태] 오예스 기획팩 840g (30g X 28봉지)</t>
+          <t>[해태] 오예스 미니 크림소다맛 192g</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>11900</v>
+        <v>2506</v>
       </c>
       <c r="E37" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F37" s="2">
         <f>D37*E37</f>
         <v/>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H37" t="n">
-        <v>607</v>
+        <v>187</v>
       </c>
       <c r="I37" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1001391146</t>
+          <t>https://www.kurly.com/goods/1002225099</t>
         </is>
       </c>
       <c r="J37" t="inlineStr"/>
@@ -1857,14 +1857,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>[오리온] 초코파이 말차쇼콜라 408g</t>
+          <t>[해태] 오예스 360g 2종 (택1)</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>4800</v>
+        <v>5280</v>
       </c>
       <c r="E38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F38" s="2">
         <f>D38*E38</f>
@@ -1874,53 +1874,14 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>950</v>
+        <v>999</v>
       </c>
       <c r="I38" s="8" t="inlineStr">
         <is>
-          <t>https://www.kurly.com/goods/1001382646</t>
+          <t>https://www.kurly.com/goods/1000201444</t>
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>추천</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>파이/케이크(개별포장)</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>[롯데] 몽쉘 생크림케이크 오리지널 408g</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="n">
-        <v>5600</v>
-      </c>
-      <c r="E39" t="n">
-        <v>2</v>
-      </c>
-      <c r="F39" s="2">
-        <f>D39*E39</f>
-        <v/>
-      </c>
-      <c r="G39" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" t="n">
-        <v>999</v>
-      </c>
-      <c r="I39" s="8" t="inlineStr">
-        <is>
-          <t>https://www.kurly.com/goods/1000175874</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1958,7 +1919,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I36" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="rId35"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1970,7 +1930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2008,15 +1968,15 @@
         </is>
       </c>
       <c r="B2">
-        <f>COUNTIF(구매목록!B5:B39,A2)</f>
+        <f>COUNTIF(구매목록!B5:B38,A2)</f>
         <v/>
       </c>
       <c r="C2" s="2">
-        <f>SUMIF(구매목록!B5:B39,A2,구매목록!F5:F39)</f>
+        <f>SUMIF(구매목록!B5:B38,A2,구매목록!F5:F38)</f>
         <v/>
       </c>
       <c r="D2" s="9">
-        <f>C2/SUM($C$2:$C$9)</f>
+        <f>C2/SUM($C$2:$C$8)</f>
         <v/>
       </c>
     </row>
@@ -2027,15 +1987,15 @@
         </is>
       </c>
       <c r="B3">
-        <f>COUNTIF(구매목록!B5:B39,A3)</f>
+        <f>COUNTIF(구매목록!B5:B38,A3)</f>
         <v/>
       </c>
       <c r="C3" s="2">
-        <f>SUMIF(구매목록!B5:B39,A3,구매목록!F5:F39)</f>
+        <f>SUMIF(구매목록!B5:B38,A3,구매목록!F5:F38)</f>
         <v/>
       </c>
       <c r="D3" s="9">
-        <f>C3/SUM($C$2:$C$9)</f>
+        <f>C3/SUM($C$2:$C$8)</f>
         <v/>
       </c>
     </row>
@@ -2046,110 +2006,91 @@
         </is>
       </c>
       <c r="B4">
-        <f>COUNTIF(구매목록!B5:B39,A4)</f>
+        <f>COUNTIF(구매목록!B5:B38,A4)</f>
         <v/>
       </c>
       <c r="C4" s="2">
-        <f>SUMIF(구매목록!B5:B39,A4,구매목록!F5:F39)</f>
+        <f>SUMIF(구매목록!B5:B38,A4,구매목록!F5:F38)</f>
         <v/>
       </c>
       <c r="D4" s="9">
-        <f>C4/SUM($C$2:$C$9)</f>
+        <f>C4/SUM($C$2:$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>베이커리 소포장</t>
+          <t>초콜릿/캔디/젤리</t>
         </is>
       </c>
       <c r="B5">
-        <f>COUNTIF(구매목록!B5:B39,A5)</f>
+        <f>COUNTIF(구매목록!B5:B38,A5)</f>
         <v/>
       </c>
       <c r="C5" s="2">
-        <f>SUMIF(구매목록!B5:B39,A5,구매목록!F5:F39)</f>
+        <f>SUMIF(구매목록!B5:B38,A5,구매목록!F5:F38)</f>
         <v/>
       </c>
       <c r="D5" s="9">
-        <f>C5/SUM($C$2:$C$9)</f>
+        <f>C5/SUM($C$2:$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>초콜릿/캔디/젤리</t>
+          <t>일본 과자</t>
         </is>
       </c>
       <c r="B6">
-        <f>COUNTIF(구매목록!B5:B39,A6)</f>
+        <f>COUNTIF(구매목록!B5:B38,A6)</f>
         <v/>
       </c>
       <c r="C6" s="2">
-        <f>SUMIF(구매목록!B5:B39,A6,구매목록!F5:F39)</f>
+        <f>SUMIF(구매목록!B5:B38,A6,구매목록!F5:F38)</f>
         <v/>
       </c>
       <c r="D6" s="9">
-        <f>C6/SUM($C$2:$C$9)</f>
+        <f>C6/SUM($C$2:$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>일본 과자</t>
+          <t>개별포장 스낵/감자칩</t>
         </is>
       </c>
       <c r="B7">
-        <f>COUNTIF(구매목록!B5:B39,A7)</f>
+        <f>COUNTIF(구매목록!B5:B38,A7)</f>
         <v/>
       </c>
       <c r="C7" s="2">
-        <f>SUMIF(구매목록!B5:B39,A7,구매목록!F5:F39)</f>
+        <f>SUMIF(구매목록!B5:B38,A7,구매목록!F5:F38)</f>
         <v/>
       </c>
       <c r="D7" s="9">
-        <f>C7/SUM($C$2:$C$9)</f>
+        <f>C7/SUM($C$2:$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>개별포장 스낵/감자칩</t>
+          <t>에너지바</t>
         </is>
       </c>
       <c r="B8">
-        <f>COUNTIF(구매목록!B5:B39,A8)</f>
+        <f>COUNTIF(구매목록!B5:B38,A8)</f>
         <v/>
       </c>
       <c r="C8" s="2">
-        <f>SUMIF(구매목록!B5:B39,A8,구매목록!F5:F39)</f>
+        <f>SUMIF(구매목록!B5:B38,A8,구매목록!F5:F38)</f>
         <v/>
       </c>
       <c r="D8" s="9">
-        <f>C8/SUM($C$2:$C$9)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>에너지바</t>
-        </is>
-      </c>
-      <c r="B9">
-        <f>COUNTIF(구매목록!B5:B39,A9)</f>
-        <v/>
-      </c>
-      <c r="C9" s="2">
-        <f>SUMIF(구매목록!B5:B39,A9,구매목록!F5:F39)</f>
-        <v/>
-      </c>
-      <c r="D9" s="9">
-        <f>C9/SUM($C$2:$C$9)</f>
+        <f>C8/SUM($C$2:$C$8)</f>
         <v/>
       </c>
     </row>

--- a/다과_구매목록.xlsx
+++ b/다과_구매목록.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6457" uniqueCount="4015">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6449" uniqueCount="4015">
   <si>
     <t>회사 다과 구매 목록 (마켓컬리)</t>
   </si>
@@ -171,955 +171,955 @@
     <t>https://www.kurly.com/goods/5095165</t>
   </si>
   <si>
+    <t>[해태] 구운감자 27g x 5입</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5110063</t>
+  </si>
+  <si>
+    <t>[해태] 자가비 소포장 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000343575</t>
+  </si>
+  <si>
+    <t>에너지바</t>
+  </si>
+  <si>
+    <t>[네이처밸리] 그래놀라 바 3종 ,택1</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5007664</t>
+  </si>
+  <si>
+    <t>[닥터유] 미니 에너지바 &amp; 단백질바 2종</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5055905</t>
+  </si>
+  <si>
+    <t>초콜릿/캔디/젤리</t>
+  </si>
+  <si>
+    <t>[하리보] 폭신한 과일맛 젤리 3종, 택1</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001069960</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[하리보] 요즘 트렌드 얼먹 젤리 3종 (택1) </t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002033102</t>
+  </si>
+  <si>
+    <t>[하리보] 핑크빛 젤리 2종, 택1</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000548776</t>
+  </si>
+  <si>
+    <t>[하리보] 헬로 제주 젤리 2종, 택1</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002378241</t>
+  </si>
+  <si>
+    <t>쿠키/비스킷(개별포장)</t>
+  </si>
+  <si>
+    <t>[오리온] 촉촉한초코칩 320g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5067311</t>
+  </si>
+  <si>
+    <t>[크라운] 쿠크다스 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5121160</t>
+  </si>
+  <si>
+    <t>[롯데] 마가렛트 오리지널 352g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000339526</t>
+  </si>
+  <si>
+    <t>[브레댄코] 리얼 브라우니 쿠키 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5061562</t>
+  </si>
+  <si>
+    <t>[롯데제과] 카스타드 오리지널 230g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5061939</t>
+  </si>
+  <si>
+    <t>[롯데] 칙촉 오리지널 벌크 180g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5132978</t>
+  </si>
+  <si>
+    <t>[롯데] 빈츠 204g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5079340</t>
+  </si>
+  <si>
+    <t>[오리온] 카스타드 딸기 생크림 276g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001137097</t>
+  </si>
+  <si>
+    <t>[해태] 에이스 씬 솔티카라멜 291g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002110078</t>
+  </si>
+  <si>
+    <t>[오리온] 다이제 초코 카라멜슈가맛 씬 252g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002419584</t>
+  </si>
+  <si>
+    <t>파이/케이크(개별포장)</t>
+  </si>
+  <si>
+    <t>[오리온] 초코파이 12입</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5061296</t>
+  </si>
+  <si>
+    <t>[오리온] 카스타드 12개입 276g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000875718</t>
+  </si>
+  <si>
+    <t>[오리온] 초코파이 말차쇼콜라 408g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001382646</t>
+  </si>
+  <si>
+    <t>[롯데] 몽쉘 생크림케이크 오리지널 408g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000175874</t>
+  </si>
+  <si>
+    <t>[롯데] 몽쉘 생크림케이크 카카오 408g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000175876</t>
+  </si>
+  <si>
+    <t>[해태] 오예스 미니 크림소다맛 192g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002225099</t>
+  </si>
+  <si>
+    <t>[해태] 오예스 360g 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000201444</t>
+  </si>
+  <si>
+    <t>품목수</t>
+  </si>
+  <si>
+    <t>비중</t>
+  </si>
+  <si>
+    <t>상품번호</t>
+  </si>
+  <si>
+    <t>가격</t>
+  </si>
+  <si>
+    <t>정가</t>
+  </si>
+  <si>
+    <t>할인율</t>
+  </si>
+  <si>
+    <t>품절</t>
+  </si>
+  <si>
+    <t>검색어</t>
+  </si>
+  <si>
+    <t>[마요라] 아페티토 스틱 스낵 2종, 택1</t>
+  </si>
+  <si>
+    <t>가성비 과자</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002110052</t>
+  </si>
+  <si>
+    <t>[해태] 아이비 309g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000747182</t>
+  </si>
+  <si>
+    <t>대만 누가크래커 대용량 32개입 448g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000862247</t>
+  </si>
+  <si>
+    <t>[비타비고] 이탈리안 브레드 스틱 4종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000178183</t>
+  </si>
+  <si>
+    <t>[밤부] 누가 크래커 140g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5031072</t>
+  </si>
+  <si>
+    <t>[무직타이거] 옛날과자 골라담기 5종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000875821</t>
+  </si>
+  <si>
+    <t>[포테이토 크리스프] 감자칩 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000651310</t>
+  </si>
+  <si>
+    <t>[리츠] 크래커 3종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000321598</t>
+  </si>
+  <si>
+    <t>[해태] 에이스 364g (24g x 15봉지)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5077465</t>
+  </si>
+  <si>
+    <t>[롯데] 꼬깔콘 스낵(소) 4번들</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5079319</t>
+  </si>
+  <si>
+    <t>[해태] 맛동산 304g (38g x 8팩)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5077461</t>
+  </si>
+  <si>
+    <t>[맥비티] 다이제스티브 비스킷 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000975389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[농심] 인기 봉지 과자 7종 (택1) </t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000198192</t>
+  </si>
+  <si>
+    <t>[만전김] 김스깡 3번들 (60g x 3묶음)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5151421</t>
+  </si>
+  <si>
+    <t>인기 일본과자 10종 골라담기 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001272797</t>
+  </si>
+  <si>
+    <t>[해태] 오사쯔 100g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001029494</t>
+  </si>
+  <si>
+    <t>[가렛팝콘] 프리미엄 수제 팝콘 3종 (백)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5030780</t>
+  </si>
+  <si>
+    <t>[롯데] 야채 크래커 249g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000339529</t>
+  </si>
+  <si>
+    <t>[잇츠베러] 잇츠베러 크래커 4종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5036524</t>
+  </si>
+  <si>
+    <t>홈파티 맥주 안주 간식 8종 모아보기 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000356676</t>
+  </si>
+  <si>
+    <t>[TEMOLE] 아보카도칩 3종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000963099</t>
+  </si>
+  <si>
+    <t>[마이산] 스카이 플레이크 크래커 600g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5088236</t>
+  </si>
+  <si>
+    <t>[닥터유] 단백질칩 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000617577</t>
+  </si>
+  <si>
+    <t>[비타비고] 이탈리안 스낵 비타팝 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000455773</t>
+  </si>
+  <si>
+    <t>[마마메] 템페 칩스 5종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000137075</t>
+  </si>
+  <si>
+    <t>[씬] 감자칩 3종, 택 1</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002134596</t>
+  </si>
+  <si>
+    <t>[리츠] 바삭 김 크래커 73g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001447521</t>
+  </si>
+  <si>
+    <t>[오레오] 웨하스 스틱 150g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001421531</t>
+  </si>
+  <si>
+    <t>[아미고] 나쵸칩 그랩앤고 치즈 콤보 (100g x 6입)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000269917</t>
+  </si>
+  <si>
+    <t>[크라운] 참 크래커 알프스 295g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001592465</t>
+  </si>
+  <si>
+    <t>[HBAF] 와사비맛 아몬드 190g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5054491</t>
+  </si>
+  <si>
+    <t>[더다믐] 김칩스 오리지널 44g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001919935</t>
+  </si>
+  <si>
+    <t>[크라운] 버터와플 316g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5062899</t>
+  </si>
+  <si>
+    <t>[오리온] 감자패밀리팩 대용량 180g (포카칩 &amp; 스윙칩 &amp; 오감자)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000875710</t>
+  </si>
+  <si>
+    <t>[미주라] 소이아 크래커 400g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5006818</t>
+  </si>
+  <si>
+    <t>[해태] 가루비 감자칩 오리지널 40g X 3개입</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000582944</t>
+  </si>
+  <si>
+    <t>[라아부엘라니에베스] 스페인 수제 감자칩 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000206111</t>
+  </si>
+  <si>
+    <t>[마요라] 커피조이 351g (39g X 9개입)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000643389</t>
+  </si>
+  <si>
+    <t>[해태] 가루비 감자칩 오리지널 96g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000439362</t>
+  </si>
+  <si>
+    <t>[헌터즈] 트러플 감자칩 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000166566</t>
+  </si>
+  <si>
+    <t>[DJ&amp;A] 표고버섯/베지 크리스프 3종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000526145</t>
+  </si>
+  <si>
+    <t>[베프코] 홋카이도 센베 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000789439</t>
+  </si>
+  <si>
+    <t>홈파티 와인 안주 간식 8종 모아보기 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000356687</t>
+  </si>
+  <si>
+    <t>[크라운] 인기스낵 모음 12팩</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5153242</t>
+  </si>
+  <si>
+    <t>[프롬잇] 프로틴칩 6종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000033235</t>
+  </si>
+  <si>
+    <t>[발스낵] 그랜드 감자칩 2묶음 7종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001570087</t>
+  </si>
+  <si>
+    <t>[농심] 빵부장 초코빵 55g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000942359</t>
+  </si>
+  <si>
+    <t>[해태] 계란과자 45g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001397540</t>
+  </si>
+  <si>
+    <t>[그레타] 허브 크래커 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000927112</t>
+  </si>
+  <si>
+    <t>[덴로쿠] 스낵 믹스팩 294g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5103484</t>
+  </si>
+  <si>
+    <t>[아미카] 감자칩 멀티팩 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000605988</t>
+  </si>
+  <si>
+    <t>[타코맨] 나쵸 토틸라칩 320g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5060050</t>
+  </si>
+  <si>
+    <t>[이메이] 대파 소다 크래커 225g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002324203</t>
+  </si>
+  <si>
+    <t>[크라운] 참쌀선과 253g (44봉)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000178191</t>
+  </si>
+  <si>
+    <t>[바다해] 캠핑&amp;홈파티 마른안주 플래터 360g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000914382</t>
+  </si>
+  <si>
+    <t>[ALLO] 하몽 크래커 319g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002014581</t>
+  </si>
+  <si>
+    <t>[레인코스트] 크리스프 크래커 7종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5052362</t>
+  </si>
+  <si>
+    <t>[크라운] 치즈샌드 Rich 180g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000958549</t>
+  </si>
+  <si>
+    <t>[오리온] 호호감자크래커 177g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002010936</t>
+  </si>
+  <si>
+    <t>[퀼리] 스페인 브래드스틱 6종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000242960</t>
+  </si>
+  <si>
+    <t>[롯데] 군위 사과 시리즈 11종, 택1</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002482468</t>
+  </si>
+  <si>
+    <t>[미주라] 통밀크래커 385g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5058855</t>
+  </si>
+  <si>
+    <t>대용량 트러플 카사바칩 500g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000783621</t>
+  </si>
+  <si>
+    <t>[아미카] 엘도라다 포테이토칩 대용량  400g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000525224</t>
+  </si>
+  <si>
     <t>[오리온] 썬 핫스파이시 4번들</t>
   </si>
   <si>
     <t>https://www.kurly.com/goods/1000365879</t>
   </si>
   <si>
+    <t>[브렛츠] 감자칩 7종, 택1</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002133624</t>
+  </si>
+  <si>
+    <t>[롯데] 치토스 바비큐 164g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000339558</t>
+  </si>
+  <si>
+    <t>[크라운] 참 크래커 280g (18.67g x 15입)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5081478</t>
+  </si>
+  <si>
+    <t>[미주라] 토스트 비스켓 320g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5005540</t>
+  </si>
+  <si>
+    <t>[DJ&amp;A] 포테이토 웨지 스낵 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000526148</t>
+  </si>
+  <si>
+    <t>[빙그레] 인기스낵 4종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000677312</t>
+  </si>
+  <si>
+    <t>[크라운] 그레이스 298g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001407039</t>
+  </si>
+  <si>
+    <t>[오리온] 인기 봉지 과자 지퍼백 5종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000248448</t>
+  </si>
+  <si>
+    <t>땅콩 한입 꽈배기 520g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001027192</t>
+  </si>
+  <si>
+    <t>[오리온] 고소미 216g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5067308</t>
+  </si>
+  <si>
+    <t>[HBAF] 시그니처 팝콘 골라담기 7종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000942860</t>
+  </si>
+  <si>
+    <t>[미카쿠토] 오사츠도키 칩 2종, 택1</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001991119</t>
+  </si>
+  <si>
+    <t>[더다믐] 김칩스 매운맛 44g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5132664</t>
+  </si>
+  <si>
+    <t>[오리온] 무뚝뚝 감자칩 &amp; 고구마 스낵 3종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000640854</t>
+  </si>
+  <si>
+    <t>[마주] 버섯스낵 바삭칩 2종</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000045935</t>
+  </si>
+  <si>
+    <t>[농심] 빵부장 소금빵 55g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000349505</t>
+  </si>
+  <si>
+    <t>[PNB] 고소한 수제 전병 4종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5060582</t>
+  </si>
+  <si>
+    <t>[농심] 인기 봉지 과자 7종 골라담기 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001363953</t>
+  </si>
+  <si>
+    <t>[카수가이] 오부쿠로 와사비마메 227g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5103372</t>
+  </si>
+  <si>
+    <t>[농심] 와사비 새우깡 70g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001501063</t>
+  </si>
+  <si>
+    <t>[이토비스킷] 랑그리 크림 쿠키 2종</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000443353</t>
+  </si>
+  <si>
+    <t>[발센] 라이브니즈 비스킷 2종, 택1</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002221133</t>
+  </si>
+  <si>
+    <t>[오가마마] 바삭바삭 고구마칩 150g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000136966</t>
+  </si>
+  <si>
+    <t>[생미쉘] 비스킷 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000799985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[HBAF] 와사비마요 팝콘 80g </t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000960165</t>
+  </si>
+  <si>
+    <t>[마켓오] 브라우니 바이트 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001337989</t>
+  </si>
+  <si>
+    <t>[맥스봉] 구운풍미 마늘 후랑크 80g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002104225</t>
+  </si>
+  <si>
+    <t>[시그달] 크리스피 크래커 3종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002020133</t>
+  </si>
+  <si>
+    <t>수입 과자 10종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000360436</t>
+  </si>
+  <si>
+    <t>[해태] 버터링 골드 194g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001042362</t>
+  </si>
+  <si>
+    <t>[크런틴] 프사삭 5mm 통감자칩 4종, 택1</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002340554</t>
+  </si>
+  <si>
+    <t>[해태] 에이스 바스크 치즈 케이크 364g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000490099</t>
+  </si>
+  <si>
+    <t>[CJ] 맛군밤 4개입</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5077641</t>
+  </si>
+  <si>
+    <t>[롯데] 꼬깔콘 고소한맛 67g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001397631</t>
+  </si>
+  <si>
+    <t>[CJ] 바삭칩 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001942440</t>
+  </si>
+  <si>
+    <t>[발센] 와플텐 웨이퍼롤 2종, 택1</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002221138</t>
+  </si>
+  <si>
+    <t>[아미카] 이탈리아 감자칩 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000216544</t>
+  </si>
+  <si>
+    <t>[롯데] 쌀로별 오리지널 156g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5118057</t>
+  </si>
+  <si>
+    <t>[카메다] 소프트 사라다 145.2g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000656471</t>
+  </si>
+  <si>
+    <t>[곡물그대로21] 크리스피롤 3종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001073370</t>
+  </si>
+  <si>
+    <t>[해태] 맛동산 300g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000365868</t>
+  </si>
+  <si>
+    <t>[유니온] 와인 페어링 타랄리니 스낵 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001740101</t>
+  </si>
+  <si>
+    <t>[해태] 칼로리바란스 치즈 (38g x 7개)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000125337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Lay's] 감자칩 7종 (택1) </t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5013230</t>
+  </si>
+  <si>
+    <t>[아티장 비스킷] 치즈를 위한 토스트 (데이츠&amp;헤이즐넛) 100g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5043538</t>
+  </si>
+  <si>
+    <t>7일 이내 로스팅한 구운 캐슈넛 200g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001382381</t>
+  </si>
+  <si>
+    <t>[다르다] 통밀칩 45g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002159262</t>
+  </si>
+  <si>
+    <t>[해태] 맛동산 3번들 210g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002286852</t>
+  </si>
+  <si>
+    <t>[하루견과] 빠삭칩 200g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5052356</t>
+  </si>
+  <si>
+    <t>[마이산] 스카이 플레이크 크래커 마늘맛 800g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000499057</t>
+  </si>
+  <si>
+    <t>[소이조이] 대두로 만든 단백질 스낵 6종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000791609</t>
+  </si>
+  <si>
+    <t>[더단백] 팝칩 12개입 3종, 택1</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000074625</t>
+  </si>
+  <si>
+    <t>[크라운] 참쌀설병 270g (30봉)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5077457</t>
+  </si>
+  <si>
+    <t>[해태] 구운 양파 110g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000349503</t>
+  </si>
+  <si>
+    <t>[카스테이블워터] 영국 크래커 4종 (택 1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5054219</t>
+  </si>
+  <si>
+    <t>[오리온] 찍먹 오감자 버터갈릭감자튀김맛 115g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001959559</t>
+  </si>
+  <si>
+    <t>[카수가이] 땅콩 간식 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000777595</t>
+  </si>
+  <si>
+    <t>[해태] 에이스 야채 291g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002225093</t>
+  </si>
+  <si>
+    <t>통연근 그대로 튀긴 연근칩 30g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5030130</t>
+  </si>
+  <si>
+    <t>[해태] 구운 고구마 135g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001317277</t>
+  </si>
+  <si>
+    <t>[롯데] 꼬깔콘 시리즈 3종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5118059</t>
+  </si>
+  <si>
     <t>[오리온] 고래밥 20g x 10입</t>
   </si>
   <si>
     <t>https://www.kurly.com/goods/5081412</t>
-  </si>
-  <si>
-    <t>[해태] 구운감자 27g x 5입</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5110063</t>
-  </si>
-  <si>
-    <t>[해태] 자가비 소포장 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000343575</t>
-  </si>
-  <si>
-    <t>에너지바</t>
-  </si>
-  <si>
-    <t>[네이처밸리] 그래놀라 바 3종 ,택1</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5007664</t>
-  </si>
-  <si>
-    <t>[닥터유] 미니 에너지바 &amp; 단백질바 2종</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5055905</t>
-  </si>
-  <si>
-    <t>초콜릿/캔디/젤리</t>
-  </si>
-  <si>
-    <t>[하리보] 폭신한 과일맛 젤리 3종, 택1</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001069960</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[하리보] 요즘 트렌드 얼먹 젤리 3종 (택1) </t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002033102</t>
-  </si>
-  <si>
-    <t>[하리보] 핑크빛 젤리 2종, 택1</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000548776</t>
-  </si>
-  <si>
-    <t>[하리보] 헬로 제주 젤리 2종, 택1</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002378241</t>
-  </si>
-  <si>
-    <t>쿠키/비스킷(개별포장)</t>
-  </si>
-  <si>
-    <t>[오리온] 촉촉한초코칩 320g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5067311</t>
-  </si>
-  <si>
-    <t>[크라운] 쿠크다스 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5121160</t>
-  </si>
-  <si>
-    <t>[롯데] 마가렛트 오리지널 352g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000339526</t>
-  </si>
-  <si>
-    <t>[브레댄코] 리얼 브라우니 쿠키 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5061562</t>
-  </si>
-  <si>
-    <t>[롯데제과] 카스타드 오리지널 230g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5061939</t>
-  </si>
-  <si>
-    <t>[롯데] 칙촉 오리지널 벌크 180g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5132978</t>
-  </si>
-  <si>
-    <t>[롯데] 빈츠 204g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5079340</t>
-  </si>
-  <si>
-    <t>[오리온] 카스타드 딸기 생크림 276g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001137097</t>
-  </si>
-  <si>
-    <t>[해태] 에이스 씬 솔티카라멜 291g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002110078</t>
-  </si>
-  <si>
-    <t>[오리온] 다이제 초코 카라멜슈가맛 씬 252g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002419584</t>
-  </si>
-  <si>
-    <t>파이/케이크(개별포장)</t>
-  </si>
-  <si>
-    <t>[오리온] 초코파이 12입</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5061296</t>
-  </si>
-  <si>
-    <t>[오리온] 카스타드 12개입 276g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000875718</t>
-  </si>
-  <si>
-    <t>[오리온] 초코파이 말차쇼콜라 408g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001382646</t>
-  </si>
-  <si>
-    <t>[롯데] 몽쉘 생크림케이크 오리지널 408g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000175874</t>
-  </si>
-  <si>
-    <t>[롯데] 몽쉘 생크림케이크 카카오 408g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000175876</t>
-  </si>
-  <si>
-    <t>[해태] 오예스 미니 크림소다맛 192g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002225099</t>
-  </si>
-  <si>
-    <t>[해태] 오예스 360g 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000201444</t>
-  </si>
-  <si>
-    <t>품목수</t>
-  </si>
-  <si>
-    <t>비중</t>
-  </si>
-  <si>
-    <t>상품번호</t>
-  </si>
-  <si>
-    <t>가격</t>
-  </si>
-  <si>
-    <t>정가</t>
-  </si>
-  <si>
-    <t>할인율</t>
-  </si>
-  <si>
-    <t>품절</t>
-  </si>
-  <si>
-    <t>검색어</t>
-  </si>
-  <si>
-    <t>[마요라] 아페티토 스틱 스낵 2종, 택1</t>
-  </si>
-  <si>
-    <t>가성비 과자</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002110052</t>
-  </si>
-  <si>
-    <t>[해태] 아이비 309g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000747182</t>
-  </si>
-  <si>
-    <t>대만 누가크래커 대용량 32개입 448g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000862247</t>
-  </si>
-  <si>
-    <t>[비타비고] 이탈리안 브레드 스틱 4종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000178183</t>
-  </si>
-  <si>
-    <t>[밤부] 누가 크래커 140g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5031072</t>
-  </si>
-  <si>
-    <t>[무직타이거] 옛날과자 골라담기 5종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000875821</t>
-  </si>
-  <si>
-    <t>[포테이토 크리스프] 감자칩 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000651310</t>
-  </si>
-  <si>
-    <t>[리츠] 크래커 3종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000321598</t>
-  </si>
-  <si>
-    <t>[해태] 에이스 364g (24g x 15봉지)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5077465</t>
-  </si>
-  <si>
-    <t>[롯데] 꼬깔콘 스낵(소) 4번들</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5079319</t>
-  </si>
-  <si>
-    <t>[해태] 맛동산 304g (38g x 8팩)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5077461</t>
-  </si>
-  <si>
-    <t>[맥비티] 다이제스티브 비스킷 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000975389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[농심] 인기 봉지 과자 7종 (택1) </t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000198192</t>
-  </si>
-  <si>
-    <t>[만전김] 김스깡 3번들 (60g x 3묶음)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5151421</t>
-  </si>
-  <si>
-    <t>인기 일본과자 10종 골라담기 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001272797</t>
-  </si>
-  <si>
-    <t>[해태] 오사쯔 100g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001029494</t>
-  </si>
-  <si>
-    <t>[가렛팝콘] 프리미엄 수제 팝콘 3종 (백)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5030780</t>
-  </si>
-  <si>
-    <t>[롯데] 야채 크래커 249g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000339529</t>
-  </si>
-  <si>
-    <t>[잇츠베러] 잇츠베러 크래커 4종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5036524</t>
-  </si>
-  <si>
-    <t>홈파티 맥주 안주 간식 8종 모아보기 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000356676</t>
-  </si>
-  <si>
-    <t>[TEMOLE] 아보카도칩 3종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000963099</t>
-  </si>
-  <si>
-    <t>[마이산] 스카이 플레이크 크래커 600g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5088236</t>
-  </si>
-  <si>
-    <t>[닥터유] 단백질칩 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000617577</t>
-  </si>
-  <si>
-    <t>[비타비고] 이탈리안 스낵 비타팝 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000455773</t>
-  </si>
-  <si>
-    <t>[마마메] 템페 칩스 5종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000137075</t>
-  </si>
-  <si>
-    <t>[씬] 감자칩 3종, 택 1</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002134596</t>
-  </si>
-  <si>
-    <t>[리츠] 바삭 김 크래커 73g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001447521</t>
-  </si>
-  <si>
-    <t>[오레오] 웨하스 스틱 150g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001421531</t>
-  </si>
-  <si>
-    <t>[아미고] 나쵸칩 그랩앤고 치즈 콤보 (100g x 6입)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000269917</t>
-  </si>
-  <si>
-    <t>[크라운] 참 크래커 알프스 295g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001592465</t>
-  </si>
-  <si>
-    <t>[HBAF] 와사비맛 아몬드 190g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5054491</t>
-  </si>
-  <si>
-    <t>[더다믐] 김칩스 오리지널 44g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001919935</t>
-  </si>
-  <si>
-    <t>[크라운] 버터와플 316g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5062899</t>
-  </si>
-  <si>
-    <t>[오리온] 감자패밀리팩 대용량 180g (포카칩 &amp; 스윙칩 &amp; 오감자)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000875710</t>
-  </si>
-  <si>
-    <t>[미주라] 소이아 크래커 400g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5006818</t>
-  </si>
-  <si>
-    <t>[해태] 가루비 감자칩 오리지널 40g X 3개입</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000582944</t>
-  </si>
-  <si>
-    <t>[라아부엘라니에베스] 스페인 수제 감자칩 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000206111</t>
-  </si>
-  <si>
-    <t>[마요라] 커피조이 351g (39g X 9개입)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000643389</t>
-  </si>
-  <si>
-    <t>[해태] 가루비 감자칩 오리지널 96g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000439362</t>
-  </si>
-  <si>
-    <t>[헌터즈] 트러플 감자칩 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000166566</t>
-  </si>
-  <si>
-    <t>[DJ&amp;A] 표고버섯/베지 크리스프 3종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000526145</t>
-  </si>
-  <si>
-    <t>[베프코] 홋카이도 센베 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000789439</t>
-  </si>
-  <si>
-    <t>홈파티 와인 안주 간식 8종 모아보기 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000356687</t>
-  </si>
-  <si>
-    <t>[크라운] 인기스낵 모음 12팩</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5153242</t>
-  </si>
-  <si>
-    <t>[프롬잇] 프로틴칩 6종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000033235</t>
-  </si>
-  <si>
-    <t>[발스낵] 그랜드 감자칩 2묶음 7종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001570087</t>
-  </si>
-  <si>
-    <t>[농심] 빵부장 초코빵 55g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000942359</t>
-  </si>
-  <si>
-    <t>[해태] 계란과자 45g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001397540</t>
-  </si>
-  <si>
-    <t>[그레타] 허브 크래커 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000927112</t>
-  </si>
-  <si>
-    <t>[덴로쿠] 스낵 믹스팩 294g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5103484</t>
-  </si>
-  <si>
-    <t>[아미카] 감자칩 멀티팩 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000605988</t>
-  </si>
-  <si>
-    <t>[타코맨] 나쵸 토틸라칩 320g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5060050</t>
-  </si>
-  <si>
-    <t>[이메이] 대파 소다 크래커 225g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002324203</t>
-  </si>
-  <si>
-    <t>[크라운] 참쌀선과 253g (44봉)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000178191</t>
-  </si>
-  <si>
-    <t>[바다해] 캠핑&amp;홈파티 마른안주 플래터 360g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000914382</t>
-  </si>
-  <si>
-    <t>[ALLO] 하몽 크래커 319g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002014581</t>
-  </si>
-  <si>
-    <t>[레인코스트] 크리스프 크래커 7종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5052362</t>
-  </si>
-  <si>
-    <t>[크라운] 치즈샌드 Rich 180g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000958549</t>
-  </si>
-  <si>
-    <t>[오리온] 호호감자크래커 177g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002010936</t>
-  </si>
-  <si>
-    <t>[퀼리] 스페인 브래드스틱 6종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000242960</t>
-  </si>
-  <si>
-    <t>[롯데] 군위 사과 시리즈 11종, 택1</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002482468</t>
-  </si>
-  <si>
-    <t>[미주라] 통밀크래커 385g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5058855</t>
-  </si>
-  <si>
-    <t>대용량 트러플 카사바칩 500g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000783621</t>
-  </si>
-  <si>
-    <t>[아미카] 엘도라다 포테이토칩 대용량  400g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000525224</t>
-  </si>
-  <si>
-    <t>[브렛츠] 감자칩 7종, 택1</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002133624</t>
-  </si>
-  <si>
-    <t>[롯데] 치토스 바비큐 164g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000339558</t>
-  </si>
-  <si>
-    <t>[크라운] 참 크래커 280g (18.67g x 15입)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5081478</t>
-  </si>
-  <si>
-    <t>[미주라] 토스트 비스켓 320g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5005540</t>
-  </si>
-  <si>
-    <t>[DJ&amp;A] 포테이토 웨지 스낵 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000526148</t>
-  </si>
-  <si>
-    <t>[빙그레] 인기스낵 4종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000677312</t>
-  </si>
-  <si>
-    <t>[크라운] 그레이스 298g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001407039</t>
-  </si>
-  <si>
-    <t>[오리온] 인기 봉지 과자 지퍼백 5종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000248448</t>
-  </si>
-  <si>
-    <t>땅콩 한입 꽈배기 520g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001027192</t>
-  </si>
-  <si>
-    <t>[오리온] 고소미 216g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5067308</t>
-  </si>
-  <si>
-    <t>[HBAF] 시그니처 팝콘 골라담기 7종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000942860</t>
-  </si>
-  <si>
-    <t>[미카쿠토] 오사츠도키 칩 2종, 택1</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001991119</t>
-  </si>
-  <si>
-    <t>[더다믐] 김칩스 매운맛 44g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5132664</t>
-  </si>
-  <si>
-    <t>[오리온] 무뚝뚝 감자칩 &amp; 고구마 스낵 3종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000640854</t>
-  </si>
-  <si>
-    <t>[마주] 버섯스낵 바삭칩 2종</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000045935</t>
-  </si>
-  <si>
-    <t>[농심] 빵부장 소금빵 55g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000349505</t>
-  </si>
-  <si>
-    <t>[PNB] 고소한 수제 전병 4종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5060582</t>
-  </si>
-  <si>
-    <t>[농심] 인기 봉지 과자 7종 골라담기 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001363953</t>
-  </si>
-  <si>
-    <t>[카수가이] 오부쿠로 와사비마메 227g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5103372</t>
-  </si>
-  <si>
-    <t>[농심] 와사비 새우깡 70g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001501063</t>
-  </si>
-  <si>
-    <t>[이토비스킷] 랑그리 크림 쿠키 2종</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000443353</t>
-  </si>
-  <si>
-    <t>[발센] 라이브니즈 비스킷 2종, 택1</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002221133</t>
-  </si>
-  <si>
-    <t>[오가마마] 바삭바삭 고구마칩 150g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000136966</t>
-  </si>
-  <si>
-    <t>[생미쉘] 비스킷 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000799985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[HBAF] 와사비마요 팝콘 80g </t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000960165</t>
-  </si>
-  <si>
-    <t>[마켓오] 브라우니 바이트 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001337989</t>
-  </si>
-  <si>
-    <t>[맥스봉] 구운풍미 마늘 후랑크 80g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002104225</t>
-  </si>
-  <si>
-    <t>[시그달] 크리스피 크래커 3종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002020133</t>
-  </si>
-  <si>
-    <t>수입 과자 10종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000360436</t>
-  </si>
-  <si>
-    <t>[해태] 버터링 골드 194g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001042362</t>
-  </si>
-  <si>
-    <t>[크런틴] 프사삭 5mm 통감자칩 4종, 택1</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002340554</t>
-  </si>
-  <si>
-    <t>[해태] 에이스 바스크 치즈 케이크 364g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000490099</t>
-  </si>
-  <si>
-    <t>[CJ] 맛군밤 4개입</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5077641</t>
-  </si>
-  <si>
-    <t>[롯데] 꼬깔콘 고소한맛 67g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001397631</t>
-  </si>
-  <si>
-    <t>[CJ] 바삭칩 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001942440</t>
-  </si>
-  <si>
-    <t>[발센] 와플텐 웨이퍼롤 2종, 택1</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002221138</t>
-  </si>
-  <si>
-    <t>[아미카] 이탈리아 감자칩 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000216544</t>
-  </si>
-  <si>
-    <t>[롯데] 쌀로별 오리지널 156g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5118057</t>
-  </si>
-  <si>
-    <t>[카메다] 소프트 사라다 145.2g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000656471</t>
-  </si>
-  <si>
-    <t>[곡물그대로21] 크리스피롤 3종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001073370</t>
-  </si>
-  <si>
-    <t>[해태] 맛동산 300g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000365868</t>
-  </si>
-  <si>
-    <t>[유니온] 와인 페어링 타랄리니 스낵 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001740101</t>
-  </si>
-  <si>
-    <t>[해태] 칼로리바란스 치즈 (38g x 7개)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000125337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[Lay's] 감자칩 7종 (택1) </t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5013230</t>
-  </si>
-  <si>
-    <t>[아티장 비스킷] 치즈를 위한 토스트 (데이츠&amp;헤이즐넛) 100g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5043538</t>
-  </si>
-  <si>
-    <t>7일 이내 로스팅한 구운 캐슈넛 200g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001382381</t>
-  </si>
-  <si>
-    <t>[다르다] 통밀칩 45g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002159262</t>
-  </si>
-  <si>
-    <t>[해태] 맛동산 3번들 210g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002286852</t>
-  </si>
-  <si>
-    <t>[하루견과] 빠삭칩 200g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5052356</t>
-  </si>
-  <si>
-    <t>[마이산] 스카이 플레이크 크래커 마늘맛 800g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000499057</t>
-  </si>
-  <si>
-    <t>[소이조이] 대두로 만든 단백질 스낵 6종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000791609</t>
-  </si>
-  <si>
-    <t>[더단백] 팝칩 12개입 3종, 택1</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000074625</t>
-  </si>
-  <si>
-    <t>[크라운] 참쌀설병 270g (30봉)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5077457</t>
-  </si>
-  <si>
-    <t>[해태] 구운 양파 110g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000349503</t>
-  </si>
-  <si>
-    <t>[카스테이블워터] 영국 크래커 4종 (택 1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5054219</t>
-  </si>
-  <si>
-    <t>[오리온] 찍먹 오감자 버터갈릭감자튀김맛 115g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001959559</t>
-  </si>
-  <si>
-    <t>[카수가이] 땅콩 간식 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000777595</t>
-  </si>
-  <si>
-    <t>[해태] 에이스 야채 291g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002225093</t>
-  </si>
-  <si>
-    <t>통연근 그대로 튀긴 연근칩 30g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5030130</t>
-  </si>
-  <si>
-    <t>[해태] 구운 고구마 135g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001317277</t>
-  </si>
-  <si>
-    <t>[롯데] 꼬깔콘 시리즈 3종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5118059</t>
   </si>
   <si>
     <t>[오리온] 다이제 샌드 우도땅콩 392g</t>
@@ -12467,7 +12467,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J47"/>
+  <dimension ref="A1:J45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.7109375" customWidth="1"/>
@@ -12498,15 +12498,15 @@
         <v>2</v>
       </c>
       <c r="D2" s="3">
-        <f>SUM(F5:F47)</f>
-        <v>497374</v>
+        <f>SUM(F5:F45)</f>
+        <v>498144</v>
       </c>
       <c r="E2" t="s">
         <v>3</v>
       </c>
       <c r="F2" s="3">
         <f>B2-D2</f>
-        <v>2626</v>
+        <v>1856</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -12767,11 +12767,11 @@
         <v>2850</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12" s="2">
         <f>D12*E12</f>
-        <v>2850</v>
+        <v>5700</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -12827,11 +12827,11 @@
         <v>3480</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14" s="2">
         <f>D14*E14</f>
-        <v>3480</v>
+        <v>6960</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -12857,11 +12857,11 @@
         <v>4080</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F15" s="2">
         <f>D15*E15</f>
-        <v>4080</v>
+        <v>8160</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -12887,11 +12887,11 @@
         <v>4080</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" s="2">
         <f>D16*E16</f>
-        <v>4080</v>
+        <v>8160</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -12917,11 +12917,11 @@
         <v>2480</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F17" s="2">
         <f>D17*E17</f>
-        <v>2480</v>
+        <v>7440</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -12947,11 +12947,11 @@
         <v>2480</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F18" s="2">
         <f>D18*E18</f>
-        <v>2480</v>
+        <v>7440</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -13034,17 +13034,17 @@
         <v>50</v>
       </c>
       <c r="D21" s="2">
-        <v>3380</v>
+        <v>3780</v>
       </c>
       <c r="E21">
         <v>3</v>
       </c>
       <c r="F21" s="2">
         <f>D21*E21</f>
-        <v>10140</v>
+        <v>11340</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H21">
         <v>999</v>
@@ -13064,14 +13064,14 @@
         <v>52</v>
       </c>
       <c r="D22" s="2">
-        <v>4500</v>
+        <v>3580</v>
       </c>
       <c r="E22">
         <v>3</v>
       </c>
       <c r="F22" s="2">
         <f>D22*E22</f>
-        <v>13500</v>
+        <v>10740</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -13088,29 +13088,29 @@
         <v>19</v>
       </c>
       <c r="B23" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="C23" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D23" s="2">
-        <v>3780</v>
+        <v>3980</v>
       </c>
       <c r="E23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F23" s="2">
         <f>D23*E23</f>
-        <v>11340</v>
+        <v>7960</v>
       </c>
       <c r="G23">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="H23">
-        <v>999</v>
+        <v>9999</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -13118,29 +13118,29 @@
         <v>19</v>
       </c>
       <c r="B24" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="C24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D24" s="2">
-        <v>3580</v>
+        <v>5120</v>
       </c>
       <c r="E24">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F24" s="2">
         <f>D24*E24</f>
-        <v>10740</v>
+        <v>5120</v>
       </c>
       <c r="G24">
         <v>0</v>
       </c>
       <c r="H24">
-        <v>999</v>
+        <v>9999</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -13148,29 +13148,29 @@
         <v>19</v>
       </c>
       <c r="B25" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C25" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D25" s="2">
-        <v>3980</v>
+        <v>2180</v>
       </c>
       <c r="E25">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F25" s="2">
         <f>D25*E25</f>
-        <v>7960</v>
+        <v>21800</v>
       </c>
       <c r="G25">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="H25">
-        <v>9999</v>
+        <v>835</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -13178,29 +13178,29 @@
         <v>19</v>
       </c>
       <c r="B26" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C26" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D26" s="2">
-        <v>5120</v>
+        <v>2180</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F26" s="2">
         <f>D26*E26</f>
-        <v>5120</v>
+        <v>21800</v>
       </c>
       <c r="G26">
         <v>0</v>
       </c>
       <c r="H26">
-        <v>9999</v>
+        <v>741</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -13208,7 +13208,7 @@
         <v>19</v>
       </c>
       <c r="B27" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C27" t="s">
         <v>64</v>
@@ -13227,7 +13227,7 @@
         <v>0</v>
       </c>
       <c r="H27">
-        <v>835</v>
+        <v>520</v>
       </c>
       <c r="I27" s="8" t="s">
         <v>65</v>
@@ -13238,7 +13238,7 @@
         <v>19</v>
       </c>
       <c r="B28" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C28" t="s">
         <v>66</v>
@@ -13257,7 +13257,7 @@
         <v>0</v>
       </c>
       <c r="H28">
-        <v>741</v>
+        <v>243</v>
       </c>
       <c r="I28" s="8" t="s">
         <v>67</v>
@@ -13268,29 +13268,29 @@
         <v>19</v>
       </c>
       <c r="B29" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C29" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D29" s="2">
-        <v>2180</v>
+        <v>4480</v>
       </c>
       <c r="E29">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F29" s="2">
         <f>D29*E29</f>
-        <v>21800</v>
+        <v>8960</v>
       </c>
       <c r="G29">
         <v>0</v>
       </c>
       <c r="H29">
-        <v>520</v>
+        <v>999</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -13298,29 +13298,29 @@
         <v>19</v>
       </c>
       <c r="B30" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C30" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D30" s="2">
-        <v>2180</v>
+        <v>4380</v>
       </c>
       <c r="E30">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F30" s="2">
         <f>D30*E30</f>
-        <v>21800</v>
+        <v>8760</v>
       </c>
       <c r="G30">
         <v>0</v>
       </c>
       <c r="H30">
-        <v>243</v>
+        <v>999</v>
       </c>
       <c r="I30" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -13328,26 +13328,26 @@
         <v>19</v>
       </c>
       <c r="B31" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C31" t="s">
         <v>73</v>
       </c>
       <c r="D31" s="2">
-        <v>4480</v>
+        <v>5440</v>
       </c>
       <c r="E31">
         <v>2</v>
       </c>
       <c r="F31" s="2">
         <f>D31*E31</f>
-        <v>8960</v>
+        <v>10880</v>
       </c>
       <c r="G31">
         <v>0</v>
       </c>
       <c r="H31">
-        <v>999</v>
+        <v>956</v>
       </c>
       <c r="I31" s="8" t="s">
         <v>74</v>
@@ -13358,26 +13358,26 @@
         <v>19</v>
       </c>
       <c r="B32" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C32" t="s">
         <v>75</v>
       </c>
       <c r="D32" s="2">
-        <v>4380</v>
+        <v>3690</v>
       </c>
       <c r="E32">
         <v>2</v>
       </c>
       <c r="F32" s="2">
         <f>D32*E32</f>
-        <v>8760</v>
+        <v>7380</v>
       </c>
       <c r="G32">
         <v>0</v>
       </c>
       <c r="H32">
-        <v>999</v>
+        <v>9999</v>
       </c>
       <c r="I32" s="8" t="s">
         <v>76</v>
@@ -13388,26 +13388,26 @@
         <v>19</v>
       </c>
       <c r="B33" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C33" t="s">
         <v>77</v>
       </c>
       <c r="D33" s="2">
-        <v>5440</v>
+        <v>4780</v>
       </c>
       <c r="E33">
         <v>2</v>
       </c>
       <c r="F33" s="2">
         <f>D33*E33</f>
-        <v>10880</v>
+        <v>9560</v>
       </c>
       <c r="G33">
         <v>0</v>
       </c>
       <c r="H33">
-        <v>956</v>
+        <v>999</v>
       </c>
       <c r="I33" s="8" t="s">
         <v>78</v>
@@ -13418,26 +13418,26 @@
         <v>19</v>
       </c>
       <c r="B34" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C34" t="s">
         <v>79</v>
       </c>
       <c r="D34" s="2">
-        <v>3690</v>
+        <v>4200</v>
       </c>
       <c r="E34">
         <v>2</v>
       </c>
       <c r="F34" s="2">
         <f>D34*E34</f>
-        <v>7380</v>
+        <v>8400</v>
       </c>
       <c r="G34">
         <v>0</v>
       </c>
       <c r="H34">
-        <v>9999</v>
+        <v>999</v>
       </c>
       <c r="I34" s="8" t="s">
         <v>80</v>
@@ -13448,20 +13448,20 @@
         <v>19</v>
       </c>
       <c r="B35" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C35" t="s">
         <v>81</v>
       </c>
       <c r="D35" s="2">
-        <v>4780</v>
+        <v>5280</v>
       </c>
       <c r="E35">
         <v>2</v>
       </c>
       <c r="F35" s="2">
         <f>D35*E35</f>
-        <v>9560</v>
+        <v>10560</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -13478,26 +13478,26 @@
         <v>19</v>
       </c>
       <c r="B36" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C36" t="s">
         <v>83</v>
       </c>
       <c r="D36" s="2">
-        <v>4200</v>
+        <v>4780</v>
       </c>
       <c r="E36">
         <v>2</v>
       </c>
       <c r="F36" s="2">
         <f>D36*E36</f>
-        <v>8400</v>
+        <v>9560</v>
       </c>
       <c r="G36">
         <v>0</v>
       </c>
       <c r="H36">
-        <v>999</v>
+        <v>477</v>
       </c>
       <c r="I36" s="8" t="s">
         <v>84</v>
@@ -13508,26 +13508,26 @@
         <v>19</v>
       </c>
       <c r="B37" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C37" t="s">
         <v>85</v>
       </c>
       <c r="D37" s="2">
-        <v>5280</v>
+        <v>3980</v>
       </c>
       <c r="E37">
         <v>2</v>
       </c>
       <c r="F37" s="2">
         <f>D37*E37</f>
-        <v>10560</v>
+        <v>7960</v>
       </c>
       <c r="G37">
         <v>0</v>
       </c>
       <c r="H37">
-        <v>999</v>
+        <v>314</v>
       </c>
       <c r="I37" s="8" t="s">
         <v>86</v>
@@ -13538,26 +13538,26 @@
         <v>19</v>
       </c>
       <c r="B38" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C38" t="s">
         <v>87</v>
       </c>
       <c r="D38" s="2">
-        <v>4780</v>
+        <v>3200</v>
       </c>
       <c r="E38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F38" s="2">
         <f>D38*E38</f>
-        <v>9560</v>
+        <v>9600</v>
       </c>
       <c r="G38">
         <v>0</v>
       </c>
       <c r="H38">
-        <v>477</v>
+        <v>215</v>
       </c>
       <c r="I38" s="8" t="s">
         <v>88</v>
@@ -13568,29 +13568,29 @@
         <v>19</v>
       </c>
       <c r="B39" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="C39" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D39" s="2">
-        <v>3980</v>
+        <v>4320</v>
       </c>
       <c r="E39">
         <v>2</v>
       </c>
       <c r="F39" s="2">
         <f>D39*E39</f>
-        <v>7960</v>
+        <v>8640</v>
       </c>
       <c r="G39">
         <v>0</v>
       </c>
       <c r="H39">
-        <v>314</v>
+        <v>9999</v>
       </c>
       <c r="I39" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -13598,29 +13598,29 @@
         <v>19</v>
       </c>
       <c r="B40" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="C40" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D40" s="2">
-        <v>3200</v>
+        <v>4320</v>
       </c>
       <c r="E40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F40" s="2">
         <f>D40*E40</f>
-        <v>9600</v>
+        <v>8640</v>
       </c>
       <c r="G40">
         <v>0</v>
       </c>
       <c r="H40">
-        <v>215</v>
+        <v>745</v>
       </c>
       <c r="I40" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -13628,26 +13628,26 @@
         <v>19</v>
       </c>
       <c r="B41" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C41" t="s">
         <v>94</v>
       </c>
       <c r="D41" s="2">
-        <v>4320</v>
+        <v>4800</v>
       </c>
       <c r="E41">
         <v>2</v>
       </c>
       <c r="F41" s="2">
         <f>D41*E41</f>
-        <v>8640</v>
+        <v>9600</v>
       </c>
       <c r="G41">
         <v>0</v>
       </c>
       <c r="H41">
-        <v>9999</v>
+        <v>950</v>
       </c>
       <c r="I41" s="8" t="s">
         <v>95</v>
@@ -13658,26 +13658,26 @@
         <v>19</v>
       </c>
       <c r="B42" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C42" t="s">
         <v>96</v>
       </c>
       <c r="D42" s="2">
-        <v>4320</v>
+        <v>5600</v>
       </c>
       <c r="E42">
         <v>2</v>
       </c>
       <c r="F42" s="2">
         <f>D42*E42</f>
-        <v>8640</v>
+        <v>11200</v>
       </c>
       <c r="G42">
         <v>0</v>
       </c>
       <c r="H42">
-        <v>745</v>
+        <v>999</v>
       </c>
       <c r="I42" s="8" t="s">
         <v>97</v>
@@ -13688,26 +13688,26 @@
         <v>19</v>
       </c>
       <c r="B43" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C43" t="s">
         <v>98</v>
       </c>
       <c r="D43" s="2">
-        <v>4800</v>
+        <v>5600</v>
       </c>
       <c r="E43">
         <v>2</v>
       </c>
       <c r="F43" s="2">
         <f>D43*E43</f>
-        <v>9600</v>
+        <v>11200</v>
       </c>
       <c r="G43">
         <v>0</v>
       </c>
       <c r="H43">
-        <v>950</v>
+        <v>999</v>
       </c>
       <c r="I43" s="8" t="s">
         <v>99</v>
@@ -13718,26 +13718,26 @@
         <v>19</v>
       </c>
       <c r="B44" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C44" t="s">
         <v>100</v>
       </c>
       <c r="D44" s="2">
-        <v>5600</v>
+        <v>2506</v>
       </c>
       <c r="E44">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F44" s="2">
         <f>D44*E44</f>
-        <v>11200</v>
+        <v>10024</v>
       </c>
       <c r="G44">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H44">
-        <v>999</v>
+        <v>187</v>
       </c>
       <c r="I44" s="8" t="s">
         <v>101</v>
@@ -13748,20 +13748,20 @@
         <v>19</v>
       </c>
       <c r="B45" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C45" t="s">
         <v>102</v>
       </c>
       <c r="D45" s="2">
-        <v>5600</v>
+        <v>5280</v>
       </c>
       <c r="E45">
         <v>2</v>
       </c>
       <c r="F45" s="2">
         <f>D45*E45</f>
-        <v>11200</v>
+        <v>10560</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -13771,66 +13771,6 @@
       </c>
       <c r="I45" s="8" t="s">
         <v>103</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9">
-      <c r="A46" t="s">
-        <v>19</v>
-      </c>
-      <c r="B46" t="s">
-        <v>93</v>
-      </c>
-      <c r="C46" t="s">
-        <v>104</v>
-      </c>
-      <c r="D46" s="2">
-        <v>2506</v>
-      </c>
-      <c r="E46">
-        <v>4</v>
-      </c>
-      <c r="F46" s="2">
-        <f>D46*E46</f>
-        <v>10024</v>
-      </c>
-      <c r="G46">
-        <v>30</v>
-      </c>
-      <c r="H46">
-        <v>187</v>
-      </c>
-      <c r="I46" s="8" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9">
-      <c r="A47" t="s">
-        <v>19</v>
-      </c>
-      <c r="B47" t="s">
-        <v>93</v>
-      </c>
-      <c r="C47" t="s">
-        <v>106</v>
-      </c>
-      <c r="D47" s="2">
-        <v>5280</v>
-      </c>
-      <c r="E47">
-        <v>2</v>
-      </c>
-      <c r="F47" s="2">
-        <f>D47*E47</f>
-        <v>10560</v>
-      </c>
-      <c r="G47">
-        <v>0</v>
-      </c>
-      <c r="H47">
-        <v>999</v>
-      </c>
-      <c r="I47" s="8" t="s">
-        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -13876,8 +13816,6 @@
     <hyperlink ref="I43" r:id="rId39"/>
     <hyperlink ref="I44" r:id="rId40"/>
     <hyperlink ref="I45" r:id="rId41"/>
-    <hyperlink ref="I46" r:id="rId42"/>
-    <hyperlink ref="I47" r:id="rId43"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -13899,13 +13837,13 @@
         <v>5</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -13913,67 +13851,67 @@
         <v>14</v>
       </c>
       <c r="B2">
-        <f>COUNTIF(구매목록!B5:B47,A2)</f>
+        <f>COUNTIF(구매목록!B5:B45,A2)</f>
         <v>2</v>
       </c>
       <c r="C2" s="2">
-        <f>SUMIF(구매목록!B5:B47,A2,구매목록!F5:F47)</f>
+        <f>SUMIF(구매목록!B5:B45,A2,구매목록!F5:F45)</f>
         <v>104700</v>
       </c>
       <c r="D2" s="9">
         <f>C2/SUM($C$2:$C$8)</f>
-        <v>0.21050557528137778</v>
+        <v>0.21018018886105222</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B3">
-        <f>COUNTIF(구매목록!B5:B47,A3)</f>
+        <f>COUNTIF(구매목록!B5:B45,A3)</f>
         <v>7</v>
       </c>
       <c r="C3" s="2">
-        <f>SUMIF(구매목록!B5:B47,A3,구매목록!F5:F47)</f>
+        <f>SUMIF(구매목록!B5:B45,A3,구매목록!F5:F45)</f>
         <v>69864</v>
       </c>
       <c r="D3" s="9">
         <f>C3/SUM($C$2:$C$8)</f>
-        <v>0.1404657259929148</v>
+        <v>0.14024860281364424</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B4">
-        <f>COUNTIF(구매목록!B5:B47,A4)</f>
+        <f>COUNTIF(구매목록!B5:B45,A4)</f>
         <v>10</v>
       </c>
       <c r="C4" s="2">
-        <f>SUMIF(구매목록!B5:B47,A4,구매목록!F5:F47)</f>
+        <f>SUMIF(구매목록!B5:B45,A4,구매목록!F5:F45)</f>
         <v>91620</v>
       </c>
       <c r="D4" s="9">
         <f>C4/SUM($C$2:$C$8)</f>
-        <v>0.18420745756714263</v>
+        <v>0.18392272114087493</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B5">
-        <f>COUNTIF(구매목록!B5:B47,A5)</f>
+        <f>COUNTIF(구매목록!B5:B45,A5)</f>
         <v>4</v>
       </c>
       <c r="C5" s="2">
-        <f>SUMIF(구매목록!B5:B47,A5,구매목록!F5:F47)</f>
+        <f>SUMIF(구매목록!B5:B45,A5,구매목록!F5:F45)</f>
         <v>87200</v>
       </c>
       <c r="D5" s="9">
         <f>C5/SUM($C$2:$C$8)</f>
-        <v>0.17532078476156776</v>
+        <v>0.175049784801182</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -13981,16 +13919,16 @@
         <v>20</v>
       </c>
       <c r="B6">
-        <f>COUNTIF(구매목록!B5:B47,A6)</f>
+        <f>COUNTIF(구매목록!B5:B45,A6)</f>
         <v>12</v>
       </c>
       <c r="C6" s="2">
-        <f>SUMIF(구매목록!B5:B47,A6,구매목록!F5:F47)</f>
-        <v>63710</v>
+        <f>SUMIF(구매목록!B5:B45,A6,구매목록!F5:F45)</f>
+        <v>88120</v>
       </c>
       <c r="D6" s="9">
         <f>C6/SUM($C$2:$C$8)</f>
-        <v>0.1280927430866913</v>
+        <v>0.17689664032890087</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -13998,33 +13936,33 @@
         <v>45</v>
       </c>
       <c r="B7">
-        <f>COUNTIF(구매목록!B5:B47,A7)</f>
-        <v>6</v>
+        <f>COUNTIF(구매목록!B5:B45,A7)</f>
+        <v>4</v>
       </c>
       <c r="C7" s="2">
-        <f>SUMIF(구매목록!B5:B47,A7,구매목록!F5:F47)</f>
-        <v>67200</v>
+        <f>SUMIF(구매목록!B5:B45,A7,구매목록!F5:F45)</f>
+        <v>43560</v>
       </c>
       <c r="D7" s="9">
         <f>C7/SUM($C$2:$C$8)</f>
-        <v>0.13510959559607055</v>
+        <v>0.08744459433416843</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B8">
-        <f>COUNTIF(구매목록!B5:B47,A8)</f>
+        <f>COUNTIF(구매목록!B5:B45,A8)</f>
         <v>2</v>
       </c>
       <c r="C8" s="2">
-        <f>SUMIF(구매목록!B5:B47,A8,구매목록!F5:F47)</f>
+        <f>SUMIF(구매목록!B5:B45,A8,구매목록!F5:F45)</f>
         <v>13080</v>
       </c>
       <c r="D8" s="9">
         <f>C8/SUM($C$2:$C$8)</f>
-        <v>0.026298117714235163</v>
+        <v>0.0262574677201773</v>
       </c>
     </row>
   </sheetData>
@@ -14048,28 +13986,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="4" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>11</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="I1" s="4" t="s">
         <v>12</v>
@@ -14080,7 +14018,7 @@
         <v>1002110052</v>
       </c>
       <c r="B2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C2">
         <v>8900</v>
@@ -14095,10 +14033,10 @@
         <v>60</v>
       </c>
       <c r="H2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I2" s="10" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -14106,7 +14044,7 @@
         <v>1000747182</v>
       </c>
       <c r="B3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C3">
         <v>3680</v>
@@ -14121,10 +14059,10 @@
         <v>999</v>
       </c>
       <c r="H3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -14132,7 +14070,7 @@
         <v>1000343575</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C4">
         <v>3580</v>
@@ -14147,10 +14085,10 @@
         <v>999</v>
       </c>
       <c r="H4" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -14158,7 +14096,7 @@
         <v>1000862247</v>
       </c>
       <c r="B5" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C5">
         <v>13400</v>
@@ -14173,10 +14111,10 @@
         <v>875</v>
       </c>
       <c r="H5" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -14184,7 +14122,7 @@
         <v>1000178183</v>
       </c>
       <c r="B6" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C6">
         <v>4500</v>
@@ -14199,10 +14137,10 @@
         <v>999</v>
       </c>
       <c r="H6" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -14210,7 +14148,7 @@
         <v>5031072</v>
       </c>
       <c r="B7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C7">
         <v>5980</v>
@@ -14225,10 +14163,10 @@
         <v>999</v>
       </c>
       <c r="H7" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -14236,7 +14174,7 @@
         <v>1000875821</v>
       </c>
       <c r="B8" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C8">
         <v>1690</v>
@@ -14251,10 +14189,10 @@
         <v>999</v>
       </c>
       <c r="H8" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -14262,7 +14200,7 @@
         <v>1000651310</v>
       </c>
       <c r="B9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C9">
         <v>7490</v>
@@ -14277,10 +14215,10 @@
         <v>793</v>
       </c>
       <c r="H9" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -14288,7 +14226,7 @@
         <v>1000321598</v>
       </c>
       <c r="B10" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C10">
         <v>1790</v>
@@ -14303,10 +14241,10 @@
         <v>999</v>
       </c>
       <c r="H10" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -14314,7 +14252,7 @@
         <v>5077465</v>
       </c>
       <c r="B11" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C11">
         <v>3980</v>
@@ -14329,10 +14267,10 @@
         <v>999</v>
       </c>
       <c r="H11" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -14340,7 +14278,7 @@
         <v>5079319</v>
       </c>
       <c r="B12" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C12">
         <v>3580</v>
@@ -14355,10 +14293,10 @@
         <v>999</v>
       </c>
       <c r="H12" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -14381,7 +14319,7 @@
         <v>999</v>
       </c>
       <c r="H13" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I13" s="10" t="s">
         <v>16</v>
@@ -14392,7 +14330,7 @@
         <v>5077461</v>
       </c>
       <c r="B14" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C14">
         <v>4640</v>
@@ -14407,10 +14345,10 @@
         <v>999</v>
       </c>
       <c r="H14" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -14418,7 +14356,7 @@
         <v>1000975389</v>
       </c>
       <c r="B15" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C15">
         <v>2990</v>
@@ -14433,10 +14371,10 @@
         <v>999</v>
       </c>
       <c r="H15" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -14444,7 +14382,7 @@
         <v>5079340</v>
       </c>
       <c r="B16" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C16">
         <v>5280</v>
@@ -14459,10 +14397,10 @@
         <v>999</v>
       </c>
       <c r="H16" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -14470,7 +14408,7 @@
         <v>1000198192</v>
       </c>
       <c r="B17" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C17">
         <v>4540</v>
@@ -14485,10 +14423,10 @@
         <v>9999</v>
       </c>
       <c r="H17" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -14496,7 +14434,7 @@
         <v>5151421</v>
       </c>
       <c r="B18" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C18">
         <v>5940</v>
@@ -14511,10 +14449,10 @@
         <v>999</v>
       </c>
       <c r="H18" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -14522,7 +14460,7 @@
         <v>1001272797</v>
       </c>
       <c r="B19" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C19">
         <v>2980</v>
@@ -14537,10 +14475,10 @@
         <v>999</v>
       </c>
       <c r="H19" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -14548,7 +14486,7 @@
         <v>1001029494</v>
       </c>
       <c r="B20" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C20">
         <v>2280</v>
@@ -14563,10 +14501,10 @@
         <v>597</v>
       </c>
       <c r="H20" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -14574,7 +14512,7 @@
         <v>5030780</v>
       </c>
       <c r="B21" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C21">
         <v>5800</v>
@@ -14589,10 +14527,10 @@
         <v>9999</v>
       </c>
       <c r="H21" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -14600,7 +14538,7 @@
         <v>1000339529</v>
       </c>
       <c r="B22" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C22">
         <v>3980</v>
@@ -14615,10 +14553,10 @@
         <v>557</v>
       </c>
       <c r="H22" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -14626,7 +14564,7 @@
         <v>5036524</v>
       </c>
       <c r="B23" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C23">
         <v>2520</v>
@@ -14641,10 +14579,10 @@
         <v>9999</v>
       </c>
       <c r="H23" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -14652,7 +14590,7 @@
         <v>1000356676</v>
       </c>
       <c r="B24" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C24">
         <v>3800</v>
@@ -14667,10 +14605,10 @@
         <v>9999</v>
       </c>
       <c r="H24" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -14678,7 +14616,7 @@
         <v>1000963099</v>
       </c>
       <c r="B25" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C25">
         <v>4780</v>
@@ -14693,10 +14631,10 @@
         <v>999</v>
       </c>
       <c r="H25" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -14704,7 +14642,7 @@
         <v>5088236</v>
       </c>
       <c r="B26" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C26">
         <v>8980</v>
@@ -14719,10 +14657,10 @@
         <v>999</v>
       </c>
       <c r="H26" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -14730,7 +14668,7 @@
         <v>1000617577</v>
       </c>
       <c r="B27" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C27">
         <v>1360</v>
@@ -14745,10 +14683,10 @@
         <v>9999</v>
       </c>
       <c r="H27" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -14756,7 +14694,7 @@
         <v>1000455773</v>
       </c>
       <c r="B28" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C28">
         <v>4500</v>
@@ -14771,10 +14709,10 @@
         <v>434</v>
       </c>
       <c r="H28" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -14782,7 +14720,7 @@
         <v>1000137075</v>
       </c>
       <c r="B29" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C29">
         <v>4480</v>
@@ -14797,10 +14735,10 @@
         <v>999</v>
       </c>
       <c r="H29" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -14808,7 +14746,7 @@
         <v>1002134596</v>
       </c>
       <c r="B30" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C30">
         <v>5980</v>
@@ -14823,10 +14761,10 @@
         <v>81</v>
       </c>
       <c r="H30" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -14834,7 +14772,7 @@
         <v>1001447521</v>
       </c>
       <c r="B31" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C31">
         <v>1440</v>
@@ -14849,10 +14787,10 @@
         <v>258</v>
       </c>
       <c r="H31" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I31" s="10" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -14860,7 +14798,7 @@
         <v>1001421531</v>
       </c>
       <c r="B32" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C32">
         <v>4980</v>
@@ -14875,10 +14813,10 @@
         <v>602</v>
       </c>
       <c r="H32" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -14886,7 +14824,7 @@
         <v>1000269917</v>
       </c>
       <c r="B33" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C33">
         <v>12800</v>
@@ -14901,10 +14839,10 @@
         <v>988</v>
       </c>
       <c r="H33" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -14912,7 +14850,7 @@
         <v>1001592465</v>
       </c>
       <c r="B34" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C34">
         <v>3880</v>
@@ -14927,10 +14865,10 @@
         <v>520</v>
       </c>
       <c r="H34" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -14938,7 +14876,7 @@
         <v>5054491</v>
       </c>
       <c r="B35" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="C35">
         <v>6590</v>
@@ -14953,10 +14891,10 @@
         <v>999</v>
       </c>
       <c r="H35" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -14964,7 +14902,7 @@
         <v>1001919935</v>
       </c>
       <c r="B36" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C36">
         <v>3800</v>
@@ -14979,10 +14917,10 @@
         <v>313</v>
       </c>
       <c r="H36" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I36" s="10" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
     </row>
     <row r="37" spans="1:9">
@@ -14990,7 +14928,7 @@
         <v>5062899</v>
       </c>
       <c r="B37" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C37">
         <v>4580</v>
@@ -15005,10 +14943,10 @@
         <v>999</v>
       </c>
       <c r="H37" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I37" s="10" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -15016,7 +14954,7 @@
         <v>1000875710</v>
       </c>
       <c r="B38" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C38">
         <v>4580</v>
@@ -15031,10 +14969,10 @@
         <v>999</v>
       </c>
       <c r="H38" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I38" s="10" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -15042,7 +14980,7 @@
         <v>5006818</v>
       </c>
       <c r="B39" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C39">
         <v>8500</v>
@@ -15057,10 +14995,10 @@
         <v>999</v>
       </c>
       <c r="H39" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I39" s="10" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -15068,7 +15006,7 @@
         <v>1000582944</v>
       </c>
       <c r="B40" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C40">
         <v>2780</v>
@@ -15083,10 +15021,10 @@
         <v>594</v>
       </c>
       <c r="H40" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I40" s="10" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -15094,7 +15032,7 @@
         <v>1000206111</v>
       </c>
       <c r="B41" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C41">
         <v>5900</v>
@@ -15109,10 +15047,10 @@
         <v>9999</v>
       </c>
       <c r="H41" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I41" s="10" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="42" spans="1:9">
@@ -15120,7 +15058,7 @@
         <v>1000643389</v>
       </c>
       <c r="B42" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C42">
         <v>5480</v>
@@ -15135,10 +15073,10 @@
         <v>444</v>
       </c>
       <c r="H42" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I42" s="10" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
     </row>
     <row r="43" spans="1:9">
@@ -15146,7 +15084,7 @@
         <v>1000439362</v>
       </c>
       <c r="B43" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C43">
         <v>2250</v>
@@ -15161,10 +15099,10 @@
         <v>999</v>
       </c>
       <c r="H43" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I43" s="10" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="44" spans="1:9">
@@ -15172,7 +15110,7 @@
         <v>1000166566</v>
       </c>
       <c r="B44" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C44">
         <v>12000</v>
@@ -15187,10 +15125,10 @@
         <v>9999</v>
       </c>
       <c r="H44" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I44" s="10" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
     </row>
     <row r="45" spans="1:9">
@@ -15198,7 +15136,7 @@
         <v>1000526145</v>
       </c>
       <c r="B45" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C45">
         <v>8900</v>
@@ -15213,10 +15151,10 @@
         <v>999</v>
       </c>
       <c r="H45" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I45" s="10" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
     </row>
     <row r="46" spans="1:9">
@@ -15224,7 +15162,7 @@
         <v>1000789439</v>
       </c>
       <c r="B46" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C46">
         <v>3590</v>
@@ -15239,10 +15177,10 @@
         <v>324</v>
       </c>
       <c r="H46" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I46" s="10" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
     </row>
     <row r="47" spans="1:9">
@@ -15250,7 +15188,7 @@
         <v>1000356687</v>
       </c>
       <c r="B47" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C47">
         <v>4400</v>
@@ -15265,10 +15203,10 @@
         <v>999</v>
       </c>
       <c r="H47" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I47" s="10" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
     </row>
     <row r="48" spans="1:9">
@@ -15276,7 +15214,7 @@
         <v>5153242</v>
       </c>
       <c r="B48" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C48">
         <v>9980</v>
@@ -15291,10 +15229,10 @@
         <v>503</v>
       </c>
       <c r="H48" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I48" s="10" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
     </row>
     <row r="49" spans="1:9">
@@ -15302,7 +15240,7 @@
         <v>1000033235</v>
       </c>
       <c r="B49" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C49">
         <v>2600</v>
@@ -15317,10 +15255,10 @@
         <v>9999</v>
       </c>
       <c r="H49" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I49" s="10" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -15328,7 +15266,7 @@
         <v>1001570087</v>
       </c>
       <c r="B50" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="C50">
         <v>6080</v>
@@ -15343,10 +15281,10 @@
         <v>999</v>
       </c>
       <c r="H50" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I50" s="10" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -15369,7 +15307,7 @@
         <v>9999</v>
       </c>
       <c r="H51" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I51" s="10" t="s">
         <v>22</v>
@@ -15380,7 +15318,7 @@
         <v>1000942359</v>
       </c>
       <c r="B52" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C52">
         <v>1440</v>
@@ -15395,10 +15333,10 @@
         <v>999</v>
       </c>
       <c r="H52" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I52" s="10" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="53" spans="1:9">
@@ -15406,7 +15344,7 @@
         <v>1001397540</v>
       </c>
       <c r="B53" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="C53">
         <v>1080</v>
@@ -15421,10 +15359,10 @@
         <v>928</v>
       </c>
       <c r="H53" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I53" s="10" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="54" spans="1:9">
@@ -15432,7 +15370,7 @@
         <v>1000927112</v>
       </c>
       <c r="B54" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="C54">
         <v>3325</v>
@@ -15447,10 +15385,10 @@
         <v>999</v>
       </c>
       <c r="H54" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I54" s="10" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="55" spans="1:9">
@@ -15458,7 +15396,7 @@
         <v>5103484</v>
       </c>
       <c r="B55" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="C55">
         <v>11980</v>
@@ -15473,10 +15411,10 @@
         <v>999</v>
       </c>
       <c r="H55" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I55" s="10" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="56" spans="1:9">
@@ -15484,7 +15422,7 @@
         <v>1000605988</v>
       </c>
       <c r="B56" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="C56">
         <v>4180</v>
@@ -15499,10 +15437,10 @@
         <v>723</v>
       </c>
       <c r="H56" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I56" s="10" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
     </row>
     <row r="57" spans="1:9">
@@ -15510,7 +15448,7 @@
         <v>5060050</v>
       </c>
       <c r="B57" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C57">
         <v>5980</v>
@@ -15525,10 +15463,10 @@
         <v>9999</v>
       </c>
       <c r="H57" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I57" s="10" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="58" spans="1:9">
@@ -15536,7 +15474,7 @@
         <v>1002324203</v>
       </c>
       <c r="B58" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C58">
         <v>6980</v>
@@ -15551,10 +15489,10 @@
         <v>22</v>
       </c>
       <c r="H58" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I58" s="10" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="59" spans="1:9">
@@ -15577,7 +15515,7 @@
         <v>999</v>
       </c>
       <c r="H59" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I59" s="10" t="s">
         <v>49</v>
@@ -15588,7 +15526,7 @@
         <v>1000178191</v>
       </c>
       <c r="B60" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C60">
         <v>4150</v>
@@ -15603,10 +15541,10 @@
         <v>9999</v>
       </c>
       <c r="H60" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I60" s="10" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
     </row>
     <row r="61" spans="1:9">
@@ -15614,7 +15552,7 @@
         <v>1000914382</v>
       </c>
       <c r="B61" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C61">
         <v>15500</v>
@@ -15629,10 +15567,10 @@
         <v>658</v>
       </c>
       <c r="H61" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I61" s="10" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
     </row>
     <row r="62" spans="1:9">
@@ -15640,7 +15578,7 @@
         <v>1002014581</v>
       </c>
       <c r="B62" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C62">
         <v>4950</v>
@@ -15655,10 +15593,10 @@
         <v>999</v>
       </c>
       <c r="H62" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I62" s="10" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="63" spans="1:9">
@@ -15666,7 +15604,7 @@
         <v>5052362</v>
       </c>
       <c r="B63" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C63">
         <v>13900</v>
@@ -15681,10 +15619,10 @@
         <v>999</v>
       </c>
       <c r="H63" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I63" s="10" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
     </row>
     <row r="64" spans="1:9">
@@ -15692,7 +15630,7 @@
         <v>5121160</v>
       </c>
       <c r="B64" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C64">
         <v>4380</v>
@@ -15707,10 +15645,10 @@
         <v>999</v>
       </c>
       <c r="H64" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I64" s="10" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="65" spans="1:9">
@@ -15718,7 +15656,7 @@
         <v>1000958549</v>
       </c>
       <c r="B65" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C65">
         <v>3380</v>
@@ -15733,10 +15671,10 @@
         <v>711</v>
       </c>
       <c r="H65" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I65" s="10" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="66" spans="1:9">
@@ -15744,7 +15682,7 @@
         <v>1002010936</v>
       </c>
       <c r="B66" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="C66">
         <v>2800</v>
@@ -15759,10 +15697,10 @@
         <v>416</v>
       </c>
       <c r="H66" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I66" s="10" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="67" spans="1:9">
@@ -15770,7 +15708,7 @@
         <v>1000242960</v>
       </c>
       <c r="B67" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="C67">
         <v>7000</v>
@@ -15785,10 +15723,10 @@
         <v>999</v>
       </c>
       <c r="H67" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I67" s="10" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
     </row>
     <row r="68" spans="1:9">
@@ -15796,7 +15734,7 @@
         <v>1002482468</v>
       </c>
       <c r="B68" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="C68">
         <v>2130</v>
@@ -15811,10 +15749,10 @@
         <v>492</v>
       </c>
       <c r="H68" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I68" s="10" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
     </row>
     <row r="69" spans="1:9">
@@ -15822,7 +15760,7 @@
         <v>5058855</v>
       </c>
       <c r="B69" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C69">
         <v>8500</v>
@@ -15837,10 +15775,10 @@
         <v>9999</v>
       </c>
       <c r="H69" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I69" s="10" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
     </row>
     <row r="70" spans="1:9">
@@ -15848,7 +15786,7 @@
         <v>1000783621</v>
       </c>
       <c r="B70" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="C70">
         <v>10960</v>
@@ -15863,10 +15801,10 @@
         <v>175</v>
       </c>
       <c r="H70" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I70" s="10" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
     </row>
     <row r="71" spans="1:9">
@@ -15874,7 +15812,7 @@
         <v>1000525224</v>
       </c>
       <c r="B71" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C71">
         <v>12980</v>
@@ -15889,10 +15827,10 @@
         <v>191</v>
       </c>
       <c r="H71" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I71" s="10" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
     </row>
     <row r="72" spans="1:9">
@@ -15900,7 +15838,7 @@
         <v>1000365879</v>
       </c>
       <c r="B72" t="s">
-        <v>50</v>
+        <v>241</v>
       </c>
       <c r="C72">
         <v>3380</v>
@@ -15915,10 +15853,10 @@
         <v>999</v>
       </c>
       <c r="H72" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I72" s="10" t="s">
-        <v>51</v>
+        <v>242</v>
       </c>
     </row>
     <row r="73" spans="1:9">
@@ -15926,7 +15864,7 @@
         <v>1002133624</v>
       </c>
       <c r="B73" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C73">
         <v>6300</v>
@@ -15941,10 +15879,10 @@
         <v>97</v>
       </c>
       <c r="H73" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I73" s="10" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="74" spans="1:9">
@@ -15952,7 +15890,7 @@
         <v>1000339558</v>
       </c>
       <c r="B74" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C74">
         <v>2720</v>
@@ -15967,10 +15905,10 @@
         <v>448</v>
       </c>
       <c r="H74" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I74" s="10" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="75" spans="1:9">
@@ -15978,7 +15916,7 @@
         <v>5081478</v>
       </c>
       <c r="B75" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C75">
         <v>3360</v>
@@ -15993,10 +15931,10 @@
         <v>9999</v>
       </c>
       <c r="H75" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I75" s="10" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="76" spans="1:9">
@@ -16004,7 +15942,7 @@
         <v>5005540</v>
       </c>
       <c r="B76" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C76">
         <v>8000</v>
@@ -16019,10 +15957,10 @@
         <v>9999</v>
       </c>
       <c r="H76" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I76" s="10" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="77" spans="1:9">
@@ -16030,7 +15968,7 @@
         <v>1000526148</v>
       </c>
       <c r="B77" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C77">
         <v>8900</v>
@@ -16045,10 +15983,10 @@
         <v>276</v>
       </c>
       <c r="H77" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I77" s="10" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="78" spans="1:9">
@@ -16056,7 +15994,7 @@
         <v>1000677312</v>
       </c>
       <c r="B78" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C78">
         <v>1480</v>
@@ -16071,10 +16009,10 @@
         <v>999</v>
       </c>
       <c r="H78" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I78" s="10" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="79" spans="1:9">
@@ -16082,7 +16020,7 @@
         <v>1001407039</v>
       </c>
       <c r="B79" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C79">
         <v>3980</v>
@@ -16097,10 +16035,10 @@
         <v>145</v>
       </c>
       <c r="H79" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I79" s="10" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="80" spans="1:9">
@@ -16108,7 +16046,7 @@
         <v>1000248448</v>
       </c>
       <c r="B80" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C80">
         <v>5200</v>
@@ -16123,10 +16061,10 @@
         <v>9999</v>
       </c>
       <c r="H80" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I80" s="10" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="81" spans="1:9">
@@ -16134,7 +16072,7 @@
         <v>1001027192</v>
       </c>
       <c r="B81" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C81">
         <v>9000</v>
@@ -16149,10 +16087,10 @@
         <v>361</v>
       </c>
       <c r="H81" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I81" s="10" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="82" spans="1:9">
@@ -16160,7 +16098,7 @@
         <v>5067308</v>
       </c>
       <c r="B82" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C82">
         <v>2880</v>
@@ -16175,10 +16113,10 @@
         <v>999</v>
       </c>
       <c r="H82" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I82" s="10" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="83" spans="1:9">
@@ -16186,7 +16124,7 @@
         <v>1000942860</v>
       </c>
       <c r="B83" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C83">
         <v>1390</v>
@@ -16201,10 +16139,10 @@
         <v>999</v>
       </c>
       <c r="H83" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I83" s="10" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="84" spans="1:9">
@@ -16212,7 +16150,7 @@
         <v>1001991119</v>
       </c>
       <c r="B84" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C84">
         <v>3480</v>
@@ -16227,10 +16165,10 @@
         <v>999</v>
       </c>
       <c r="H84" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I84" s="10" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="85" spans="1:9">
@@ -16238,7 +16176,7 @@
         <v>5132664</v>
       </c>
       <c r="B85" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C85">
         <v>3800</v>
@@ -16253,10 +16191,10 @@
         <v>999</v>
       </c>
       <c r="H85" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I85" s="10" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="86" spans="1:9">
@@ -16264,7 +16202,7 @@
         <v>1000640854</v>
       </c>
       <c r="B86" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C86">
         <v>2720</v>
@@ -16279,10 +16217,10 @@
         <v>999</v>
       </c>
       <c r="H86" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I86" s="10" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="87" spans="1:9">
@@ -16290,7 +16228,7 @@
         <v>1000045935</v>
       </c>
       <c r="B87" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C87">
         <v>5990</v>
@@ -16305,10 +16243,10 @@
         <v>999</v>
       </c>
       <c r="H87" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I87" s="10" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="88" spans="1:9">
@@ -16316,7 +16254,7 @@
         <v>1000349505</v>
       </c>
       <c r="B88" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C88">
         <v>1440</v>
@@ -16331,10 +16269,10 @@
         <v>999</v>
       </c>
       <c r="H88" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I88" s="10" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="89" spans="1:9">
@@ -16342,7 +16280,7 @@
         <v>5060582</v>
       </c>
       <c r="B89" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C89">
         <v>10000</v>
@@ -16357,10 +16295,10 @@
         <v>999</v>
       </c>
       <c r="H89" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I89" s="10" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="90" spans="1:9">
@@ -16368,7 +16306,7 @@
         <v>1001363953</v>
       </c>
       <c r="B90" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C90">
         <v>2180</v>
@@ -16383,10 +16321,10 @@
         <v>999</v>
       </c>
       <c r="H90" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I90" s="10" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="91" spans="1:9">
@@ -16394,7 +16332,7 @@
         <v>5103372</v>
       </c>
       <c r="B91" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C91">
         <v>11980</v>
@@ -16409,10 +16347,10 @@
         <v>999</v>
       </c>
       <c r="H91" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I91" s="10" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="92" spans="1:9">
@@ -16420,7 +16358,7 @@
         <v>1001501063</v>
       </c>
       <c r="B92" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C92">
         <v>1260</v>
@@ -16435,10 +16373,10 @@
         <v>980</v>
       </c>
       <c r="H92" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I92" s="10" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="93" spans="1:9">
@@ -16446,7 +16384,7 @@
         <v>1000443353</v>
       </c>
       <c r="B93" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C93">
         <v>4040</v>
@@ -16461,10 +16399,10 @@
         <v>999</v>
       </c>
       <c r="H93" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I93" s="10" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="94" spans="1:9">
@@ -16472,7 +16410,7 @@
         <v>1002221133</v>
       </c>
       <c r="B94" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C94">
         <v>4980</v>
@@ -16487,10 +16425,10 @@
         <v>81</v>
       </c>
       <c r="H94" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I94" s="10" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="95" spans="1:9">
@@ -16498,7 +16436,7 @@
         <v>1000136966</v>
       </c>
       <c r="B95" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C95">
         <v>9000</v>
@@ -16513,10 +16451,10 @@
         <v>999</v>
       </c>
       <c r="H95" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I95" s="10" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="96" spans="1:9">
@@ -16524,7 +16462,7 @@
         <v>1000799985</v>
       </c>
       <c r="B96" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C96">
         <v>4980</v>
@@ -16539,10 +16477,10 @@
         <v>612</v>
       </c>
       <c r="H96" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I96" s="10" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="97" spans="1:9">
@@ -16550,7 +16488,7 @@
         <v>1000960165</v>
       </c>
       <c r="B97" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C97">
         <v>1390</v>
@@ -16565,10 +16503,10 @@
         <v>539</v>
       </c>
       <c r="H97" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I97" s="10" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="98" spans="1:9">
@@ -16576,7 +16514,7 @@
         <v>1001337989</v>
       </c>
       <c r="B98" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C98">
         <v>5280</v>
@@ -16591,10 +16529,10 @@
         <v>613</v>
       </c>
       <c r="H98" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I98" s="10" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="99" spans="1:9">
@@ -16617,7 +16555,7 @@
         <v>999</v>
       </c>
       <c r="H99" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I99" s="10" t="s">
         <v>38</v>
@@ -16643,7 +16581,7 @@
         <v>999</v>
       </c>
       <c r="H100" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I100" s="10" t="s">
         <v>47</v>
@@ -16654,7 +16592,7 @@
         <v>1002104225</v>
       </c>
       <c r="B101" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C101">
         <v>1280</v>
@@ -16669,10 +16607,10 @@
         <v>98</v>
       </c>
       <c r="H101" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I101" s="10" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="102" spans="1:9">
@@ -16680,7 +16618,7 @@
         <v>1002020133</v>
       </c>
       <c r="B102" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C102">
         <v>9030</v>
@@ -16695,10 +16633,10 @@
         <v>159</v>
       </c>
       <c r="H102" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I102" s="10" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="103" spans="1:9">
@@ -16706,7 +16644,7 @@
         <v>1000360436</v>
       </c>
       <c r="B103" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C103">
         <v>4480</v>
@@ -16721,10 +16659,10 @@
         <v>999</v>
       </c>
       <c r="H103" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I103" s="10" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="104" spans="1:9">
@@ -16732,7 +16670,7 @@
         <v>1001042362</v>
       </c>
       <c r="B104" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C104">
         <v>3980</v>
@@ -16747,10 +16685,10 @@
         <v>958</v>
       </c>
       <c r="H104" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I104" s="10" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="105" spans="1:9">
@@ -16758,7 +16696,7 @@
         <v>1002340554</v>
       </c>
       <c r="B105" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C105">
         <v>4250</v>
@@ -16773,10 +16711,10 @@
         <v>342</v>
       </c>
       <c r="H105" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I105" s="10" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="106" spans="1:9">
@@ -16784,7 +16722,7 @@
         <v>1000490099</v>
       </c>
       <c r="B106" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C106">
         <v>3980</v>
@@ -16799,10 +16737,10 @@
         <v>999</v>
       </c>
       <c r="H106" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I106" s="10" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="107" spans="1:9">
@@ -16810,7 +16748,7 @@
         <v>5077641</v>
       </c>
       <c r="B107" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C107">
         <v>7080</v>
@@ -16825,10 +16763,10 @@
         <v>999</v>
       </c>
       <c r="H107" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I107" s="10" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="108" spans="1:9">
@@ -16836,7 +16774,7 @@
         <v>1001397631</v>
       </c>
       <c r="B108" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C108">
         <v>1360</v>
@@ -16851,10 +16789,10 @@
         <v>772</v>
       </c>
       <c r="H108" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I108" s="10" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="109" spans="1:9">
@@ -16862,7 +16800,7 @@
         <v>1001942440</v>
       </c>
       <c r="B109" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C109">
         <v>2500</v>
@@ -16877,10 +16815,10 @@
         <v>751</v>
       </c>
       <c r="H109" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I109" s="10" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="110" spans="1:9">
@@ -16903,7 +16841,7 @@
         <v>889</v>
       </c>
       <c r="H110" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I110" s="10" t="s">
         <v>36</v>
@@ -16929,7 +16867,7 @@
         <v>999</v>
       </c>
       <c r="H111" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I111" s="10" t="s">
         <v>26</v>
@@ -16940,7 +16878,7 @@
         <v>1002221138</v>
       </c>
       <c r="B112" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C112">
         <v>4480</v>
@@ -16955,10 +16893,10 @@
         <v>134</v>
       </c>
       <c r="H112" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I112" s="10" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="113" spans="1:9">
@@ -16966,7 +16904,7 @@
         <v>1000216544</v>
       </c>
       <c r="B113" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C113">
         <v>4380</v>
@@ -16981,10 +16919,10 @@
         <v>999</v>
       </c>
       <c r="H113" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I113" s="10" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="114" spans="1:9">
@@ -16992,7 +16930,7 @@
         <v>5118057</v>
       </c>
       <c r="B114" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C114">
         <v>2720</v>
@@ -17007,10 +16945,10 @@
         <v>999</v>
       </c>
       <c r="H114" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I114" s="10" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="115" spans="1:9">
@@ -17018,7 +16956,7 @@
         <v>1000656471</v>
       </c>
       <c r="B115" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C115">
         <v>5850</v>
@@ -17033,10 +16971,10 @@
         <v>71</v>
       </c>
       <c r="H115" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I115" s="10" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="116" spans="1:9">
@@ -17044,7 +16982,7 @@
         <v>1001073370</v>
       </c>
       <c r="B116" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C116">
         <v>3500</v>
@@ -17059,10 +16997,10 @@
         <v>999</v>
       </c>
       <c r="H116" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I116" s="10" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="117" spans="1:9">
@@ -17070,7 +17008,7 @@
         <v>1000365868</v>
       </c>
       <c r="B117" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C117">
         <v>4380</v>
@@ -17085,10 +17023,10 @@
         <v>627</v>
       </c>
       <c r="H117" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I117" s="10" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="118" spans="1:9">
@@ -17096,7 +17034,7 @@
         <v>1001740101</v>
       </c>
       <c r="B118" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C118">
         <v>4200</v>
@@ -17111,10 +17049,10 @@
         <v>391</v>
       </c>
       <c r="H118" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I118" s="10" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="119" spans="1:9">
@@ -17122,7 +17060,7 @@
         <v>1000339526</v>
       </c>
       <c r="B119" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C119">
         <v>5440</v>
@@ -17137,10 +17075,10 @@
         <v>956</v>
       </c>
       <c r="H119" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I119" s="10" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="120" spans="1:9">
@@ -17148,7 +17086,7 @@
         <v>1000125337</v>
       </c>
       <c r="B120" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C120">
         <v>6280</v>
@@ -17163,10 +17101,10 @@
         <v>999</v>
       </c>
       <c r="H120" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I120" s="10" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="121" spans="1:9">
@@ -17174,7 +17112,7 @@
         <v>5013230</v>
       </c>
       <c r="B121" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C121">
         <v>4780</v>
@@ -17189,10 +17127,10 @@
         <v>9999</v>
       </c>
       <c r="H121" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I121" s="10" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="122" spans="1:9">
@@ -17200,7 +17138,7 @@
         <v>5043538</v>
       </c>
       <c r="B122" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C122">
         <v>11500</v>
@@ -17215,10 +17153,10 @@
         <v>999</v>
       </c>
       <c r="H122" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I122" s="10" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="123" spans="1:9">
@@ -17226,7 +17164,7 @@
         <v>1001382381</v>
       </c>
       <c r="B123" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C123">
         <v>8990</v>
@@ -17241,10 +17179,10 @@
         <v>999</v>
       </c>
       <c r="H123" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I123" s="10" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="124" spans="1:9">
@@ -17252,7 +17190,7 @@
         <v>1002159262</v>
       </c>
       <c r="B124" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C124">
         <v>2500</v>
@@ -17267,10 +17205,10 @@
         <v>197</v>
       </c>
       <c r="H124" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I124" s="10" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="125" spans="1:9">
@@ -17278,7 +17216,7 @@
         <v>1002286852</v>
       </c>
       <c r="B125" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C125">
         <v>3540</v>
@@ -17293,10 +17231,10 @@
         <v>191</v>
       </c>
       <c r="H125" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I125" s="10" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="126" spans="1:9">
@@ -17304,7 +17242,7 @@
         <v>5052356</v>
       </c>
       <c r="B126" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C126">
         <v>12300</v>
@@ -17319,10 +17257,10 @@
         <v>999</v>
       </c>
       <c r="H126" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I126" s="10" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="127" spans="1:9">
@@ -17330,7 +17268,7 @@
         <v>1000499057</v>
       </c>
       <c r="B127" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C127">
         <v>11980</v>
@@ -17345,10 +17283,10 @@
         <v>232</v>
       </c>
       <c r="H127" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I127" s="10" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="128" spans="1:9">
@@ -17356,7 +17294,7 @@
         <v>1000791609</v>
       </c>
       <c r="B128" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C128">
         <v>1520</v>
@@ -17371,10 +17309,10 @@
         <v>999</v>
       </c>
       <c r="H128" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I128" s="10" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="129" spans="1:9">
@@ -17382,7 +17320,7 @@
         <v>1000074625</v>
       </c>
       <c r="B129" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C129">
         <v>20900</v>
@@ -17397,10 +17335,10 @@
         <v>690</v>
       </c>
       <c r="H129" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I129" s="10" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="130" spans="1:9">
@@ -17408,7 +17346,7 @@
         <v>5077457</v>
       </c>
       <c r="B130" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C130">
         <v>4320</v>
@@ -17423,10 +17361,10 @@
         <v>999</v>
       </c>
       <c r="H130" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I130" s="10" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="131" spans="1:9">
@@ -17434,7 +17372,7 @@
         <v>1000349503</v>
       </c>
       <c r="B131" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C131">
         <v>2250</v>
@@ -17449,10 +17387,10 @@
         <v>786</v>
       </c>
       <c r="H131" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I131" s="10" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="132" spans="1:9">
@@ -17460,7 +17398,7 @@
         <v>5110063</v>
       </c>
       <c r="B132" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C132">
         <v>3780</v>
@@ -17475,10 +17413,10 @@
         <v>999</v>
       </c>
       <c r="H132" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I132" s="10" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="133" spans="1:9">
@@ -17486,7 +17424,7 @@
         <v>5054219</v>
       </c>
       <c r="B133" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C133">
         <v>2490</v>
@@ -17501,10 +17439,10 @@
         <v>9999</v>
       </c>
       <c r="H133" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I133" s="10" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="134" spans="1:9">
@@ -17512,7 +17450,7 @@
         <v>1001959559</v>
       </c>
       <c r="B134" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C134">
         <v>2400</v>
@@ -17527,10 +17465,10 @@
         <v>615</v>
       </c>
       <c r="H134" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I134" s="10" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="135" spans="1:9">
@@ -17538,7 +17476,7 @@
         <v>5132978</v>
       </c>
       <c r="B135" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C135">
         <v>4200</v>
@@ -17553,10 +17491,10 @@
         <v>999</v>
       </c>
       <c r="H135" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I135" s="10" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="136" spans="1:9">
@@ -17564,7 +17502,7 @@
         <v>1000777595</v>
       </c>
       <c r="B136" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C136">
         <v>2980</v>
@@ -17579,10 +17517,10 @@
         <v>776</v>
       </c>
       <c r="H136" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I136" s="10" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="137" spans="1:9">
@@ -17590,7 +17528,7 @@
         <v>5067311</v>
       </c>
       <c r="B137" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C137">
         <v>4480</v>
@@ -17605,10 +17543,10 @@
         <v>999</v>
       </c>
       <c r="H137" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I137" s="10" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="138" spans="1:9">
@@ -17616,7 +17554,7 @@
         <v>1002225093</v>
       </c>
       <c r="B138" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C138">
         <v>3980</v>
@@ -17631,10 +17569,10 @@
         <v>324</v>
       </c>
       <c r="H138" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I138" s="10" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="139" spans="1:9">
@@ -17642,7 +17580,7 @@
         <v>5030130</v>
       </c>
       <c r="B139" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C139">
         <v>3980</v>
@@ -17657,10 +17595,10 @@
         <v>9999</v>
       </c>
       <c r="H139" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I139" s="10" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="140" spans="1:9">
@@ -17668,7 +17606,7 @@
         <v>1001317277</v>
       </c>
       <c r="B140" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C140">
         <v>3780</v>
@@ -17683,10 +17621,10 @@
         <v>359</v>
       </c>
       <c r="H140" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I140" s="10" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="141" spans="1:9">
@@ -17694,7 +17632,7 @@
         <v>5118059</v>
       </c>
       <c r="B141" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C141">
         <v>2720</v>
@@ -17709,10 +17647,10 @@
         <v>999</v>
       </c>
       <c r="H141" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I141" s="10" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="142" spans="1:9">
@@ -17720,7 +17658,7 @@
         <v>5081412</v>
       </c>
       <c r="B142" t="s">
-        <v>52</v>
+        <v>365</v>
       </c>
       <c r="C142">
         <v>4500</v>
@@ -17735,10 +17673,10 @@
         <v>999</v>
       </c>
       <c r="H142" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I142" s="10" t="s">
-        <v>53</v>
+        <v>366</v>
       </c>
     </row>
     <row r="143" spans="1:9">
@@ -17761,7 +17699,7 @@
         <v>613</v>
       </c>
       <c r="H143" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I143" s="10" t="s">
         <v>368</v>
@@ -17787,7 +17725,7 @@
         <v>87</v>
       </c>
       <c r="H144" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I144" s="10" t="s">
         <v>370</v>
@@ -17813,7 +17751,7 @@
         <v>304</v>
       </c>
       <c r="H145" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I145" s="10" t="s">
         <v>372</v>
@@ -17839,7 +17777,7 @@
         <v>9999</v>
       </c>
       <c r="H146" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I146" s="10" t="s">
         <v>374</v>
@@ -17865,7 +17803,7 @@
         <v>999</v>
       </c>
       <c r="H147" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I147" s="10" t="s">
         <v>376</v>
@@ -17891,7 +17829,7 @@
         <v>999</v>
       </c>
       <c r="H148" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I148" s="10" t="s">
         <v>378</v>
@@ -17917,7 +17855,7 @@
         <v>999</v>
       </c>
       <c r="H149" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I149" s="10" t="s">
         <v>380</v>
@@ -17943,7 +17881,7 @@
         <v>826</v>
       </c>
       <c r="H150" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I150" s="10" t="s">
         <v>382</v>
@@ -17969,7 +17907,7 @@
         <v>622</v>
       </c>
       <c r="H151" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I151" s="10" t="s">
         <v>384</v>
@@ -17995,7 +17933,7 @@
         <v>866</v>
       </c>
       <c r="H152" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I152" s="10" t="s">
         <v>386</v>
@@ -18021,7 +17959,7 @@
         <v>999</v>
       </c>
       <c r="H153" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I153" s="10" t="s">
         <v>388</v>
@@ -18047,7 +17985,7 @@
         <v>416</v>
       </c>
       <c r="H154" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I154" s="10" t="s">
         <v>390</v>
@@ -18073,7 +18011,7 @@
         <v>181</v>
       </c>
       <c r="H155" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I155" s="10" t="s">
         <v>392</v>
@@ -18099,7 +18037,7 @@
         <v>999</v>
       </c>
       <c r="H156" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I156" s="10" t="s">
         <v>394</v>
@@ -18125,7 +18063,7 @@
         <v>999</v>
       </c>
       <c r="H157" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I157" s="10" t="s">
         <v>396</v>
@@ -18151,7 +18089,7 @@
         <v>533</v>
       </c>
       <c r="H158" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I158" s="10" t="s">
         <v>398</v>
@@ -18177,7 +18115,7 @@
         <v>718</v>
       </c>
       <c r="H159" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I159" s="10" t="s">
         <v>400</v>
@@ -18203,7 +18141,7 @@
         <v>999</v>
       </c>
       <c r="H160" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I160" s="10" t="s">
         <v>402</v>
@@ -18229,7 +18167,7 @@
         <v>999</v>
       </c>
       <c r="H161" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I161" s="10" t="s">
         <v>404</v>
@@ -18255,7 +18193,7 @@
         <v>361</v>
       </c>
       <c r="H162" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I162" s="10" t="s">
         <v>406</v>
@@ -18281,7 +18219,7 @@
         <v>511</v>
       </c>
       <c r="H163" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I163" s="10" t="s">
         <v>408</v>
@@ -18307,7 +18245,7 @@
         <v>106</v>
       </c>
       <c r="H164" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I164" s="10" t="s">
         <v>410</v>
@@ -18333,7 +18271,7 @@
         <v>184</v>
       </c>
       <c r="H165" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I165" s="10" t="s">
         <v>412</v>
@@ -18359,7 +18297,7 @@
         <v>509</v>
       </c>
       <c r="H166" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I166" s="10" t="s">
         <v>414</v>
@@ -18385,7 +18323,7 @@
         <v>255</v>
       </c>
       <c r="H167" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I167" s="10" t="s">
         <v>416</v>
@@ -18411,7 +18349,7 @@
         <v>999</v>
       </c>
       <c r="H168" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I168" s="10" t="s">
         <v>418</v>
@@ -18437,7 +18375,7 @@
         <v>637</v>
       </c>
       <c r="H169" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I169" s="10" t="s">
         <v>420</v>
@@ -18463,7 +18401,7 @@
         <v>999</v>
       </c>
       <c r="H170" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I170" s="10" t="s">
         <v>422</v>
@@ -18489,7 +18427,7 @@
         <v>216</v>
       </c>
       <c r="H171" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I171" s="10" t="s">
         <v>424</v>
@@ -18515,7 +18453,7 @@
         <v>732</v>
       </c>
       <c r="H172" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I172" s="10" t="s">
         <v>426</v>
@@ -18541,7 +18479,7 @@
         <v>999</v>
       </c>
       <c r="H173" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I173" s="10" t="s">
         <v>30</v>
@@ -18567,7 +18505,7 @@
         <v>999</v>
       </c>
       <c r="H174" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I174" s="10" t="s">
         <v>428</v>
@@ -18593,7 +18531,7 @@
         <v>999</v>
       </c>
       <c r="H175" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I175" s="10" t="s">
         <v>430</v>
@@ -18619,7 +18557,7 @@
         <v>9999</v>
       </c>
       <c r="H176" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I176" s="10" t="s">
         <v>432</v>
@@ -18645,7 +18583,7 @@
         <v>384</v>
       </c>
       <c r="H177" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I177" s="10" t="s">
         <v>434</v>
@@ -18671,7 +18609,7 @@
         <v>9999</v>
       </c>
       <c r="H178" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I178" s="10" t="s">
         <v>436</v>
@@ -18697,7 +18635,7 @@
         <v>477</v>
       </c>
       <c r="H179" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I179" s="10" t="s">
         <v>438</v>
@@ -18723,7 +18661,7 @@
         <v>284</v>
       </c>
       <c r="H180" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I180" s="10" t="s">
         <v>440</v>
@@ -18749,7 +18687,7 @@
         <v>585</v>
       </c>
       <c r="H181" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I181" s="10" t="s">
         <v>442</v>
@@ -18775,7 +18713,7 @@
         <v>999</v>
       </c>
       <c r="H182" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I182" s="10" t="s">
         <v>444</v>
@@ -18801,7 +18739,7 @@
         <v>623</v>
       </c>
       <c r="H183" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I183" s="10" t="s">
         <v>446</v>
@@ -18827,7 +18765,7 @@
         <v>999</v>
       </c>
       <c r="H184" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I184" s="10" t="s">
         <v>448</v>
@@ -18853,7 +18791,7 @@
         <v>999</v>
       </c>
       <c r="H185" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I185" s="10" t="s">
         <v>40</v>
@@ -18879,7 +18817,7 @@
         <v>999</v>
       </c>
       <c r="H186" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I186" s="10" t="s">
         <v>450</v>
@@ -18905,7 +18843,7 @@
         <v>92</v>
       </c>
       <c r="H187" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I187" s="10" t="s">
         <v>452</v>
@@ -18931,7 +18869,7 @@
         <v>100</v>
       </c>
       <c r="H188" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I188" s="10" t="s">
         <v>454</v>
@@ -18957,7 +18895,7 @@
         <v>999</v>
       </c>
       <c r="H189" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I189" s="10" t="s">
         <v>456</v>
@@ -18983,7 +18921,7 @@
         <v>220</v>
       </c>
       <c r="H190" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I190" s="10" t="s">
         <v>458</v>
@@ -19009,7 +18947,7 @@
         <v>418</v>
       </c>
       <c r="H191" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I191" s="10" t="s">
         <v>460</v>
@@ -19035,7 +18973,7 @@
         <v>999</v>
       </c>
       <c r="H192" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I192" s="10" t="s">
         <v>462</v>
@@ -19061,7 +18999,7 @@
         <v>999</v>
       </c>
       <c r="H193" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I193" s="10" t="s">
         <v>464</v>
@@ -21279,7 +21217,7 @@
         <v>5061562</v>
       </c>
       <c r="B279" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C279">
         <v>3690</v>
@@ -21297,7 +21235,7 @@
         <v>631</v>
       </c>
       <c r="I279" s="10" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="280" spans="1:9">
@@ -22215,7 +22153,7 @@
         <v>1000175874</v>
       </c>
       <c r="B315" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C315">
         <v>5600</v>
@@ -22233,7 +22171,7 @@
         <v>631</v>
       </c>
       <c r="I315" s="10" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="316" spans="1:9">
@@ -22449,7 +22387,7 @@
         <v>1000875718</v>
       </c>
       <c r="B324" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C324">
         <v>4320</v>
@@ -22467,7 +22405,7 @@
         <v>631</v>
       </c>
       <c r="I324" s="10" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="325" spans="1:9">
@@ -22969,7 +22907,7 @@
         <v>5061939</v>
       </c>
       <c r="B344" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C344">
         <v>4780</v>
@@ -22987,7 +22925,7 @@
         <v>631</v>
       </c>
       <c r="I344" s="10" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="345" spans="1:9">
@@ -23613,7 +23551,7 @@
         <v>1002110078</v>
       </c>
       <c r="B369" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C369">
         <v>3980</v>
@@ -23631,7 +23569,7 @@
         <v>631</v>
       </c>
       <c r="I369" s="10" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="370" spans="1:9">
@@ -25693,7 +25631,7 @@
         <v>1002033102</v>
       </c>
       <c r="B449" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C449">
         <v>2180</v>
@@ -25711,7 +25649,7 @@
         <v>912</v>
       </c>
       <c r="I449" s="10" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="450" spans="1:9">
@@ -26707,7 +26645,7 @@
         <v>1001069960</v>
       </c>
       <c r="B488" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C488">
         <v>2180</v>
@@ -26725,7 +26663,7 @@
         <v>912</v>
       </c>
       <c r="I488" s="10" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="489" spans="1:9">
@@ -27679,7 +27617,7 @@
         <v>5007664</v>
       </c>
       <c r="B524" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C524">
         <v>3980</v>
@@ -27697,7 +27635,7 @@
         <v>1114</v>
       </c>
       <c r="I524" s="10" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="525" spans="1:9">
@@ -28251,7 +28189,7 @@
         <v>5055905</v>
       </c>
       <c r="B546" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C546">
         <v>5120</v>
@@ -28269,7 +28207,7 @@
         <v>1114</v>
       </c>
       <c r="I546" s="10" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="547" spans="1:9">
@@ -44393,7 +44331,7 @@
         <v>1000175876</v>
       </c>
       <c r="B1153" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C1153">
         <v>5600</v>
@@ -44411,7 +44349,7 @@
         <v>2207</v>
       </c>
       <c r="I1153" s="10" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="1154" spans="1:9">
@@ -45508,7 +45446,7 @@
         <v>1002225099</v>
       </c>
       <c r="B1196" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C1196">
         <v>2506</v>
@@ -45526,7 +45464,7 @@
         <v>2434</v>
       </c>
       <c r="I1196" s="10" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="1197" spans="1:9">
@@ -45664,7 +45602,7 @@
         <v>5061296</v>
       </c>
       <c r="B1202" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C1202">
         <v>4320</v>
@@ -45682,7 +45620,7 @@
         <v>2434</v>
       </c>
       <c r="I1202" s="10" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="1203" spans="1:9">
@@ -46256,7 +46194,7 @@
         <v>1002419584</v>
       </c>
       <c r="B1225" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C1225">
         <v>3200</v>
@@ -46274,7 +46212,7 @@
         <v>2483</v>
       </c>
       <c r="I1225" s="10" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="1226" spans="1:9">
@@ -46672,7 +46610,7 @@
         <v>1001382646</v>
       </c>
       <c r="B1241" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C1241">
         <v>4800</v>
@@ -46690,7 +46628,7 @@
         <v>2483</v>
       </c>
       <c r="I1241" s="10" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="1242" spans="1:9">
@@ -47816,7 +47754,7 @@
         <v>1001137097</v>
       </c>
       <c r="B1285" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C1285">
         <v>4780</v>
@@ -47834,7 +47772,7 @@
         <v>2483</v>
       </c>
       <c r="I1285" s="10" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="1286" spans="1:9">
@@ -48515,7 +48453,7 @@
         <v>1002378241</v>
       </c>
       <c r="B1312" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C1312">
         <v>2180</v>
@@ -48533,7 +48471,7 @@
         <v>2665</v>
       </c>
       <c r="I1312" s="10" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="1313" spans="1:9">
@@ -49419,7 +49357,7 @@
         <v>1000548776</v>
       </c>
       <c r="B1347" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C1347">
         <v>2180</v>
@@ -49437,7 +49375,7 @@
         <v>2665</v>
       </c>
       <c r="I1347" s="10" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="1348" spans="1:9">
@@ -53125,7 +53063,7 @@
         <v>1000201444</v>
       </c>
       <c r="B1484" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C1484">
         <v>5280</v>
@@ -53143,7 +53081,7 @@
         <v>3014</v>
       </c>
       <c r="I1484" s="10" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="1485" spans="1:9">
@@ -58184,7 +58122,7 @@
         <v>3</v>
       </c>
       <c r="H1675" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="I1675" s="10" t="s">
         <v>3409</v>
@@ -58210,7 +58148,7 @@
         <v>999</v>
       </c>
       <c r="H1676" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="I1676" s="10" t="s">
         <v>3411</v>
@@ -58233,7 +58171,7 @@
         <v>15</v>
       </c>
       <c r="H1677" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="I1677" s="10" t="s">
         <v>3413</v>
@@ -58256,7 +58194,7 @@
         <v>15</v>
       </c>
       <c r="H1678" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="I1678" s="10" t="s">
         <v>3415</v>
@@ -58279,7 +58217,7 @@
         <v>15</v>
       </c>
       <c r="H1679" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="I1679" s="10" t="s">
         <v>3417</v>
@@ -58308,7 +58246,7 @@
         <v>1088</v>
       </c>
       <c r="H1680" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="I1680" s="10" t="s">
         <v>3419</v>
@@ -58337,7 +58275,7 @@
         <v>1088</v>
       </c>
       <c r="H1681" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="I1681" s="10" t="s">
         <v>3421</v>
@@ -58366,7 +58304,7 @@
         <v>1088</v>
       </c>
       <c r="H1682" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="I1682" s="10" t="s">
         <v>3423</v>

--- a/다과_구매목록.xlsx
+++ b/다과_구매목록.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6457" uniqueCount="4015">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6461" uniqueCount="4015">
   <si>
     <t>회사 다과 구매 목록 (마켓컬리)</t>
   </si>
@@ -171,6 +171,12 @@
     <t>https://www.kurly.com/goods/5095165</t>
   </si>
   <si>
+    <t>[오리온] 고래밥 20g x 10입</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5081412</t>
+  </si>
+  <si>
     <t>[해태] 구운감자 27g x 5입</t>
   </si>
   <si>
@@ -1126,12 +1132,6 @@
   </si>
   <si>
     <t>https://www.kurly.com/goods/5118059</t>
-  </si>
-  <si>
-    <t>[오리온] 고래밥 20g x 10입</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5081412</t>
   </si>
   <si>
     <t>[오리온] 다이제 샌드 우도땅콩 392g</t>
@@ -12467,7 +12467,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J47"/>
+  <dimension ref="A1:J48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.7109375" customWidth="1"/>
@@ -12498,15 +12498,15 @@
         <v>2</v>
       </c>
       <c r="D2" s="3">
-        <f>SUM(F5:F47)</f>
-        <v>497904</v>
+        <f>SUM(F5:F48)</f>
+        <v>498284</v>
       </c>
       <c r="E2" t="s">
         <v>3</v>
       </c>
       <c r="F2" s="3">
         <f>B2-D2</f>
-        <v>2096</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -12857,11 +12857,11 @@
         <v>4080</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F15" s="2">
         <f>D15*E15</f>
-        <v>8160</v>
+        <v>4080</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -12887,11 +12887,11 @@
         <v>4080</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16" s="2">
         <f>D16*E16</f>
-        <v>8160</v>
+        <v>4080</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -12947,11 +12947,11 @@
         <v>2480</v>
       </c>
       <c r="E18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F18" s="2">
         <f>D18*E18</f>
-        <v>7440</v>
+        <v>2480</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -13034,17 +13034,17 @@
         <v>50</v>
       </c>
       <c r="D21" s="2">
-        <v>3780</v>
+        <v>4500</v>
       </c>
       <c r="E21">
         <v>3</v>
       </c>
       <c r="F21" s="2">
         <f>D21*E21</f>
-        <v>11340</v>
+        <v>13500</v>
       </c>
       <c r="G21">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H21">
         <v>999</v>
@@ -13064,17 +13064,17 @@
         <v>52</v>
       </c>
       <c r="D22" s="2">
-        <v>3580</v>
+        <v>3780</v>
       </c>
       <c r="E22">
         <v>3</v>
       </c>
       <c r="F22" s="2">
         <f>D22*E22</f>
-        <v>10740</v>
+        <v>11340</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H22">
         <v>999</v>
@@ -13088,29 +13088,29 @@
         <v>19</v>
       </c>
       <c r="B23" t="s">
+        <v>45</v>
+      </c>
+      <c r="C23" t="s">
         <v>54</v>
       </c>
-      <c r="C23" t="s">
-        <v>55</v>
-      </c>
       <c r="D23" s="2">
-        <v>3980</v>
+        <v>3580</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F23" s="2">
         <f>D23*E23</f>
-        <v>7960</v>
+        <v>10740</v>
       </c>
       <c r="G23">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="H23">
-        <v>9999</v>
+        <v>999</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -13118,23 +13118,23 @@
         <v>19</v>
       </c>
       <c r="B24" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C24" t="s">
         <v>57</v>
       </c>
       <c r="D24" s="2">
-        <v>5120</v>
+        <v>3980</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F24" s="2">
         <f>D24*E24</f>
-        <v>5120</v>
+        <v>7960</v>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="H24">
         <v>9999</v>
@@ -13148,29 +13148,29 @@
         <v>19</v>
       </c>
       <c r="B25" t="s">
+        <v>56</v>
+      </c>
+      <c r="C25" t="s">
         <v>59</v>
       </c>
-      <c r="C25" t="s">
-        <v>60</v>
-      </c>
       <c r="D25" s="2">
-        <v>2980</v>
+        <v>5120</v>
       </c>
       <c r="E25">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F25" s="2">
         <f>D25*E25</f>
-        <v>17880</v>
+        <v>5120</v>
       </c>
       <c r="G25">
         <v>0</v>
       </c>
       <c r="H25">
-        <v>999</v>
+        <v>9999</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -13178,26 +13178,26 @@
         <v>19</v>
       </c>
       <c r="B26" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C26" t="s">
         <v>62</v>
       </c>
       <c r="D26" s="2">
-        <v>2180</v>
+        <v>2980</v>
       </c>
       <c r="E26">
         <v>6</v>
       </c>
       <c r="F26" s="2">
         <f>D26*E26</f>
-        <v>13080</v>
+        <v>17880</v>
       </c>
       <c r="G26">
         <v>0</v>
       </c>
       <c r="H26">
-        <v>835</v>
+        <v>999</v>
       </c>
       <c r="I26" s="8" t="s">
         <v>63</v>
@@ -13208,26 +13208,26 @@
         <v>19</v>
       </c>
       <c r="B27" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C27" t="s">
         <v>64</v>
       </c>
       <c r="D27" s="2">
-        <v>2980</v>
+        <v>2180</v>
       </c>
       <c r="E27">
         <v>6</v>
       </c>
       <c r="F27" s="2">
         <f>D27*E27</f>
-        <v>17880</v>
+        <v>13080</v>
       </c>
       <c r="G27">
         <v>0</v>
       </c>
       <c r="H27">
-        <v>692</v>
+        <v>835</v>
       </c>
       <c r="I27" s="8" t="s">
         <v>65</v>
@@ -13238,26 +13238,26 @@
         <v>19</v>
       </c>
       <c r="B28" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C28" t="s">
         <v>66</v>
       </c>
       <c r="D28" s="2">
-        <v>2500</v>
+        <v>2980</v>
       </c>
       <c r="E28">
         <v>6</v>
       </c>
       <c r="F28" s="2">
         <f>D28*E28</f>
-        <v>15000</v>
+        <v>17880</v>
       </c>
       <c r="G28">
         <v>0</v>
       </c>
       <c r="H28">
-        <v>962</v>
+        <v>692</v>
       </c>
       <c r="I28" s="8" t="s">
         <v>67</v>
@@ -13268,7 +13268,7 @@
         <v>19</v>
       </c>
       <c r="B29" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C29" t="s">
         <v>68</v>
@@ -13287,7 +13287,7 @@
         <v>0</v>
       </c>
       <c r="H29">
-        <v>999</v>
+        <v>962</v>
       </c>
       <c r="I29" s="8" t="s">
         <v>69</v>
@@ -13298,26 +13298,26 @@
         <v>19</v>
       </c>
       <c r="B30" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C30" t="s">
         <v>70</v>
       </c>
       <c r="D30" s="2">
-        <v>2180</v>
+        <v>2500</v>
       </c>
       <c r="E30">
         <v>6</v>
       </c>
       <c r="F30" s="2">
         <f>D30*E30</f>
-        <v>13080</v>
+        <v>15000</v>
       </c>
       <c r="G30">
         <v>0</v>
       </c>
       <c r="H30">
-        <v>741</v>
+        <v>999</v>
       </c>
       <c r="I30" s="8" t="s">
         <v>71</v>
@@ -13328,29 +13328,29 @@
         <v>19</v>
       </c>
       <c r="B31" t="s">
+        <v>61</v>
+      </c>
+      <c r="C31" t="s">
         <v>72</v>
       </c>
-      <c r="C31" t="s">
-        <v>73</v>
-      </c>
       <c r="D31" s="2">
-        <v>4480</v>
+        <v>2180</v>
       </c>
       <c r="E31">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F31" s="2">
         <f>D31*E31</f>
-        <v>8960</v>
+        <v>13080</v>
       </c>
       <c r="G31">
         <v>0</v>
       </c>
       <c r="H31">
-        <v>999</v>
+        <v>741</v>
       </c>
       <c r="I31" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -13358,20 +13358,20 @@
         <v>19</v>
       </c>
       <c r="B32" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C32" t="s">
         <v>75</v>
       </c>
       <c r="D32" s="2">
-        <v>4380</v>
+        <v>4480</v>
       </c>
       <c r="E32">
         <v>2</v>
       </c>
       <c r="F32" s="2">
         <f>D32*E32</f>
-        <v>8760</v>
+        <v>8960</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -13388,26 +13388,26 @@
         <v>19</v>
       </c>
       <c r="B33" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C33" t="s">
         <v>77</v>
       </c>
       <c r="D33" s="2">
-        <v>5440</v>
+        <v>4380</v>
       </c>
       <c r="E33">
         <v>2</v>
       </c>
       <c r="F33" s="2">
         <f>D33*E33</f>
-        <v>10880</v>
+        <v>8760</v>
       </c>
       <c r="G33">
         <v>0</v>
       </c>
       <c r="H33">
-        <v>956</v>
+        <v>999</v>
       </c>
       <c r="I33" s="8" t="s">
         <v>78</v>
@@ -13418,26 +13418,26 @@
         <v>19</v>
       </c>
       <c r="B34" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C34" t="s">
         <v>79</v>
       </c>
       <c r="D34" s="2">
-        <v>3690</v>
+        <v>5440</v>
       </c>
       <c r="E34">
         <v>2</v>
       </c>
       <c r="F34" s="2">
         <f>D34*E34</f>
-        <v>7380</v>
+        <v>10880</v>
       </c>
       <c r="G34">
         <v>0</v>
       </c>
       <c r="H34">
-        <v>9999</v>
+        <v>956</v>
       </c>
       <c r="I34" s="8" t="s">
         <v>80</v>
@@ -13448,26 +13448,26 @@
         <v>19</v>
       </c>
       <c r="B35" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C35" t="s">
         <v>81</v>
       </c>
       <c r="D35" s="2">
-        <v>4780</v>
+        <v>3690</v>
       </c>
       <c r="E35">
         <v>2</v>
       </c>
       <c r="F35" s="2">
         <f>D35*E35</f>
-        <v>9560</v>
+        <v>7380</v>
       </c>
       <c r="G35">
         <v>0</v>
       </c>
       <c r="H35">
-        <v>999</v>
+        <v>9999</v>
       </c>
       <c r="I35" s="8" t="s">
         <v>82</v>
@@ -13478,20 +13478,20 @@
         <v>19</v>
       </c>
       <c r="B36" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C36" t="s">
         <v>83</v>
       </c>
       <c r="D36" s="2">
-        <v>4200</v>
+        <v>4780</v>
       </c>
       <c r="E36">
         <v>2</v>
       </c>
       <c r="F36" s="2">
         <f>D36*E36</f>
-        <v>8400</v>
+        <v>9560</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -13508,20 +13508,20 @@
         <v>19</v>
       </c>
       <c r="B37" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C37" t="s">
         <v>85</v>
       </c>
       <c r="D37" s="2">
-        <v>5280</v>
+        <v>4200</v>
       </c>
       <c r="E37">
         <v>2</v>
       </c>
       <c r="F37" s="2">
         <f>D37*E37</f>
-        <v>10560</v>
+        <v>8400</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -13538,26 +13538,26 @@
         <v>19</v>
       </c>
       <c r="B38" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C38" t="s">
         <v>87</v>
       </c>
       <c r="D38" s="2">
-        <v>4780</v>
+        <v>5280</v>
       </c>
       <c r="E38">
         <v>2</v>
       </c>
       <c r="F38" s="2">
         <f>D38*E38</f>
-        <v>9560</v>
+        <v>10560</v>
       </c>
       <c r="G38">
         <v>0</v>
       </c>
       <c r="H38">
-        <v>477</v>
+        <v>999</v>
       </c>
       <c r="I38" s="8" t="s">
         <v>88</v>
@@ -13568,26 +13568,26 @@
         <v>19</v>
       </c>
       <c r="B39" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C39" t="s">
         <v>89</v>
       </c>
       <c r="D39" s="2">
-        <v>3980</v>
+        <v>4780</v>
       </c>
       <c r="E39">
         <v>2</v>
       </c>
       <c r="F39" s="2">
         <f>D39*E39</f>
-        <v>7960</v>
+        <v>9560</v>
       </c>
       <c r="G39">
         <v>0</v>
       </c>
       <c r="H39">
-        <v>314</v>
+        <v>477</v>
       </c>
       <c r="I39" s="8" t="s">
         <v>90</v>
@@ -13598,26 +13598,26 @@
         <v>19</v>
       </c>
       <c r="B40" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C40" t="s">
         <v>91</v>
       </c>
       <c r="D40" s="2">
-        <v>3200</v>
+        <v>3980</v>
       </c>
       <c r="E40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F40" s="2">
         <f>D40*E40</f>
-        <v>9600</v>
+        <v>7960</v>
       </c>
       <c r="G40">
         <v>0</v>
       </c>
       <c r="H40">
-        <v>215</v>
+        <v>314</v>
       </c>
       <c r="I40" s="8" t="s">
         <v>92</v>
@@ -13628,29 +13628,29 @@
         <v>19</v>
       </c>
       <c r="B41" t="s">
+        <v>74</v>
+      </c>
+      <c r="C41" t="s">
         <v>93</v>
       </c>
-      <c r="C41" t="s">
-        <v>94</v>
-      </c>
       <c r="D41" s="2">
-        <v>4320</v>
+        <v>3200</v>
       </c>
       <c r="E41">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F41" s="2">
         <f>D41*E41</f>
-        <v>8640</v>
+        <v>9600</v>
       </c>
       <c r="G41">
         <v>0</v>
       </c>
       <c r="H41">
-        <v>9999</v>
+        <v>215</v>
       </c>
       <c r="I41" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="42" spans="1:9">
@@ -13658,7 +13658,7 @@
         <v>19</v>
       </c>
       <c r="B42" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C42" t="s">
         <v>96</v>
@@ -13677,7 +13677,7 @@
         <v>0</v>
       </c>
       <c r="H42">
-        <v>745</v>
+        <v>9999</v>
       </c>
       <c r="I42" s="8" t="s">
         <v>97</v>
@@ -13688,26 +13688,26 @@
         <v>19</v>
       </c>
       <c r="B43" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C43" t="s">
         <v>98</v>
       </c>
       <c r="D43" s="2">
-        <v>4800</v>
+        <v>4320</v>
       </c>
       <c r="E43">
         <v>2</v>
       </c>
       <c r="F43" s="2">
         <f>D43*E43</f>
-        <v>9600</v>
+        <v>8640</v>
       </c>
       <c r="G43">
         <v>0</v>
       </c>
       <c r="H43">
-        <v>950</v>
+        <v>745</v>
       </c>
       <c r="I43" s="8" t="s">
         <v>99</v>
@@ -13718,26 +13718,26 @@
         <v>19</v>
       </c>
       <c r="B44" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C44" t="s">
         <v>100</v>
       </c>
       <c r="D44" s="2">
-        <v>5600</v>
+        <v>4800</v>
       </c>
       <c r="E44">
         <v>2</v>
       </c>
       <c r="F44" s="2">
         <f>D44*E44</f>
-        <v>11200</v>
+        <v>9600</v>
       </c>
       <c r="G44">
         <v>0</v>
       </c>
       <c r="H44">
-        <v>999</v>
+        <v>950</v>
       </c>
       <c r="I44" s="8" t="s">
         <v>101</v>
@@ -13748,7 +13748,7 @@
         <v>19</v>
       </c>
       <c r="B45" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C45" t="s">
         <v>102</v>
@@ -13778,26 +13778,26 @@
         <v>19</v>
       </c>
       <c r="B46" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C46" t="s">
         <v>104</v>
       </c>
       <c r="D46" s="2">
-        <v>2506</v>
+        <v>5600</v>
       </c>
       <c r="E46">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F46" s="2">
         <f>D46*E46</f>
-        <v>10024</v>
+        <v>11200</v>
       </c>
       <c r="G46">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H46">
-        <v>187</v>
+        <v>999</v>
       </c>
       <c r="I46" s="8" t="s">
         <v>105</v>
@@ -13808,29 +13808,59 @@
         <v>19</v>
       </c>
       <c r="B47" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C47" t="s">
         <v>106</v>
       </c>
       <c r="D47" s="2">
-        <v>5280</v>
+        <v>2506</v>
       </c>
       <c r="E47">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F47" s="2">
         <f>D47*E47</f>
-        <v>10560</v>
+        <v>10024</v>
       </c>
       <c r="G47">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H47">
-        <v>999</v>
+        <v>187</v>
       </c>
       <c r="I47" s="8" t="s">
         <v>107</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
+      <c r="A48" t="s">
+        <v>19</v>
+      </c>
+      <c r="B48" t="s">
+        <v>95</v>
+      </c>
+      <c r="C48" t="s">
+        <v>108</v>
+      </c>
+      <c r="D48" s="2">
+        <v>5280</v>
+      </c>
+      <c r="E48">
+        <v>2</v>
+      </c>
+      <c r="F48" s="2">
+        <f>D48*E48</f>
+        <v>10560</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>999</v>
+      </c>
+      <c r="I48" s="8" t="s">
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -13878,6 +13908,7 @@
     <hyperlink ref="I45" r:id="rId41"/>
     <hyperlink ref="I46" r:id="rId42"/>
     <hyperlink ref="I47" r:id="rId43"/>
+    <hyperlink ref="I48" r:id="rId44"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -13899,13 +13930,13 @@
         <v>5</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -13913,67 +13944,67 @@
         <v>14</v>
       </c>
       <c r="B2">
-        <f>COUNTIF(구매목록!B5:B47,A2)</f>
+        <f>COUNTIF(구매목록!B5:B48,A2)</f>
         <v>2</v>
       </c>
       <c r="C2" s="2">
-        <f>SUMIF(구매목록!B5:B47,A2,구매목록!F5:F47)</f>
+        <f>SUMIF(구매목록!B5:B48,A2,구매목록!F5:F48)</f>
         <v>104700</v>
       </c>
       <c r="D2" s="9">
         <f>C2/SUM($C$2:$C$8)</f>
-        <v>0.21028150004820206</v>
+        <v>0.21012113573785232</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B3">
-        <f>COUNTIF(구매목록!B5:B47,A3)</f>
+        <f>COUNTIF(구매목록!B5:B48,A3)</f>
         <v>7</v>
       </c>
       <c r="C3" s="2">
-        <f>SUMIF(구매목록!B5:B47,A3,구매목록!F5:F47)</f>
+        <f>SUMIF(구매목록!B5:B48,A3,구매목록!F5:F48)</f>
         <v>69864</v>
       </c>
       <c r="D3" s="9">
         <f>C3/SUM($C$2:$C$8)</f>
-        <v>0.14031620553359683</v>
+        <v>0.1402091979674242</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B4">
-        <f>COUNTIF(구매목록!B5:B47,A4)</f>
+        <f>COUNTIF(구매목록!B5:B48,A4)</f>
         <v>10</v>
       </c>
       <c r="C4" s="2">
-        <f>SUMIF(구매목록!B5:B47,A4,구매목록!F5:F47)</f>
+        <f>SUMIF(구매목록!B5:B48,A4,구매목록!F5:F48)</f>
         <v>91620</v>
       </c>
       <c r="D4" s="9">
         <f>C4/SUM($C$2:$C$8)</f>
-        <v>0.1840113756868794</v>
+        <v>0.18387104542790858</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B5">
-        <f>COUNTIF(구매목록!B5:B47,A5)</f>
+        <f>COUNTIF(구매목록!B5:B48,A5)</f>
         <v>6</v>
       </c>
       <c r="C5" s="2">
-        <f>SUMIF(구매목록!B5:B47,A5,구매목록!F5:F47)</f>
+        <f>SUMIF(구매목록!B5:B48,A5,구매목록!F5:F48)</f>
         <v>91920</v>
       </c>
       <c r="D5" s="9">
         <f>C5/SUM($C$2:$C$8)</f>
-        <v>0.18461390147498313</v>
+        <v>0.18447311171942105</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -13981,16 +14012,16 @@
         <v>20</v>
       </c>
       <c r="B6">
-        <f>COUNTIF(구매목록!B5:B47,A6)</f>
+        <f>COUNTIF(구매목록!B5:B48,A6)</f>
         <v>12</v>
       </c>
       <c r="C6" s="2">
-        <f>SUMIF(구매목록!B5:B47,A6,구매목록!F5:F47)</f>
-        <v>83160</v>
+        <f>SUMIF(구매목록!B5:B48,A6,구매목록!F5:F48)</f>
+        <v>70040</v>
       </c>
       <c r="D6" s="9">
         <f>C6/SUM($C$2:$C$8)</f>
-        <v>0.1670201484623542</v>
+        <v>0.14056241019177818</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -13998,33 +14029,33 @@
         <v>45</v>
       </c>
       <c r="B7">
-        <f>COUNTIF(구매목록!B5:B47,A7)</f>
-        <v>4</v>
+        <f>COUNTIF(구매목록!B5:B48,A7)</f>
+        <v>5</v>
       </c>
       <c r="C7" s="2">
-        <f>SUMIF(구매목록!B5:B47,A7,구매목록!F5:F47)</f>
-        <v>43560</v>
+        <f>SUMIF(구매목록!B5:B48,A7,구매목록!F5:F48)</f>
+        <v>57060</v>
       </c>
       <c r="D7" s="9">
         <f>C7/SUM($C$2:$C$8)</f>
-        <v>0.08748674443266172</v>
+        <v>0.11451300864567195</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B8">
-        <f>COUNTIF(구매목록!B5:B47,A8)</f>
+        <f>COUNTIF(구매목록!B5:B48,A8)</f>
         <v>2</v>
       </c>
       <c r="C8" s="2">
-        <f>SUMIF(구매목록!B5:B47,A8,구매목록!F5:F47)</f>
+        <f>SUMIF(구매목록!B5:B48,A8,구매목록!F5:F48)</f>
         <v>13080</v>
       </c>
       <c r="D8" s="9">
         <f>C8/SUM($C$2:$C$8)</f>
-        <v>0.026270124361322665</v>
+        <v>0.026250090309943727</v>
       </c>
     </row>
   </sheetData>
@@ -14048,28 +14079,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>11</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I1" s="4" t="s">
         <v>12</v>
@@ -14080,7 +14111,7 @@
         <v>1002110052</v>
       </c>
       <c r="B2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C2">
         <v>8900</v>
@@ -14095,10 +14126,10 @@
         <v>60</v>
       </c>
       <c r="H2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I2" s="10" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -14106,7 +14137,7 @@
         <v>1000747182</v>
       </c>
       <c r="B3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C3">
         <v>3680</v>
@@ -14121,10 +14152,10 @@
         <v>999</v>
       </c>
       <c r="H3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -14132,7 +14163,7 @@
         <v>1000343575</v>
       </c>
       <c r="B4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C4">
         <v>3580</v>
@@ -14147,10 +14178,10 @@
         <v>999</v>
       </c>
       <c r="H4" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -14158,7 +14189,7 @@
         <v>1000862247</v>
       </c>
       <c r="B5" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C5">
         <v>13400</v>
@@ -14173,10 +14204,10 @@
         <v>875</v>
       </c>
       <c r="H5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -14184,7 +14215,7 @@
         <v>1000178183</v>
       </c>
       <c r="B6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C6">
         <v>4500</v>
@@ -14199,10 +14230,10 @@
         <v>999</v>
       </c>
       <c r="H6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -14210,7 +14241,7 @@
         <v>5031072</v>
       </c>
       <c r="B7" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C7">
         <v>5980</v>
@@ -14225,10 +14256,10 @@
         <v>999</v>
       </c>
       <c r="H7" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -14236,7 +14267,7 @@
         <v>1000875821</v>
       </c>
       <c r="B8" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C8">
         <v>1690</v>
@@ -14251,10 +14282,10 @@
         <v>999</v>
       </c>
       <c r="H8" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -14262,7 +14293,7 @@
         <v>1000651310</v>
       </c>
       <c r="B9" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C9">
         <v>7490</v>
@@ -14277,10 +14308,10 @@
         <v>793</v>
       </c>
       <c r="H9" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -14288,7 +14319,7 @@
         <v>1000321598</v>
       </c>
       <c r="B10" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C10">
         <v>1790</v>
@@ -14303,10 +14334,10 @@
         <v>999</v>
       </c>
       <c r="H10" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -14314,7 +14345,7 @@
         <v>5077465</v>
       </c>
       <c r="B11" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C11">
         <v>3980</v>
@@ -14329,10 +14360,10 @@
         <v>999</v>
       </c>
       <c r="H11" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -14340,7 +14371,7 @@
         <v>5079319</v>
       </c>
       <c r="B12" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C12">
         <v>3580</v>
@@ -14355,10 +14386,10 @@
         <v>999</v>
       </c>
       <c r="H12" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -14381,7 +14412,7 @@
         <v>999</v>
       </c>
       <c r="H13" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I13" s="10" t="s">
         <v>16</v>
@@ -14392,7 +14423,7 @@
         <v>5077461</v>
       </c>
       <c r="B14" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C14">
         <v>4640</v>
@@ -14407,10 +14438,10 @@
         <v>999</v>
       </c>
       <c r="H14" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -14418,7 +14449,7 @@
         <v>1000975389</v>
       </c>
       <c r="B15" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C15">
         <v>2990</v>
@@ -14433,10 +14464,10 @@
         <v>999</v>
       </c>
       <c r="H15" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -14444,7 +14475,7 @@
         <v>5079340</v>
       </c>
       <c r="B16" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C16">
         <v>5280</v>
@@ -14459,10 +14490,10 @@
         <v>999</v>
       </c>
       <c r="H16" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -14470,7 +14501,7 @@
         <v>1000198192</v>
       </c>
       <c r="B17" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C17">
         <v>4540</v>
@@ -14485,10 +14516,10 @@
         <v>9999</v>
       </c>
       <c r="H17" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -14496,7 +14527,7 @@
         <v>5151421</v>
       </c>
       <c r="B18" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C18">
         <v>5940</v>
@@ -14511,10 +14542,10 @@
         <v>999</v>
       </c>
       <c r="H18" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -14522,7 +14553,7 @@
         <v>1001272797</v>
       </c>
       <c r="B19" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C19">
         <v>2980</v>
@@ -14537,10 +14568,10 @@
         <v>999</v>
       </c>
       <c r="H19" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -14548,7 +14579,7 @@
         <v>1001029494</v>
       </c>
       <c r="B20" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C20">
         <v>2280</v>
@@ -14563,10 +14594,10 @@
         <v>597</v>
       </c>
       <c r="H20" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -14574,7 +14605,7 @@
         <v>5030780</v>
       </c>
       <c r="B21" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C21">
         <v>5800</v>
@@ -14589,10 +14620,10 @@
         <v>9999</v>
       </c>
       <c r="H21" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -14600,7 +14631,7 @@
         <v>1000339529</v>
       </c>
       <c r="B22" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C22">
         <v>3980</v>
@@ -14615,10 +14646,10 @@
         <v>557</v>
       </c>
       <c r="H22" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -14626,7 +14657,7 @@
         <v>5036524</v>
       </c>
       <c r="B23" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C23">
         <v>2520</v>
@@ -14641,10 +14672,10 @@
         <v>9999</v>
       </c>
       <c r="H23" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -14652,7 +14683,7 @@
         <v>1000356676</v>
       </c>
       <c r="B24" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C24">
         <v>3800</v>
@@ -14667,10 +14698,10 @@
         <v>9999</v>
       </c>
       <c r="H24" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -14678,7 +14709,7 @@
         <v>1000963099</v>
       </c>
       <c r="B25" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C25">
         <v>4780</v>
@@ -14693,10 +14724,10 @@
         <v>999</v>
       </c>
       <c r="H25" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -14704,7 +14735,7 @@
         <v>5088236</v>
       </c>
       <c r="B26" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C26">
         <v>8980</v>
@@ -14719,10 +14750,10 @@
         <v>999</v>
       </c>
       <c r="H26" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -14730,7 +14761,7 @@
         <v>1000617577</v>
       </c>
       <c r="B27" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C27">
         <v>1360</v>
@@ -14745,10 +14776,10 @@
         <v>9999</v>
       </c>
       <c r="H27" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -14756,7 +14787,7 @@
         <v>1000455773</v>
       </c>
       <c r="B28" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C28">
         <v>4500</v>
@@ -14771,10 +14802,10 @@
         <v>434</v>
       </c>
       <c r="H28" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -14782,7 +14813,7 @@
         <v>1000137075</v>
       </c>
       <c r="B29" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C29">
         <v>4480</v>
@@ -14797,10 +14828,10 @@
         <v>999</v>
       </c>
       <c r="H29" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -14808,7 +14839,7 @@
         <v>1002134596</v>
       </c>
       <c r="B30" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C30">
         <v>5980</v>
@@ -14823,10 +14854,10 @@
         <v>81</v>
       </c>
       <c r="H30" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -14834,7 +14865,7 @@
         <v>1001447521</v>
       </c>
       <c r="B31" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C31">
         <v>1440</v>
@@ -14849,10 +14880,10 @@
         <v>258</v>
       </c>
       <c r="H31" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I31" s="10" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -14860,7 +14891,7 @@
         <v>1001421531</v>
       </c>
       <c r="B32" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C32">
         <v>4980</v>
@@ -14875,10 +14906,10 @@
         <v>602</v>
       </c>
       <c r="H32" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -14886,7 +14917,7 @@
         <v>1000269917</v>
       </c>
       <c r="B33" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C33">
         <v>12800</v>
@@ -14901,10 +14932,10 @@
         <v>988</v>
       </c>
       <c r="H33" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -14912,7 +14943,7 @@
         <v>1001592465</v>
       </c>
       <c r="B34" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C34">
         <v>3880</v>
@@ -14927,10 +14958,10 @@
         <v>520</v>
       </c>
       <c r="H34" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -14938,7 +14969,7 @@
         <v>5054491</v>
       </c>
       <c r="B35" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C35">
         <v>6590</v>
@@ -14953,10 +14984,10 @@
         <v>999</v>
       </c>
       <c r="H35" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -14964,7 +14995,7 @@
         <v>1001919935</v>
       </c>
       <c r="B36" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C36">
         <v>3800</v>
@@ -14979,10 +15010,10 @@
         <v>313</v>
       </c>
       <c r="H36" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I36" s="10" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="37" spans="1:9">
@@ -14990,7 +15021,7 @@
         <v>5062899</v>
       </c>
       <c r="B37" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C37">
         <v>4580</v>
@@ -15005,10 +15036,10 @@
         <v>999</v>
       </c>
       <c r="H37" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I37" s="10" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -15016,7 +15047,7 @@
         <v>1000875710</v>
       </c>
       <c r="B38" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C38">
         <v>4580</v>
@@ -15031,10 +15062,10 @@
         <v>999</v>
       </c>
       <c r="H38" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I38" s="10" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -15042,7 +15073,7 @@
         <v>5006818</v>
       </c>
       <c r="B39" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C39">
         <v>8500</v>
@@ -15057,10 +15088,10 @@
         <v>999</v>
       </c>
       <c r="H39" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I39" s="10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -15068,7 +15099,7 @@
         <v>1000582944</v>
       </c>
       <c r="B40" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C40">
         <v>2780</v>
@@ -15083,10 +15114,10 @@
         <v>594</v>
       </c>
       <c r="H40" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I40" s="10" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -15094,7 +15125,7 @@
         <v>1000206111</v>
       </c>
       <c r="B41" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C41">
         <v>5900</v>
@@ -15109,10 +15140,10 @@
         <v>9999</v>
       </c>
       <c r="H41" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I41" s="10" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="42" spans="1:9">
@@ -15120,7 +15151,7 @@
         <v>1000643389</v>
       </c>
       <c r="B42" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C42">
         <v>5480</v>
@@ -15135,10 +15166,10 @@
         <v>444</v>
       </c>
       <c r="H42" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I42" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="43" spans="1:9">
@@ -15146,7 +15177,7 @@
         <v>1000439362</v>
       </c>
       <c r="B43" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C43">
         <v>2250</v>
@@ -15161,10 +15192,10 @@
         <v>999</v>
       </c>
       <c r="H43" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I43" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="44" spans="1:9">
@@ -15172,7 +15203,7 @@
         <v>1000166566</v>
       </c>
       <c r="B44" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C44">
         <v>12000</v>
@@ -15187,10 +15218,10 @@
         <v>9999</v>
       </c>
       <c r="H44" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I44" s="10" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="45" spans="1:9">
@@ -15198,7 +15229,7 @@
         <v>1000526145</v>
       </c>
       <c r="B45" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C45">
         <v>8900</v>
@@ -15213,10 +15244,10 @@
         <v>999</v>
       </c>
       <c r="H45" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I45" s="10" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="46" spans="1:9">
@@ -15224,7 +15255,7 @@
         <v>1000789439</v>
       </c>
       <c r="B46" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C46">
         <v>3590</v>
@@ -15239,10 +15270,10 @@
         <v>324</v>
       </c>
       <c r="H46" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I46" s="10" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="47" spans="1:9">
@@ -15250,7 +15281,7 @@
         <v>1000356687</v>
       </c>
       <c r="B47" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C47">
         <v>4400</v>
@@ -15265,10 +15296,10 @@
         <v>999</v>
       </c>
       <c r="H47" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I47" s="10" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="48" spans="1:9">
@@ -15276,7 +15307,7 @@
         <v>5153242</v>
       </c>
       <c r="B48" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C48">
         <v>9980</v>
@@ -15291,10 +15322,10 @@
         <v>503</v>
       </c>
       <c r="H48" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I48" s="10" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="49" spans="1:9">
@@ -15302,7 +15333,7 @@
         <v>1000033235</v>
       </c>
       <c r="B49" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C49">
         <v>2600</v>
@@ -15317,10 +15348,10 @@
         <v>9999</v>
       </c>
       <c r="H49" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I49" s="10" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -15328,7 +15359,7 @@
         <v>1001570087</v>
       </c>
       <c r="B50" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C50">
         <v>6080</v>
@@ -15343,10 +15374,10 @@
         <v>999</v>
       </c>
       <c r="H50" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I50" s="10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -15369,7 +15400,7 @@
         <v>9999</v>
       </c>
       <c r="H51" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I51" s="10" t="s">
         <v>22</v>
@@ -15380,7 +15411,7 @@
         <v>1000942359</v>
       </c>
       <c r="B52" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C52">
         <v>1440</v>
@@ -15395,10 +15426,10 @@
         <v>999</v>
       </c>
       <c r="H52" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I52" s="10" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="53" spans="1:9">
@@ -15406,7 +15437,7 @@
         <v>1001397540</v>
       </c>
       <c r="B53" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C53">
         <v>1080</v>
@@ -15421,10 +15452,10 @@
         <v>928</v>
       </c>
       <c r="H53" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I53" s="10" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="54" spans="1:9">
@@ -15432,7 +15463,7 @@
         <v>1000927112</v>
       </c>
       <c r="B54" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C54">
         <v>3325</v>
@@ -15447,10 +15478,10 @@
         <v>999</v>
       </c>
       <c r="H54" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I54" s="10" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="55" spans="1:9">
@@ -15458,7 +15489,7 @@
         <v>5103484</v>
       </c>
       <c r="B55" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C55">
         <v>11980</v>
@@ -15473,10 +15504,10 @@
         <v>999</v>
       </c>
       <c r="H55" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I55" s="10" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="56" spans="1:9">
@@ -15484,7 +15515,7 @@
         <v>1000605988</v>
       </c>
       <c r="B56" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C56">
         <v>4180</v>
@@ -15499,10 +15530,10 @@
         <v>723</v>
       </c>
       <c r="H56" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I56" s="10" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="57" spans="1:9">
@@ -15510,7 +15541,7 @@
         <v>5060050</v>
       </c>
       <c r="B57" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C57">
         <v>5980</v>
@@ -15525,10 +15556,10 @@
         <v>9999</v>
       </c>
       <c r="H57" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I57" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="58" spans="1:9">
@@ -15536,7 +15567,7 @@
         <v>1002324203</v>
       </c>
       <c r="B58" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C58">
         <v>6980</v>
@@ -15551,10 +15582,10 @@
         <v>22</v>
       </c>
       <c r="H58" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I58" s="10" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="59" spans="1:9">
@@ -15577,7 +15608,7 @@
         <v>999</v>
       </c>
       <c r="H59" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I59" s="10" t="s">
         <v>49</v>
@@ -15588,7 +15619,7 @@
         <v>1000178191</v>
       </c>
       <c r="B60" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C60">
         <v>4150</v>
@@ -15603,10 +15634,10 @@
         <v>9999</v>
       </c>
       <c r="H60" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I60" s="10" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="61" spans="1:9">
@@ -15614,7 +15645,7 @@
         <v>1000914382</v>
       </c>
       <c r="B61" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C61">
         <v>15500</v>
@@ -15629,10 +15660,10 @@
         <v>658</v>
       </c>
       <c r="H61" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I61" s="10" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="62" spans="1:9">
@@ -15640,7 +15671,7 @@
         <v>1002014581</v>
       </c>
       <c r="B62" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C62">
         <v>4950</v>
@@ -15655,10 +15686,10 @@
         <v>999</v>
       </c>
       <c r="H62" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I62" s="10" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="63" spans="1:9">
@@ -15666,7 +15697,7 @@
         <v>5052362</v>
       </c>
       <c r="B63" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C63">
         <v>13900</v>
@@ -15681,10 +15712,10 @@
         <v>999</v>
       </c>
       <c r="H63" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I63" s="10" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="64" spans="1:9">
@@ -15692,7 +15723,7 @@
         <v>5121160</v>
       </c>
       <c r="B64" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C64">
         <v>4380</v>
@@ -15707,10 +15738,10 @@
         <v>999</v>
       </c>
       <c r="H64" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I64" s="10" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="65" spans="1:9">
@@ -15718,7 +15749,7 @@
         <v>1000958549</v>
       </c>
       <c r="B65" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C65">
         <v>3380</v>
@@ -15733,10 +15764,10 @@
         <v>711</v>
       </c>
       <c r="H65" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I65" s="10" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="66" spans="1:9">
@@ -15744,7 +15775,7 @@
         <v>1002010936</v>
       </c>
       <c r="B66" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C66">
         <v>2800</v>
@@ -15759,10 +15790,10 @@
         <v>416</v>
       </c>
       <c r="H66" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I66" s="10" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="67" spans="1:9">
@@ -15770,7 +15801,7 @@
         <v>1000242960</v>
       </c>
       <c r="B67" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C67">
         <v>7000</v>
@@ -15785,10 +15816,10 @@
         <v>999</v>
       </c>
       <c r="H67" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I67" s="10" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="68" spans="1:9">
@@ -15796,7 +15827,7 @@
         <v>1002482468</v>
       </c>
       <c r="B68" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C68">
         <v>2130</v>
@@ -15811,10 +15842,10 @@
         <v>492</v>
       </c>
       <c r="H68" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I68" s="10" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="69" spans="1:9">
@@ -15822,7 +15853,7 @@
         <v>5058855</v>
       </c>
       <c r="B69" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C69">
         <v>8500</v>
@@ -15837,10 +15868,10 @@
         <v>9999</v>
       </c>
       <c r="H69" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I69" s="10" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="70" spans="1:9">
@@ -15848,7 +15879,7 @@
         <v>1000783621</v>
       </c>
       <c r="B70" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C70">
         <v>10960</v>
@@ -15863,10 +15894,10 @@
         <v>175</v>
       </c>
       <c r="H70" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I70" s="10" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="71" spans="1:9">
@@ -15874,7 +15905,7 @@
         <v>1000525224</v>
       </c>
       <c r="B71" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C71">
         <v>12980</v>
@@ -15889,10 +15920,10 @@
         <v>191</v>
       </c>
       <c r="H71" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I71" s="10" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="72" spans="1:9">
@@ -15900,7 +15931,7 @@
         <v>1000365879</v>
       </c>
       <c r="B72" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C72">
         <v>3380</v>
@@ -15915,10 +15946,10 @@
         <v>999</v>
       </c>
       <c r="H72" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I72" s="10" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="73" spans="1:9">
@@ -15926,7 +15957,7 @@
         <v>1002133624</v>
       </c>
       <c r="B73" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C73">
         <v>6300</v>
@@ -15941,10 +15972,10 @@
         <v>97</v>
       </c>
       <c r="H73" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I73" s="10" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="74" spans="1:9">
@@ -15952,7 +15983,7 @@
         <v>1000339558</v>
       </c>
       <c r="B74" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C74">
         <v>2720</v>
@@ -15967,10 +15998,10 @@
         <v>448</v>
       </c>
       <c r="H74" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I74" s="10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="75" spans="1:9">
@@ -15978,7 +16009,7 @@
         <v>5081478</v>
       </c>
       <c r="B75" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C75">
         <v>3360</v>
@@ -15993,10 +16024,10 @@
         <v>9999</v>
       </c>
       <c r="H75" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I75" s="10" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="76" spans="1:9">
@@ -16004,7 +16035,7 @@
         <v>5005540</v>
       </c>
       <c r="B76" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C76">
         <v>8000</v>
@@ -16019,10 +16050,10 @@
         <v>9999</v>
       </c>
       <c r="H76" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I76" s="10" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="77" spans="1:9">
@@ -16030,7 +16061,7 @@
         <v>1000526148</v>
       </c>
       <c r="B77" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C77">
         <v>8900</v>
@@ -16045,10 +16076,10 @@
         <v>276</v>
       </c>
       <c r="H77" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I77" s="10" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="78" spans="1:9">
@@ -16056,7 +16087,7 @@
         <v>1000677312</v>
       </c>
       <c r="B78" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C78">
         <v>1480</v>
@@ -16071,10 +16102,10 @@
         <v>999</v>
       </c>
       <c r="H78" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I78" s="10" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="79" spans="1:9">
@@ -16082,7 +16113,7 @@
         <v>1001407039</v>
       </c>
       <c r="B79" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C79">
         <v>3980</v>
@@ -16097,10 +16128,10 @@
         <v>145</v>
       </c>
       <c r="H79" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I79" s="10" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="80" spans="1:9">
@@ -16108,7 +16139,7 @@
         <v>1000248448</v>
       </c>
       <c r="B80" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C80">
         <v>5200</v>
@@ -16123,10 +16154,10 @@
         <v>9999</v>
       </c>
       <c r="H80" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I80" s="10" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="81" spans="1:9">
@@ -16134,7 +16165,7 @@
         <v>1001027192</v>
       </c>
       <c r="B81" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C81">
         <v>9000</v>
@@ -16149,10 +16180,10 @@
         <v>361</v>
       </c>
       <c r="H81" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I81" s="10" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="82" spans="1:9">
@@ -16160,7 +16191,7 @@
         <v>5067308</v>
       </c>
       <c r="B82" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C82">
         <v>2880</v>
@@ -16175,10 +16206,10 @@
         <v>999</v>
       </c>
       <c r="H82" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I82" s="10" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="83" spans="1:9">
@@ -16186,7 +16217,7 @@
         <v>1000942860</v>
       </c>
       <c r="B83" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C83">
         <v>1390</v>
@@ -16201,10 +16232,10 @@
         <v>999</v>
       </c>
       <c r="H83" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I83" s="10" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="84" spans="1:9">
@@ -16212,7 +16243,7 @@
         <v>1001991119</v>
       </c>
       <c r="B84" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C84">
         <v>3480</v>
@@ -16227,10 +16258,10 @@
         <v>999</v>
       </c>
       <c r="H84" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I84" s="10" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="85" spans="1:9">
@@ -16238,7 +16269,7 @@
         <v>5132664</v>
       </c>
       <c r="B85" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C85">
         <v>3800</v>
@@ -16253,10 +16284,10 @@
         <v>999</v>
       </c>
       <c r="H85" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I85" s="10" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="86" spans="1:9">
@@ -16264,7 +16295,7 @@
         <v>1000640854</v>
       </c>
       <c r="B86" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C86">
         <v>2720</v>
@@ -16279,10 +16310,10 @@
         <v>999</v>
       </c>
       <c r="H86" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I86" s="10" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="87" spans="1:9">
@@ -16290,7 +16321,7 @@
         <v>1000045935</v>
       </c>
       <c r="B87" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C87">
         <v>5990</v>
@@ -16305,10 +16336,10 @@
         <v>999</v>
       </c>
       <c r="H87" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I87" s="10" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="88" spans="1:9">
@@ -16316,7 +16347,7 @@
         <v>1000349505</v>
       </c>
       <c r="B88" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C88">
         <v>1440</v>
@@ -16331,10 +16362,10 @@
         <v>999</v>
       </c>
       <c r="H88" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I88" s="10" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="89" spans="1:9">
@@ -16342,7 +16373,7 @@
         <v>5060582</v>
       </c>
       <c r="B89" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C89">
         <v>10000</v>
@@ -16357,10 +16388,10 @@
         <v>999</v>
       </c>
       <c r="H89" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I89" s="10" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="90" spans="1:9">
@@ -16368,7 +16399,7 @@
         <v>1001363953</v>
       </c>
       <c r="B90" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C90">
         <v>2180</v>
@@ -16383,10 +16414,10 @@
         <v>999</v>
       </c>
       <c r="H90" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I90" s="10" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="91" spans="1:9">
@@ -16394,7 +16425,7 @@
         <v>5103372</v>
       </c>
       <c r="B91" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C91">
         <v>11980</v>
@@ -16409,10 +16440,10 @@
         <v>999</v>
       </c>
       <c r="H91" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I91" s="10" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="92" spans="1:9">
@@ -16420,7 +16451,7 @@
         <v>1001501063</v>
       </c>
       <c r="B92" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C92">
         <v>1260</v>
@@ -16435,10 +16466,10 @@
         <v>980</v>
       </c>
       <c r="H92" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I92" s="10" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="93" spans="1:9">
@@ -16446,7 +16477,7 @@
         <v>1000443353</v>
       </c>
       <c r="B93" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C93">
         <v>4040</v>
@@ -16461,10 +16492,10 @@
         <v>999</v>
       </c>
       <c r="H93" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I93" s="10" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="94" spans="1:9">
@@ -16472,7 +16503,7 @@
         <v>1002221133</v>
       </c>
       <c r="B94" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C94">
         <v>4980</v>
@@ -16487,10 +16518,10 @@
         <v>81</v>
       </c>
       <c r="H94" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I94" s="10" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="95" spans="1:9">
@@ -16498,7 +16529,7 @@
         <v>1000136966</v>
       </c>
       <c r="B95" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C95">
         <v>9000</v>
@@ -16513,10 +16544,10 @@
         <v>999</v>
       </c>
       <c r="H95" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I95" s="10" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="96" spans="1:9">
@@ -16524,7 +16555,7 @@
         <v>1000799985</v>
       </c>
       <c r="B96" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C96">
         <v>4980</v>
@@ -16539,10 +16570,10 @@
         <v>612</v>
       </c>
       <c r="H96" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I96" s="10" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="97" spans="1:9">
@@ -16550,7 +16581,7 @@
         <v>1000960165</v>
       </c>
       <c r="B97" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C97">
         <v>1390</v>
@@ -16565,10 +16596,10 @@
         <v>539</v>
       </c>
       <c r="H97" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I97" s="10" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="98" spans="1:9">
@@ -16576,7 +16607,7 @@
         <v>1001337989</v>
       </c>
       <c r="B98" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C98">
         <v>5280</v>
@@ -16591,10 +16622,10 @@
         <v>613</v>
       </c>
       <c r="H98" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I98" s="10" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="99" spans="1:9">
@@ -16617,7 +16648,7 @@
         <v>999</v>
       </c>
       <c r="H99" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I99" s="10" t="s">
         <v>38</v>
@@ -16643,7 +16674,7 @@
         <v>999</v>
       </c>
       <c r="H100" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I100" s="10" t="s">
         <v>47</v>
@@ -16654,7 +16685,7 @@
         <v>1002104225</v>
       </c>
       <c r="B101" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C101">
         <v>1280</v>
@@ -16669,10 +16700,10 @@
         <v>98</v>
       </c>
       <c r="H101" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I101" s="10" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="102" spans="1:9">
@@ -16680,7 +16711,7 @@
         <v>1002020133</v>
       </c>
       <c r="B102" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C102">
         <v>9030</v>
@@ -16695,10 +16726,10 @@
         <v>159</v>
       </c>
       <c r="H102" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I102" s="10" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="103" spans="1:9">
@@ -16706,7 +16737,7 @@
         <v>1000360436</v>
       </c>
       <c r="B103" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C103">
         <v>4480</v>
@@ -16721,10 +16752,10 @@
         <v>999</v>
       </c>
       <c r="H103" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I103" s="10" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="104" spans="1:9">
@@ -16732,7 +16763,7 @@
         <v>1001042362</v>
       </c>
       <c r="B104" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C104">
         <v>3980</v>
@@ -16747,10 +16778,10 @@
         <v>958</v>
       </c>
       <c r="H104" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I104" s="10" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="105" spans="1:9">
@@ -16758,7 +16789,7 @@
         <v>1002340554</v>
       </c>
       <c r="B105" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C105">
         <v>4250</v>
@@ -16773,10 +16804,10 @@
         <v>342</v>
       </c>
       <c r="H105" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I105" s="10" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="106" spans="1:9">
@@ -16784,7 +16815,7 @@
         <v>1000490099</v>
       </c>
       <c r="B106" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C106">
         <v>3980</v>
@@ -16799,10 +16830,10 @@
         <v>999</v>
       </c>
       <c r="H106" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I106" s="10" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="107" spans="1:9">
@@ -16810,7 +16841,7 @@
         <v>5077641</v>
       </c>
       <c r="B107" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C107">
         <v>7080</v>
@@ -16825,10 +16856,10 @@
         <v>999</v>
       </c>
       <c r="H107" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I107" s="10" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="108" spans="1:9">
@@ -16836,7 +16867,7 @@
         <v>1001397631</v>
       </c>
       <c r="B108" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C108">
         <v>1360</v>
@@ -16851,10 +16882,10 @@
         <v>772</v>
       </c>
       <c r="H108" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I108" s="10" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="109" spans="1:9">
@@ -16862,7 +16893,7 @@
         <v>1001942440</v>
       </c>
       <c r="B109" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C109">
         <v>2500</v>
@@ -16877,10 +16908,10 @@
         <v>751</v>
       </c>
       <c r="H109" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I109" s="10" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="110" spans="1:9">
@@ -16903,7 +16934,7 @@
         <v>889</v>
       </c>
       <c r="H110" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I110" s="10" t="s">
         <v>36</v>
@@ -16929,7 +16960,7 @@
         <v>999</v>
       </c>
       <c r="H111" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I111" s="10" t="s">
         <v>26</v>
@@ -16940,7 +16971,7 @@
         <v>1002221138</v>
       </c>
       <c r="B112" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C112">
         <v>4480</v>
@@ -16955,10 +16986,10 @@
         <v>134</v>
       </c>
       <c r="H112" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I112" s="10" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="113" spans="1:9">
@@ -16966,7 +16997,7 @@
         <v>1000216544</v>
       </c>
       <c r="B113" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C113">
         <v>4380</v>
@@ -16981,10 +17012,10 @@
         <v>999</v>
       </c>
       <c r="H113" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I113" s="10" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="114" spans="1:9">
@@ -16992,7 +17023,7 @@
         <v>5118057</v>
       </c>
       <c r="B114" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C114">
         <v>2720</v>
@@ -17007,10 +17038,10 @@
         <v>999</v>
       </c>
       <c r="H114" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I114" s="10" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="115" spans="1:9">
@@ -17018,7 +17049,7 @@
         <v>1000656471</v>
       </c>
       <c r="B115" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C115">
         <v>5850</v>
@@ -17033,10 +17064,10 @@
         <v>71</v>
       </c>
       <c r="H115" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I115" s="10" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="116" spans="1:9">
@@ -17044,7 +17075,7 @@
         <v>1001073370</v>
       </c>
       <c r="B116" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C116">
         <v>3500</v>
@@ -17059,10 +17090,10 @@
         <v>999</v>
       </c>
       <c r="H116" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I116" s="10" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="117" spans="1:9">
@@ -17070,7 +17101,7 @@
         <v>1000365868</v>
       </c>
       <c r="B117" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C117">
         <v>4380</v>
@@ -17085,10 +17116,10 @@
         <v>627</v>
       </c>
       <c r="H117" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I117" s="10" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="118" spans="1:9">
@@ -17096,7 +17127,7 @@
         <v>1001740101</v>
       </c>
       <c r="B118" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C118">
         <v>4200</v>
@@ -17111,10 +17142,10 @@
         <v>391</v>
       </c>
       <c r="H118" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I118" s="10" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="119" spans="1:9">
@@ -17122,7 +17153,7 @@
         <v>1000339526</v>
       </c>
       <c r="B119" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C119">
         <v>5440</v>
@@ -17137,10 +17168,10 @@
         <v>956</v>
       </c>
       <c r="H119" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I119" s="10" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="120" spans="1:9">
@@ -17148,7 +17179,7 @@
         <v>1000125337</v>
       </c>
       <c r="B120" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C120">
         <v>6280</v>
@@ -17163,10 +17194,10 @@
         <v>999</v>
       </c>
       <c r="H120" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I120" s="10" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="121" spans="1:9">
@@ -17174,7 +17205,7 @@
         <v>5013230</v>
       </c>
       <c r="B121" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C121">
         <v>4780</v>
@@ -17189,10 +17220,10 @@
         <v>9999</v>
       </c>
       <c r="H121" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I121" s="10" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="122" spans="1:9">
@@ -17200,7 +17231,7 @@
         <v>5043538</v>
       </c>
       <c r="B122" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C122">
         <v>11500</v>
@@ -17215,10 +17246,10 @@
         <v>999</v>
       </c>
       <c r="H122" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I122" s="10" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="123" spans="1:9">
@@ -17226,7 +17257,7 @@
         <v>1001382381</v>
       </c>
       <c r="B123" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C123">
         <v>8990</v>
@@ -17241,10 +17272,10 @@
         <v>999</v>
       </c>
       <c r="H123" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I123" s="10" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="124" spans="1:9">
@@ -17252,7 +17283,7 @@
         <v>1002159262</v>
       </c>
       <c r="B124" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C124">
         <v>2500</v>
@@ -17267,10 +17298,10 @@
         <v>197</v>
       </c>
       <c r="H124" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I124" s="10" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="125" spans="1:9">
@@ -17278,7 +17309,7 @@
         <v>1002286852</v>
       </c>
       <c r="B125" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C125">
         <v>3540</v>
@@ -17293,10 +17324,10 @@
         <v>191</v>
       </c>
       <c r="H125" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I125" s="10" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="126" spans="1:9">
@@ -17304,7 +17335,7 @@
         <v>5052356</v>
       </c>
       <c r="B126" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C126">
         <v>12300</v>
@@ -17319,10 +17350,10 @@
         <v>999</v>
       </c>
       <c r="H126" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I126" s="10" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="127" spans="1:9">
@@ -17330,7 +17361,7 @@
         <v>1000499057</v>
       </c>
       <c r="B127" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C127">
         <v>11980</v>
@@ -17345,10 +17376,10 @@
         <v>232</v>
       </c>
       <c r="H127" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I127" s="10" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="128" spans="1:9">
@@ -17356,7 +17387,7 @@
         <v>1000791609</v>
       </c>
       <c r="B128" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C128">
         <v>1520</v>
@@ -17371,10 +17402,10 @@
         <v>999</v>
       </c>
       <c r="H128" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I128" s="10" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="129" spans="1:9">
@@ -17382,7 +17413,7 @@
         <v>1000074625</v>
       </c>
       <c r="B129" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C129">
         <v>20900</v>
@@ -17397,10 +17428,10 @@
         <v>690</v>
       </c>
       <c r="H129" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I129" s="10" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="130" spans="1:9">
@@ -17408,7 +17439,7 @@
         <v>5077457</v>
       </c>
       <c r="B130" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C130">
         <v>4320</v>
@@ -17423,10 +17454,10 @@
         <v>999</v>
       </c>
       <c r="H130" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I130" s="10" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="131" spans="1:9">
@@ -17434,7 +17465,7 @@
         <v>1000349503</v>
       </c>
       <c r="B131" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C131">
         <v>2250</v>
@@ -17449,10 +17480,10 @@
         <v>786</v>
       </c>
       <c r="H131" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I131" s="10" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="132" spans="1:9">
@@ -17460,7 +17491,7 @@
         <v>5110063</v>
       </c>
       <c r="B132" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C132">
         <v>3780</v>
@@ -17475,10 +17506,10 @@
         <v>999</v>
       </c>
       <c r="H132" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I132" s="10" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="133" spans="1:9">
@@ -17486,7 +17517,7 @@
         <v>5054219</v>
       </c>
       <c r="B133" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C133">
         <v>2490</v>
@@ -17501,10 +17532,10 @@
         <v>9999</v>
       </c>
       <c r="H133" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I133" s="10" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="134" spans="1:9">
@@ -17512,7 +17543,7 @@
         <v>1001959559</v>
       </c>
       <c r="B134" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C134">
         <v>2400</v>
@@ -17527,10 +17558,10 @@
         <v>615</v>
       </c>
       <c r="H134" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I134" s="10" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="135" spans="1:9">
@@ -17538,7 +17569,7 @@
         <v>5132978</v>
       </c>
       <c r="B135" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C135">
         <v>4200</v>
@@ -17553,10 +17584,10 @@
         <v>999</v>
       </c>
       <c r="H135" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I135" s="10" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="136" spans="1:9">
@@ -17564,7 +17595,7 @@
         <v>1000777595</v>
       </c>
       <c r="B136" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C136">
         <v>2980</v>
@@ -17579,10 +17610,10 @@
         <v>776</v>
       </c>
       <c r="H136" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I136" s="10" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="137" spans="1:9">
@@ -17590,7 +17621,7 @@
         <v>5067311</v>
       </c>
       <c r="B137" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C137">
         <v>4480</v>
@@ -17605,10 +17636,10 @@
         <v>999</v>
       </c>
       <c r="H137" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I137" s="10" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="138" spans="1:9">
@@ -17616,7 +17647,7 @@
         <v>1002225093</v>
       </c>
       <c r="B138" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C138">
         <v>3980</v>
@@ -17631,10 +17662,10 @@
         <v>324</v>
       </c>
       <c r="H138" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I138" s="10" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="139" spans="1:9">
@@ -17642,7 +17673,7 @@
         <v>5030130</v>
       </c>
       <c r="B139" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C139">
         <v>3980</v>
@@ -17657,10 +17688,10 @@
         <v>9999</v>
       </c>
       <c r="H139" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I139" s="10" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="140" spans="1:9">
@@ -17668,7 +17699,7 @@
         <v>1001317277</v>
       </c>
       <c r="B140" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C140">
         <v>3780</v>
@@ -17683,10 +17714,10 @@
         <v>359</v>
       </c>
       <c r="H140" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I140" s="10" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="141" spans="1:9">
@@ -17694,7 +17725,7 @@
         <v>5118059</v>
       </c>
       <c r="B141" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C141">
         <v>2720</v>
@@ -17709,10 +17740,10 @@
         <v>999</v>
       </c>
       <c r="H141" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I141" s="10" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="142" spans="1:9">
@@ -17720,7 +17751,7 @@
         <v>5081412</v>
       </c>
       <c r="B142" t="s">
-        <v>369</v>
+        <v>50</v>
       </c>
       <c r="C142">
         <v>4500</v>
@@ -17735,10 +17766,10 @@
         <v>999</v>
       </c>
       <c r="H142" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I142" s="10" t="s">
-        <v>370</v>
+        <v>51</v>
       </c>
     </row>
     <row r="143" spans="1:9">
@@ -17761,7 +17792,7 @@
         <v>613</v>
       </c>
       <c r="H143" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I143" s="10" t="s">
         <v>372</v>
@@ -17787,7 +17818,7 @@
         <v>87</v>
       </c>
       <c r="H144" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I144" s="10" t="s">
         <v>374</v>
@@ -17813,7 +17844,7 @@
         <v>304</v>
       </c>
       <c r="H145" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I145" s="10" t="s">
         <v>376</v>
@@ -17839,7 +17870,7 @@
         <v>9999</v>
       </c>
       <c r="H146" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I146" s="10" t="s">
         <v>378</v>
@@ -17865,7 +17896,7 @@
         <v>999</v>
       </c>
       <c r="H147" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I147" s="10" t="s">
         <v>380</v>
@@ -17891,7 +17922,7 @@
         <v>999</v>
       </c>
       <c r="H148" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I148" s="10" t="s">
         <v>382</v>
@@ -17917,7 +17948,7 @@
         <v>999</v>
       </c>
       <c r="H149" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I149" s="10" t="s">
         <v>384</v>
@@ -17943,7 +17974,7 @@
         <v>826</v>
       </c>
       <c r="H150" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I150" s="10" t="s">
         <v>386</v>
@@ -17969,7 +18000,7 @@
         <v>622</v>
       </c>
       <c r="H151" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I151" s="10" t="s">
         <v>388</v>
@@ -17995,7 +18026,7 @@
         <v>866</v>
       </c>
       <c r="H152" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I152" s="10" t="s">
         <v>390</v>
@@ -18021,7 +18052,7 @@
         <v>999</v>
       </c>
       <c r="H153" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I153" s="10" t="s">
         <v>392</v>
@@ -18047,7 +18078,7 @@
         <v>416</v>
       </c>
       <c r="H154" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I154" s="10" t="s">
         <v>394</v>
@@ -18073,7 +18104,7 @@
         <v>181</v>
       </c>
       <c r="H155" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I155" s="10" t="s">
         <v>396</v>
@@ -18099,7 +18130,7 @@
         <v>999</v>
       </c>
       <c r="H156" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I156" s="10" t="s">
         <v>398</v>
@@ -18125,7 +18156,7 @@
         <v>999</v>
       </c>
       <c r="H157" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I157" s="10" t="s">
         <v>400</v>
@@ -18151,7 +18182,7 @@
         <v>533</v>
       </c>
       <c r="H158" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I158" s="10" t="s">
         <v>402</v>
@@ -18177,7 +18208,7 @@
         <v>718</v>
       </c>
       <c r="H159" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I159" s="10" t="s">
         <v>404</v>
@@ -18203,7 +18234,7 @@
         <v>999</v>
       </c>
       <c r="H160" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I160" s="10" t="s">
         <v>406</v>
@@ -18229,7 +18260,7 @@
         <v>999</v>
       </c>
       <c r="H161" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I161" s="10" t="s">
         <v>408</v>
@@ -18255,7 +18286,7 @@
         <v>361</v>
       </c>
       <c r="H162" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I162" s="10" t="s">
         <v>410</v>
@@ -18281,7 +18312,7 @@
         <v>511</v>
       </c>
       <c r="H163" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I163" s="10" t="s">
         <v>412</v>
@@ -18307,7 +18338,7 @@
         <v>106</v>
       </c>
       <c r="H164" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I164" s="10" t="s">
         <v>414</v>
@@ -18333,7 +18364,7 @@
         <v>184</v>
       </c>
       <c r="H165" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I165" s="10" t="s">
         <v>416</v>
@@ -18359,7 +18390,7 @@
         <v>509</v>
       </c>
       <c r="H166" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I166" s="10" t="s">
         <v>418</v>
@@ -18385,7 +18416,7 @@
         <v>255</v>
       </c>
       <c r="H167" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I167" s="10" t="s">
         <v>420</v>
@@ -18411,7 +18442,7 @@
         <v>999</v>
       </c>
       <c r="H168" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I168" s="10" t="s">
         <v>422</v>
@@ -18437,7 +18468,7 @@
         <v>637</v>
       </c>
       <c r="H169" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I169" s="10" t="s">
         <v>424</v>
@@ -18463,7 +18494,7 @@
         <v>999</v>
       </c>
       <c r="H170" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I170" s="10" t="s">
         <v>426</v>
@@ -18489,7 +18520,7 @@
         <v>216</v>
       </c>
       <c r="H171" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I171" s="10" t="s">
         <v>428</v>
@@ -18515,7 +18546,7 @@
         <v>732</v>
       </c>
       <c r="H172" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I172" s="10" t="s">
         <v>430</v>
@@ -18541,7 +18572,7 @@
         <v>999</v>
       </c>
       <c r="H173" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I173" s="10" t="s">
         <v>30</v>
@@ -18567,7 +18598,7 @@
         <v>999</v>
       </c>
       <c r="H174" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I174" s="10" t="s">
         <v>432</v>
@@ -18593,7 +18624,7 @@
         <v>999</v>
       </c>
       <c r="H175" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I175" s="10" t="s">
         <v>434</v>
@@ -18619,7 +18650,7 @@
         <v>9999</v>
       </c>
       <c r="H176" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I176" s="10" t="s">
         <v>436</v>
@@ -18645,7 +18676,7 @@
         <v>384</v>
       </c>
       <c r="H177" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I177" s="10" t="s">
         <v>438</v>
@@ -18671,7 +18702,7 @@
         <v>9999</v>
       </c>
       <c r="H178" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I178" s="10" t="s">
         <v>440</v>
@@ -18697,7 +18728,7 @@
         <v>477</v>
       </c>
       <c r="H179" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I179" s="10" t="s">
         <v>442</v>
@@ -18723,7 +18754,7 @@
         <v>284</v>
       </c>
       <c r="H180" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I180" s="10" t="s">
         <v>444</v>
@@ -18749,7 +18780,7 @@
         <v>585</v>
       </c>
       <c r="H181" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I181" s="10" t="s">
         <v>446</v>
@@ -18775,7 +18806,7 @@
         <v>999</v>
       </c>
       <c r="H182" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I182" s="10" t="s">
         <v>448</v>
@@ -18801,7 +18832,7 @@
         <v>623</v>
       </c>
       <c r="H183" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I183" s="10" t="s">
         <v>450</v>
@@ -18827,7 +18858,7 @@
         <v>999</v>
       </c>
       <c r="H184" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I184" s="10" t="s">
         <v>452</v>
@@ -18853,7 +18884,7 @@
         <v>999</v>
       </c>
       <c r="H185" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I185" s="10" t="s">
         <v>40</v>
@@ -18879,7 +18910,7 @@
         <v>999</v>
       </c>
       <c r="H186" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I186" s="10" t="s">
         <v>454</v>
@@ -18905,7 +18936,7 @@
         <v>92</v>
       </c>
       <c r="H187" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I187" s="10" t="s">
         <v>456</v>
@@ -18931,7 +18962,7 @@
         <v>100</v>
       </c>
       <c r="H188" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I188" s="10" t="s">
         <v>458</v>
@@ -18957,7 +18988,7 @@
         <v>999</v>
       </c>
       <c r="H189" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I189" s="10" t="s">
         <v>460</v>
@@ -18983,7 +19014,7 @@
         <v>220</v>
       </c>
       <c r="H190" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I190" s="10" t="s">
         <v>462</v>
@@ -19009,7 +19040,7 @@
         <v>418</v>
       </c>
       <c r="H191" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I191" s="10" t="s">
         <v>464</v>
@@ -19035,7 +19066,7 @@
         <v>999</v>
       </c>
       <c r="H192" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I192" s="10" t="s">
         <v>466</v>
@@ -19061,7 +19092,7 @@
         <v>999</v>
       </c>
       <c r="H193" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I193" s="10" t="s">
         <v>468</v>
@@ -21279,7 +21310,7 @@
         <v>5061562</v>
       </c>
       <c r="B279" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C279">
         <v>3690</v>
@@ -21297,7 +21328,7 @@
         <v>635</v>
       </c>
       <c r="I279" s="10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="280" spans="1:9">
@@ -22215,7 +22246,7 @@
         <v>1000175874</v>
       </c>
       <c r="B315" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C315">
         <v>5600</v>
@@ -22233,7 +22264,7 @@
         <v>635</v>
       </c>
       <c r="I315" s="10" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="316" spans="1:9">
@@ -22449,7 +22480,7 @@
         <v>1000875718</v>
       </c>
       <c r="B324" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C324">
         <v>4320</v>
@@ -22467,7 +22498,7 @@
         <v>635</v>
       </c>
       <c r="I324" s="10" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="325" spans="1:9">
@@ -22969,7 +23000,7 @@
         <v>5061939</v>
       </c>
       <c r="B344" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C344">
         <v>4780</v>
@@ -22987,7 +23018,7 @@
         <v>635</v>
       </c>
       <c r="I344" s="10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="345" spans="1:9">
@@ -23613,7 +23644,7 @@
         <v>1002110078</v>
       </c>
       <c r="B369" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C369">
         <v>3980</v>
@@ -23631,7 +23662,7 @@
         <v>635</v>
       </c>
       <c r="I369" s="10" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="370" spans="1:9">
@@ -25693,7 +25724,7 @@
         <v>1002033102</v>
       </c>
       <c r="B449" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C449">
         <v>2180</v>
@@ -25711,7 +25742,7 @@
         <v>916</v>
       </c>
       <c r="I449" s="10" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="450" spans="1:9">
@@ -26707,7 +26738,7 @@
         <v>1001069960</v>
       </c>
       <c r="B488" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C488">
         <v>2180</v>
@@ -26725,7 +26756,7 @@
         <v>916</v>
       </c>
       <c r="I488" s="10" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="489" spans="1:9">
@@ -27679,7 +27710,7 @@
         <v>5007664</v>
       </c>
       <c r="B524" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C524">
         <v>3980</v>
@@ -27697,7 +27728,7 @@
         <v>1118</v>
       </c>
       <c r="I524" s="10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="525" spans="1:9">
@@ -28251,7 +28282,7 @@
         <v>5055905</v>
       </c>
       <c r="B546" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C546">
         <v>5120</v>
@@ -28269,7 +28300,7 @@
         <v>1118</v>
       </c>
       <c r="I546" s="10" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="547" spans="1:9">
@@ -44393,7 +44424,7 @@
         <v>1000175876</v>
       </c>
       <c r="B1153" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C1153">
         <v>5600</v>
@@ -44411,7 +44442,7 @@
         <v>2211</v>
       </c>
       <c r="I1153" s="10" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="1154" spans="1:9">
@@ -45508,7 +45539,7 @@
         <v>1002225099</v>
       </c>
       <c r="B1196" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C1196">
         <v>2506</v>
@@ -45526,7 +45557,7 @@
         <v>2438</v>
       </c>
       <c r="I1196" s="10" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="1197" spans="1:9">
@@ -45664,7 +45695,7 @@
         <v>5061296</v>
       </c>
       <c r="B1202" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C1202">
         <v>4320</v>
@@ -45682,7 +45713,7 @@
         <v>2438</v>
       </c>
       <c r="I1202" s="10" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="1203" spans="1:9">
@@ -46256,7 +46287,7 @@
         <v>1002419584</v>
       </c>
       <c r="B1225" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C1225">
         <v>3200</v>
@@ -46274,7 +46305,7 @@
         <v>2487</v>
       </c>
       <c r="I1225" s="10" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="1226" spans="1:9">
@@ -46672,7 +46703,7 @@
         <v>1001382646</v>
       </c>
       <c r="B1241" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C1241">
         <v>4800</v>
@@ -46690,7 +46721,7 @@
         <v>2487</v>
       </c>
       <c r="I1241" s="10" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="1242" spans="1:9">
@@ -47140,7 +47171,7 @@
         <v>1000844430</v>
       </c>
       <c r="B1259" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C1259">
         <v>2980</v>
@@ -47158,7 +47189,7 @@
         <v>2487</v>
       </c>
       <c r="I1259" s="10" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="1260" spans="1:9">
@@ -47816,7 +47847,7 @@
         <v>1001137097</v>
       </c>
       <c r="B1285" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C1285">
         <v>4780</v>
@@ -47834,7 +47865,7 @@
         <v>2487</v>
       </c>
       <c r="I1285" s="10" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="1286" spans="1:9">
@@ -48440,7 +48471,7 @@
         <v>1000279292</v>
       </c>
       <c r="B1309" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C1309">
         <v>2980</v>
@@ -48458,7 +48489,7 @@
         <v>2667</v>
       </c>
       <c r="I1309" s="10" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="1310" spans="1:9">
@@ -48749,7 +48780,7 @@
         <v>1000558079</v>
       </c>
       <c r="B1321" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C1321">
         <v>2500</v>
@@ -48767,7 +48798,7 @@
         <v>2667</v>
       </c>
       <c r="I1321" s="10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="1322" spans="1:9">
@@ -53125,7 +53156,7 @@
         <v>1000201444</v>
       </c>
       <c r="B1484" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C1484">
         <v>5280</v>
@@ -53143,7 +53174,7 @@
         <v>3016</v>
       </c>
       <c r="I1484" s="10" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="1485" spans="1:9">
@@ -58184,7 +58215,7 @@
         <v>3</v>
       </c>
       <c r="H1675" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I1675" s="10" t="s">
         <v>3411</v>
@@ -58210,7 +58241,7 @@
         <v>999</v>
       </c>
       <c r="H1676" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I1676" s="10" t="s">
         <v>3413</v>
@@ -58233,7 +58264,7 @@
         <v>15</v>
       </c>
       <c r="H1677" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I1677" s="10" t="s">
         <v>3415</v>
@@ -58256,7 +58287,7 @@
         <v>15</v>
       </c>
       <c r="H1678" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I1678" s="10" t="s">
         <v>3417</v>
@@ -58279,7 +58310,7 @@
         <v>15</v>
       </c>
       <c r="H1679" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I1679" s="10" t="s">
         <v>3419</v>
@@ -58308,7 +58339,7 @@
         <v>1092</v>
       </c>
       <c r="H1680" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I1680" s="10" t="s">
         <v>3421</v>
@@ -58337,7 +58368,7 @@
         <v>1092</v>
       </c>
       <c r="H1681" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I1681" s="10" t="s">
         <v>3423</v>
@@ -58366,7 +58397,7 @@
         <v>1092</v>
       </c>
       <c r="H1682" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I1682" s="10" t="s">
         <v>3425</v>
@@ -64402,7 +64433,7 @@
         <v>1000568647</v>
       </c>
       <c r="B1913" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C1913">
         <v>2500</v>
@@ -64420,7 +64451,7 @@
         <v>3825</v>
       </c>
       <c r="I1913" s="10" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="1914" spans="1:9">

--- a/다과_구매목록.xlsx
+++ b/다과_구매목록.xlsx
@@ -264,6 +264,12 @@
     <t>https://www.kurly.com/goods/1000339526</t>
   </si>
   <si>
+    <t>[브레댄코] 리얼 브라우니 쿠키 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5061562</t>
+  </si>
+  <si>
     <t>[롯데제과] 카스타드 오리지널 230g</t>
   </si>
   <si>
@@ -300,1660 +306,1654 @@
     <t>https://www.kurly.com/goods/1002419584</t>
   </si>
   <si>
+    <t>파이/케이크(개별포장)</t>
+  </si>
+  <si>
+    <t>[오리온] 초코파이 12입</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5061296</t>
+  </si>
+  <si>
+    <t>[오리온] 카스타드 12개입 276g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000875718</t>
+  </si>
+  <si>
+    <t>[오리온] 초코파이 말차쇼콜라 408g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001382646</t>
+  </si>
+  <si>
+    <t>[롯데] 몽쉘 생크림케이크 오리지널 408g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000175874</t>
+  </si>
+  <si>
+    <t>[롯데] 몽쉘 생크림케이크 카카오 408g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000175876</t>
+  </si>
+  <si>
+    <t>[해태] 오예스 미니 크림소다맛 192g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002225099</t>
+  </si>
+  <si>
+    <t>[해태] 오예스 360g 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000201444</t>
+  </si>
+  <si>
+    <t>품목수</t>
+  </si>
+  <si>
+    <t>비중</t>
+  </si>
+  <si>
+    <t>상품번호</t>
+  </si>
+  <si>
+    <t>가격</t>
+  </si>
+  <si>
+    <t>정가</t>
+  </si>
+  <si>
+    <t>할인율</t>
+  </si>
+  <si>
+    <t>품절</t>
+  </si>
+  <si>
+    <t>검색어</t>
+  </si>
+  <si>
+    <t>[마요라] 아페티토 스틱 스낵 2종, 택1</t>
+  </si>
+  <si>
+    <t>가성비 과자</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002110052</t>
+  </si>
+  <si>
+    <t>[해태] 아이비 309g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000747182</t>
+  </si>
+  <si>
+    <t>대만 누가크래커 대용량 32개입 448g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000862247</t>
+  </si>
+  <si>
+    <t>[비타비고] 이탈리안 브레드 스틱 4종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000178183</t>
+  </si>
+  <si>
+    <t>[밤부] 누가 크래커 140g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5031072</t>
+  </si>
+  <si>
+    <t>[무직타이거] 옛날과자 골라담기 5종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000875821</t>
+  </si>
+  <si>
+    <t>[포테이토 크리스프] 감자칩 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000651310</t>
+  </si>
+  <si>
+    <t>[리츠] 크래커 3종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000321598</t>
+  </si>
+  <si>
+    <t>[해태] 에이스 364g (24g x 15봉지)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5077465</t>
+  </si>
+  <si>
+    <t>[롯데] 꼬깔콘 스낵(소) 4번들</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5079319</t>
+  </si>
+  <si>
+    <t>[해태] 맛동산 304g (38g x 8팩)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5077461</t>
+  </si>
+  <si>
+    <t>[맥비티] 다이제스티브 비스킷 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000975389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[농심] 인기 봉지 과자 7종 (택1) </t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000198192</t>
+  </si>
+  <si>
+    <t>[만전김] 김스깡 3번들 (60g x 3묶음)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5151421</t>
+  </si>
+  <si>
+    <t>인기 일본과자 10종 골라담기 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001272797</t>
+  </si>
+  <si>
+    <t>[해태] 오사쯔 100g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001029494</t>
+  </si>
+  <si>
+    <t>[가렛팝콘] 프리미엄 수제 팝콘 3종 (백)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5030780</t>
+  </si>
+  <si>
+    <t>[롯데] 야채 크래커 249g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000339529</t>
+  </si>
+  <si>
+    <t>[잇츠베러] 잇츠베러 크래커 4종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5036524</t>
+  </si>
+  <si>
+    <t>홈파티 맥주 안주 간식 8종 모아보기 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000356676</t>
+  </si>
+  <si>
+    <t>[TEMOLE] 아보카도칩 3종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000963099</t>
+  </si>
+  <si>
+    <t>[마이산] 스카이 플레이크 크래커 600g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5088236</t>
+  </si>
+  <si>
+    <t>[닥터유] 단백질칩 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000617577</t>
+  </si>
+  <si>
+    <t>[비타비고] 이탈리안 스낵 비타팝 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000455773</t>
+  </si>
+  <si>
+    <t>[마마메] 템페 칩스 5종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000137075</t>
+  </si>
+  <si>
+    <t>[씬] 감자칩 3종, 택 1</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002134596</t>
+  </si>
+  <si>
+    <t>[리츠] 바삭 김 크래커 73g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001447521</t>
+  </si>
+  <si>
+    <t>[오레오] 웨하스 스틱 150g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001421531</t>
+  </si>
+  <si>
+    <t>[아미고] 나쵸칩 그랩앤고 치즈 콤보 (100g x 6입)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000269917</t>
+  </si>
+  <si>
+    <t>[크라운] 참 크래커 알프스 295g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001592465</t>
+  </si>
+  <si>
+    <t>[HBAF] 와사비맛 아몬드 190g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5054491</t>
+  </si>
+  <si>
+    <t>[더다믐] 김칩스 오리지널 44g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001919935</t>
+  </si>
+  <si>
+    <t>[크라운] 버터와플 316g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5062899</t>
+  </si>
+  <si>
+    <t>[오리온] 감자패밀리팩 대용량 180g (포카칩 &amp; 스윙칩 &amp; 오감자)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000875710</t>
+  </si>
+  <si>
+    <t>[미주라] 소이아 크래커 400g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5006818</t>
+  </si>
+  <si>
+    <t>[해태] 가루비 감자칩 오리지널 40g X 3개입</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000582944</t>
+  </si>
+  <si>
+    <t>[라아부엘라니에베스] 스페인 수제 감자칩 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000206111</t>
+  </si>
+  <si>
+    <t>[마요라] 커피조이 351g (39g X 9개입)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000643389</t>
+  </si>
+  <si>
+    <t>[해태] 가루비 감자칩 오리지널 96g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000439362</t>
+  </si>
+  <si>
+    <t>[헌터즈] 트러플 감자칩 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000166566</t>
+  </si>
+  <si>
+    <t>[DJ&amp;A] 표고버섯/베지 크리스프 3종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000526145</t>
+  </si>
+  <si>
+    <t>[베프코] 홋카이도 센베 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000789439</t>
+  </si>
+  <si>
+    <t>홈파티 와인 안주 간식 8종 모아보기 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000356687</t>
+  </si>
+  <si>
+    <t>[크라운] 인기스낵 모음 12팩</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5153242</t>
+  </si>
+  <si>
+    <t>[프롬잇] 프로틴칩 6종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000033235</t>
+  </si>
+  <si>
+    <t>[발스낵] 그랜드 감자칩 2묶음 7종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001570087</t>
+  </si>
+  <si>
+    <t>[농심] 빵부장 초코빵 55g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000942359</t>
+  </si>
+  <si>
+    <t>[해태] 계란과자 45g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001397540</t>
+  </si>
+  <si>
+    <t>[그레타] 허브 크래커 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000927112</t>
+  </si>
+  <si>
+    <t>[덴로쿠] 스낵 믹스팩 294g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5103484</t>
+  </si>
+  <si>
+    <t>[아미카] 감자칩 멀티팩 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000605988</t>
+  </si>
+  <si>
+    <t>[타코맨] 나쵸 토틸라칩 320g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5060050</t>
+  </si>
+  <si>
+    <t>[이메이] 대파 소다 크래커 225g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002324203</t>
+  </si>
+  <si>
+    <t>[크라운] 참쌀선과 253g (44봉)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000178191</t>
+  </si>
+  <si>
+    <t>[바다해] 캠핑&amp;홈파티 마른안주 플래터 360g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000914382</t>
+  </si>
+  <si>
+    <t>[ALLO] 하몽 크래커 319g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002014581</t>
+  </si>
+  <si>
+    <t>[레인코스트] 크리스프 크래커 7종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5052362</t>
+  </si>
+  <si>
+    <t>[크라운] 치즈샌드 Rich 180g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000958549</t>
+  </si>
+  <si>
+    <t>[오리온] 호호감자크래커 177g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002010936</t>
+  </si>
+  <si>
+    <t>[퀼리] 스페인 브래드스틱 6종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000242960</t>
+  </si>
+  <si>
+    <t>[롯데] 군위 사과 시리즈 11종, 택1</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002482468</t>
+  </si>
+  <si>
+    <t>[미주라] 통밀크래커 385g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5058855</t>
+  </si>
+  <si>
+    <t>대용량 트러플 카사바칩 500g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000783621</t>
+  </si>
+  <si>
+    <t>[아미카] 엘도라다 포테이토칩 대용량  400g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000525224</t>
+  </si>
+  <si>
+    <t>[오리온] 썬 핫스파이시 4번들</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000365879</t>
+  </si>
+  <si>
+    <t>[브렛츠] 감자칩 7종, 택1</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002133624</t>
+  </si>
+  <si>
+    <t>[롯데] 치토스 바비큐 164g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000339558</t>
+  </si>
+  <si>
+    <t>[크라운] 참 크래커 280g (18.67g x 15입)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5081478</t>
+  </si>
+  <si>
+    <t>[미주라] 토스트 비스켓 320g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5005540</t>
+  </si>
+  <si>
+    <t>[DJ&amp;A] 포테이토 웨지 스낵 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000526148</t>
+  </si>
+  <si>
+    <t>[빙그레] 인기스낵 4종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000677312</t>
+  </si>
+  <si>
+    <t>[크라운] 그레이스 298g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001407039</t>
+  </si>
+  <si>
+    <t>[오리온] 인기 봉지 과자 지퍼백 5종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000248448</t>
+  </si>
+  <si>
+    <t>땅콩 한입 꽈배기 520g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001027192</t>
+  </si>
+  <si>
+    <t>[오리온] 고소미 216g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5067308</t>
+  </si>
+  <si>
+    <t>[HBAF] 시그니처 팝콘 골라담기 7종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000942860</t>
+  </si>
+  <si>
+    <t>[미카쿠토] 오사츠도키 칩 2종, 택1</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001991119</t>
+  </si>
+  <si>
+    <t>[더다믐] 김칩스 매운맛 44g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5132664</t>
+  </si>
+  <si>
+    <t>[오리온] 무뚝뚝 감자칩 &amp; 고구마 스낵 3종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000640854</t>
+  </si>
+  <si>
+    <t>[마주] 버섯스낵 바삭칩 2종</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000045935</t>
+  </si>
+  <si>
+    <t>[농심] 빵부장 소금빵 55g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000349505</t>
+  </si>
+  <si>
+    <t>[PNB] 고소한 수제 전병 4종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5060582</t>
+  </si>
+  <si>
+    <t>[농심] 인기 봉지 과자 7종 골라담기 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001363953</t>
+  </si>
+  <si>
+    <t>[카수가이] 오부쿠로 와사비마메 227g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5103372</t>
+  </si>
+  <si>
+    <t>[농심] 와사비 새우깡 70g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001501063</t>
+  </si>
+  <si>
+    <t>[이토비스킷] 랑그리 크림 쿠키 2종</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000443353</t>
+  </si>
+  <si>
+    <t>[발센] 라이브니즈 비스킷 2종, 택1</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002221133</t>
+  </si>
+  <si>
+    <t>[오가마마] 바삭바삭 고구마칩 150g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000136966</t>
+  </si>
+  <si>
+    <t>[생미쉘] 비스킷 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000799985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[HBAF] 와사비마요 팝콘 80g </t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000960165</t>
+  </si>
+  <si>
+    <t>[마켓오] 브라우니 바이트 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001337989</t>
+  </si>
+  <si>
+    <t>[맥스봉] 구운풍미 마늘 후랑크 80g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002104225</t>
+  </si>
+  <si>
+    <t>[시그달] 크리스피 크래커 3종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002020133</t>
+  </si>
+  <si>
+    <t>수입 과자 10종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000360436</t>
+  </si>
+  <si>
+    <t>[해태] 버터링 골드 194g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001042362</t>
+  </si>
+  <si>
+    <t>[크런틴] 프사삭 5mm 통감자칩 4종, 택1</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002340554</t>
+  </si>
+  <si>
+    <t>[해태] 에이스 바스크 치즈 케이크 364g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000490099</t>
+  </si>
+  <si>
+    <t>[CJ] 맛군밤 4개입</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5077641</t>
+  </si>
+  <si>
+    <t>[롯데] 꼬깔콘 고소한맛 67g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001397631</t>
+  </si>
+  <si>
+    <t>[CJ] 바삭칩 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001942440</t>
+  </si>
+  <si>
+    <t>[발센] 와플텐 웨이퍼롤 2종, 택1</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002221138</t>
+  </si>
+  <si>
+    <t>[아미카] 이탈리아 감자칩 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000216544</t>
+  </si>
+  <si>
+    <t>[롯데] 쌀로별 오리지널 156g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5118057</t>
+  </si>
+  <si>
+    <t>[카메다] 소프트 사라다 145.2g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000656471</t>
+  </si>
+  <si>
+    <t>[곡물그대로21] 크리스피롤 3종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001073370</t>
+  </si>
+  <si>
+    <t>[해태] 맛동산 300g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000365868</t>
+  </si>
+  <si>
+    <t>[유니온] 와인 페어링 타랄리니 스낵 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001740101</t>
+  </si>
+  <si>
+    <t>[해태] 칼로리바란스 치즈 (38g x 7개)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000125337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Lay's] 감자칩 7종 (택1) </t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5013230</t>
+  </si>
+  <si>
+    <t>[아티장 비스킷] 치즈를 위한 토스트 (데이츠&amp;헤이즐넛) 100g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5043538</t>
+  </si>
+  <si>
+    <t>7일 이내 로스팅한 구운 캐슈넛 200g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001382381</t>
+  </si>
+  <si>
+    <t>[다르다] 통밀칩 45g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002159262</t>
+  </si>
+  <si>
+    <t>[해태] 맛동산 3번들 210g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002286852</t>
+  </si>
+  <si>
+    <t>[하루견과] 빠삭칩 200g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5052356</t>
+  </si>
+  <si>
+    <t>[마이산] 스카이 플레이크 크래커 마늘맛 800g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000499057</t>
+  </si>
+  <si>
+    <t>[소이조이] 대두로 만든 단백질 스낵 6종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000791609</t>
+  </si>
+  <si>
+    <t>[더단백] 팝칩 12개입 3종, 택1</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000074625</t>
+  </si>
+  <si>
+    <t>[크라운] 참쌀설병 270g (30봉)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5077457</t>
+  </si>
+  <si>
+    <t>[해태] 구운 양파 110g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000349503</t>
+  </si>
+  <si>
+    <t>[카스테이블워터] 영국 크래커 4종 (택 1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5054219</t>
+  </si>
+  <si>
+    <t>[오리온] 찍먹 오감자 버터갈릭감자튀김맛 115g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001959559</t>
+  </si>
+  <si>
+    <t>[카수가이] 땅콩 간식 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000777595</t>
+  </si>
+  <si>
+    <t>[해태] 에이스 야채 291g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002225093</t>
+  </si>
+  <si>
+    <t>통연근 그대로 튀긴 연근칩 30g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5030130</t>
+  </si>
+  <si>
+    <t>[해태] 구운 고구마 135g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001317277</t>
+  </si>
+  <si>
+    <t>[롯데] 꼬깔콘 시리즈 3종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5118059</t>
+  </si>
+  <si>
+    <t>[오리온] 다이제 샌드 우도땅콩 392g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001861625</t>
+  </si>
+  <si>
+    <t>[DJ&amp;A] 크리스피 베지칩 2종, 택1</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002108866</t>
+  </si>
+  <si>
+    <t>[발센] 라이브니즈 미니스 비스킷 2종, 택1</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002221130</t>
+  </si>
+  <si>
+    <t>[반두아] 코코넛 크래커 150g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5049808</t>
+  </si>
+  <si>
+    <t>[해태] 에이스 씬 에스프레소 291g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000528989</t>
+  </si>
+  <si>
+    <t>일본 이색 센베 과자 5종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000739633</t>
+  </si>
+  <si>
+    <t>[크라운] 콘칲 군옥수수맛 148g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5121162</t>
+  </si>
+  <si>
+    <t>[올가] 국산 통밀 크리스피 크래커 3종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000891294</t>
+  </si>
+  <si>
+    <t>[농심] 육포깡 90g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002280048</t>
+  </si>
+  <si>
+    <t>[마이노멀] 밀가루 없는 제로칩 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002003498</t>
+  </si>
+  <si>
+    <t>[밀크클래식] 쌀과자 240g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000485694</t>
+  </si>
+  <si>
+    <t>[프리토스] 콘칩 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000612634</t>
+  </si>
+  <si>
+    <t>[해태] 오예스 베이크하우스 얼그레이&amp;쇼콜라 280g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002475314</t>
+  </si>
+  <si>
+    <t>[오리온] 다이제 쏙쏙포장 5종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000198198</t>
+  </si>
+  <si>
+    <t>[HBAF] 넛츠앤스낵스 땅콩 120g 5종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000147459</t>
+  </si>
+  <si>
+    <t>[긴비스] 동물모양 비스킷 138g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000030463</t>
+  </si>
+  <si>
+    <t>[아미카] 알프레도 올리브 오일 포테이토칩 130g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000525222</t>
+  </si>
+  <si>
+    <t>[속초 세렝게티커피] 티그레 6종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000330137</t>
+  </si>
+  <si>
+    <t>[로투스] 비스코프 4종, 택1</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5071375</t>
+  </si>
+  <si>
+    <t>[해태] 허니버터칩 캐슬 갈릭브레드맛 100g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001333045</t>
+  </si>
+  <si>
+    <t>[크라운] 메이플콘 74g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001406908</t>
+  </si>
+  <si>
+    <t>[해태] 가루비 감자칩 연어초밥맛 96g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002185327</t>
+  </si>
+  <si>
+    <t>[빼바] 프로틴 바삭칩 60g 2종, 택1</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002295305</t>
+  </si>
+  <si>
+    <t>[크라운] 참그레인 우리밀 192g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000506290</t>
+  </si>
+  <si>
+    <t>[로아커] 샌드 비스킷 3종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001701315</t>
+  </si>
+  <si>
+    <t>[오리온] 가짜같은 진짜, 만우절 한정 감자스낵 4종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001171286</t>
+  </si>
+  <si>
+    <t>[농심] 포스틱 84g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002129045</t>
+  </si>
+  <si>
+    <t>[해태] 허니버터칩 4번들 (40g x 4묶음)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000263120</t>
+  </si>
+  <si>
+    <t>[TEMOLE] 아몬드칩 사우어크림 40g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002131257</t>
+  </si>
+  <si>
+    <t>[게메즈] 에낙 라면스낵 스파이시 (28gX5입)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000679265</t>
+  </si>
+  <si>
+    <t>[롯데] 아몬드 팔각 빼빼로 132g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5086556</t>
+  </si>
+  <si>
+    <t>[잇츠베러] 제로슈가 쿠키 4종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000608510</t>
+  </si>
+  <si>
+    <t>[오리온] 포카칩 4개입 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000648498</t>
+  </si>
+  <si>
+    <t>[유니온] 와인 페어링 타랄리니 스낵 오리지널 35gX6개입</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001740103</t>
+  </si>
+  <si>
+    <t>[우리밀] 두부과자 100g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5004416</t>
+  </si>
+  <si>
+    <t>[워커스] 쇼트브레드 어쏘트먼트 168g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001241376</t>
+  </si>
+  <si>
+    <t>[이노센트] 저당 프로틴 크런치볼 2종</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000957506</t>
+  </si>
+  <si>
+    <t>[마켓오] 크림치즈 브라우니 240g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001391101</t>
+  </si>
+  <si>
+    <t>[아미고] 나쵸칩 454g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5009519</t>
+  </si>
+  <si>
+    <t>[오리온] 치킨팝 65g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001399104</t>
+  </si>
+  <si>
+    <t>[농심] 먹태깡 60g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000215789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[아티장 비스킷] 치즈 크래커 2종 </t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5042489</t>
+  </si>
+  <si>
+    <t>두 번 튀겨 더 고소한 맛뻥 84g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002214154</t>
+  </si>
+  <si>
+    <t>[롯데] KBO 빼빼로 화이트쿠키 10종, 택1</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002130774</t>
+  </si>
+  <si>
+    <t>[오리온] 오징어땅콩 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000757615</t>
+  </si>
+  <si>
+    <t>[로아커] 웨하스 씬 3종, 택1</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002049283</t>
+  </si>
+  <si>
+    <t>[부르본] 에브리버거 초코비스킷 66g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001100806</t>
+  </si>
+  <si>
+    <t>[롯데] 꼬깔콘 군옥수수맛 67g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001397633</t>
+  </si>
+  <si>
+    <t>[오리온] 다이제 오리지널 351g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000033205</t>
+  </si>
+  <si>
+    <t>[ALLO] 감자크래커 2종 (택1)</t>
+  </si>
+  <si>
+    <t>감자 스낵</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002014584</t>
+  </si>
+  <si>
+    <t>[오리온] 오감자 감자그라탕맛 96g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001985656</t>
+  </si>
+  <si>
+    <t>[농심] 감자깡 75g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002129012</t>
+  </si>
+  <si>
+    <t>[가루비] CALBEE 일본 감자칩 스낵 6종</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001421090</t>
+  </si>
+  <si>
+    <t>[오리온] 눈을감자 칠리치즈프라이즈 96g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001170989</t>
+  </si>
+  <si>
+    <t>[농심] 감자깡 250g (지퍼백)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5134076</t>
+  </si>
+  <si>
+    <t>[오리온] 눈을감자 96g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000640848</t>
+  </si>
+  <si>
+    <t>[가루비] 쟈가리코 감자 스낵 샐러드맛 57g x 12개입 (가루비 쟈가리코 샐러드맛 57g 12개입)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001318650</t>
+  </si>
+  <si>
+    <t>[풀무원] 특등급 국산콩 두부칩 감자 40g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001937064</t>
+  </si>
+  <si>
+    <t>[러플스] 오리지날 감자칩 184.2g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000612631</t>
+  </si>
+  <si>
+    <t>[올가] 순감자칩, 순고구마칩 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000891279</t>
+  </si>
+  <si>
+    <t>[푸르나이] 제대로 햇감자칩 2종, 택1</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002380802</t>
+  </si>
+  <si>
+    <t>[케오스] 아이리시 씨솔트 크링클 감자칩 125g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000584460</t>
+  </si>
+  <si>
+    <t>[아로마트러플] 블랙 써머 트러플 감자칩 3종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000179453</t>
+  </si>
+  <si>
+    <t>[켈로그] 프링글스 치즈맛 110g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000570013</t>
+  </si>
+  <si>
+    <t>[크라운] 어썸체다치즈 45g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002247128</t>
+  </si>
+  <si>
+    <t>[농심] 포테토칩 오리지널 160g (40g x 4봉)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002129077</t>
+  </si>
+  <si>
+    <t>[농심] 포테토칩 오리지널 110g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002129075</t>
+  </si>
+  <si>
+    <t>나들이 맞이 스낵 &amp; 캔디젤리 간식 7종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001212964</t>
+  </si>
+  <si>
+    <t>[켈로그] 프링글스 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5073031</t>
+  </si>
+  <si>
+    <t>[농심] 포테토칩 오리지널 60g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002129073</t>
+  </si>
+  <si>
+    <t>[농심] 포스틱 133g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002129047</t>
+  </si>
+  <si>
+    <t>[켈로그] 프링글스 스윗어니언맛 100g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001098485</t>
+  </si>
+  <si>
+    <t>[농심] 오리지널 봉지 과자 7종 (택1)(중사이즈)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000205257</t>
+  </si>
+  <si>
+    <t>[오리온] 즐겨요 응원의 맛 3종, 택1</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002242483</t>
+  </si>
+  <si>
+    <t>[오리온] 스윙칩 볶음고추장맛 210g (지퍼백)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5155641</t>
+  </si>
+  <si>
+    <t>[오리온] 스윙칩 까르보나라불닭맛 112g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002326317</t>
+  </si>
+  <si>
+    <t>[헌터즈] 트러플 감자칩 원형 틴 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000391076</t>
+  </si>
+  <si>
+    <t>[오리온] 찍먹 예감 마요소스맛 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001391095</t>
+  </si>
+  <si>
+    <t>[농심] 포테토칩 교촌간장치킨맛 55g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002064464</t>
+  </si>
+  <si>
+    <t>[농심] 새우깡 미니팩 30g x 4입</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000198131</t>
+  </si>
+  <si>
+    <t>[농심] 새우깡 90g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5061325</t>
+  </si>
+  <si>
+    <t>[농심] 포테토칩 K양념치킨맛 50g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002129079</t>
+  </si>
+  <si>
+    <t>[해태] 허니버터칩 미니 박스 33g x 12개입</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001228129</t>
+  </si>
+  <si>
+    <t>[부르본] 코메노칩스 2종, 택1</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002324004</t>
+  </si>
+  <si>
+    <t>[켈로그] 프링글스 매운맛 110g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000570015</t>
+  </si>
+  <si>
+    <t>[케오스] 치즈 어니언 감자칩</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000584474</t>
+  </si>
+  <si>
+    <t>[켈로그] 프링글스 버터카라멜맛 110g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000570032</t>
+  </si>
+  <si>
+    <t>[농심] 고구마깡 83g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002129009</t>
+  </si>
+  <si>
+    <t>바삭함부터 달콤함까지 인기 간식 7종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001384411</t>
+  </si>
+  <si>
+    <t>[토스티토스] 또띨라 나쵸칩 3종</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5161381</t>
+  </si>
+  <si>
+    <t>[크라운] 콘치 66g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001406961</t>
+  </si>
+  <si>
+    <t>[농심] 쌀새우깡 80g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000952281</t>
+  </si>
+  <si>
+    <t>[Lay's] 스파이시 마라맛 감자칩 170g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000927098</t>
+  </si>
+  <si>
+    <t>[상하농원] 황토고구마칩 오리지널 40g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001388382</t>
+  </si>
+  <si>
+    <t>[제주 아침미소목장] 우유샌드 234g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002207194</t>
+  </si>
+  <si>
+    <t>[농심] 양파깡 83g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002129049</t>
+  </si>
+  <si>
+    <t>[농심] 오징어집 78g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002129039</t>
+  </si>
+  <si>
+    <t>[해태] 프리츠 토마토 33g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001397641</t>
+  </si>
+  <si>
+    <t>[해태] 홈런볼 옥수수 소프트콘맛 4번들 156g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002185329</t>
+  </si>
+  <si>
+    <t>[농심] 수미칩 85g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001434820</t>
+  </si>
+  <si>
+    <t>[농심] 포테토칩 엽떡로제맛 55g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002296291</t>
+  </si>
+  <si>
+    <t>[오리온] 땅콩강정 3번들</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000365877</t>
+  </si>
+  <si>
+    <t>[스마트푸드] 화이트 체다치즈 팝콘</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5073060</t>
+  </si>
+  <si>
+    <t>[켈로그] 프링글스 미트 치즈 라자냐맛 100g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002327637</t>
+  </si>
+  <si>
+    <t>[던킨] 베이글칩 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001065190</t>
+  </si>
+  <si>
+    <t>[농심] 새우깡 블랙 72g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5136204</t>
+  </si>
+  <si>
+    <t>[크라운] 신짱 245g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5077459</t>
+  </si>
+  <si>
+    <t>[다이코] 노리텐 김부각 과자 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000858865</t>
+  </si>
+  <si>
+    <t>[크라운] 당을 줄인 신짱 300g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002492970</t>
+  </si>
+  <si>
+    <t>[게메즈] 에낙 라면스낵 150g (30g x 5개)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002326631</t>
+  </si>
+  <si>
+    <t>[치즐스] 치즈스낵 125g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002134600</t>
+  </si>
+  <si>
+    <t>[농심] 새우깡블랙 105g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001485461</t>
+  </si>
+  <si>
+    <t>[더하루] 슬라이스칩 2종, 택1</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002058181</t>
+  </si>
+  <si>
+    <t>[위메이드] 치즈 오트 크래커 56g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002313083</t>
+  </si>
+  <si>
+    <t>[일동후디스] 아이얌 두부와플 2종</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5118755</t>
+  </si>
+  <si>
+    <t>[리츠] 멕시칸 타코맛 크래커 73g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002015596</t>
+  </si>
+  <si>
+    <t>[남양] 아이꼬야 퐁 아기과자 3종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000472716</t>
+  </si>
+  <si>
+    <t>[맥케인] 포테이토 펍스 700g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5155683</t>
+  </si>
+  <si>
+    <t>[하인즈] 미니 테이터 토트 (감자볼) 793g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5114891</t>
+  </si>
+  <si>
+    <t>[HBAF] 팝콘 골라담기 7종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000942888</t>
+  </si>
+  <si>
+    <t>[잭링크스] 인기 육포 모아보기 5종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001092106</t>
+  </si>
+  <si>
+    <t>[루토사] 웨지감자 400g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001803388</t>
+  </si>
+  <si>
+    <t>[크라운] 밤양갱 50g X 5입</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000472613</t>
+  </si>
+  <si>
+    <t>[크라운] 마이쮸 토마토 120g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002369661</t>
+  </si>
+  <si>
+    <t>[오뚜기] 콘크림스프 팝콘 55g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000605483</t>
+  </si>
+  <si>
+    <t>[크라운] 엠쉘 2종, 택1</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002303054</t>
+  </si>
+  <si>
+    <t>[해태] 알사탕 319g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001397542</t>
+  </si>
+  <si>
+    <t>[HBAF] 뉴욕치즈버거맛 팝콘 80g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000960167</t>
+  </si>
+  <si>
+    <t>[농심] 나토리 치타라 어포 치즈 24g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002099803</t>
+  </si>
+  <si>
+    <t>[맥스봉] 청양고추 후랑크 80g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002104217</t>
+  </si>
+  <si>
+    <t>[CJ] 바삭팝콘 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001942437</t>
+  </si>
+  <si>
+    <t>[댄케이크] 싱글서브 버터쿠키 18입</t>
+  </si>
+  <si>
+    <t>개별포장 쿠키</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5038276</t>
+  </si>
+  <si>
+    <t>[댄케이크] 싱글서브 초콜릿칩 쿠키 18입</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5043922</t>
+  </si>
+  <si>
+    <t>[댄케이크] 2믹스 싱글서브쿠키 18입</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000639928</t>
+  </si>
+  <si>
+    <t>[생미쉘] 마들렝 150g (6개입, 개별포장)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5050887</t>
+  </si>
+  <si>
     <t>[리치] 버터 와플 270g (15g x 18입)</t>
   </si>
   <si>
     <t>https://www.kurly.com/goods/5066715</t>
-  </si>
-  <si>
-    <t>파이/케이크(개별포장)</t>
-  </si>
-  <si>
-    <t>[오리온] 초코파이 12입</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5061296</t>
-  </si>
-  <si>
-    <t>[오리온] 카스타드 12개입 276g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000875718</t>
-  </si>
-  <si>
-    <t>[오리온] 초코파이 말차쇼콜라 408g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001382646</t>
-  </si>
-  <si>
-    <t>[롯데] 몽쉘 생크림케이크 오리지널 408g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000175874</t>
-  </si>
-  <si>
-    <t>[롯데] 몽쉘 생크림케이크 카카오 408g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000175876</t>
-  </si>
-  <si>
-    <t>[해태] 오예스 미니 크림소다맛 192g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002225099</t>
-  </si>
-  <si>
-    <t>[해태] 오예스 360g 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000201444</t>
-  </si>
-  <si>
-    <t>품목수</t>
-  </si>
-  <si>
-    <t>비중</t>
-  </si>
-  <si>
-    <t>상품번호</t>
-  </si>
-  <si>
-    <t>가격</t>
-  </si>
-  <si>
-    <t>정가</t>
-  </si>
-  <si>
-    <t>할인율</t>
-  </si>
-  <si>
-    <t>품절</t>
-  </si>
-  <si>
-    <t>검색어</t>
-  </si>
-  <si>
-    <t>[마요라] 아페티토 스틱 스낵 2종, 택1</t>
-  </si>
-  <si>
-    <t>가성비 과자</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002110052</t>
-  </si>
-  <si>
-    <t>[해태] 아이비 309g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000747182</t>
-  </si>
-  <si>
-    <t>대만 누가크래커 대용량 32개입 448g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000862247</t>
-  </si>
-  <si>
-    <t>[비타비고] 이탈리안 브레드 스틱 4종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000178183</t>
-  </si>
-  <si>
-    <t>[밤부] 누가 크래커 140g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5031072</t>
-  </si>
-  <si>
-    <t>[무직타이거] 옛날과자 골라담기 5종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000875821</t>
-  </si>
-  <si>
-    <t>[포테이토 크리스프] 감자칩 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000651310</t>
-  </si>
-  <si>
-    <t>[리츠] 크래커 3종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000321598</t>
-  </si>
-  <si>
-    <t>[해태] 에이스 364g (24g x 15봉지)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5077465</t>
-  </si>
-  <si>
-    <t>[롯데] 꼬깔콘 스낵(소) 4번들</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5079319</t>
-  </si>
-  <si>
-    <t>[해태] 맛동산 304g (38g x 8팩)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5077461</t>
-  </si>
-  <si>
-    <t>[맥비티] 다이제스티브 비스킷 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000975389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[농심] 인기 봉지 과자 7종 (택1) </t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000198192</t>
-  </si>
-  <si>
-    <t>[만전김] 김스깡 3번들 (60g x 3묶음)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5151421</t>
-  </si>
-  <si>
-    <t>인기 일본과자 10종 골라담기 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001272797</t>
-  </si>
-  <si>
-    <t>[해태] 오사쯔 100g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001029494</t>
-  </si>
-  <si>
-    <t>[가렛팝콘] 프리미엄 수제 팝콘 3종 (백)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5030780</t>
-  </si>
-  <si>
-    <t>[롯데] 야채 크래커 249g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000339529</t>
-  </si>
-  <si>
-    <t>[잇츠베러] 잇츠베러 크래커 4종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5036524</t>
-  </si>
-  <si>
-    <t>홈파티 맥주 안주 간식 8종 모아보기 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000356676</t>
-  </si>
-  <si>
-    <t>[TEMOLE] 아보카도칩 3종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000963099</t>
-  </si>
-  <si>
-    <t>[마이산] 스카이 플레이크 크래커 600g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5088236</t>
-  </si>
-  <si>
-    <t>[닥터유] 단백질칩 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000617577</t>
-  </si>
-  <si>
-    <t>[비타비고] 이탈리안 스낵 비타팝 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000455773</t>
-  </si>
-  <si>
-    <t>[마마메] 템페 칩스 5종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000137075</t>
-  </si>
-  <si>
-    <t>[씬] 감자칩 3종, 택 1</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002134596</t>
-  </si>
-  <si>
-    <t>[리츠] 바삭 김 크래커 73g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001447521</t>
-  </si>
-  <si>
-    <t>[오레오] 웨하스 스틱 150g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001421531</t>
-  </si>
-  <si>
-    <t>[아미고] 나쵸칩 그랩앤고 치즈 콤보 (100g x 6입)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000269917</t>
-  </si>
-  <si>
-    <t>[크라운] 참 크래커 알프스 295g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001592465</t>
-  </si>
-  <si>
-    <t>[HBAF] 와사비맛 아몬드 190g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5054491</t>
-  </si>
-  <si>
-    <t>[더다믐] 김칩스 오리지널 44g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001919935</t>
-  </si>
-  <si>
-    <t>[크라운] 버터와플 316g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5062899</t>
-  </si>
-  <si>
-    <t>[오리온] 감자패밀리팩 대용량 180g (포카칩 &amp; 스윙칩 &amp; 오감자)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000875710</t>
-  </si>
-  <si>
-    <t>[미주라] 소이아 크래커 400g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5006818</t>
-  </si>
-  <si>
-    <t>[해태] 가루비 감자칩 오리지널 40g X 3개입</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000582944</t>
-  </si>
-  <si>
-    <t>[라아부엘라니에베스] 스페인 수제 감자칩 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000206111</t>
-  </si>
-  <si>
-    <t>[마요라] 커피조이 351g (39g X 9개입)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000643389</t>
-  </si>
-  <si>
-    <t>[해태] 가루비 감자칩 오리지널 96g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000439362</t>
-  </si>
-  <si>
-    <t>[헌터즈] 트러플 감자칩 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000166566</t>
-  </si>
-  <si>
-    <t>[DJ&amp;A] 표고버섯/베지 크리스프 3종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000526145</t>
-  </si>
-  <si>
-    <t>[베프코] 홋카이도 센베 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000789439</t>
-  </si>
-  <si>
-    <t>홈파티 와인 안주 간식 8종 모아보기 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000356687</t>
-  </si>
-  <si>
-    <t>[크라운] 인기스낵 모음 12팩</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5153242</t>
-  </si>
-  <si>
-    <t>[프롬잇] 프로틴칩 6종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000033235</t>
-  </si>
-  <si>
-    <t>[발스낵] 그랜드 감자칩 2묶음 7종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001570087</t>
-  </si>
-  <si>
-    <t>[농심] 빵부장 초코빵 55g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000942359</t>
-  </si>
-  <si>
-    <t>[해태] 계란과자 45g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001397540</t>
-  </si>
-  <si>
-    <t>[그레타] 허브 크래커 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000927112</t>
-  </si>
-  <si>
-    <t>[덴로쿠] 스낵 믹스팩 294g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5103484</t>
-  </si>
-  <si>
-    <t>[아미카] 감자칩 멀티팩 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000605988</t>
-  </si>
-  <si>
-    <t>[타코맨] 나쵸 토틸라칩 320g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5060050</t>
-  </si>
-  <si>
-    <t>[이메이] 대파 소다 크래커 225g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002324203</t>
-  </si>
-  <si>
-    <t>[크라운] 참쌀선과 253g (44봉)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000178191</t>
-  </si>
-  <si>
-    <t>[바다해] 캠핑&amp;홈파티 마른안주 플래터 360g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000914382</t>
-  </si>
-  <si>
-    <t>[ALLO] 하몽 크래커 319g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002014581</t>
-  </si>
-  <si>
-    <t>[레인코스트] 크리스프 크래커 7종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5052362</t>
-  </si>
-  <si>
-    <t>[크라운] 치즈샌드 Rich 180g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000958549</t>
-  </si>
-  <si>
-    <t>[오리온] 호호감자크래커 177g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002010936</t>
-  </si>
-  <si>
-    <t>[퀼리] 스페인 브래드스틱 6종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000242960</t>
-  </si>
-  <si>
-    <t>[롯데] 군위 사과 시리즈 11종, 택1</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002482468</t>
-  </si>
-  <si>
-    <t>[미주라] 통밀크래커 385g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5058855</t>
-  </si>
-  <si>
-    <t>대용량 트러플 카사바칩 500g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000783621</t>
-  </si>
-  <si>
-    <t>[아미카] 엘도라다 포테이토칩 대용량  400g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000525224</t>
-  </si>
-  <si>
-    <t>[오리온] 썬 핫스파이시 4번들</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000365879</t>
-  </si>
-  <si>
-    <t>[브렛츠] 감자칩 7종, 택1</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002133624</t>
-  </si>
-  <si>
-    <t>[롯데] 치토스 바비큐 164g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000339558</t>
-  </si>
-  <si>
-    <t>[크라운] 참 크래커 280g (18.67g x 15입)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5081478</t>
-  </si>
-  <si>
-    <t>[미주라] 토스트 비스켓 320g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5005540</t>
-  </si>
-  <si>
-    <t>[DJ&amp;A] 포테이토 웨지 스낵 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000526148</t>
-  </si>
-  <si>
-    <t>[빙그레] 인기스낵 4종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000677312</t>
-  </si>
-  <si>
-    <t>[크라운] 그레이스 298g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001407039</t>
-  </si>
-  <si>
-    <t>[오리온] 인기 봉지 과자 지퍼백 5종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000248448</t>
-  </si>
-  <si>
-    <t>땅콩 한입 꽈배기 520g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001027192</t>
-  </si>
-  <si>
-    <t>[오리온] 고소미 216g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5067308</t>
-  </si>
-  <si>
-    <t>[HBAF] 시그니처 팝콘 골라담기 7종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000942860</t>
-  </si>
-  <si>
-    <t>[미카쿠토] 오사츠도키 칩 2종, 택1</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001991119</t>
-  </si>
-  <si>
-    <t>[더다믐] 김칩스 매운맛 44g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5132664</t>
-  </si>
-  <si>
-    <t>[오리온] 무뚝뚝 감자칩 &amp; 고구마 스낵 3종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000640854</t>
-  </si>
-  <si>
-    <t>[마주] 버섯스낵 바삭칩 2종</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000045935</t>
-  </si>
-  <si>
-    <t>[농심] 빵부장 소금빵 55g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000349505</t>
-  </si>
-  <si>
-    <t>[PNB] 고소한 수제 전병 4종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5060582</t>
-  </si>
-  <si>
-    <t>[농심] 인기 봉지 과자 7종 골라담기 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001363953</t>
-  </si>
-  <si>
-    <t>[카수가이] 오부쿠로 와사비마메 227g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5103372</t>
-  </si>
-  <si>
-    <t>[농심] 와사비 새우깡 70g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001501063</t>
-  </si>
-  <si>
-    <t>[이토비스킷] 랑그리 크림 쿠키 2종</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000443353</t>
-  </si>
-  <si>
-    <t>[발센] 라이브니즈 비스킷 2종, 택1</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002221133</t>
-  </si>
-  <si>
-    <t>[오가마마] 바삭바삭 고구마칩 150g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000136966</t>
-  </si>
-  <si>
-    <t>[생미쉘] 비스킷 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000799985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[HBAF] 와사비마요 팝콘 80g </t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000960165</t>
-  </si>
-  <si>
-    <t>[마켓오] 브라우니 바이트 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001337989</t>
-  </si>
-  <si>
-    <t>[맥스봉] 구운풍미 마늘 후랑크 80g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002104225</t>
-  </si>
-  <si>
-    <t>[시그달] 크리스피 크래커 3종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002020133</t>
-  </si>
-  <si>
-    <t>수입 과자 10종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000360436</t>
-  </si>
-  <si>
-    <t>[해태] 버터링 골드 194g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001042362</t>
-  </si>
-  <si>
-    <t>[크런틴] 프사삭 5mm 통감자칩 4종, 택1</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002340554</t>
-  </si>
-  <si>
-    <t>[해태] 에이스 바스크 치즈 케이크 364g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000490099</t>
-  </si>
-  <si>
-    <t>[CJ] 맛군밤 4개입</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5077641</t>
-  </si>
-  <si>
-    <t>[롯데] 꼬깔콘 고소한맛 67g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001397631</t>
-  </si>
-  <si>
-    <t>[CJ] 바삭칩 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001942440</t>
-  </si>
-  <si>
-    <t>[발센] 와플텐 웨이퍼롤 2종, 택1</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002221138</t>
-  </si>
-  <si>
-    <t>[아미카] 이탈리아 감자칩 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000216544</t>
-  </si>
-  <si>
-    <t>[롯데] 쌀로별 오리지널 156g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5118057</t>
-  </si>
-  <si>
-    <t>[카메다] 소프트 사라다 145.2g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000656471</t>
-  </si>
-  <si>
-    <t>[곡물그대로21] 크리스피롤 3종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001073370</t>
-  </si>
-  <si>
-    <t>[해태] 맛동산 300g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000365868</t>
-  </si>
-  <si>
-    <t>[유니온] 와인 페어링 타랄리니 스낵 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001740101</t>
-  </si>
-  <si>
-    <t>[해태] 칼로리바란스 치즈 (38g x 7개)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000125337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[Lay's] 감자칩 7종 (택1) </t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5013230</t>
-  </si>
-  <si>
-    <t>[아티장 비스킷] 치즈를 위한 토스트 (데이츠&amp;헤이즐넛) 100g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5043538</t>
-  </si>
-  <si>
-    <t>7일 이내 로스팅한 구운 캐슈넛 200g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001382381</t>
-  </si>
-  <si>
-    <t>[다르다] 통밀칩 45g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002159262</t>
-  </si>
-  <si>
-    <t>[해태] 맛동산 3번들 210g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002286852</t>
-  </si>
-  <si>
-    <t>[하루견과] 빠삭칩 200g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5052356</t>
-  </si>
-  <si>
-    <t>[마이산] 스카이 플레이크 크래커 마늘맛 800g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000499057</t>
-  </si>
-  <si>
-    <t>[소이조이] 대두로 만든 단백질 스낵 6종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000791609</t>
-  </si>
-  <si>
-    <t>[더단백] 팝칩 12개입 3종, 택1</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000074625</t>
-  </si>
-  <si>
-    <t>[크라운] 참쌀설병 270g (30봉)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5077457</t>
-  </si>
-  <si>
-    <t>[해태] 구운 양파 110g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000349503</t>
-  </si>
-  <si>
-    <t>[카스테이블워터] 영국 크래커 4종 (택 1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5054219</t>
-  </si>
-  <si>
-    <t>[오리온] 찍먹 오감자 버터갈릭감자튀김맛 115g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001959559</t>
-  </si>
-  <si>
-    <t>[카수가이] 땅콩 간식 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000777595</t>
-  </si>
-  <si>
-    <t>[해태] 에이스 야채 291g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002225093</t>
-  </si>
-  <si>
-    <t>통연근 그대로 튀긴 연근칩 30g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5030130</t>
-  </si>
-  <si>
-    <t>[해태] 구운 고구마 135g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001317277</t>
-  </si>
-  <si>
-    <t>[롯데] 꼬깔콘 시리즈 3종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5118059</t>
-  </si>
-  <si>
-    <t>[오리온] 다이제 샌드 우도땅콩 392g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001861625</t>
-  </si>
-  <si>
-    <t>[DJ&amp;A] 크리스피 베지칩 2종, 택1</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002108866</t>
-  </si>
-  <si>
-    <t>[발센] 라이브니즈 미니스 비스킷 2종, 택1</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002221130</t>
-  </si>
-  <si>
-    <t>[반두아] 코코넛 크래커 150g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5049808</t>
-  </si>
-  <si>
-    <t>[해태] 에이스 씬 에스프레소 291g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000528989</t>
-  </si>
-  <si>
-    <t>일본 이색 센베 과자 5종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000739633</t>
-  </si>
-  <si>
-    <t>[크라운] 콘칲 군옥수수맛 148g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5121162</t>
-  </si>
-  <si>
-    <t>[올가] 국산 통밀 크리스피 크래커 3종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000891294</t>
-  </si>
-  <si>
-    <t>[농심] 육포깡 90g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002280048</t>
-  </si>
-  <si>
-    <t>[마이노멀] 밀가루 없는 제로칩 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002003498</t>
-  </si>
-  <si>
-    <t>[밀크클래식] 쌀과자 240g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000485694</t>
-  </si>
-  <si>
-    <t>[프리토스] 콘칩 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000612634</t>
-  </si>
-  <si>
-    <t>[해태] 오예스 베이크하우스 얼그레이&amp;쇼콜라 280g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002475314</t>
-  </si>
-  <si>
-    <t>[오리온] 다이제 쏙쏙포장 5종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000198198</t>
-  </si>
-  <si>
-    <t>[HBAF] 넛츠앤스낵스 땅콩 120g 5종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000147459</t>
-  </si>
-  <si>
-    <t>[긴비스] 동물모양 비스킷 138g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000030463</t>
-  </si>
-  <si>
-    <t>[아미카] 알프레도 올리브 오일 포테이토칩 130g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000525222</t>
-  </si>
-  <si>
-    <t>[속초 세렝게티커피] 티그레 6종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000330137</t>
-  </si>
-  <si>
-    <t>[로투스] 비스코프 4종, 택1</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5071375</t>
-  </si>
-  <si>
-    <t>[해태] 허니버터칩 캐슬 갈릭브레드맛 100g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001333045</t>
-  </si>
-  <si>
-    <t>[크라운] 메이플콘 74g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001406908</t>
-  </si>
-  <si>
-    <t>[해태] 가루비 감자칩 연어초밥맛 96g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002185327</t>
-  </si>
-  <si>
-    <t>[빼바] 프로틴 바삭칩 60g 2종, 택1</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002295305</t>
-  </si>
-  <si>
-    <t>[크라운] 참그레인 우리밀 192g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000506290</t>
-  </si>
-  <si>
-    <t>[로아커] 샌드 비스킷 3종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001701315</t>
-  </si>
-  <si>
-    <t>[오리온] 가짜같은 진짜, 만우절 한정 감자스낵 4종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001171286</t>
-  </si>
-  <si>
-    <t>[농심] 포스틱 84g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002129045</t>
-  </si>
-  <si>
-    <t>[해태] 허니버터칩 4번들 (40g x 4묶음)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000263120</t>
-  </si>
-  <si>
-    <t>[TEMOLE] 아몬드칩 사우어크림 40g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002131257</t>
-  </si>
-  <si>
-    <t>[게메즈] 에낙 라면스낵 스파이시 (28gX5입)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000679265</t>
-  </si>
-  <si>
-    <t>[롯데] 아몬드 팔각 빼빼로 132g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5086556</t>
-  </si>
-  <si>
-    <t>[잇츠베러] 제로슈가 쿠키 4종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000608510</t>
-  </si>
-  <si>
-    <t>[오리온] 포카칩 4개입 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000648498</t>
-  </si>
-  <si>
-    <t>[유니온] 와인 페어링 타랄리니 스낵 오리지널 35gX6개입</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001740103</t>
-  </si>
-  <si>
-    <t>[우리밀] 두부과자 100g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5004416</t>
-  </si>
-  <si>
-    <t>[워커스] 쇼트브레드 어쏘트먼트 168g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001241376</t>
-  </si>
-  <si>
-    <t>[이노센트] 저당 프로틴 크런치볼 2종</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000957506</t>
-  </si>
-  <si>
-    <t>[마켓오] 크림치즈 브라우니 240g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001391101</t>
-  </si>
-  <si>
-    <t>[아미고] 나쵸칩 454g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5009519</t>
-  </si>
-  <si>
-    <t>[오리온] 치킨팝 65g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001399104</t>
-  </si>
-  <si>
-    <t>[농심] 먹태깡 60g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000215789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[아티장 비스킷] 치즈 크래커 2종 </t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5042489</t>
-  </si>
-  <si>
-    <t>두 번 튀겨 더 고소한 맛뻥 84g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002214154</t>
-  </si>
-  <si>
-    <t>[롯데] KBO 빼빼로 화이트쿠키 10종, 택1</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002130774</t>
-  </si>
-  <si>
-    <t>[오리온] 오징어땅콩 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000757615</t>
-  </si>
-  <si>
-    <t>[로아커] 웨하스 씬 3종, 택1</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002049283</t>
-  </si>
-  <si>
-    <t>[부르본] 에브리버거 초코비스킷 66g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001100806</t>
-  </si>
-  <si>
-    <t>[롯데] 꼬깔콘 군옥수수맛 67g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001397633</t>
-  </si>
-  <si>
-    <t>[오리온] 다이제 오리지널 351g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000033205</t>
-  </si>
-  <si>
-    <t>[ALLO] 감자크래커 2종 (택1)</t>
-  </si>
-  <si>
-    <t>감자 스낵</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002014584</t>
-  </si>
-  <si>
-    <t>[오리온] 오감자 감자그라탕맛 96g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001985656</t>
-  </si>
-  <si>
-    <t>[농심] 감자깡 75g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002129012</t>
-  </si>
-  <si>
-    <t>[가루비] CALBEE 일본 감자칩 스낵 6종</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001421090</t>
-  </si>
-  <si>
-    <t>[오리온] 눈을감자 칠리치즈프라이즈 96g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001170989</t>
-  </si>
-  <si>
-    <t>[농심] 감자깡 250g (지퍼백)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5134076</t>
-  </si>
-  <si>
-    <t>[오리온] 눈을감자 96g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000640848</t>
-  </si>
-  <si>
-    <t>[가루비] 쟈가리코 감자 스낵 샐러드맛 57g x 12개입 (가루비 쟈가리코 샐러드맛 57g 12개입)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001318650</t>
-  </si>
-  <si>
-    <t>[풀무원] 특등급 국산콩 두부칩 감자 40g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001937064</t>
-  </si>
-  <si>
-    <t>[러플스] 오리지날 감자칩 184.2g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000612631</t>
-  </si>
-  <si>
-    <t>[올가] 순감자칩, 순고구마칩 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000891279</t>
-  </si>
-  <si>
-    <t>[푸르나이] 제대로 햇감자칩 2종, 택1</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002380802</t>
-  </si>
-  <si>
-    <t>[케오스] 아이리시 씨솔트 크링클 감자칩 125g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000584460</t>
-  </si>
-  <si>
-    <t>[아로마트러플] 블랙 써머 트러플 감자칩 3종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000179453</t>
-  </si>
-  <si>
-    <t>[켈로그] 프링글스 치즈맛 110g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000570013</t>
-  </si>
-  <si>
-    <t>[크라운] 어썸체다치즈 45g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002247128</t>
-  </si>
-  <si>
-    <t>[농심] 포테토칩 오리지널 160g (40g x 4봉)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002129077</t>
-  </si>
-  <si>
-    <t>[농심] 포테토칩 오리지널 110g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002129075</t>
-  </si>
-  <si>
-    <t>나들이 맞이 스낵 &amp; 캔디젤리 간식 7종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001212964</t>
-  </si>
-  <si>
-    <t>[켈로그] 프링글스 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5073031</t>
-  </si>
-  <si>
-    <t>[농심] 포테토칩 오리지널 60g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002129073</t>
-  </si>
-  <si>
-    <t>[농심] 포스틱 133g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002129047</t>
-  </si>
-  <si>
-    <t>[켈로그] 프링글스 스윗어니언맛 100g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001098485</t>
-  </si>
-  <si>
-    <t>[농심] 오리지널 봉지 과자 7종 (택1)(중사이즈)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000205257</t>
-  </si>
-  <si>
-    <t>[오리온] 즐겨요 응원의 맛 3종, 택1</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002242483</t>
-  </si>
-  <si>
-    <t>[오리온] 스윙칩 볶음고추장맛 210g (지퍼백)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5155641</t>
-  </si>
-  <si>
-    <t>[오리온] 스윙칩 까르보나라불닭맛 112g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002326317</t>
-  </si>
-  <si>
-    <t>[헌터즈] 트러플 감자칩 원형 틴 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000391076</t>
-  </si>
-  <si>
-    <t>[오리온] 찍먹 예감 마요소스맛 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001391095</t>
-  </si>
-  <si>
-    <t>[농심] 포테토칩 교촌간장치킨맛 55g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002064464</t>
-  </si>
-  <si>
-    <t>[농심] 새우깡 미니팩 30g x 4입</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000198131</t>
-  </si>
-  <si>
-    <t>[농심] 새우깡 90g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5061325</t>
-  </si>
-  <si>
-    <t>[농심] 포테토칩 K양념치킨맛 50g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002129079</t>
-  </si>
-  <si>
-    <t>[해태] 허니버터칩 미니 박스 33g x 12개입</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001228129</t>
-  </si>
-  <si>
-    <t>[부르본] 코메노칩스 2종, 택1</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002324004</t>
-  </si>
-  <si>
-    <t>[켈로그] 프링글스 매운맛 110g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000570015</t>
-  </si>
-  <si>
-    <t>[케오스] 치즈 어니언 감자칩</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000584474</t>
-  </si>
-  <si>
-    <t>[켈로그] 프링글스 버터카라멜맛 110g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000570032</t>
-  </si>
-  <si>
-    <t>[농심] 고구마깡 83g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002129009</t>
-  </si>
-  <si>
-    <t>바삭함부터 달콤함까지 인기 간식 7종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001384411</t>
-  </si>
-  <si>
-    <t>[토스티토스] 또띨라 나쵸칩 3종</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5161381</t>
-  </si>
-  <si>
-    <t>[크라운] 콘치 66g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001406961</t>
-  </si>
-  <si>
-    <t>[농심] 쌀새우깡 80g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000952281</t>
-  </si>
-  <si>
-    <t>[Lay's] 스파이시 마라맛 감자칩 170g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000927098</t>
-  </si>
-  <si>
-    <t>[상하농원] 황토고구마칩 오리지널 40g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001388382</t>
-  </si>
-  <si>
-    <t>[제주 아침미소목장] 우유샌드 234g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002207194</t>
-  </si>
-  <si>
-    <t>[농심] 양파깡 83g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002129049</t>
-  </si>
-  <si>
-    <t>[농심] 오징어집 78g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002129039</t>
-  </si>
-  <si>
-    <t>[해태] 프리츠 토마토 33g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001397641</t>
-  </si>
-  <si>
-    <t>[해태] 홈런볼 옥수수 소프트콘맛 4번들 156g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002185329</t>
-  </si>
-  <si>
-    <t>[농심] 수미칩 85g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001434820</t>
-  </si>
-  <si>
-    <t>[농심] 포테토칩 엽떡로제맛 55g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002296291</t>
-  </si>
-  <si>
-    <t>[오리온] 땅콩강정 3번들</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000365877</t>
-  </si>
-  <si>
-    <t>[스마트푸드] 화이트 체다치즈 팝콘</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5073060</t>
-  </si>
-  <si>
-    <t>[켈로그] 프링글스 미트 치즈 라자냐맛 100g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002327637</t>
-  </si>
-  <si>
-    <t>[던킨] 베이글칩 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001065190</t>
-  </si>
-  <si>
-    <t>[농심] 새우깡 블랙 72g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5136204</t>
-  </si>
-  <si>
-    <t>[크라운] 신짱 245g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5077459</t>
-  </si>
-  <si>
-    <t>[다이코] 노리텐 김부각 과자 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000858865</t>
-  </si>
-  <si>
-    <t>[크라운] 당을 줄인 신짱 300g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002492970</t>
-  </si>
-  <si>
-    <t>[게메즈] 에낙 라면스낵 150g (30g x 5개)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002326631</t>
-  </si>
-  <si>
-    <t>[치즐스] 치즈스낵 125g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002134600</t>
-  </si>
-  <si>
-    <t>[농심] 새우깡블랙 105g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001485461</t>
-  </si>
-  <si>
-    <t>[더하루] 슬라이스칩 2종, 택1</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002058181</t>
-  </si>
-  <si>
-    <t>[위메이드] 치즈 오트 크래커 56g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002313083</t>
-  </si>
-  <si>
-    <t>[일동후디스] 아이얌 두부와플 2종</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5118755</t>
-  </si>
-  <si>
-    <t>[리츠] 멕시칸 타코맛 크래커 73g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002015596</t>
-  </si>
-  <si>
-    <t>[남양] 아이꼬야 퐁 아기과자 3종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000472716</t>
-  </si>
-  <si>
-    <t>[맥케인] 포테이토 펍스 700g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5155683</t>
-  </si>
-  <si>
-    <t>[하인즈] 미니 테이터 토트 (감자볼) 793g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5114891</t>
-  </si>
-  <si>
-    <t>[HBAF] 팝콘 골라담기 7종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000942888</t>
-  </si>
-  <si>
-    <t>[잭링크스] 인기 육포 모아보기 5종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001092106</t>
-  </si>
-  <si>
-    <t>[루토사] 웨지감자 400g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001803388</t>
-  </si>
-  <si>
-    <t>[크라운] 밤양갱 50g X 5입</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000472613</t>
-  </si>
-  <si>
-    <t>[크라운] 마이쮸 토마토 120g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002369661</t>
-  </si>
-  <si>
-    <t>[오뚜기] 콘크림스프 팝콘 55g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000605483</t>
-  </si>
-  <si>
-    <t>[크라운] 엠쉘 2종, 택1</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002303054</t>
-  </si>
-  <si>
-    <t>[해태] 알사탕 319g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001397542</t>
-  </si>
-  <si>
-    <t>[HBAF] 뉴욕치즈버거맛 팝콘 80g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000960167</t>
-  </si>
-  <si>
-    <t>[농심] 나토리 치타라 어포 치즈 24g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002099803</t>
-  </si>
-  <si>
-    <t>[맥스봉] 청양고추 후랑크 80g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002104217</t>
-  </si>
-  <si>
-    <t>[CJ] 바삭팝콘 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001942437</t>
-  </si>
-  <si>
-    <t>[댄케이크] 싱글서브 버터쿠키 18입</t>
-  </si>
-  <si>
-    <t>개별포장 쿠키</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5038276</t>
-  </si>
-  <si>
-    <t>[댄케이크] 싱글서브 초콜릿칩 쿠키 18입</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5043922</t>
-  </si>
-  <si>
-    <t>[댄케이크] 2믹스 싱글서브쿠키 18입</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000639928</t>
-  </si>
-  <si>
-    <t>[브레댄코] 리얼 브라우니 쿠키 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5061562</t>
-  </si>
-  <si>
-    <t>[생미쉘] 마들렝 150g (6개입, 개별포장)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5050887</t>
   </si>
   <si>
     <t>[껠끄쇼즈] 샌드쿠키 4종 (택1)</t>
@@ -12499,14 +12499,14 @@
       </c>
       <c r="D2" s="3">
         <f>SUM(F5:F48)</f>
-        <v>498164</v>
+        <v>498344</v>
       </c>
       <c r="E2" t="s">
         <v>3</v>
       </c>
       <c r="F2" s="3">
         <f>B2-D2</f>
-        <v>1836</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -13454,20 +13454,20 @@
         <v>81</v>
       </c>
       <c r="D35" s="2">
-        <v>4780</v>
+        <v>3690</v>
       </c>
       <c r="E35">
         <v>2</v>
       </c>
       <c r="F35" s="2">
         <f>D35*E35</f>
-        <v>9560</v>
+        <v>7380</v>
       </c>
       <c r="G35">
         <v>0</v>
       </c>
       <c r="H35">
-        <v>999</v>
+        <v>9999</v>
       </c>
       <c r="I35" s="8" t="s">
         <v>82</v>
@@ -13484,14 +13484,14 @@
         <v>83</v>
       </c>
       <c r="D36" s="2">
-        <v>4200</v>
+        <v>4780</v>
       </c>
       <c r="E36">
         <v>2</v>
       </c>
       <c r="F36" s="2">
         <f>D36*E36</f>
-        <v>8400</v>
+        <v>9560</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -13514,14 +13514,14 @@
         <v>85</v>
       </c>
       <c r="D37" s="2">
-        <v>5280</v>
+        <v>4200</v>
       </c>
       <c r="E37">
         <v>2</v>
       </c>
       <c r="F37" s="2">
         <f>D37*E37</f>
-        <v>10560</v>
+        <v>8400</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -13544,20 +13544,20 @@
         <v>87</v>
       </c>
       <c r="D38" s="2">
-        <v>4780</v>
+        <v>5280</v>
       </c>
       <c r="E38">
         <v>2</v>
       </c>
       <c r="F38" s="2">
         <f>D38*E38</f>
-        <v>9560</v>
+        <v>10560</v>
       </c>
       <c r="G38">
         <v>0</v>
       </c>
       <c r="H38">
-        <v>477</v>
+        <v>999</v>
       </c>
       <c r="I38" s="8" t="s">
         <v>88</v>
@@ -13574,20 +13574,20 @@
         <v>89</v>
       </c>
       <c r="D39" s="2">
-        <v>3980</v>
+        <v>4780</v>
       </c>
       <c r="E39">
         <v>2</v>
       </c>
       <c r="F39" s="2">
         <f>D39*E39</f>
-        <v>7960</v>
+        <v>9560</v>
       </c>
       <c r="G39">
         <v>0</v>
       </c>
       <c r="H39">
-        <v>314</v>
+        <v>477</v>
       </c>
       <c r="I39" s="8" t="s">
         <v>90</v>
@@ -13604,20 +13604,20 @@
         <v>91</v>
       </c>
       <c r="D40" s="2">
-        <v>3200</v>
+        <v>3980</v>
       </c>
       <c r="E40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F40" s="2">
         <f>D40*E40</f>
-        <v>9600</v>
+        <v>7960</v>
       </c>
       <c r="G40">
         <v>0</v>
       </c>
       <c r="H40">
-        <v>215</v>
+        <v>314</v>
       </c>
       <c r="I40" s="8" t="s">
         <v>92</v>
@@ -13634,20 +13634,20 @@
         <v>93</v>
       </c>
       <c r="D41" s="2">
-        <v>3600</v>
+        <v>3200</v>
       </c>
       <c r="E41">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F41" s="2">
         <f>D41*E41</f>
-        <v>7200</v>
+        <v>9600</v>
       </c>
       <c r="G41">
         <v>0</v>
       </c>
       <c r="H41">
-        <v>999</v>
+        <v>215</v>
       </c>
       <c r="I41" s="8" t="s">
         <v>94</v>
@@ -13953,7 +13953,7 @@
       </c>
       <c r="D2" s="9">
         <f>C2/SUM($C$2:$C$8)</f>
-        <v>0.21017175066845456</v>
+        <v>0.21009583741351356</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -13970,7 +13970,7 @@
       </c>
       <c r="D3" s="9">
         <f>C3/SUM($C$2:$C$8)</f>
-        <v>0.14024297219389598</v>
+        <v>0.1401923169537508</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -13983,11 +13983,11 @@
       </c>
       <c r="C4" s="2">
         <f>SUMIF(구매목록!B5:B48,A4,구매목록!F5:F48)</f>
-        <v>91440</v>
+        <v>91620</v>
       </c>
       <c r="D4" s="9">
         <f>C4/SUM($C$2:$C$8)</f>
-        <v>0.18355401032591676</v>
+        <v>0.1838489075819113</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -14004,7 +14004,7 @@
       </c>
       <c r="D5" s="9">
         <f>C5/SUM($C$2:$C$8)</f>
-        <v>0.18451754843786383</v>
+        <v>0.18445090138538842</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -14021,7 +14021,7 @@
       </c>
       <c r="D6" s="9">
         <f>C6/SUM($C$2:$C$8)</f>
-        <v>0.1407167117656033</v>
+        <v>0.14066588541248615</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -14038,7 +14038,7 @@
       </c>
       <c r="D7" s="9">
         <f>C7/SUM($C$2:$C$8)</f>
-        <v>0.1145405930577079</v>
+        <v>0.1144992214213475</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -14055,7 +14055,7 @@
       </c>
       <c r="D8" s="9">
         <f>C8/SUM($C$2:$C$8)</f>
-        <v>0.026256413550557647</v>
+        <v>0.02624692983160227</v>
       </c>
     </row>
   </sheetData>
@@ -14475,7 +14475,7 @@
         <v>5079340</v>
       </c>
       <c r="B16" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C16">
         <v>5280</v>
@@ -14493,7 +14493,7 @@
         <v>119</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -17569,7 +17569,7 @@
         <v>5132978</v>
       </c>
       <c r="B135" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C135">
         <v>4200</v>
@@ -17587,7 +17587,7 @@
         <v>119</v>
       </c>
       <c r="I135" s="10" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="136" spans="1:9">
@@ -21310,7 +21310,7 @@
         <v>5061562</v>
       </c>
       <c r="B279" t="s">
-        <v>641</v>
+        <v>81</v>
       </c>
       <c r="C279">
         <v>3690</v>
@@ -21328,7 +21328,7 @@
         <v>635</v>
       </c>
       <c r="I279" s="10" t="s">
-        <v>642</v>
+        <v>82</v>
       </c>
     </row>
     <row r="280" spans="1:9">
@@ -21336,7 +21336,7 @@
         <v>5050887</v>
       </c>
       <c r="B280" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C280">
         <v>3980</v>
@@ -21354,7 +21354,7 @@
         <v>635</v>
       </c>
       <c r="I280" s="10" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
     </row>
     <row r="281" spans="1:9">
@@ -21362,7 +21362,7 @@
         <v>5066715</v>
       </c>
       <c r="B281" t="s">
-        <v>93</v>
+        <v>643</v>
       </c>
       <c r="C281">
         <v>3600</v>
@@ -21380,7 +21380,7 @@
         <v>635</v>
       </c>
       <c r="I281" s="10" t="s">
-        <v>94</v>
+        <v>644</v>
       </c>
     </row>
     <row r="282" spans="1:9">
@@ -23000,7 +23000,7 @@
         <v>5061939</v>
       </c>
       <c r="B344" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C344">
         <v>4780</v>
@@ -23018,7 +23018,7 @@
         <v>635</v>
       </c>
       <c r="I344" s="10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="345" spans="1:9">
@@ -23644,7 +23644,7 @@
         <v>1002110078</v>
       </c>
       <c r="B369" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C369">
         <v>3980</v>
@@ -23662,7 +23662,7 @@
         <v>635</v>
       </c>
       <c r="I369" s="10" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="370" spans="1:9">
@@ -46287,7 +46287,7 @@
         <v>1002419584</v>
       </c>
       <c r="B1225" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C1225">
         <v>3200</v>
@@ -46305,7 +46305,7 @@
         <v>2489</v>
       </c>
       <c r="I1225" s="10" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="1226" spans="1:9">
@@ -47847,7 +47847,7 @@
         <v>1001137097</v>
       </c>
       <c r="B1285" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C1285">
         <v>4780</v>
@@ -47865,7 +47865,7 @@
         <v>2489</v>
       </c>
       <c r="I1285" s="10" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="1286" spans="1:9">

--- a/다과_구매목록.xlsx
+++ b/다과_구매목록.xlsx
@@ -264,1696 +264,1696 @@
     <t>https://www.kurly.com/goods/1000339526</t>
   </si>
   <si>
+    <t>[롯데제과] 카스타드 오리지널 230g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5061939</t>
+  </si>
+  <si>
+    <t>[롯데] 칙촉 오리지널 벌크 180g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5132978</t>
+  </si>
+  <si>
+    <t>[롯데] 빈츠 204g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5079340</t>
+  </si>
+  <si>
+    <t>[오리온] 카스타드 딸기 생크림 276g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001137097</t>
+  </si>
+  <si>
+    <t>[해태] 에이스 씬 솔티카라멜 291g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002110078</t>
+  </si>
+  <si>
+    <t>[오리온] 다이제 초코 카라멜슈가맛 씬 252g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002419584</t>
+  </si>
+  <si>
+    <t>[리치] 버터 와플 270g (15g x 18입)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5066715</t>
+  </si>
+  <si>
+    <t>파이/케이크(개별포장)</t>
+  </si>
+  <si>
+    <t>[오리온] 초코파이 12입</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5061296</t>
+  </si>
+  <si>
+    <t>[오리온] 카스타드 12개입 276g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000875718</t>
+  </si>
+  <si>
+    <t>[오리온] 초코파이 말차쇼콜라 408g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001382646</t>
+  </si>
+  <si>
+    <t>[롯데] 몽쉘 생크림케이크 오리지널 408g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000175874</t>
+  </si>
+  <si>
+    <t>[롯데] 몽쉘 생크림케이크 카카오 408g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000175876</t>
+  </si>
+  <si>
+    <t>[해태] 오예스 미니 크림소다맛 192g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002225099</t>
+  </si>
+  <si>
+    <t>[해태] 오예스 360g 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000201444</t>
+  </si>
+  <si>
+    <t>품목수</t>
+  </si>
+  <si>
+    <t>비중</t>
+  </si>
+  <si>
+    <t>상품번호</t>
+  </si>
+  <si>
+    <t>가격</t>
+  </si>
+  <si>
+    <t>정가</t>
+  </si>
+  <si>
+    <t>할인율</t>
+  </si>
+  <si>
+    <t>품절</t>
+  </si>
+  <si>
+    <t>검색어</t>
+  </si>
+  <si>
+    <t>[마요라] 아페티토 스틱 스낵 2종, 택1</t>
+  </si>
+  <si>
+    <t>가성비 과자</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002110052</t>
+  </si>
+  <si>
+    <t>[해태] 아이비 309g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000747182</t>
+  </si>
+  <si>
+    <t>대만 누가크래커 대용량 32개입 448g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000862247</t>
+  </si>
+  <si>
+    <t>[비타비고] 이탈리안 브레드 스틱 4종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000178183</t>
+  </si>
+  <si>
+    <t>[밤부] 누가 크래커 140g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5031072</t>
+  </si>
+  <si>
+    <t>[무직타이거] 옛날과자 골라담기 5종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000875821</t>
+  </si>
+  <si>
+    <t>[포테이토 크리스프] 감자칩 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000651310</t>
+  </si>
+  <si>
+    <t>[리츠] 크래커 3종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000321598</t>
+  </si>
+  <si>
+    <t>[해태] 에이스 364g (24g x 15봉지)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5077465</t>
+  </si>
+  <si>
+    <t>[롯데] 꼬깔콘 스낵(소) 4번들</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5079319</t>
+  </si>
+  <si>
+    <t>[해태] 맛동산 304g (38g x 8팩)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5077461</t>
+  </si>
+  <si>
+    <t>[맥비티] 다이제스티브 비스킷 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000975389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[농심] 인기 봉지 과자 7종 (택1) </t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000198192</t>
+  </si>
+  <si>
+    <t>[만전김] 김스깡 3번들 (60g x 3묶음)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5151421</t>
+  </si>
+  <si>
+    <t>인기 일본과자 10종 골라담기 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001272797</t>
+  </si>
+  <si>
+    <t>[해태] 오사쯔 100g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001029494</t>
+  </si>
+  <si>
+    <t>[가렛팝콘] 프리미엄 수제 팝콘 3종 (백)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5030780</t>
+  </si>
+  <si>
+    <t>[롯데] 야채 크래커 249g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000339529</t>
+  </si>
+  <si>
+    <t>[잇츠베러] 잇츠베러 크래커 4종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5036524</t>
+  </si>
+  <si>
+    <t>홈파티 맥주 안주 간식 8종 모아보기 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000356676</t>
+  </si>
+  <si>
+    <t>[TEMOLE] 아보카도칩 3종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000963099</t>
+  </si>
+  <si>
+    <t>[마이산] 스카이 플레이크 크래커 600g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5088236</t>
+  </si>
+  <si>
+    <t>[닥터유] 단백질칩 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000617577</t>
+  </si>
+  <si>
+    <t>[비타비고] 이탈리안 스낵 비타팝 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000455773</t>
+  </si>
+  <si>
+    <t>[마마메] 템페 칩스 5종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000137075</t>
+  </si>
+  <si>
+    <t>[씬] 감자칩 3종, 택 1</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002134596</t>
+  </si>
+  <si>
+    <t>[리츠] 바삭 김 크래커 73g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001447521</t>
+  </si>
+  <si>
+    <t>[오레오] 웨하스 스틱 150g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001421531</t>
+  </si>
+  <si>
+    <t>[아미고] 나쵸칩 그랩앤고 치즈 콤보 (100g x 6입)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000269917</t>
+  </si>
+  <si>
+    <t>[크라운] 참 크래커 알프스 295g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001592465</t>
+  </si>
+  <si>
+    <t>[HBAF] 와사비맛 아몬드 190g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5054491</t>
+  </si>
+  <si>
+    <t>[더다믐] 김칩스 오리지널 44g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001919935</t>
+  </si>
+  <si>
+    <t>[크라운] 버터와플 316g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5062899</t>
+  </si>
+  <si>
+    <t>[오리온] 감자패밀리팩 대용량 180g (포카칩 &amp; 스윙칩 &amp; 오감자)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000875710</t>
+  </si>
+  <si>
+    <t>[미주라] 소이아 크래커 400g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5006818</t>
+  </si>
+  <si>
+    <t>[해태] 가루비 감자칩 오리지널 40g X 3개입</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000582944</t>
+  </si>
+  <si>
+    <t>[라아부엘라니에베스] 스페인 수제 감자칩 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000206111</t>
+  </si>
+  <si>
+    <t>[마요라] 커피조이 351g (39g X 9개입)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000643389</t>
+  </si>
+  <si>
+    <t>[해태] 가루비 감자칩 오리지널 96g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000439362</t>
+  </si>
+  <si>
+    <t>[헌터즈] 트러플 감자칩 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000166566</t>
+  </si>
+  <si>
+    <t>[DJ&amp;A] 표고버섯/베지 크리스프 3종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000526145</t>
+  </si>
+  <si>
+    <t>[베프코] 홋카이도 센베 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000789439</t>
+  </si>
+  <si>
+    <t>홈파티 와인 안주 간식 8종 모아보기 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000356687</t>
+  </si>
+  <si>
+    <t>[크라운] 인기스낵 모음 12팩</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5153242</t>
+  </si>
+  <si>
+    <t>[프롬잇] 프로틴칩 6종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000033235</t>
+  </si>
+  <si>
+    <t>[발스낵] 그랜드 감자칩 2묶음 7종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001570087</t>
+  </si>
+  <si>
+    <t>[농심] 빵부장 초코빵 55g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000942359</t>
+  </si>
+  <si>
+    <t>[해태] 계란과자 45g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001397540</t>
+  </si>
+  <si>
+    <t>[그레타] 허브 크래커 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000927112</t>
+  </si>
+  <si>
+    <t>[덴로쿠] 스낵 믹스팩 294g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5103484</t>
+  </si>
+  <si>
+    <t>[아미카] 감자칩 멀티팩 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000605988</t>
+  </si>
+  <si>
+    <t>[타코맨] 나쵸 토틸라칩 320g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5060050</t>
+  </si>
+  <si>
+    <t>[이메이] 대파 소다 크래커 225g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002324203</t>
+  </si>
+  <si>
+    <t>[크라운] 참쌀선과 253g (44봉)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000178191</t>
+  </si>
+  <si>
+    <t>[바다해] 캠핑&amp;홈파티 마른안주 플래터 360g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000914382</t>
+  </si>
+  <si>
+    <t>[ALLO] 하몽 크래커 319g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002014581</t>
+  </si>
+  <si>
+    <t>[레인코스트] 크리스프 크래커 7종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5052362</t>
+  </si>
+  <si>
+    <t>[크라운] 치즈샌드 Rich 180g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000958549</t>
+  </si>
+  <si>
+    <t>[오리온] 호호감자크래커 177g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002010936</t>
+  </si>
+  <si>
+    <t>[퀼리] 스페인 브래드스틱 6종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000242960</t>
+  </si>
+  <si>
+    <t>[롯데] 군위 사과 시리즈 11종, 택1</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002482468</t>
+  </si>
+  <si>
+    <t>[미주라] 통밀크래커 385g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5058855</t>
+  </si>
+  <si>
+    <t>대용량 트러플 카사바칩 500g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000783621</t>
+  </si>
+  <si>
+    <t>[아미카] 엘도라다 포테이토칩 대용량  400g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000525224</t>
+  </si>
+  <si>
+    <t>[오리온] 썬 핫스파이시 4번들</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000365879</t>
+  </si>
+  <si>
+    <t>[브렛츠] 감자칩 7종, 택1</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002133624</t>
+  </si>
+  <si>
+    <t>[롯데] 치토스 바비큐 164g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000339558</t>
+  </si>
+  <si>
+    <t>[크라운] 참 크래커 280g (18.67g x 15입)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5081478</t>
+  </si>
+  <si>
+    <t>[미주라] 토스트 비스켓 320g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5005540</t>
+  </si>
+  <si>
+    <t>[DJ&amp;A] 포테이토 웨지 스낵 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000526148</t>
+  </si>
+  <si>
+    <t>[빙그레] 인기스낵 4종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000677312</t>
+  </si>
+  <si>
+    <t>[크라운] 그레이스 298g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001407039</t>
+  </si>
+  <si>
+    <t>[오리온] 인기 봉지 과자 지퍼백 5종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000248448</t>
+  </si>
+  <si>
+    <t>땅콩 한입 꽈배기 520g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001027192</t>
+  </si>
+  <si>
+    <t>[오리온] 고소미 216g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5067308</t>
+  </si>
+  <si>
+    <t>[HBAF] 시그니처 팝콘 골라담기 7종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000942860</t>
+  </si>
+  <si>
+    <t>[미카쿠토] 오사츠도키 칩 2종, 택1</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001991119</t>
+  </si>
+  <si>
+    <t>[더다믐] 김칩스 매운맛 44g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5132664</t>
+  </si>
+  <si>
+    <t>[오리온] 무뚝뚝 감자칩 &amp; 고구마 스낵 3종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000640854</t>
+  </si>
+  <si>
+    <t>[마주] 버섯스낵 바삭칩 2종</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000045935</t>
+  </si>
+  <si>
+    <t>[농심] 빵부장 소금빵 55g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000349505</t>
+  </si>
+  <si>
+    <t>[PNB] 고소한 수제 전병 4종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5060582</t>
+  </si>
+  <si>
+    <t>[농심] 인기 봉지 과자 7종 골라담기 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001363953</t>
+  </si>
+  <si>
+    <t>[카수가이] 오부쿠로 와사비마메 227g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5103372</t>
+  </si>
+  <si>
+    <t>[농심] 와사비 새우깡 70g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001501063</t>
+  </si>
+  <si>
+    <t>[이토비스킷] 랑그리 크림 쿠키 2종</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000443353</t>
+  </si>
+  <si>
+    <t>[발센] 라이브니즈 비스킷 2종, 택1</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002221133</t>
+  </si>
+  <si>
+    <t>[오가마마] 바삭바삭 고구마칩 150g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000136966</t>
+  </si>
+  <si>
+    <t>[생미쉘] 비스킷 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000799985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[HBAF] 와사비마요 팝콘 80g </t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000960165</t>
+  </si>
+  <si>
+    <t>[마켓오] 브라우니 바이트 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001337989</t>
+  </si>
+  <si>
+    <t>[맥스봉] 구운풍미 마늘 후랑크 80g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002104225</t>
+  </si>
+  <si>
+    <t>[시그달] 크리스피 크래커 3종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002020133</t>
+  </si>
+  <si>
+    <t>수입 과자 10종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000360436</t>
+  </si>
+  <si>
+    <t>[해태] 버터링 골드 194g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001042362</t>
+  </si>
+  <si>
+    <t>[크런틴] 프사삭 5mm 통감자칩 4종, 택1</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002340554</t>
+  </si>
+  <si>
+    <t>[해태] 에이스 바스크 치즈 케이크 364g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000490099</t>
+  </si>
+  <si>
+    <t>[CJ] 맛군밤 4개입</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5077641</t>
+  </si>
+  <si>
+    <t>[롯데] 꼬깔콘 고소한맛 67g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001397631</t>
+  </si>
+  <si>
+    <t>[CJ] 바삭칩 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001942440</t>
+  </si>
+  <si>
+    <t>[발센] 와플텐 웨이퍼롤 2종, 택1</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002221138</t>
+  </si>
+  <si>
+    <t>[아미카] 이탈리아 감자칩 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000216544</t>
+  </si>
+  <si>
+    <t>[롯데] 쌀로별 오리지널 156g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5118057</t>
+  </si>
+  <si>
+    <t>[카메다] 소프트 사라다 145.2g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000656471</t>
+  </si>
+  <si>
+    <t>[곡물그대로21] 크리스피롤 3종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001073370</t>
+  </si>
+  <si>
+    <t>[해태] 맛동산 300g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000365868</t>
+  </si>
+  <si>
+    <t>[유니온] 와인 페어링 타랄리니 스낵 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001740101</t>
+  </si>
+  <si>
+    <t>[해태] 칼로리바란스 치즈 (38g x 7개)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000125337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Lay's] 감자칩 7종 (택1) </t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5013230</t>
+  </si>
+  <si>
+    <t>[아티장 비스킷] 치즈를 위한 토스트 (데이츠&amp;헤이즐넛) 100g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5043538</t>
+  </si>
+  <si>
+    <t>7일 이내 로스팅한 구운 캐슈넛 200g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001382381</t>
+  </si>
+  <si>
+    <t>[다르다] 통밀칩 45g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002159262</t>
+  </si>
+  <si>
+    <t>[해태] 맛동산 3번들 210g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002286852</t>
+  </si>
+  <si>
+    <t>[하루견과] 빠삭칩 200g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5052356</t>
+  </si>
+  <si>
+    <t>[마이산] 스카이 플레이크 크래커 마늘맛 800g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000499057</t>
+  </si>
+  <si>
+    <t>[소이조이] 대두로 만든 단백질 스낵 6종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000791609</t>
+  </si>
+  <si>
+    <t>[더단백] 팝칩 12개입 3종, 택1</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000074625</t>
+  </si>
+  <si>
+    <t>[크라운] 참쌀설병 270g (30봉)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5077457</t>
+  </si>
+  <si>
+    <t>[해태] 구운 양파 110g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000349503</t>
+  </si>
+  <si>
+    <t>[카스테이블워터] 영국 크래커 4종 (택 1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5054219</t>
+  </si>
+  <si>
+    <t>[오리온] 찍먹 오감자 버터갈릭감자튀김맛 115g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001959559</t>
+  </si>
+  <si>
+    <t>[카수가이] 땅콩 간식 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000777595</t>
+  </si>
+  <si>
+    <t>[해태] 에이스 야채 291g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002225093</t>
+  </si>
+  <si>
+    <t>통연근 그대로 튀긴 연근칩 30g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5030130</t>
+  </si>
+  <si>
+    <t>[해태] 구운 고구마 135g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001317277</t>
+  </si>
+  <si>
+    <t>[롯데] 꼬깔콘 시리즈 3종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5118059</t>
+  </si>
+  <si>
+    <t>[오리온] 다이제 샌드 우도땅콩 392g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001861625</t>
+  </si>
+  <si>
+    <t>[DJ&amp;A] 크리스피 베지칩 2종, 택1</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002108866</t>
+  </si>
+  <si>
+    <t>[발센] 라이브니즈 미니스 비스킷 2종, 택1</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002221130</t>
+  </si>
+  <si>
+    <t>[반두아] 코코넛 크래커 150g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5049808</t>
+  </si>
+  <si>
+    <t>[해태] 에이스 씬 에스프레소 291g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000528989</t>
+  </si>
+  <si>
+    <t>일본 이색 센베 과자 5종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000739633</t>
+  </si>
+  <si>
+    <t>[크라운] 콘칲 군옥수수맛 148g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5121162</t>
+  </si>
+  <si>
+    <t>[올가] 국산 통밀 크리스피 크래커 3종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000891294</t>
+  </si>
+  <si>
+    <t>[농심] 육포깡 90g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002280048</t>
+  </si>
+  <si>
+    <t>[마이노멀] 밀가루 없는 제로칩 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002003498</t>
+  </si>
+  <si>
+    <t>[밀크클래식] 쌀과자 240g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000485694</t>
+  </si>
+  <si>
+    <t>[프리토스] 콘칩 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000612634</t>
+  </si>
+  <si>
+    <t>[해태] 오예스 베이크하우스 얼그레이&amp;쇼콜라 280g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002475314</t>
+  </si>
+  <si>
+    <t>[오리온] 다이제 쏙쏙포장 5종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000198198</t>
+  </si>
+  <si>
+    <t>[HBAF] 넛츠앤스낵스 땅콩 120g 5종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000147459</t>
+  </si>
+  <si>
+    <t>[긴비스] 동물모양 비스킷 138g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000030463</t>
+  </si>
+  <si>
+    <t>[아미카] 알프레도 올리브 오일 포테이토칩 130g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000525222</t>
+  </si>
+  <si>
+    <t>[속초 세렝게티커피] 티그레 6종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000330137</t>
+  </si>
+  <si>
+    <t>[로투스] 비스코프 4종, 택1</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5071375</t>
+  </si>
+  <si>
+    <t>[해태] 허니버터칩 캐슬 갈릭브레드맛 100g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001333045</t>
+  </si>
+  <si>
+    <t>[크라운] 메이플콘 74g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001406908</t>
+  </si>
+  <si>
+    <t>[해태] 가루비 감자칩 연어초밥맛 96g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002185327</t>
+  </si>
+  <si>
+    <t>[빼바] 프로틴 바삭칩 60g 2종, 택1</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002295305</t>
+  </si>
+  <si>
+    <t>[크라운] 참그레인 우리밀 192g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000506290</t>
+  </si>
+  <si>
+    <t>[로아커] 샌드 비스킷 3종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001701315</t>
+  </si>
+  <si>
+    <t>[오리온] 가짜같은 진짜, 만우절 한정 감자스낵 4종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001171286</t>
+  </si>
+  <si>
+    <t>[농심] 포스틱 84g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002129045</t>
+  </si>
+  <si>
+    <t>[해태] 허니버터칩 4번들 (40g x 4묶음)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000263120</t>
+  </si>
+  <si>
+    <t>[TEMOLE] 아몬드칩 사우어크림 40g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002131257</t>
+  </si>
+  <si>
+    <t>[게메즈] 에낙 라면스낵 스파이시 (28gX5입)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000679265</t>
+  </si>
+  <si>
+    <t>[롯데] 아몬드 팔각 빼빼로 132g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5086556</t>
+  </si>
+  <si>
+    <t>[잇츠베러] 제로슈가 쿠키 4종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000608510</t>
+  </si>
+  <si>
+    <t>[오리온] 포카칩 4개입 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000648498</t>
+  </si>
+  <si>
+    <t>[유니온] 와인 페어링 타랄리니 스낵 오리지널 35gX6개입</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001740103</t>
+  </si>
+  <si>
+    <t>[우리밀] 두부과자 100g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5004416</t>
+  </si>
+  <si>
+    <t>[워커스] 쇼트브레드 어쏘트먼트 168g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001241376</t>
+  </si>
+  <si>
+    <t>[이노센트] 저당 프로틴 크런치볼 2종</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000957506</t>
+  </si>
+  <si>
+    <t>[마켓오] 크림치즈 브라우니 240g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001391101</t>
+  </si>
+  <si>
+    <t>[아미고] 나쵸칩 454g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5009519</t>
+  </si>
+  <si>
+    <t>[오리온] 치킨팝 65g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001399104</t>
+  </si>
+  <si>
+    <t>[농심] 먹태깡 60g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000215789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[아티장 비스킷] 치즈 크래커 2종 </t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5042489</t>
+  </si>
+  <si>
+    <t>두 번 튀겨 더 고소한 맛뻥 84g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002214154</t>
+  </si>
+  <si>
+    <t>[롯데] KBO 빼빼로 화이트쿠키 10종, 택1</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002130774</t>
+  </si>
+  <si>
+    <t>[오리온] 오징어땅콩 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000757615</t>
+  </si>
+  <si>
+    <t>[로아커] 웨하스 씬 3종, 택1</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002049283</t>
+  </si>
+  <si>
+    <t>[부르본] 에브리버거 초코비스킷 66g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001100806</t>
+  </si>
+  <si>
+    <t>[롯데] 꼬깔콘 군옥수수맛 67g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001397633</t>
+  </si>
+  <si>
+    <t>[오리온] 다이제 오리지널 351g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000033205</t>
+  </si>
+  <si>
+    <t>[ALLO] 감자크래커 2종 (택1)</t>
+  </si>
+  <si>
+    <t>감자 스낵</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002014584</t>
+  </si>
+  <si>
+    <t>[오리온] 오감자 감자그라탕맛 96g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001985656</t>
+  </si>
+  <si>
+    <t>[농심] 감자깡 75g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002129012</t>
+  </si>
+  <si>
+    <t>[가루비] CALBEE 일본 감자칩 스낵 6종</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001421090</t>
+  </si>
+  <si>
+    <t>[오리온] 눈을감자 칠리치즈프라이즈 96g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001170989</t>
+  </si>
+  <si>
+    <t>[농심] 감자깡 250g (지퍼백)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5134076</t>
+  </si>
+  <si>
+    <t>[오리온] 눈을감자 96g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000640848</t>
+  </si>
+  <si>
+    <t>[가루비] 쟈가리코 감자 스낵 샐러드맛 57g x 12개입 (가루비 쟈가리코 샐러드맛 57g 12개입)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001318650</t>
+  </si>
+  <si>
+    <t>[풀무원] 특등급 국산콩 두부칩 감자 40g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001937064</t>
+  </si>
+  <si>
+    <t>[러플스] 오리지날 감자칩 184.2g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000612631</t>
+  </si>
+  <si>
+    <t>[올가] 순감자칩, 순고구마칩 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000891279</t>
+  </si>
+  <si>
+    <t>[푸르나이] 제대로 햇감자칩 2종, 택1</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002380802</t>
+  </si>
+  <si>
+    <t>[케오스] 아이리시 씨솔트 크링클 감자칩 125g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000584460</t>
+  </si>
+  <si>
+    <t>[아로마트러플] 블랙 써머 트러플 감자칩 3종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000179453</t>
+  </si>
+  <si>
+    <t>[켈로그] 프링글스 치즈맛 110g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000570013</t>
+  </si>
+  <si>
+    <t>[크라운] 어썸체다치즈 45g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002247128</t>
+  </si>
+  <si>
+    <t>[농심] 포테토칩 오리지널 160g (40g x 4봉)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002129077</t>
+  </si>
+  <si>
+    <t>[농심] 포테토칩 오리지널 110g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002129075</t>
+  </si>
+  <si>
+    <t>나들이 맞이 스낵 &amp; 캔디젤리 간식 7종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001212964</t>
+  </si>
+  <si>
+    <t>[켈로그] 프링글스 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5073031</t>
+  </si>
+  <si>
+    <t>[농심] 포테토칩 오리지널 60g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002129073</t>
+  </si>
+  <si>
+    <t>[농심] 포스틱 133g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002129047</t>
+  </si>
+  <si>
+    <t>[켈로그] 프링글스 스윗어니언맛 100g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001098485</t>
+  </si>
+  <si>
+    <t>[농심] 오리지널 봉지 과자 7종 (택1)(중사이즈)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000205257</t>
+  </si>
+  <si>
+    <t>[오리온] 즐겨요 응원의 맛 3종, 택1</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002242483</t>
+  </si>
+  <si>
+    <t>[오리온] 스윙칩 볶음고추장맛 210g (지퍼백)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5155641</t>
+  </si>
+  <si>
+    <t>[오리온] 스윙칩 까르보나라불닭맛 112g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002326317</t>
+  </si>
+  <si>
+    <t>[헌터즈] 트러플 감자칩 원형 틴 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000391076</t>
+  </si>
+  <si>
+    <t>[오리온] 찍먹 예감 마요소스맛 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001391095</t>
+  </si>
+  <si>
+    <t>[농심] 포테토칩 교촌간장치킨맛 55g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002064464</t>
+  </si>
+  <si>
+    <t>[농심] 새우깡 미니팩 30g x 4입</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000198131</t>
+  </si>
+  <si>
+    <t>[농심] 새우깡 90g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5061325</t>
+  </si>
+  <si>
+    <t>[농심] 포테토칩 K양념치킨맛 50g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002129079</t>
+  </si>
+  <si>
+    <t>[해태] 허니버터칩 미니 박스 33g x 12개입</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001228129</t>
+  </si>
+  <si>
+    <t>[부르본] 코메노칩스 2종, 택1</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002324004</t>
+  </si>
+  <si>
+    <t>[켈로그] 프링글스 매운맛 110g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000570015</t>
+  </si>
+  <si>
+    <t>[케오스] 치즈 어니언 감자칩</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000584474</t>
+  </si>
+  <si>
+    <t>[켈로그] 프링글스 버터카라멜맛 110g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000570032</t>
+  </si>
+  <si>
+    <t>[농심] 고구마깡 83g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002129009</t>
+  </si>
+  <si>
+    <t>바삭함부터 달콤함까지 인기 간식 7종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001384411</t>
+  </si>
+  <si>
+    <t>[토스티토스] 또띨라 나쵸칩 3종</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5161381</t>
+  </si>
+  <si>
+    <t>[크라운] 콘치 66g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001406961</t>
+  </si>
+  <si>
+    <t>[농심] 쌀새우깡 80g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000952281</t>
+  </si>
+  <si>
+    <t>[Lay's] 스파이시 마라맛 감자칩 170g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000927098</t>
+  </si>
+  <si>
+    <t>[상하농원] 황토고구마칩 오리지널 40g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001388382</t>
+  </si>
+  <si>
+    <t>[제주 아침미소목장] 우유샌드 234g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002207194</t>
+  </si>
+  <si>
+    <t>[농심] 양파깡 83g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002129049</t>
+  </si>
+  <si>
+    <t>[농심] 오징어집 78g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002129039</t>
+  </si>
+  <si>
+    <t>[해태] 프리츠 토마토 33g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001397641</t>
+  </si>
+  <si>
+    <t>[해태] 홈런볼 옥수수 소프트콘맛 4번들 156g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002185329</t>
+  </si>
+  <si>
+    <t>[농심] 수미칩 85g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001434820</t>
+  </si>
+  <si>
+    <t>[농심] 포테토칩 엽떡로제맛 55g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002296291</t>
+  </si>
+  <si>
+    <t>[오리온] 땅콩강정 3번들</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000365877</t>
+  </si>
+  <si>
+    <t>[스마트푸드] 화이트 체다치즈 팝콘</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5073060</t>
+  </si>
+  <si>
+    <t>[켈로그] 프링글스 미트 치즈 라자냐맛 100g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002327637</t>
+  </si>
+  <si>
+    <t>[던킨] 베이글칩 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001065190</t>
+  </si>
+  <si>
+    <t>[농심] 새우깡 블랙 72g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5136204</t>
+  </si>
+  <si>
+    <t>[크라운] 신짱 245g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5077459</t>
+  </si>
+  <si>
+    <t>[다이코] 노리텐 김부각 과자 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000858865</t>
+  </si>
+  <si>
+    <t>[크라운] 당을 줄인 신짱 300g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002492970</t>
+  </si>
+  <si>
+    <t>[게메즈] 에낙 라면스낵 150g (30g x 5개)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002326631</t>
+  </si>
+  <si>
+    <t>[치즐스] 치즈스낵 125g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002134600</t>
+  </si>
+  <si>
+    <t>[농심] 새우깡블랙 105g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001485461</t>
+  </si>
+  <si>
+    <t>[더하루] 슬라이스칩 2종, 택1</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002058181</t>
+  </si>
+  <si>
+    <t>[위메이드] 치즈 오트 크래커 56g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002313083</t>
+  </si>
+  <si>
+    <t>[일동후디스] 아이얌 두부와플 2종</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5118755</t>
+  </si>
+  <si>
+    <t>[리츠] 멕시칸 타코맛 크래커 73g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002015596</t>
+  </si>
+  <si>
+    <t>[남양] 아이꼬야 퐁 아기과자 3종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000472716</t>
+  </si>
+  <si>
+    <t>[맥케인] 포테이토 펍스 700g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5155683</t>
+  </si>
+  <si>
+    <t>[하인즈] 미니 테이터 토트 (감자볼) 793g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5114891</t>
+  </si>
+  <si>
+    <t>[HBAF] 팝콘 골라담기 7종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000942888</t>
+  </si>
+  <si>
+    <t>[잭링크스] 인기 육포 모아보기 5종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001092106</t>
+  </si>
+  <si>
+    <t>[루토사] 웨지감자 400g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001803388</t>
+  </si>
+  <si>
+    <t>[크라운] 밤양갱 50g X 5입</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000472613</t>
+  </si>
+  <si>
+    <t>[크라운] 마이쮸 토마토 120g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002369661</t>
+  </si>
+  <si>
+    <t>[오뚜기] 콘크림스프 팝콘 55g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000605483</t>
+  </si>
+  <si>
+    <t>[크라운] 엠쉘 2종, 택1</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002303054</t>
+  </si>
+  <si>
+    <t>[해태] 알사탕 319g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001397542</t>
+  </si>
+  <si>
+    <t>[HBAF] 뉴욕치즈버거맛 팝콘 80g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000960167</t>
+  </si>
+  <si>
+    <t>[농심] 나토리 치타라 어포 치즈 24g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002099803</t>
+  </si>
+  <si>
+    <t>[맥스봉] 청양고추 후랑크 80g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002104217</t>
+  </si>
+  <si>
+    <t>[CJ] 바삭팝콘 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1001942437</t>
+  </si>
+  <si>
+    <t>[댄케이크] 싱글서브 버터쿠키 18입</t>
+  </si>
+  <si>
+    <t>개별포장 쿠키</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5038276</t>
+  </si>
+  <si>
+    <t>[댄케이크] 싱글서브 초콜릿칩 쿠키 18입</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5043922</t>
+  </si>
+  <si>
+    <t>[댄케이크] 2믹스 싱글서브쿠키 18입</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000639928</t>
+  </si>
+  <si>
     <t>[브레댄코] 리얼 브라우니 쿠키 2종 (택1)</t>
   </si>
   <si>
     <t>https://www.kurly.com/goods/5061562</t>
   </si>
   <si>
-    <t>[롯데제과] 카스타드 오리지널 230g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5061939</t>
-  </si>
-  <si>
-    <t>[롯데] 칙촉 오리지널 벌크 180g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5132978</t>
-  </si>
-  <si>
-    <t>[롯데] 빈츠 204g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5079340</t>
-  </si>
-  <si>
-    <t>[오리온] 카스타드 딸기 생크림 276g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001137097</t>
-  </si>
-  <si>
-    <t>[해태] 에이스 씬 솔티카라멜 291g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002110078</t>
-  </si>
-  <si>
-    <t>[오리온] 다이제 초코 카라멜슈가맛 씬 252g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002419584</t>
-  </si>
-  <si>
-    <t>파이/케이크(개별포장)</t>
-  </si>
-  <si>
-    <t>[오리온] 초코파이 12입</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5061296</t>
-  </si>
-  <si>
-    <t>[오리온] 카스타드 12개입 276g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000875718</t>
-  </si>
-  <si>
-    <t>[오리온] 초코파이 말차쇼콜라 408g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001382646</t>
-  </si>
-  <si>
-    <t>[롯데] 몽쉘 생크림케이크 오리지널 408g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000175874</t>
-  </si>
-  <si>
-    <t>[롯데] 몽쉘 생크림케이크 카카오 408g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000175876</t>
-  </si>
-  <si>
-    <t>[해태] 오예스 미니 크림소다맛 192g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002225099</t>
-  </si>
-  <si>
-    <t>[해태] 오예스 360g 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000201444</t>
-  </si>
-  <si>
-    <t>품목수</t>
-  </si>
-  <si>
-    <t>비중</t>
-  </si>
-  <si>
-    <t>상품번호</t>
-  </si>
-  <si>
-    <t>가격</t>
-  </si>
-  <si>
-    <t>정가</t>
-  </si>
-  <si>
-    <t>할인율</t>
-  </si>
-  <si>
-    <t>품절</t>
-  </si>
-  <si>
-    <t>검색어</t>
-  </si>
-  <si>
-    <t>[마요라] 아페티토 스틱 스낵 2종, 택1</t>
-  </si>
-  <si>
-    <t>가성비 과자</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002110052</t>
-  </si>
-  <si>
-    <t>[해태] 아이비 309g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000747182</t>
-  </si>
-  <si>
-    <t>대만 누가크래커 대용량 32개입 448g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000862247</t>
-  </si>
-  <si>
-    <t>[비타비고] 이탈리안 브레드 스틱 4종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000178183</t>
-  </si>
-  <si>
-    <t>[밤부] 누가 크래커 140g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5031072</t>
-  </si>
-  <si>
-    <t>[무직타이거] 옛날과자 골라담기 5종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000875821</t>
-  </si>
-  <si>
-    <t>[포테이토 크리스프] 감자칩 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000651310</t>
-  </si>
-  <si>
-    <t>[리츠] 크래커 3종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000321598</t>
-  </si>
-  <si>
-    <t>[해태] 에이스 364g (24g x 15봉지)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5077465</t>
-  </si>
-  <si>
-    <t>[롯데] 꼬깔콘 스낵(소) 4번들</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5079319</t>
-  </si>
-  <si>
-    <t>[해태] 맛동산 304g (38g x 8팩)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5077461</t>
-  </si>
-  <si>
-    <t>[맥비티] 다이제스티브 비스킷 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000975389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[농심] 인기 봉지 과자 7종 (택1) </t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000198192</t>
-  </si>
-  <si>
-    <t>[만전김] 김스깡 3번들 (60g x 3묶음)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5151421</t>
-  </si>
-  <si>
-    <t>인기 일본과자 10종 골라담기 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001272797</t>
-  </si>
-  <si>
-    <t>[해태] 오사쯔 100g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001029494</t>
-  </si>
-  <si>
-    <t>[가렛팝콘] 프리미엄 수제 팝콘 3종 (백)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5030780</t>
-  </si>
-  <si>
-    <t>[롯데] 야채 크래커 249g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000339529</t>
-  </si>
-  <si>
-    <t>[잇츠베러] 잇츠베러 크래커 4종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5036524</t>
-  </si>
-  <si>
-    <t>홈파티 맥주 안주 간식 8종 모아보기 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000356676</t>
-  </si>
-  <si>
-    <t>[TEMOLE] 아보카도칩 3종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000963099</t>
-  </si>
-  <si>
-    <t>[마이산] 스카이 플레이크 크래커 600g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5088236</t>
-  </si>
-  <si>
-    <t>[닥터유] 단백질칩 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000617577</t>
-  </si>
-  <si>
-    <t>[비타비고] 이탈리안 스낵 비타팝 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000455773</t>
-  </si>
-  <si>
-    <t>[마마메] 템페 칩스 5종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000137075</t>
-  </si>
-  <si>
-    <t>[씬] 감자칩 3종, 택 1</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002134596</t>
-  </si>
-  <si>
-    <t>[리츠] 바삭 김 크래커 73g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001447521</t>
-  </si>
-  <si>
-    <t>[오레오] 웨하스 스틱 150g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001421531</t>
-  </si>
-  <si>
-    <t>[아미고] 나쵸칩 그랩앤고 치즈 콤보 (100g x 6입)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000269917</t>
-  </si>
-  <si>
-    <t>[크라운] 참 크래커 알프스 295g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001592465</t>
-  </si>
-  <si>
-    <t>[HBAF] 와사비맛 아몬드 190g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5054491</t>
-  </si>
-  <si>
-    <t>[더다믐] 김칩스 오리지널 44g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001919935</t>
-  </si>
-  <si>
-    <t>[크라운] 버터와플 316g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5062899</t>
-  </si>
-  <si>
-    <t>[오리온] 감자패밀리팩 대용량 180g (포카칩 &amp; 스윙칩 &amp; 오감자)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000875710</t>
-  </si>
-  <si>
-    <t>[미주라] 소이아 크래커 400g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5006818</t>
-  </si>
-  <si>
-    <t>[해태] 가루비 감자칩 오리지널 40g X 3개입</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000582944</t>
-  </si>
-  <si>
-    <t>[라아부엘라니에베스] 스페인 수제 감자칩 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000206111</t>
-  </si>
-  <si>
-    <t>[마요라] 커피조이 351g (39g X 9개입)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000643389</t>
-  </si>
-  <si>
-    <t>[해태] 가루비 감자칩 오리지널 96g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000439362</t>
-  </si>
-  <si>
-    <t>[헌터즈] 트러플 감자칩 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000166566</t>
-  </si>
-  <si>
-    <t>[DJ&amp;A] 표고버섯/베지 크리스프 3종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000526145</t>
-  </si>
-  <si>
-    <t>[베프코] 홋카이도 센베 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000789439</t>
-  </si>
-  <si>
-    <t>홈파티 와인 안주 간식 8종 모아보기 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000356687</t>
-  </si>
-  <si>
-    <t>[크라운] 인기스낵 모음 12팩</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5153242</t>
-  </si>
-  <si>
-    <t>[프롬잇] 프로틴칩 6종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000033235</t>
-  </si>
-  <si>
-    <t>[발스낵] 그랜드 감자칩 2묶음 7종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001570087</t>
-  </si>
-  <si>
-    <t>[농심] 빵부장 초코빵 55g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000942359</t>
-  </si>
-  <si>
-    <t>[해태] 계란과자 45g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001397540</t>
-  </si>
-  <si>
-    <t>[그레타] 허브 크래커 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000927112</t>
-  </si>
-  <si>
-    <t>[덴로쿠] 스낵 믹스팩 294g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5103484</t>
-  </si>
-  <si>
-    <t>[아미카] 감자칩 멀티팩 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000605988</t>
-  </si>
-  <si>
-    <t>[타코맨] 나쵸 토틸라칩 320g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5060050</t>
-  </si>
-  <si>
-    <t>[이메이] 대파 소다 크래커 225g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002324203</t>
-  </si>
-  <si>
-    <t>[크라운] 참쌀선과 253g (44봉)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000178191</t>
-  </si>
-  <si>
-    <t>[바다해] 캠핑&amp;홈파티 마른안주 플래터 360g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000914382</t>
-  </si>
-  <si>
-    <t>[ALLO] 하몽 크래커 319g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002014581</t>
-  </si>
-  <si>
-    <t>[레인코스트] 크리스프 크래커 7종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5052362</t>
-  </si>
-  <si>
-    <t>[크라운] 치즈샌드 Rich 180g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000958549</t>
-  </si>
-  <si>
-    <t>[오리온] 호호감자크래커 177g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002010936</t>
-  </si>
-  <si>
-    <t>[퀼리] 스페인 브래드스틱 6종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000242960</t>
-  </si>
-  <si>
-    <t>[롯데] 군위 사과 시리즈 11종, 택1</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002482468</t>
-  </si>
-  <si>
-    <t>[미주라] 통밀크래커 385g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5058855</t>
-  </si>
-  <si>
-    <t>대용량 트러플 카사바칩 500g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000783621</t>
-  </si>
-  <si>
-    <t>[아미카] 엘도라다 포테이토칩 대용량  400g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000525224</t>
-  </si>
-  <si>
-    <t>[오리온] 썬 핫스파이시 4번들</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000365879</t>
-  </si>
-  <si>
-    <t>[브렛츠] 감자칩 7종, 택1</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002133624</t>
-  </si>
-  <si>
-    <t>[롯데] 치토스 바비큐 164g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000339558</t>
-  </si>
-  <si>
-    <t>[크라운] 참 크래커 280g (18.67g x 15입)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5081478</t>
-  </si>
-  <si>
-    <t>[미주라] 토스트 비스켓 320g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5005540</t>
-  </si>
-  <si>
-    <t>[DJ&amp;A] 포테이토 웨지 스낵 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000526148</t>
-  </si>
-  <si>
-    <t>[빙그레] 인기스낵 4종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000677312</t>
-  </si>
-  <si>
-    <t>[크라운] 그레이스 298g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001407039</t>
-  </si>
-  <si>
-    <t>[오리온] 인기 봉지 과자 지퍼백 5종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000248448</t>
-  </si>
-  <si>
-    <t>땅콩 한입 꽈배기 520g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001027192</t>
-  </si>
-  <si>
-    <t>[오리온] 고소미 216g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5067308</t>
-  </si>
-  <si>
-    <t>[HBAF] 시그니처 팝콘 골라담기 7종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000942860</t>
-  </si>
-  <si>
-    <t>[미카쿠토] 오사츠도키 칩 2종, 택1</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001991119</t>
-  </si>
-  <si>
-    <t>[더다믐] 김칩스 매운맛 44g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5132664</t>
-  </si>
-  <si>
-    <t>[오리온] 무뚝뚝 감자칩 &amp; 고구마 스낵 3종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000640854</t>
-  </si>
-  <si>
-    <t>[마주] 버섯스낵 바삭칩 2종</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000045935</t>
-  </si>
-  <si>
-    <t>[농심] 빵부장 소금빵 55g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000349505</t>
-  </si>
-  <si>
-    <t>[PNB] 고소한 수제 전병 4종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5060582</t>
-  </si>
-  <si>
-    <t>[농심] 인기 봉지 과자 7종 골라담기 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001363953</t>
-  </si>
-  <si>
-    <t>[카수가이] 오부쿠로 와사비마메 227g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5103372</t>
-  </si>
-  <si>
-    <t>[농심] 와사비 새우깡 70g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001501063</t>
-  </si>
-  <si>
-    <t>[이토비스킷] 랑그리 크림 쿠키 2종</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000443353</t>
-  </si>
-  <si>
-    <t>[발센] 라이브니즈 비스킷 2종, 택1</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002221133</t>
-  </si>
-  <si>
-    <t>[오가마마] 바삭바삭 고구마칩 150g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000136966</t>
-  </si>
-  <si>
-    <t>[생미쉘] 비스킷 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000799985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[HBAF] 와사비마요 팝콘 80g </t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000960165</t>
-  </si>
-  <si>
-    <t>[마켓오] 브라우니 바이트 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001337989</t>
-  </si>
-  <si>
-    <t>[맥스봉] 구운풍미 마늘 후랑크 80g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002104225</t>
-  </si>
-  <si>
-    <t>[시그달] 크리스피 크래커 3종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002020133</t>
-  </si>
-  <si>
-    <t>수입 과자 10종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000360436</t>
-  </si>
-  <si>
-    <t>[해태] 버터링 골드 194g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001042362</t>
-  </si>
-  <si>
-    <t>[크런틴] 프사삭 5mm 통감자칩 4종, 택1</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002340554</t>
-  </si>
-  <si>
-    <t>[해태] 에이스 바스크 치즈 케이크 364g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000490099</t>
-  </si>
-  <si>
-    <t>[CJ] 맛군밤 4개입</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5077641</t>
-  </si>
-  <si>
-    <t>[롯데] 꼬깔콘 고소한맛 67g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001397631</t>
-  </si>
-  <si>
-    <t>[CJ] 바삭칩 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001942440</t>
-  </si>
-  <si>
-    <t>[발센] 와플텐 웨이퍼롤 2종, 택1</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002221138</t>
-  </si>
-  <si>
-    <t>[아미카] 이탈리아 감자칩 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000216544</t>
-  </si>
-  <si>
-    <t>[롯데] 쌀로별 오리지널 156g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5118057</t>
-  </si>
-  <si>
-    <t>[카메다] 소프트 사라다 145.2g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000656471</t>
-  </si>
-  <si>
-    <t>[곡물그대로21] 크리스피롤 3종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001073370</t>
-  </si>
-  <si>
-    <t>[해태] 맛동산 300g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000365868</t>
-  </si>
-  <si>
-    <t>[유니온] 와인 페어링 타랄리니 스낵 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001740101</t>
-  </si>
-  <si>
-    <t>[해태] 칼로리바란스 치즈 (38g x 7개)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000125337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[Lay's] 감자칩 7종 (택1) </t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5013230</t>
-  </si>
-  <si>
-    <t>[아티장 비스킷] 치즈를 위한 토스트 (데이츠&amp;헤이즐넛) 100g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5043538</t>
-  </si>
-  <si>
-    <t>7일 이내 로스팅한 구운 캐슈넛 200g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001382381</t>
-  </si>
-  <si>
-    <t>[다르다] 통밀칩 45g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002159262</t>
-  </si>
-  <si>
-    <t>[해태] 맛동산 3번들 210g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002286852</t>
-  </si>
-  <si>
-    <t>[하루견과] 빠삭칩 200g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5052356</t>
-  </si>
-  <si>
-    <t>[마이산] 스카이 플레이크 크래커 마늘맛 800g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000499057</t>
-  </si>
-  <si>
-    <t>[소이조이] 대두로 만든 단백질 스낵 6종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000791609</t>
-  </si>
-  <si>
-    <t>[더단백] 팝칩 12개입 3종, 택1</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000074625</t>
-  </si>
-  <si>
-    <t>[크라운] 참쌀설병 270g (30봉)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5077457</t>
-  </si>
-  <si>
-    <t>[해태] 구운 양파 110g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000349503</t>
-  </si>
-  <si>
-    <t>[카스테이블워터] 영국 크래커 4종 (택 1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5054219</t>
-  </si>
-  <si>
-    <t>[오리온] 찍먹 오감자 버터갈릭감자튀김맛 115g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001959559</t>
-  </si>
-  <si>
-    <t>[카수가이] 땅콩 간식 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000777595</t>
-  </si>
-  <si>
-    <t>[해태] 에이스 야채 291g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002225093</t>
-  </si>
-  <si>
-    <t>통연근 그대로 튀긴 연근칩 30g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5030130</t>
-  </si>
-  <si>
-    <t>[해태] 구운 고구마 135g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001317277</t>
-  </si>
-  <si>
-    <t>[롯데] 꼬깔콘 시리즈 3종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5118059</t>
-  </si>
-  <si>
-    <t>[오리온] 다이제 샌드 우도땅콩 392g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001861625</t>
-  </si>
-  <si>
-    <t>[DJ&amp;A] 크리스피 베지칩 2종, 택1</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002108866</t>
-  </si>
-  <si>
-    <t>[발센] 라이브니즈 미니스 비스킷 2종, 택1</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002221130</t>
-  </si>
-  <si>
-    <t>[반두아] 코코넛 크래커 150g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5049808</t>
-  </si>
-  <si>
-    <t>[해태] 에이스 씬 에스프레소 291g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000528989</t>
-  </si>
-  <si>
-    <t>일본 이색 센베 과자 5종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000739633</t>
-  </si>
-  <si>
-    <t>[크라운] 콘칲 군옥수수맛 148g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5121162</t>
-  </si>
-  <si>
-    <t>[올가] 국산 통밀 크리스피 크래커 3종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000891294</t>
-  </si>
-  <si>
-    <t>[농심] 육포깡 90g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002280048</t>
-  </si>
-  <si>
-    <t>[마이노멀] 밀가루 없는 제로칩 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002003498</t>
-  </si>
-  <si>
-    <t>[밀크클래식] 쌀과자 240g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000485694</t>
-  </si>
-  <si>
-    <t>[프리토스] 콘칩 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000612634</t>
-  </si>
-  <si>
-    <t>[해태] 오예스 베이크하우스 얼그레이&amp;쇼콜라 280g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002475314</t>
-  </si>
-  <si>
-    <t>[오리온] 다이제 쏙쏙포장 5종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000198198</t>
-  </si>
-  <si>
-    <t>[HBAF] 넛츠앤스낵스 땅콩 120g 5종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000147459</t>
-  </si>
-  <si>
-    <t>[긴비스] 동물모양 비스킷 138g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000030463</t>
-  </si>
-  <si>
-    <t>[아미카] 알프레도 올리브 오일 포테이토칩 130g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000525222</t>
-  </si>
-  <si>
-    <t>[속초 세렝게티커피] 티그레 6종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000330137</t>
-  </si>
-  <si>
-    <t>[로투스] 비스코프 4종, 택1</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5071375</t>
-  </si>
-  <si>
-    <t>[해태] 허니버터칩 캐슬 갈릭브레드맛 100g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001333045</t>
-  </si>
-  <si>
-    <t>[크라운] 메이플콘 74g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001406908</t>
-  </si>
-  <si>
-    <t>[해태] 가루비 감자칩 연어초밥맛 96g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002185327</t>
-  </si>
-  <si>
-    <t>[빼바] 프로틴 바삭칩 60g 2종, 택1</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002295305</t>
-  </si>
-  <si>
-    <t>[크라운] 참그레인 우리밀 192g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000506290</t>
-  </si>
-  <si>
-    <t>[로아커] 샌드 비스킷 3종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001701315</t>
-  </si>
-  <si>
-    <t>[오리온] 가짜같은 진짜, 만우절 한정 감자스낵 4종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001171286</t>
-  </si>
-  <si>
-    <t>[농심] 포스틱 84g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002129045</t>
-  </si>
-  <si>
-    <t>[해태] 허니버터칩 4번들 (40g x 4묶음)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000263120</t>
-  </si>
-  <si>
-    <t>[TEMOLE] 아몬드칩 사우어크림 40g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002131257</t>
-  </si>
-  <si>
-    <t>[게메즈] 에낙 라면스낵 스파이시 (28gX5입)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000679265</t>
-  </si>
-  <si>
-    <t>[롯데] 아몬드 팔각 빼빼로 132g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5086556</t>
-  </si>
-  <si>
-    <t>[잇츠베러] 제로슈가 쿠키 4종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000608510</t>
-  </si>
-  <si>
-    <t>[오리온] 포카칩 4개입 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000648498</t>
-  </si>
-  <si>
-    <t>[유니온] 와인 페어링 타랄리니 스낵 오리지널 35gX6개입</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001740103</t>
-  </si>
-  <si>
-    <t>[우리밀] 두부과자 100g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5004416</t>
-  </si>
-  <si>
-    <t>[워커스] 쇼트브레드 어쏘트먼트 168g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001241376</t>
-  </si>
-  <si>
-    <t>[이노센트] 저당 프로틴 크런치볼 2종</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000957506</t>
-  </si>
-  <si>
-    <t>[마켓오] 크림치즈 브라우니 240g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001391101</t>
-  </si>
-  <si>
-    <t>[아미고] 나쵸칩 454g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5009519</t>
-  </si>
-  <si>
-    <t>[오리온] 치킨팝 65g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001399104</t>
-  </si>
-  <si>
-    <t>[농심] 먹태깡 60g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000215789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[아티장 비스킷] 치즈 크래커 2종 </t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5042489</t>
-  </si>
-  <si>
-    <t>두 번 튀겨 더 고소한 맛뻥 84g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002214154</t>
-  </si>
-  <si>
-    <t>[롯데] KBO 빼빼로 화이트쿠키 10종, 택1</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002130774</t>
-  </si>
-  <si>
-    <t>[오리온] 오징어땅콩 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000757615</t>
-  </si>
-  <si>
-    <t>[로아커] 웨하스 씬 3종, 택1</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002049283</t>
-  </si>
-  <si>
-    <t>[부르본] 에브리버거 초코비스킷 66g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001100806</t>
-  </si>
-  <si>
-    <t>[롯데] 꼬깔콘 군옥수수맛 67g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001397633</t>
-  </si>
-  <si>
-    <t>[오리온] 다이제 오리지널 351g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000033205</t>
-  </si>
-  <si>
-    <t>[ALLO] 감자크래커 2종 (택1)</t>
-  </si>
-  <si>
-    <t>감자 스낵</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002014584</t>
-  </si>
-  <si>
-    <t>[오리온] 오감자 감자그라탕맛 96g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001985656</t>
-  </si>
-  <si>
-    <t>[농심] 감자깡 75g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002129012</t>
-  </si>
-  <si>
-    <t>[가루비] CALBEE 일본 감자칩 스낵 6종</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001421090</t>
-  </si>
-  <si>
-    <t>[오리온] 눈을감자 칠리치즈프라이즈 96g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001170989</t>
-  </si>
-  <si>
-    <t>[농심] 감자깡 250g (지퍼백)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5134076</t>
-  </si>
-  <si>
-    <t>[오리온] 눈을감자 96g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000640848</t>
-  </si>
-  <si>
-    <t>[가루비] 쟈가리코 감자 스낵 샐러드맛 57g x 12개입 (가루비 쟈가리코 샐러드맛 57g 12개입)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001318650</t>
-  </si>
-  <si>
-    <t>[풀무원] 특등급 국산콩 두부칩 감자 40g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001937064</t>
-  </si>
-  <si>
-    <t>[러플스] 오리지날 감자칩 184.2g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000612631</t>
-  </si>
-  <si>
-    <t>[올가] 순감자칩, 순고구마칩 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000891279</t>
-  </si>
-  <si>
-    <t>[푸르나이] 제대로 햇감자칩 2종, 택1</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002380802</t>
-  </si>
-  <si>
-    <t>[케오스] 아이리시 씨솔트 크링클 감자칩 125g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000584460</t>
-  </si>
-  <si>
-    <t>[아로마트러플] 블랙 써머 트러플 감자칩 3종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000179453</t>
-  </si>
-  <si>
-    <t>[켈로그] 프링글스 치즈맛 110g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000570013</t>
-  </si>
-  <si>
-    <t>[크라운] 어썸체다치즈 45g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002247128</t>
-  </si>
-  <si>
-    <t>[농심] 포테토칩 오리지널 160g (40g x 4봉)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002129077</t>
-  </si>
-  <si>
-    <t>[농심] 포테토칩 오리지널 110g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002129075</t>
-  </si>
-  <si>
-    <t>나들이 맞이 스낵 &amp; 캔디젤리 간식 7종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001212964</t>
-  </si>
-  <si>
-    <t>[켈로그] 프링글스 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5073031</t>
-  </si>
-  <si>
-    <t>[농심] 포테토칩 오리지널 60g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002129073</t>
-  </si>
-  <si>
-    <t>[농심] 포스틱 133g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002129047</t>
-  </si>
-  <si>
-    <t>[켈로그] 프링글스 스윗어니언맛 100g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001098485</t>
-  </si>
-  <si>
-    <t>[농심] 오리지널 봉지 과자 7종 (택1)(중사이즈)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000205257</t>
-  </si>
-  <si>
-    <t>[오리온] 즐겨요 응원의 맛 3종, 택1</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002242483</t>
-  </si>
-  <si>
-    <t>[오리온] 스윙칩 볶음고추장맛 210g (지퍼백)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5155641</t>
-  </si>
-  <si>
-    <t>[오리온] 스윙칩 까르보나라불닭맛 112g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002326317</t>
-  </si>
-  <si>
-    <t>[헌터즈] 트러플 감자칩 원형 틴 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000391076</t>
-  </si>
-  <si>
-    <t>[오리온] 찍먹 예감 마요소스맛 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001391095</t>
-  </si>
-  <si>
-    <t>[농심] 포테토칩 교촌간장치킨맛 55g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002064464</t>
-  </si>
-  <si>
-    <t>[농심] 새우깡 미니팩 30g x 4입</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000198131</t>
-  </si>
-  <si>
-    <t>[농심] 새우깡 90g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5061325</t>
-  </si>
-  <si>
-    <t>[농심] 포테토칩 K양념치킨맛 50g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002129079</t>
-  </si>
-  <si>
-    <t>[해태] 허니버터칩 미니 박스 33g x 12개입</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001228129</t>
-  </si>
-  <si>
-    <t>[부르본] 코메노칩스 2종, 택1</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002324004</t>
-  </si>
-  <si>
-    <t>[켈로그] 프링글스 매운맛 110g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000570015</t>
-  </si>
-  <si>
-    <t>[케오스] 치즈 어니언 감자칩</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000584474</t>
-  </si>
-  <si>
-    <t>[켈로그] 프링글스 버터카라멜맛 110g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000570032</t>
-  </si>
-  <si>
-    <t>[농심] 고구마깡 83g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002129009</t>
-  </si>
-  <si>
-    <t>바삭함부터 달콤함까지 인기 간식 7종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001384411</t>
-  </si>
-  <si>
-    <t>[토스티토스] 또띨라 나쵸칩 3종</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5161381</t>
-  </si>
-  <si>
-    <t>[크라운] 콘치 66g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001406961</t>
-  </si>
-  <si>
-    <t>[농심] 쌀새우깡 80g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000952281</t>
-  </si>
-  <si>
-    <t>[Lay's] 스파이시 마라맛 감자칩 170g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000927098</t>
-  </si>
-  <si>
-    <t>[상하농원] 황토고구마칩 오리지널 40g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001388382</t>
-  </si>
-  <si>
-    <t>[제주 아침미소목장] 우유샌드 234g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002207194</t>
-  </si>
-  <si>
-    <t>[농심] 양파깡 83g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002129049</t>
-  </si>
-  <si>
-    <t>[농심] 오징어집 78g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002129039</t>
-  </si>
-  <si>
-    <t>[해태] 프리츠 토마토 33g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001397641</t>
-  </si>
-  <si>
-    <t>[해태] 홈런볼 옥수수 소프트콘맛 4번들 156g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002185329</t>
-  </si>
-  <si>
-    <t>[농심] 수미칩 85g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001434820</t>
-  </si>
-  <si>
-    <t>[농심] 포테토칩 엽떡로제맛 55g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002296291</t>
-  </si>
-  <si>
-    <t>[오리온] 땅콩강정 3번들</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000365877</t>
-  </si>
-  <si>
-    <t>[스마트푸드] 화이트 체다치즈 팝콘</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5073060</t>
-  </si>
-  <si>
-    <t>[켈로그] 프링글스 미트 치즈 라자냐맛 100g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002327637</t>
-  </si>
-  <si>
-    <t>[던킨] 베이글칩 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001065190</t>
-  </si>
-  <si>
-    <t>[농심] 새우깡 블랙 72g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5136204</t>
-  </si>
-  <si>
-    <t>[크라운] 신짱 245g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5077459</t>
-  </si>
-  <si>
-    <t>[다이코] 노리텐 김부각 과자 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000858865</t>
-  </si>
-  <si>
-    <t>[크라운] 당을 줄인 신짱 300g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002492970</t>
-  </si>
-  <si>
-    <t>[게메즈] 에낙 라면스낵 150g (30g x 5개)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002326631</t>
-  </si>
-  <si>
-    <t>[치즐스] 치즈스낵 125g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002134600</t>
-  </si>
-  <si>
-    <t>[농심] 새우깡블랙 105g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001485461</t>
-  </si>
-  <si>
-    <t>[더하루] 슬라이스칩 2종, 택1</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002058181</t>
-  </si>
-  <si>
-    <t>[위메이드] 치즈 오트 크래커 56g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002313083</t>
-  </si>
-  <si>
-    <t>[일동후디스] 아이얌 두부와플 2종</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5118755</t>
-  </si>
-  <si>
-    <t>[리츠] 멕시칸 타코맛 크래커 73g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002015596</t>
-  </si>
-  <si>
-    <t>[남양] 아이꼬야 퐁 아기과자 3종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000472716</t>
-  </si>
-  <si>
-    <t>[맥케인] 포테이토 펍스 700g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5155683</t>
-  </si>
-  <si>
-    <t>[하인즈] 미니 테이터 토트 (감자볼) 793g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5114891</t>
-  </si>
-  <si>
-    <t>[HBAF] 팝콘 골라담기 7종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000942888</t>
-  </si>
-  <si>
-    <t>[잭링크스] 인기 육포 모아보기 5종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001092106</t>
-  </si>
-  <si>
-    <t>[루토사] 웨지감자 400g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001803388</t>
-  </si>
-  <si>
-    <t>[크라운] 밤양갱 50g X 5입</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000472613</t>
-  </si>
-  <si>
-    <t>[크라운] 마이쮸 토마토 120g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002369661</t>
-  </si>
-  <si>
-    <t>[오뚜기] 콘크림스프 팝콘 55g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000605483</t>
-  </si>
-  <si>
-    <t>[크라운] 엠쉘 2종, 택1</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002303054</t>
-  </si>
-  <si>
-    <t>[해태] 알사탕 319g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001397542</t>
-  </si>
-  <si>
-    <t>[HBAF] 뉴욕치즈버거맛 팝콘 80g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000960167</t>
-  </si>
-  <si>
-    <t>[농심] 나토리 치타라 어포 치즈 24g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002099803</t>
-  </si>
-  <si>
-    <t>[맥스봉] 청양고추 후랑크 80g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002104217</t>
-  </si>
-  <si>
-    <t>[CJ] 바삭팝콘 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1001942437</t>
-  </si>
-  <si>
-    <t>[댄케이크] 싱글서브 버터쿠키 18입</t>
-  </si>
-  <si>
-    <t>개별포장 쿠키</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5038276</t>
-  </si>
-  <si>
-    <t>[댄케이크] 싱글서브 초콜릿칩 쿠키 18입</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5043922</t>
-  </si>
-  <si>
-    <t>[댄케이크] 2믹스 싱글서브쿠키 18입</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000639928</t>
-  </si>
-  <si>
     <t>[생미쉘] 마들렝 150g (6개입, 개별포장)</t>
   </si>
   <si>
     <t>https://www.kurly.com/goods/5050887</t>
-  </si>
-  <si>
-    <t>[리치] 버터 와플 270g (15g x 18입)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5066715</t>
   </si>
   <si>
     <t>[껠끄쇼즈] 샌드쿠키 4종 (택1)</t>
@@ -12499,14 +12499,14 @@
       </c>
       <c r="D2" s="3">
         <f>SUM(F5:F48)</f>
-        <v>498344</v>
+        <v>498164</v>
       </c>
       <c r="E2" t="s">
         <v>3</v>
       </c>
       <c r="F2" s="3">
         <f>B2-D2</f>
-        <v>1656</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -13454,20 +13454,20 @@
         <v>81</v>
       </c>
       <c r="D35" s="2">
-        <v>3690</v>
+        <v>4780</v>
       </c>
       <c r="E35">
         <v>2</v>
       </c>
       <c r="F35" s="2">
         <f>D35*E35</f>
-        <v>7380</v>
+        <v>9560</v>
       </c>
       <c r="G35">
         <v>0</v>
       </c>
       <c r="H35">
-        <v>9999</v>
+        <v>999</v>
       </c>
       <c r="I35" s="8" t="s">
         <v>82</v>
@@ -13484,14 +13484,14 @@
         <v>83</v>
       </c>
       <c r="D36" s="2">
-        <v>4780</v>
+        <v>4200</v>
       </c>
       <c r="E36">
         <v>2</v>
       </c>
       <c r="F36" s="2">
         <f>D36*E36</f>
-        <v>9560</v>
+        <v>8400</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -13514,14 +13514,14 @@
         <v>85</v>
       </c>
       <c r="D37" s="2">
-        <v>4200</v>
+        <v>5280</v>
       </c>
       <c r="E37">
         <v>2</v>
       </c>
       <c r="F37" s="2">
         <f>D37*E37</f>
-        <v>8400</v>
+        <v>10560</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -13544,20 +13544,20 @@
         <v>87</v>
       </c>
       <c r="D38" s="2">
-        <v>5280</v>
+        <v>4780</v>
       </c>
       <c r="E38">
         <v>2</v>
       </c>
       <c r="F38" s="2">
         <f>D38*E38</f>
-        <v>10560</v>
+        <v>9560</v>
       </c>
       <c r="G38">
         <v>0</v>
       </c>
       <c r="H38">
-        <v>999</v>
+        <v>477</v>
       </c>
       <c r="I38" s="8" t="s">
         <v>88</v>
@@ -13574,20 +13574,20 @@
         <v>89</v>
       </c>
       <c r="D39" s="2">
-        <v>4780</v>
+        <v>3980</v>
       </c>
       <c r="E39">
         <v>2</v>
       </c>
       <c r="F39" s="2">
         <f>D39*E39</f>
-        <v>9560</v>
+        <v>7960</v>
       </c>
       <c r="G39">
         <v>0</v>
       </c>
       <c r="H39">
-        <v>477</v>
+        <v>314</v>
       </c>
       <c r="I39" s="8" t="s">
         <v>90</v>
@@ -13604,20 +13604,20 @@
         <v>91</v>
       </c>
       <c r="D40" s="2">
-        <v>3980</v>
+        <v>3200</v>
       </c>
       <c r="E40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F40" s="2">
         <f>D40*E40</f>
-        <v>7960</v>
+        <v>9600</v>
       </c>
       <c r="G40">
         <v>0</v>
       </c>
       <c r="H40">
-        <v>314</v>
+        <v>215</v>
       </c>
       <c r="I40" s="8" t="s">
         <v>92</v>
@@ -13634,20 +13634,20 @@
         <v>93</v>
       </c>
       <c r="D41" s="2">
-        <v>3200</v>
+        <v>3600</v>
       </c>
       <c r="E41">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F41" s="2">
         <f>D41*E41</f>
-        <v>9600</v>
+        <v>7200</v>
       </c>
       <c r="G41">
         <v>0</v>
       </c>
       <c r="H41">
-        <v>215</v>
+        <v>999</v>
       </c>
       <c r="I41" s="8" t="s">
         <v>94</v>
@@ -13953,7 +13953,7 @@
       </c>
       <c r="D2" s="9">
         <f>C2/SUM($C$2:$C$8)</f>
-        <v>0.21009583741351356</v>
+        <v>0.21017175066845456</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -13970,7 +13970,7 @@
       </c>
       <c r="D3" s="9">
         <f>C3/SUM($C$2:$C$8)</f>
-        <v>0.1401923169537508</v>
+        <v>0.14024297219389598</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -13983,11 +13983,11 @@
       </c>
       <c r="C4" s="2">
         <f>SUMIF(구매목록!B5:B48,A4,구매목록!F5:F48)</f>
-        <v>91620</v>
+        <v>91440</v>
       </c>
       <c r="D4" s="9">
         <f>C4/SUM($C$2:$C$8)</f>
-        <v>0.1838489075819113</v>
+        <v>0.18355401032591676</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -14004,7 +14004,7 @@
       </c>
       <c r="D5" s="9">
         <f>C5/SUM($C$2:$C$8)</f>
-        <v>0.18445090138538842</v>
+        <v>0.18451754843786383</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -14021,7 +14021,7 @@
       </c>
       <c r="D6" s="9">
         <f>C6/SUM($C$2:$C$8)</f>
-        <v>0.14066588541248615</v>
+        <v>0.1407167117656033</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -14038,7 +14038,7 @@
       </c>
       <c r="D7" s="9">
         <f>C7/SUM($C$2:$C$8)</f>
-        <v>0.1144992214213475</v>
+        <v>0.1145405930577079</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -14055,7 +14055,7 @@
       </c>
       <c r="D8" s="9">
         <f>C8/SUM($C$2:$C$8)</f>
-        <v>0.02624692983160227</v>
+        <v>0.026256413550557647</v>
       </c>
     </row>
   </sheetData>
@@ -14475,7 +14475,7 @@
         <v>5079340</v>
       </c>
       <c r="B16" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C16">
         <v>5280</v>
@@ -14493,7 +14493,7 @@
         <v>119</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -17569,7 +17569,7 @@
         <v>5132978</v>
       </c>
       <c r="B135" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C135">
         <v>4200</v>
@@ -17587,7 +17587,7 @@
         <v>119</v>
       </c>
       <c r="I135" s="10" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="136" spans="1:9">
@@ -21310,7 +21310,7 @@
         <v>5061562</v>
       </c>
       <c r="B279" t="s">
-        <v>81</v>
+        <v>641</v>
       </c>
       <c r="C279">
         <v>3690</v>
@@ -21328,7 +21328,7 @@
         <v>635</v>
       </c>
       <c r="I279" s="10" t="s">
-        <v>82</v>
+        <v>642</v>
       </c>
     </row>
     <row r="280" spans="1:9">
@@ -21336,7 +21336,7 @@
         <v>5050887</v>
       </c>
       <c r="B280" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="C280">
         <v>3980</v>
@@ -21354,7 +21354,7 @@
         <v>635</v>
       </c>
       <c r="I280" s="10" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="281" spans="1:9">
@@ -21362,7 +21362,7 @@
         <v>5066715</v>
       </c>
       <c r="B281" t="s">
-        <v>643</v>
+        <v>93</v>
       </c>
       <c r="C281">
         <v>3600</v>
@@ -21380,7 +21380,7 @@
         <v>635</v>
       </c>
       <c r="I281" s="10" t="s">
-        <v>644</v>
+        <v>94</v>
       </c>
     </row>
     <row r="282" spans="1:9">
@@ -23000,7 +23000,7 @@
         <v>5061939</v>
       </c>
       <c r="B344" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C344">
         <v>4780</v>
@@ -23018,7 +23018,7 @@
         <v>635</v>
       </c>
       <c r="I344" s="10" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="345" spans="1:9">
@@ -23644,7 +23644,7 @@
         <v>1002110078</v>
       </c>
       <c r="B369" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C369">
         <v>3980</v>
@@ -23662,7 +23662,7 @@
         <v>635</v>
       </c>
       <c r="I369" s="10" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="370" spans="1:9">
@@ -46287,7 +46287,7 @@
         <v>1002419584</v>
       </c>
       <c r="B1225" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C1225">
         <v>3200</v>
@@ -46305,7 +46305,7 @@
         <v>2489</v>
       </c>
       <c r="I1225" s="10" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="1226" spans="1:9">
@@ -47847,7 +47847,7 @@
         <v>1001137097</v>
       </c>
       <c r="B1285" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C1285">
         <v>4780</v>
@@ -47865,7 +47865,7 @@
         <v>2489</v>
       </c>
       <c r="I1285" s="10" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="1286" spans="1:9">

--- a/다과_구매목록.xlsx
+++ b/다과_구매목록.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6421" uniqueCount="4015">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6425" uniqueCount="4015">
   <si>
     <t>회사 다과 구매 목록 (마켓컬리)</t>
   </si>
@@ -189,6 +189,12 @@
     <t>https://www.kurly.com/goods/1000279292</t>
   </si>
   <si>
+    <t>[하리보] 이색 젤리 4종, 택1</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000548850</t>
+  </si>
+  <si>
     <t>쿠키/비스킷(개별포장)</t>
   </si>
   <si>
@@ -240,18 +246,18 @@
     <t>https://www.kurly.com/goods/5055895</t>
   </si>
   <si>
-    <t>[하리보] 이색 젤리 4종, 택1</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000548850</t>
-  </si>
-  <si>
     <t>[오레오] 씬즈 84g 2종 (택1)</t>
   </si>
   <si>
     <t>https://www.kurly.com/goods/1000321594</t>
   </si>
   <si>
+    <t>[폴트] 프랑스 타르트 비스킷 2종</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5104102</t>
+  </si>
+  <si>
     <t>파이/케이크(개별포장)</t>
   </si>
   <si>
@@ -2020,12 +2026,6 @@
   </si>
   <si>
     <t>https://www.kurly.com/goods/1001049824</t>
-  </si>
-  <si>
-    <t>[폴트] 프랑스 타르트 비스킷 2종</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5104102</t>
   </si>
   <si>
     <t>[아우어베이커리] 빨미까레 더블팩 (90g X 2개)</t>
@@ -12467,7 +12467,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.7109375" customWidth="1"/>
@@ -12498,15 +12498,15 @@
         <v>2</v>
       </c>
       <c r="D2" s="3">
-        <f>SUM(F5:F38)</f>
-        <v>476110</v>
+        <f>SUM(F5:F39)</f>
+        <v>493840</v>
       </c>
       <c r="E2" t="s">
         <v>3</v>
       </c>
       <c r="F2" s="3">
         <f>B2-D2</f>
-        <v>23890</v>
+        <v>6160</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -13088,20 +13088,20 @@
         <v>19</v>
       </c>
       <c r="B23" t="s">
+        <v>53</v>
+      </c>
+      <c r="C23" t="s">
         <v>56</v>
       </c>
-      <c r="C23" t="s">
-        <v>57</v>
-      </c>
       <c r="D23" s="2">
-        <v>4480</v>
+        <v>4380</v>
       </c>
       <c r="E23">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F23" s="2">
         <f>D23*E23</f>
-        <v>13440</v>
+        <v>21900</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -13110,7 +13110,7 @@
         <v>999</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -13118,20 +13118,20 @@
         <v>19</v>
       </c>
       <c r="B24" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C24" t="s">
         <v>59</v>
       </c>
       <c r="D24" s="2">
-        <v>4380</v>
+        <v>4480</v>
       </c>
       <c r="E24">
         <v>3</v>
       </c>
       <c r="F24" s="2">
         <f>D24*E24</f>
-        <v>13140</v>
+        <v>13440</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -13148,26 +13148,26 @@
         <v>19</v>
       </c>
       <c r="B25" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C25" t="s">
         <v>61</v>
       </c>
       <c r="D25" s="2">
-        <v>5440</v>
+        <v>4380</v>
       </c>
       <c r="E25">
         <v>3</v>
       </c>
       <c r="F25" s="2">
         <f>D25*E25</f>
-        <v>16320</v>
+        <v>13140</v>
       </c>
       <c r="G25">
         <v>0</v>
       </c>
       <c r="H25">
-        <v>956</v>
+        <v>999</v>
       </c>
       <c r="I25" s="8" t="s">
         <v>62</v>
@@ -13178,26 +13178,26 @@
         <v>19</v>
       </c>
       <c r="B26" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C26" t="s">
         <v>63</v>
       </c>
       <c r="D26" s="2">
-        <v>4200</v>
+        <v>5440</v>
       </c>
       <c r="E26">
         <v>3</v>
       </c>
       <c r="F26" s="2">
         <f>D26*E26</f>
-        <v>12600</v>
+        <v>16320</v>
       </c>
       <c r="G26">
         <v>0</v>
       </c>
       <c r="H26">
-        <v>999</v>
+        <v>956</v>
       </c>
       <c r="I26" s="8" t="s">
         <v>64</v>
@@ -13208,20 +13208,20 @@
         <v>19</v>
       </c>
       <c r="B27" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C27" t="s">
         <v>65</v>
       </c>
       <c r="D27" s="2">
-        <v>5280</v>
+        <v>4200</v>
       </c>
       <c r="E27">
         <v>3</v>
       </c>
       <c r="F27" s="2">
         <f>D27*E27</f>
-        <v>15840</v>
+        <v>12600</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -13238,20 +13238,20 @@
         <v>19</v>
       </c>
       <c r="B28" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C28" t="s">
         <v>67</v>
       </c>
       <c r="D28" s="2">
-        <v>3600</v>
+        <v>5280</v>
       </c>
       <c r="E28">
         <v>3</v>
       </c>
       <c r="F28" s="2">
         <f>D28*E28</f>
-        <v>10800</v>
+        <v>15840</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -13268,20 +13268,20 @@
         <v>19</v>
       </c>
       <c r="B29" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C29" t="s">
         <v>69</v>
       </c>
       <c r="D29" s="2">
-        <v>4780</v>
+        <v>3600</v>
       </c>
       <c r="E29">
         <v>3</v>
       </c>
       <c r="F29" s="2">
         <f>D29*E29</f>
-        <v>14340</v>
+        <v>10800</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -13298,20 +13298,20 @@
         <v>19</v>
       </c>
       <c r="B30" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C30" t="s">
         <v>71</v>
       </c>
       <c r="D30" s="2">
-        <v>5280</v>
+        <v>4780</v>
       </c>
       <c r="E30">
         <v>3</v>
       </c>
       <c r="F30" s="2">
         <f>D30*E30</f>
-        <v>15840</v>
+        <v>14340</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -13328,20 +13328,20 @@
         <v>19</v>
       </c>
       <c r="B31" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C31" t="s">
         <v>73</v>
       </c>
       <c r="D31" s="2">
-        <v>4380</v>
+        <v>5280</v>
       </c>
       <c r="E31">
         <v>3</v>
       </c>
       <c r="F31" s="2">
         <f>D31*E31</f>
-        <v>13140</v>
+        <v>15840</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -13358,7 +13358,7 @@
         <v>19</v>
       </c>
       <c r="B32" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C32" t="s">
         <v>75</v>
@@ -13388,29 +13388,29 @@
         <v>19</v>
       </c>
       <c r="B33" t="s">
+        <v>58</v>
+      </c>
+      <c r="C33" t="s">
         <v>77</v>
       </c>
-      <c r="C33" t="s">
-        <v>78</v>
-      </c>
       <c r="D33" s="2">
-        <v>4320</v>
+        <v>2990</v>
       </c>
       <c r="E33">
         <v>3</v>
       </c>
       <c r="F33" s="2">
         <f>D33*E33</f>
-        <v>12960</v>
+        <v>8970</v>
       </c>
       <c r="G33">
         <v>0</v>
       </c>
       <c r="H33">
-        <v>9999</v>
+        <v>999</v>
       </c>
       <c r="I33" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -13418,7 +13418,7 @@
         <v>19</v>
       </c>
       <c r="B34" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C34" t="s">
         <v>80</v>
@@ -13437,7 +13437,7 @@
         <v>0</v>
       </c>
       <c r="H34">
-        <v>745</v>
+        <v>9999</v>
       </c>
       <c r="I34" s="8" t="s">
         <v>81</v>
@@ -13448,26 +13448,26 @@
         <v>19</v>
       </c>
       <c r="B35" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C35" t="s">
         <v>82</v>
       </c>
       <c r="D35" s="2">
-        <v>5600</v>
+        <v>4320</v>
       </c>
       <c r="E35">
         <v>3</v>
       </c>
       <c r="F35" s="2">
         <f>D35*E35</f>
-        <v>16800</v>
+        <v>12960</v>
       </c>
       <c r="G35">
         <v>0</v>
       </c>
       <c r="H35">
-        <v>999</v>
+        <v>745</v>
       </c>
       <c r="I35" s="8" t="s">
         <v>83</v>
@@ -13478,20 +13478,20 @@
         <v>19</v>
       </c>
       <c r="B36" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C36" t="s">
         <v>84</v>
       </c>
       <c r="D36" s="2">
-        <v>5280</v>
+        <v>5600</v>
       </c>
       <c r="E36">
         <v>3</v>
       </c>
       <c r="F36" s="2">
         <f>D36*E36</f>
-        <v>15840</v>
+        <v>16800</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -13508,20 +13508,20 @@
         <v>19</v>
       </c>
       <c r="B37" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C37" t="s">
         <v>86</v>
       </c>
       <c r="D37" s="2">
-        <v>3840</v>
+        <v>5280</v>
       </c>
       <c r="E37">
         <v>3</v>
       </c>
       <c r="F37" s="2">
         <f>D37*E37</f>
-        <v>11520</v>
+        <v>15840</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -13538,20 +13538,20 @@
         <v>19</v>
       </c>
       <c r="B38" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C38" t="s">
         <v>88</v>
       </c>
       <c r="D38" s="2">
-        <v>3580</v>
+        <v>3840</v>
       </c>
       <c r="E38">
         <v>3</v>
       </c>
       <c r="F38" s="2">
         <f>D38*E38</f>
-        <v>10740</v>
+        <v>11520</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -13561,6 +13561,36 @@
       </c>
       <c r="I38" s="8" t="s">
         <v>89</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" t="s">
+        <v>19</v>
+      </c>
+      <c r="B39" t="s">
+        <v>79</v>
+      </c>
+      <c r="C39" t="s">
+        <v>90</v>
+      </c>
+      <c r="D39" s="2">
+        <v>3580</v>
+      </c>
+      <c r="E39">
+        <v>3</v>
+      </c>
+      <c r="F39" s="2">
+        <f>D39*E39</f>
+        <v>10740</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>999</v>
+      </c>
+      <c r="I39" s="8" t="s">
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -13599,6 +13629,7 @@
     <hyperlink ref="I36" r:id="rId32"/>
     <hyperlink ref="I37" r:id="rId33"/>
     <hyperlink ref="I38" r:id="rId34"/>
+    <hyperlink ref="I39" r:id="rId35"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -13620,13 +13651,13 @@
         <v>5</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -13634,67 +13665,67 @@
         <v>14</v>
       </c>
       <c r="B2">
-        <f>COUNTIF(구매목록!B5:B38,A2)</f>
+        <f>COUNTIF(구매목록!B5:B39,A2)</f>
         <v>2</v>
       </c>
       <c r="C2" s="2">
-        <f>SUMIF(구매목록!B5:B38,A2,구매목록!F5:F38)</f>
+        <f>SUMIF(구매목록!B5:B39,A2,구매목록!F5:F39)</f>
         <v>69800</v>
       </c>
       <c r="D2" s="9">
         <f>C2/SUM($C$2:$C$8)</f>
-        <v>0.14660477620717902</v>
+        <v>0.14134132512554673</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="B3">
-        <f>COUNTIF(구매목록!B5:B38,A3)</f>
-        <v>6</v>
+        <f>COUNTIF(구매목록!B5:B39,A3)</f>
+        <v>2</v>
       </c>
       <c r="C3" s="2">
-        <f>SUMIF(구매목록!B5:B38,A3,구매목록!F5:F38)</f>
-        <v>80820</v>
+        <f>SUMIF(구매목록!B5:B39,A3,구매목록!F5:F39)</f>
+        <v>36800</v>
       </c>
       <c r="D3" s="9">
         <f>C3/SUM($C$2:$C$8)</f>
-        <v>0.1697506878662494</v>
+        <v>0.07451806253037421</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="B4">
-        <f>COUNTIF(구매목록!B5:B38,A4)</f>
-        <v>10</v>
+        <f>COUNTIF(구매목록!B5:B39,A4)</f>
+        <v>6</v>
       </c>
       <c r="C4" s="2">
-        <f>SUMIF(구매목록!B5:B38,A4,구매목록!F5:F38)</f>
-        <v>131100</v>
+        <f>SUMIF(구매목록!B5:B39,A4,구매목록!F5:F39)</f>
+        <v>80820</v>
       </c>
       <c r="D4" s="9">
         <f>C4/SUM($C$2:$C$8)</f>
-        <v>0.275356535254458</v>
+        <v>0.16365624493763162</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B5">
-        <f>COUNTIF(구매목록!B5:B38,A5)</f>
-        <v>1</v>
+        <f>COUNTIF(구매목록!B5:B39,A5)</f>
+        <v>10</v>
       </c>
       <c r="C5" s="2">
-        <f>SUMIF(구매목록!B5:B38,A5,구매목록!F5:F38)</f>
-        <v>14900</v>
+        <f>SUMIF(구매목록!B5:B39,A5,구매목록!F5:F39)</f>
+        <v>126930</v>
       </c>
       <c r="D5" s="9">
         <f>C5/SUM($C$2:$C$8)</f>
-        <v>0.03129528890382475</v>
+        <v>0.25702656730924994</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -13702,16 +13733,16 @@
         <v>20</v>
       </c>
       <c r="B6">
-        <f>COUNTIF(구매목록!B5:B38,A6)</f>
+        <f>COUNTIF(구매목록!B5:B39,A6)</f>
         <v>10</v>
       </c>
       <c r="C6" s="2">
-        <f>SUMIF(구매목록!B5:B38,A6,구매목록!F5:F38)</f>
+        <f>SUMIF(구매목록!B5:B39,A6,구매목록!F5:F39)</f>
         <v>116610</v>
       </c>
       <c r="D6" s="9">
         <f>C6/SUM($C$2:$C$8)</f>
-        <v>0.24492239188422843</v>
+        <v>0.23612911064312328</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -13719,16 +13750,16 @@
         <v>41</v>
       </c>
       <c r="B7">
-        <f>COUNTIF(구매목록!B5:B38,A7)</f>
+        <f>COUNTIF(구매목록!B5:B39,A7)</f>
         <v>3</v>
       </c>
       <c r="C7" s="2">
-        <f>SUMIF(구매목록!B5:B38,A7,구매목록!F5:F38)</f>
+        <f>SUMIF(구매목록!B5:B39,A7,구매목록!F5:F39)</f>
         <v>35580</v>
       </c>
       <c r="D7" s="9">
         <f>C7/SUM($C$2:$C$8)</f>
-        <v>0.07473062947638151</v>
+        <v>0.07204762676170419</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -13736,16 +13767,16 @@
         <v>48</v>
       </c>
       <c r="B8">
-        <f>COUNTIF(구매목록!B5:B38,A8)</f>
+        <f>COUNTIF(구매목록!B5:B39,A8)</f>
         <v>2</v>
       </c>
       <c r="C8" s="2">
-        <f>SUMIF(구매목록!B5:B38,A8,구매목록!F5:F38)</f>
+        <f>SUMIF(구매목록!B5:B39,A8,구매목록!F5:F39)</f>
         <v>27300</v>
       </c>
       <c r="D8" s="9">
         <f>C8/SUM($C$2:$C$8)</f>
-        <v>0.057339690407678896</v>
+        <v>0.05528106269237</v>
       </c>
     </row>
   </sheetData>
@@ -13769,28 +13800,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>11</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="I1" s="4" t="s">
         <v>12</v>
@@ -13801,7 +13832,7 @@
         <v>1002110052</v>
       </c>
       <c r="B2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C2">
         <v>8900</v>
@@ -13816,10 +13847,10 @@
         <v>60</v>
       </c>
       <c r="H2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I2" s="10" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -13827,7 +13858,7 @@
         <v>1000747182</v>
       </c>
       <c r="B3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C3">
         <v>3680</v>
@@ -13842,10 +13873,10 @@
         <v>999</v>
       </c>
       <c r="H3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -13853,7 +13884,7 @@
         <v>1000343575</v>
       </c>
       <c r="B4" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C4">
         <v>3580</v>
@@ -13868,10 +13899,10 @@
         <v>999</v>
       </c>
       <c r="H4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -13879,7 +13910,7 @@
         <v>1000862247</v>
       </c>
       <c r="B5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C5">
         <v>13400</v>
@@ -13894,10 +13925,10 @@
         <v>875</v>
       </c>
       <c r="H5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -13905,7 +13936,7 @@
         <v>1000178183</v>
       </c>
       <c r="B6" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C6">
         <v>4500</v>
@@ -13920,10 +13951,10 @@
         <v>999</v>
       </c>
       <c r="H6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -13931,7 +13962,7 @@
         <v>5031072</v>
       </c>
       <c r="B7" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C7">
         <v>5980</v>
@@ -13946,10 +13977,10 @@
         <v>999</v>
       </c>
       <c r="H7" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -13957,7 +13988,7 @@
         <v>1000875821</v>
       </c>
       <c r="B8" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C8">
         <v>1690</v>
@@ -13972,10 +14003,10 @@
         <v>999</v>
       </c>
       <c r="H8" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -13983,7 +14014,7 @@
         <v>1000651310</v>
       </c>
       <c r="B9" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C9">
         <v>7490</v>
@@ -13998,10 +14029,10 @@
         <v>793</v>
       </c>
       <c r="H9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -14009,7 +14040,7 @@
         <v>1000321598</v>
       </c>
       <c r="B10" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C10">
         <v>1790</v>
@@ -14024,10 +14055,10 @@
         <v>999</v>
       </c>
       <c r="H10" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -14035,7 +14066,7 @@
         <v>5077465</v>
       </c>
       <c r="B11" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C11">
         <v>3980</v>
@@ -14050,10 +14081,10 @@
         <v>999</v>
       </c>
       <c r="H11" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -14061,7 +14092,7 @@
         <v>5079319</v>
       </c>
       <c r="B12" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C12">
         <v>3580</v>
@@ -14076,10 +14107,10 @@
         <v>999</v>
       </c>
       <c r="H12" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -14102,7 +14133,7 @@
         <v>999</v>
       </c>
       <c r="H13" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I13" s="10" t="s">
         <v>16</v>
@@ -14113,7 +14144,7 @@
         <v>5077461</v>
       </c>
       <c r="B14" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C14">
         <v>4640</v>
@@ -14128,10 +14159,10 @@
         <v>999</v>
       </c>
       <c r="H14" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -14139,7 +14170,7 @@
         <v>1000975389</v>
       </c>
       <c r="B15" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C15">
         <v>2990</v>
@@ -14154,10 +14185,10 @@
         <v>999</v>
       </c>
       <c r="H15" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -14165,7 +14196,7 @@
         <v>5079340</v>
       </c>
       <c r="B16" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C16">
         <v>5280</v>
@@ -14180,10 +14211,10 @@
         <v>999</v>
       </c>
       <c r="H16" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -14191,7 +14222,7 @@
         <v>1000198192</v>
       </c>
       <c r="B17" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C17">
         <v>4540</v>
@@ -14206,10 +14237,10 @@
         <v>9999</v>
       </c>
       <c r="H17" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -14217,7 +14248,7 @@
         <v>5151421</v>
       </c>
       <c r="B18" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C18">
         <v>5940</v>
@@ -14232,10 +14263,10 @@
         <v>999</v>
       </c>
       <c r="H18" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -14243,7 +14274,7 @@
         <v>1001272797</v>
       </c>
       <c r="B19" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C19">
         <v>2980</v>
@@ -14258,10 +14289,10 @@
         <v>999</v>
       </c>
       <c r="H19" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -14269,7 +14300,7 @@
         <v>1001029494</v>
       </c>
       <c r="B20" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C20">
         <v>2280</v>
@@ -14284,10 +14315,10 @@
         <v>597</v>
       </c>
       <c r="H20" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -14295,7 +14326,7 @@
         <v>5030780</v>
       </c>
       <c r="B21" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C21">
         <v>5800</v>
@@ -14310,10 +14341,10 @@
         <v>9999</v>
       </c>
       <c r="H21" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -14321,7 +14352,7 @@
         <v>1000339529</v>
       </c>
       <c r="B22" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C22">
         <v>3980</v>
@@ -14336,10 +14367,10 @@
         <v>557</v>
       </c>
       <c r="H22" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -14347,7 +14378,7 @@
         <v>5036524</v>
       </c>
       <c r="B23" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C23">
         <v>2520</v>
@@ -14362,10 +14393,10 @@
         <v>9999</v>
       </c>
       <c r="H23" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -14373,7 +14404,7 @@
         <v>1000356676</v>
       </c>
       <c r="B24" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C24">
         <v>3800</v>
@@ -14388,10 +14419,10 @@
         <v>9999</v>
       </c>
       <c r="H24" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -14399,7 +14430,7 @@
         <v>1000963099</v>
       </c>
       <c r="B25" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C25">
         <v>4780</v>
@@ -14414,10 +14445,10 @@
         <v>999</v>
       </c>
       <c r="H25" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -14425,7 +14456,7 @@
         <v>5088236</v>
       </c>
       <c r="B26" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C26">
         <v>8980</v>
@@ -14440,10 +14471,10 @@
         <v>999</v>
       </c>
       <c r="H26" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -14451,7 +14482,7 @@
         <v>1000617577</v>
       </c>
       <c r="B27" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C27">
         <v>1360</v>
@@ -14466,10 +14497,10 @@
         <v>9999</v>
       </c>
       <c r="H27" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -14477,7 +14508,7 @@
         <v>1000455773</v>
       </c>
       <c r="B28" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C28">
         <v>4500</v>
@@ -14492,10 +14523,10 @@
         <v>434</v>
       </c>
       <c r="H28" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -14503,7 +14534,7 @@
         <v>1000137075</v>
       </c>
       <c r="B29" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C29">
         <v>4480</v>
@@ -14518,10 +14549,10 @@
         <v>999</v>
       </c>
       <c r="H29" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -14529,7 +14560,7 @@
         <v>1002134596</v>
       </c>
       <c r="B30" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C30">
         <v>5980</v>
@@ -14544,10 +14575,10 @@
         <v>81</v>
       </c>
       <c r="H30" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -14555,7 +14586,7 @@
         <v>1001447521</v>
       </c>
       <c r="B31" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C31">
         <v>1440</v>
@@ -14570,10 +14601,10 @@
         <v>258</v>
       </c>
       <c r="H31" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I31" s="10" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -14581,7 +14612,7 @@
         <v>1001421531</v>
       </c>
       <c r="B32" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C32">
         <v>4980</v>
@@ -14596,10 +14627,10 @@
         <v>602</v>
       </c>
       <c r="H32" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -14607,7 +14638,7 @@
         <v>1000269917</v>
       </c>
       <c r="B33" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C33">
         <v>12800</v>
@@ -14622,10 +14653,10 @@
         <v>988</v>
       </c>
       <c r="H33" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -14633,7 +14664,7 @@
         <v>1001592465</v>
       </c>
       <c r="B34" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C34">
         <v>3880</v>
@@ -14648,10 +14679,10 @@
         <v>520</v>
       </c>
       <c r="H34" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -14659,7 +14690,7 @@
         <v>5054491</v>
       </c>
       <c r="B35" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C35">
         <v>6590</v>
@@ -14674,10 +14705,10 @@
         <v>999</v>
       </c>
       <c r="H35" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -14685,7 +14716,7 @@
         <v>1001919935</v>
       </c>
       <c r="B36" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C36">
         <v>3800</v>
@@ -14700,10 +14731,10 @@
         <v>313</v>
       </c>
       <c r="H36" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I36" s="10" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="37" spans="1:9">
@@ -14711,7 +14742,7 @@
         <v>5062899</v>
       </c>
       <c r="B37" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C37">
         <v>4580</v>
@@ -14726,10 +14757,10 @@
         <v>999</v>
       </c>
       <c r="H37" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I37" s="10" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -14737,7 +14768,7 @@
         <v>1000875710</v>
       </c>
       <c r="B38" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C38">
         <v>4580</v>
@@ -14752,10 +14783,10 @@
         <v>999</v>
       </c>
       <c r="H38" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I38" s="10" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -14763,7 +14794,7 @@
         <v>5006818</v>
       </c>
       <c r="B39" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C39">
         <v>8500</v>
@@ -14778,10 +14809,10 @@
         <v>999</v>
       </c>
       <c r="H39" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I39" s="10" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -14789,7 +14820,7 @@
         <v>1000582944</v>
       </c>
       <c r="B40" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C40">
         <v>2780</v>
@@ -14804,10 +14835,10 @@
         <v>594</v>
       </c>
       <c r="H40" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I40" s="10" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -14815,7 +14846,7 @@
         <v>1000206111</v>
       </c>
       <c r="B41" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C41">
         <v>5900</v>
@@ -14830,10 +14861,10 @@
         <v>9999</v>
       </c>
       <c r="H41" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I41" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="42" spans="1:9">
@@ -14841,7 +14872,7 @@
         <v>1000643389</v>
       </c>
       <c r="B42" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C42">
         <v>5480</v>
@@ -14856,10 +14887,10 @@
         <v>444</v>
       </c>
       <c r="H42" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I42" s="10" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="43" spans="1:9">
@@ -14867,7 +14898,7 @@
         <v>1000439362</v>
       </c>
       <c r="B43" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C43">
         <v>2250</v>
@@ -14882,10 +14913,10 @@
         <v>999</v>
       </c>
       <c r="H43" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I43" s="10" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="44" spans="1:9">
@@ -14893,7 +14924,7 @@
         <v>1000166566</v>
       </c>
       <c r="B44" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C44">
         <v>12000</v>
@@ -14908,10 +14939,10 @@
         <v>9999</v>
       </c>
       <c r="H44" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I44" s="10" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="45" spans="1:9">
@@ -14919,7 +14950,7 @@
         <v>1000526145</v>
       </c>
       <c r="B45" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C45">
         <v>8900</v>
@@ -14934,10 +14965,10 @@
         <v>999</v>
       </c>
       <c r="H45" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I45" s="10" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="46" spans="1:9">
@@ -14945,7 +14976,7 @@
         <v>1000789439</v>
       </c>
       <c r="B46" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C46">
         <v>3590</v>
@@ -14960,10 +14991,10 @@
         <v>324</v>
       </c>
       <c r="H46" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I46" s="10" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="47" spans="1:9">
@@ -14971,7 +15002,7 @@
         <v>1000356687</v>
       </c>
       <c r="B47" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C47">
         <v>4400</v>
@@ -14986,10 +15017,10 @@
         <v>999</v>
       </c>
       <c r="H47" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I47" s="10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="48" spans="1:9">
@@ -14997,7 +15028,7 @@
         <v>5153242</v>
       </c>
       <c r="B48" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C48">
         <v>9980</v>
@@ -15012,10 +15043,10 @@
         <v>503</v>
       </c>
       <c r="H48" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I48" s="10" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="49" spans="1:9">
@@ -15023,7 +15054,7 @@
         <v>1000033235</v>
       </c>
       <c r="B49" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C49">
         <v>2600</v>
@@ -15038,10 +15069,10 @@
         <v>9999</v>
       </c>
       <c r="H49" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I49" s="10" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -15049,7 +15080,7 @@
         <v>1001570087</v>
       </c>
       <c r="B50" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C50">
         <v>6080</v>
@@ -15064,10 +15095,10 @@
         <v>999</v>
       </c>
       <c r="H50" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I50" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -15090,7 +15121,7 @@
         <v>9999</v>
       </c>
       <c r="H51" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I51" s="10" t="s">
         <v>22</v>
@@ -15101,7 +15132,7 @@
         <v>1000942359</v>
       </c>
       <c r="B52" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C52">
         <v>1440</v>
@@ -15116,10 +15147,10 @@
         <v>999</v>
       </c>
       <c r="H52" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I52" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="53" spans="1:9">
@@ -15127,7 +15158,7 @@
         <v>1001397540</v>
       </c>
       <c r="B53" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C53">
         <v>1080</v>
@@ -15142,10 +15173,10 @@
         <v>928</v>
       </c>
       <c r="H53" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I53" s="10" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="54" spans="1:9">
@@ -15153,7 +15184,7 @@
         <v>1000927112</v>
       </c>
       <c r="B54" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C54">
         <v>3325</v>
@@ -15168,10 +15199,10 @@
         <v>999</v>
       </c>
       <c r="H54" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I54" s="10" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="55" spans="1:9">
@@ -15179,7 +15210,7 @@
         <v>5103484</v>
       </c>
       <c r="B55" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C55">
         <v>11980</v>
@@ -15194,10 +15225,10 @@
         <v>999</v>
       </c>
       <c r="H55" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I55" s="10" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="56" spans="1:9">
@@ -15205,7 +15236,7 @@
         <v>1000605988</v>
       </c>
       <c r="B56" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C56">
         <v>4180</v>
@@ -15220,10 +15251,10 @@
         <v>723</v>
       </c>
       <c r="H56" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I56" s="10" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="57" spans="1:9">
@@ -15231,7 +15262,7 @@
         <v>5060050</v>
       </c>
       <c r="B57" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C57">
         <v>5980</v>
@@ -15246,10 +15277,10 @@
         <v>9999</v>
       </c>
       <c r="H57" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I57" s="10" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="58" spans="1:9">
@@ -15257,7 +15288,7 @@
         <v>1002324203</v>
       </c>
       <c r="B58" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C58">
         <v>6980</v>
@@ -15272,10 +15303,10 @@
         <v>22</v>
       </c>
       <c r="H58" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I58" s="10" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="59" spans="1:9">
@@ -15283,7 +15314,7 @@
         <v>5095165</v>
       </c>
       <c r="B59" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C59">
         <v>3580</v>
@@ -15298,10 +15329,10 @@
         <v>999</v>
       </c>
       <c r="H59" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I59" s="10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="60" spans="1:9">
@@ -15309,7 +15340,7 @@
         <v>1000178191</v>
       </c>
       <c r="B60" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C60">
         <v>4150</v>
@@ -15324,10 +15355,10 @@
         <v>9999</v>
       </c>
       <c r="H60" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I60" s="10" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="61" spans="1:9">
@@ -15335,7 +15366,7 @@
         <v>1000914382</v>
       </c>
       <c r="B61" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C61">
         <v>15500</v>
@@ -15350,10 +15381,10 @@
         <v>658</v>
       </c>
       <c r="H61" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I61" s="10" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="62" spans="1:9">
@@ -15361,7 +15392,7 @@
         <v>1002014581</v>
       </c>
       <c r="B62" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C62">
         <v>4950</v>
@@ -15376,10 +15407,10 @@
         <v>999</v>
       </c>
       <c r="H62" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I62" s="10" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="63" spans="1:9">
@@ -15387,7 +15418,7 @@
         <v>5052362</v>
       </c>
       <c r="B63" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C63">
         <v>13900</v>
@@ -15402,10 +15433,10 @@
         <v>999</v>
       </c>
       <c r="H63" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I63" s="10" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="64" spans="1:9">
@@ -15413,7 +15444,7 @@
         <v>5121160</v>
       </c>
       <c r="B64" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C64">
         <v>4380</v>
@@ -15428,10 +15459,10 @@
         <v>999</v>
       </c>
       <c r="H64" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I64" s="10" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="65" spans="1:9">
@@ -15439,7 +15470,7 @@
         <v>1000958549</v>
       </c>
       <c r="B65" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C65">
         <v>3380</v>
@@ -15454,10 +15485,10 @@
         <v>711</v>
       </c>
       <c r="H65" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I65" s="10" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="66" spans="1:9">
@@ -15465,7 +15496,7 @@
         <v>1002010936</v>
       </c>
       <c r="B66" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C66">
         <v>2800</v>
@@ -15480,10 +15511,10 @@
         <v>416</v>
       </c>
       <c r="H66" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I66" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="67" spans="1:9">
@@ -15491,7 +15522,7 @@
         <v>1000242960</v>
       </c>
       <c r="B67" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C67">
         <v>7000</v>
@@ -15506,10 +15537,10 @@
         <v>999</v>
       </c>
       <c r="H67" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I67" s="10" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="68" spans="1:9">
@@ -15517,7 +15548,7 @@
         <v>1002482468</v>
       </c>
       <c r="B68" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C68">
         <v>2130</v>
@@ -15532,10 +15563,10 @@
         <v>492</v>
       </c>
       <c r="H68" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I68" s="10" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="69" spans="1:9">
@@ -15543,7 +15574,7 @@
         <v>5058855</v>
       </c>
       <c r="B69" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C69">
         <v>8500</v>
@@ -15558,10 +15589,10 @@
         <v>9999</v>
       </c>
       <c r="H69" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I69" s="10" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="70" spans="1:9">
@@ -15569,7 +15600,7 @@
         <v>1000783621</v>
       </c>
       <c r="B70" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C70">
         <v>10960</v>
@@ -15584,10 +15615,10 @@
         <v>175</v>
       </c>
       <c r="H70" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I70" s="10" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="71" spans="1:9">
@@ -15595,7 +15626,7 @@
         <v>1000525224</v>
       </c>
       <c r="B71" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C71">
         <v>12980</v>
@@ -15610,10 +15641,10 @@
         <v>191</v>
       </c>
       <c r="H71" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I71" s="10" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="72" spans="1:9">
@@ -15621,7 +15652,7 @@
         <v>1000365879</v>
       </c>
       <c r="B72" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C72">
         <v>3380</v>
@@ -15636,10 +15667,10 @@
         <v>999</v>
       </c>
       <c r="H72" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I72" s="10" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="73" spans="1:9">
@@ -15647,7 +15678,7 @@
         <v>1002133624</v>
       </c>
       <c r="B73" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C73">
         <v>6300</v>
@@ -15662,10 +15693,10 @@
         <v>97</v>
       </c>
       <c r="H73" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I73" s="10" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="74" spans="1:9">
@@ -15673,7 +15704,7 @@
         <v>1000339558</v>
       </c>
       <c r="B74" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C74">
         <v>2720</v>
@@ -15688,10 +15719,10 @@
         <v>448</v>
       </c>
       <c r="H74" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I74" s="10" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="75" spans="1:9">
@@ -15699,7 +15730,7 @@
         <v>5081478</v>
       </c>
       <c r="B75" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C75">
         <v>3360</v>
@@ -15714,10 +15745,10 @@
         <v>9999</v>
       </c>
       <c r="H75" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I75" s="10" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="76" spans="1:9">
@@ -15725,7 +15756,7 @@
         <v>5005540</v>
       </c>
       <c r="B76" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C76">
         <v>8000</v>
@@ -15740,10 +15771,10 @@
         <v>9999</v>
       </c>
       <c r="H76" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I76" s="10" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="77" spans="1:9">
@@ -15751,7 +15782,7 @@
         <v>1000526148</v>
       </c>
       <c r="B77" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C77">
         <v>8900</v>
@@ -15766,10 +15797,10 @@
         <v>276</v>
       </c>
       <c r="H77" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I77" s="10" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="78" spans="1:9">
@@ -15777,7 +15808,7 @@
         <v>1000677312</v>
       </c>
       <c r="B78" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C78">
         <v>1480</v>
@@ -15792,10 +15823,10 @@
         <v>999</v>
       </c>
       <c r="H78" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I78" s="10" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="79" spans="1:9">
@@ -15803,7 +15834,7 @@
         <v>1001407039</v>
       </c>
       <c r="B79" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C79">
         <v>3980</v>
@@ -15818,10 +15849,10 @@
         <v>145</v>
       </c>
       <c r="H79" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I79" s="10" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="80" spans="1:9">
@@ -15829,7 +15860,7 @@
         <v>1000248448</v>
       </c>
       <c r="B80" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C80">
         <v>5200</v>
@@ -15844,10 +15875,10 @@
         <v>9999</v>
       </c>
       <c r="H80" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I80" s="10" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="81" spans="1:9">
@@ -15855,7 +15886,7 @@
         <v>1001027192</v>
       </c>
       <c r="B81" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C81">
         <v>9000</v>
@@ -15870,10 +15901,10 @@
         <v>361</v>
       </c>
       <c r="H81" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I81" s="10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="82" spans="1:9">
@@ -15881,7 +15912,7 @@
         <v>5067308</v>
       </c>
       <c r="B82" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C82">
         <v>2880</v>
@@ -15896,10 +15927,10 @@
         <v>999</v>
       </c>
       <c r="H82" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I82" s="10" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="83" spans="1:9">
@@ -15907,7 +15938,7 @@
         <v>1000942860</v>
       </c>
       <c r="B83" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C83">
         <v>1390</v>
@@ -15922,10 +15953,10 @@
         <v>999</v>
       </c>
       <c r="H83" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I83" s="10" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="84" spans="1:9">
@@ -15933,7 +15964,7 @@
         <v>1001991119</v>
       </c>
       <c r="B84" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C84">
         <v>3480</v>
@@ -15948,10 +15979,10 @@
         <v>999</v>
       </c>
       <c r="H84" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I84" s="10" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="85" spans="1:9">
@@ -15959,7 +15990,7 @@
         <v>5132664</v>
       </c>
       <c r="B85" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C85">
         <v>3800</v>
@@ -15974,10 +16005,10 @@
         <v>999</v>
       </c>
       <c r="H85" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I85" s="10" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="86" spans="1:9">
@@ -15985,7 +16016,7 @@
         <v>1000640854</v>
       </c>
       <c r="B86" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C86">
         <v>2720</v>
@@ -16000,10 +16031,10 @@
         <v>999</v>
       </c>
       <c r="H86" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I86" s="10" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="87" spans="1:9">
@@ -16011,7 +16042,7 @@
         <v>1000045935</v>
       </c>
       <c r="B87" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C87">
         <v>5990</v>
@@ -16026,10 +16057,10 @@
         <v>999</v>
       </c>
       <c r="H87" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I87" s="10" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="88" spans="1:9">
@@ -16037,7 +16068,7 @@
         <v>1000349505</v>
       </c>
       <c r="B88" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C88">
         <v>1440</v>
@@ -16052,10 +16083,10 @@
         <v>999</v>
       </c>
       <c r="H88" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I88" s="10" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="89" spans="1:9">
@@ -16063,7 +16094,7 @@
         <v>5060582</v>
       </c>
       <c r="B89" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C89">
         <v>10000</v>
@@ -16078,10 +16109,10 @@
         <v>999</v>
       </c>
       <c r="H89" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I89" s="10" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="90" spans="1:9">
@@ -16089,7 +16120,7 @@
         <v>1001363953</v>
       </c>
       <c r="B90" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C90">
         <v>2180</v>
@@ -16104,10 +16135,10 @@
         <v>999</v>
       </c>
       <c r="H90" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I90" s="10" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="91" spans="1:9">
@@ -16115,7 +16146,7 @@
         <v>5103372</v>
       </c>
       <c r="B91" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C91">
         <v>11980</v>
@@ -16130,10 +16161,10 @@
         <v>999</v>
       </c>
       <c r="H91" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I91" s="10" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="92" spans="1:9">
@@ -16141,7 +16172,7 @@
         <v>1001501063</v>
       </c>
       <c r="B92" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C92">
         <v>1260</v>
@@ -16156,10 +16187,10 @@
         <v>980</v>
       </c>
       <c r="H92" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I92" s="10" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="93" spans="1:9">
@@ -16167,7 +16198,7 @@
         <v>1000443353</v>
       </c>
       <c r="B93" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C93">
         <v>4040</v>
@@ -16182,10 +16213,10 @@
         <v>999</v>
       </c>
       <c r="H93" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I93" s="10" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="94" spans="1:9">
@@ -16193,7 +16224,7 @@
         <v>1002221133</v>
       </c>
       <c r="B94" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C94">
         <v>4980</v>
@@ -16208,10 +16239,10 @@
         <v>81</v>
       </c>
       <c r="H94" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I94" s="10" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="95" spans="1:9">
@@ -16219,7 +16250,7 @@
         <v>1000136966</v>
       </c>
       <c r="B95" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C95">
         <v>9000</v>
@@ -16234,10 +16265,10 @@
         <v>999</v>
       </c>
       <c r="H95" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I95" s="10" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="96" spans="1:9">
@@ -16245,7 +16276,7 @@
         <v>1000799985</v>
       </c>
       <c r="B96" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C96">
         <v>4980</v>
@@ -16260,10 +16291,10 @@
         <v>612</v>
       </c>
       <c r="H96" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I96" s="10" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="97" spans="1:9">
@@ -16271,7 +16302,7 @@
         <v>1000960165</v>
       </c>
       <c r="B97" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C97">
         <v>1390</v>
@@ -16286,10 +16317,10 @@
         <v>539</v>
       </c>
       <c r="H97" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I97" s="10" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="98" spans="1:9">
@@ -16297,7 +16328,7 @@
         <v>1001337989</v>
       </c>
       <c r="B98" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C98">
         <v>5280</v>
@@ -16312,10 +16343,10 @@
         <v>613</v>
       </c>
       <c r="H98" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I98" s="10" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="99" spans="1:9">
@@ -16338,7 +16369,7 @@
         <v>999</v>
       </c>
       <c r="H99" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I99" s="10" t="s">
         <v>32</v>
@@ -16364,7 +16395,7 @@
         <v>999</v>
       </c>
       <c r="H100" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I100" s="10" t="s">
         <v>43</v>
@@ -16375,7 +16406,7 @@
         <v>1002104225</v>
       </c>
       <c r="B101" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C101">
         <v>1280</v>
@@ -16390,10 +16421,10 @@
         <v>98</v>
       </c>
       <c r="H101" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I101" s="10" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="102" spans="1:9">
@@ -16401,7 +16432,7 @@
         <v>1002020133</v>
       </c>
       <c r="B102" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C102">
         <v>9030</v>
@@ -16416,10 +16447,10 @@
         <v>159</v>
       </c>
       <c r="H102" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I102" s="10" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="103" spans="1:9">
@@ -16427,7 +16458,7 @@
         <v>1000360436</v>
       </c>
       <c r="B103" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C103">
         <v>4480</v>
@@ -16442,10 +16473,10 @@
         <v>999</v>
       </c>
       <c r="H103" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I103" s="10" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="104" spans="1:9">
@@ -16453,7 +16484,7 @@
         <v>1001042362</v>
       </c>
       <c r="B104" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C104">
         <v>3980</v>
@@ -16468,10 +16499,10 @@
         <v>958</v>
       </c>
       <c r="H104" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I104" s="10" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="105" spans="1:9">
@@ -16479,7 +16510,7 @@
         <v>1002340554</v>
       </c>
       <c r="B105" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C105">
         <v>4250</v>
@@ -16494,10 +16525,10 @@
         <v>342</v>
       </c>
       <c r="H105" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I105" s="10" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="106" spans="1:9">
@@ -16505,7 +16536,7 @@
         <v>1000490099</v>
       </c>
       <c r="B106" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C106">
         <v>3980</v>
@@ -16520,10 +16551,10 @@
         <v>999</v>
       </c>
       <c r="H106" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I106" s="10" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="107" spans="1:9">
@@ -16531,7 +16562,7 @@
         <v>5077641</v>
       </c>
       <c r="B107" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C107">
         <v>7080</v>
@@ -16546,10 +16577,10 @@
         <v>999</v>
       </c>
       <c r="H107" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I107" s="10" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="108" spans="1:9">
@@ -16557,7 +16588,7 @@
         <v>1001397631</v>
       </c>
       <c r="B108" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C108">
         <v>1360</v>
@@ -16572,10 +16603,10 @@
         <v>772</v>
       </c>
       <c r="H108" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I108" s="10" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="109" spans="1:9">
@@ -16583,7 +16614,7 @@
         <v>1001942440</v>
       </c>
       <c r="B109" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C109">
         <v>2500</v>
@@ -16598,10 +16629,10 @@
         <v>751</v>
       </c>
       <c r="H109" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I109" s="10" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="110" spans="1:9">
@@ -16609,7 +16640,7 @@
         <v>1000958603</v>
       </c>
       <c r="B110" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C110">
         <v>3480</v>
@@ -16624,10 +16655,10 @@
         <v>889</v>
       </c>
       <c r="H110" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I110" s="10" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="111" spans="1:9">
@@ -16650,7 +16681,7 @@
         <v>999</v>
       </c>
       <c r="H111" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I111" s="10" t="s">
         <v>26</v>
@@ -16661,7 +16692,7 @@
         <v>1002221138</v>
       </c>
       <c r="B112" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C112">
         <v>4480</v>
@@ -16676,10 +16707,10 @@
         <v>134</v>
       </c>
       <c r="H112" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I112" s="10" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="113" spans="1:9">
@@ -16687,7 +16718,7 @@
         <v>1000216544</v>
       </c>
       <c r="B113" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C113">
         <v>4380</v>
@@ -16702,10 +16733,10 @@
         <v>999</v>
       </c>
       <c r="H113" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I113" s="10" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="114" spans="1:9">
@@ -16713,7 +16744,7 @@
         <v>5118057</v>
       </c>
       <c r="B114" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C114">
         <v>2720</v>
@@ -16728,10 +16759,10 @@
         <v>999</v>
       </c>
       <c r="H114" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I114" s="10" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="115" spans="1:9">
@@ -16739,7 +16770,7 @@
         <v>1000656471</v>
       </c>
       <c r="B115" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C115">
         <v>5850</v>
@@ -16754,10 +16785,10 @@
         <v>71</v>
       </c>
       <c r="H115" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I115" s="10" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="116" spans="1:9">
@@ -16765,7 +16796,7 @@
         <v>1001073370</v>
       </c>
       <c r="B116" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C116">
         <v>3500</v>
@@ -16780,10 +16811,10 @@
         <v>999</v>
       </c>
       <c r="H116" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I116" s="10" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="117" spans="1:9">
@@ -16791,7 +16822,7 @@
         <v>1000365868</v>
       </c>
       <c r="B117" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C117">
         <v>4380</v>
@@ -16806,10 +16837,10 @@
         <v>627</v>
       </c>
       <c r="H117" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I117" s="10" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="118" spans="1:9">
@@ -16817,7 +16848,7 @@
         <v>1001740101</v>
       </c>
       <c r="B118" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C118">
         <v>4200</v>
@@ -16832,10 +16863,10 @@
         <v>391</v>
       </c>
       <c r="H118" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I118" s="10" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="119" spans="1:9">
@@ -16843,7 +16874,7 @@
         <v>1000339526</v>
       </c>
       <c r="B119" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C119">
         <v>5440</v>
@@ -16858,10 +16889,10 @@
         <v>956</v>
       </c>
       <c r="H119" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I119" s="10" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="120" spans="1:9">
@@ -16869,7 +16900,7 @@
         <v>1000125337</v>
       </c>
       <c r="B120" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C120">
         <v>6280</v>
@@ -16884,10 +16915,10 @@
         <v>999</v>
       </c>
       <c r="H120" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I120" s="10" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="121" spans="1:9">
@@ -16895,7 +16926,7 @@
         <v>5013230</v>
       </c>
       <c r="B121" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C121">
         <v>4780</v>
@@ -16910,10 +16941,10 @@
         <v>9999</v>
       </c>
       <c r="H121" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I121" s="10" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="122" spans="1:9">
@@ -16921,7 +16952,7 @@
         <v>5043538</v>
       </c>
       <c r="B122" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C122">
         <v>11500</v>
@@ -16936,10 +16967,10 @@
         <v>999</v>
       </c>
       <c r="H122" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I122" s="10" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="123" spans="1:9">
@@ -16947,7 +16978,7 @@
         <v>1001382381</v>
       </c>
       <c r="B123" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C123">
         <v>8990</v>
@@ -16962,10 +16993,10 @@
         <v>999</v>
       </c>
       <c r="H123" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I123" s="10" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="124" spans="1:9">
@@ -16973,7 +17004,7 @@
         <v>1002159262</v>
       </c>
       <c r="B124" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C124">
         <v>2500</v>
@@ -16988,10 +17019,10 @@
         <v>197</v>
       </c>
       <c r="H124" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I124" s="10" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="125" spans="1:9">
@@ -16999,7 +17030,7 @@
         <v>1002286852</v>
       </c>
       <c r="B125" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C125">
         <v>3540</v>
@@ -17014,10 +17045,10 @@
         <v>191</v>
       </c>
       <c r="H125" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I125" s="10" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="126" spans="1:9">
@@ -17025,7 +17056,7 @@
         <v>5052356</v>
       </c>
       <c r="B126" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C126">
         <v>12300</v>
@@ -17040,10 +17071,10 @@
         <v>999</v>
       </c>
       <c r="H126" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I126" s="10" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="127" spans="1:9">
@@ -17051,7 +17082,7 @@
         <v>1000499057</v>
       </c>
       <c r="B127" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C127">
         <v>11980</v>
@@ -17066,10 +17097,10 @@
         <v>232</v>
       </c>
       <c r="H127" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I127" s="10" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="128" spans="1:9">
@@ -17077,7 +17108,7 @@
         <v>1000791609</v>
       </c>
       <c r="B128" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C128">
         <v>1520</v>
@@ -17092,10 +17123,10 @@
         <v>999</v>
       </c>
       <c r="H128" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I128" s="10" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="129" spans="1:9">
@@ -17103,7 +17134,7 @@
         <v>1000074625</v>
       </c>
       <c r="B129" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C129">
         <v>20900</v>
@@ -17118,10 +17149,10 @@
         <v>690</v>
       </c>
       <c r="H129" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I129" s="10" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="130" spans="1:9">
@@ -17129,7 +17160,7 @@
         <v>5077457</v>
       </c>
       <c r="B130" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C130">
         <v>4320</v>
@@ -17144,10 +17175,10 @@
         <v>999</v>
       </c>
       <c r="H130" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I130" s="10" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="131" spans="1:9">
@@ -17155,7 +17186,7 @@
         <v>1000349503</v>
       </c>
       <c r="B131" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C131">
         <v>2250</v>
@@ -17170,10 +17201,10 @@
         <v>786</v>
       </c>
       <c r="H131" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I131" s="10" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="132" spans="1:9">
@@ -17196,7 +17227,7 @@
         <v>999</v>
       </c>
       <c r="H132" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I132" s="10" t="s">
         <v>47</v>
@@ -17207,7 +17238,7 @@
         <v>5054219</v>
       </c>
       <c r="B133" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C133">
         <v>2490</v>
@@ -17222,10 +17253,10 @@
         <v>9999</v>
       </c>
       <c r="H133" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I133" s="10" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="134" spans="1:9">
@@ -17233,7 +17264,7 @@
         <v>1001959559</v>
       </c>
       <c r="B134" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C134">
         <v>2400</v>
@@ -17248,10 +17279,10 @@
         <v>615</v>
       </c>
       <c r="H134" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I134" s="10" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="135" spans="1:9">
@@ -17259,7 +17290,7 @@
         <v>5132978</v>
       </c>
       <c r="B135" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C135">
         <v>4200</v>
@@ -17274,10 +17305,10 @@
         <v>999</v>
       </c>
       <c r="H135" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I135" s="10" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="136" spans="1:9">
@@ -17285,7 +17316,7 @@
         <v>1000777595</v>
       </c>
       <c r="B136" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C136">
         <v>2980</v>
@@ -17300,10 +17331,10 @@
         <v>776</v>
       </c>
       <c r="H136" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I136" s="10" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="137" spans="1:9">
@@ -17311,7 +17342,7 @@
         <v>5067311</v>
       </c>
       <c r="B137" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C137">
         <v>4480</v>
@@ -17326,10 +17357,10 @@
         <v>999</v>
       </c>
       <c r="H137" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I137" s="10" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="138" spans="1:9">
@@ -17337,7 +17368,7 @@
         <v>1002225093</v>
       </c>
       <c r="B138" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C138">
         <v>3980</v>
@@ -17352,10 +17383,10 @@
         <v>324</v>
       </c>
       <c r="H138" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I138" s="10" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="139" spans="1:9">
@@ -17363,7 +17394,7 @@
         <v>5030130</v>
       </c>
       <c r="B139" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C139">
         <v>3980</v>
@@ -17378,10 +17409,10 @@
         <v>9999</v>
       </c>
       <c r="H139" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I139" s="10" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="140" spans="1:9">
@@ -17389,7 +17420,7 @@
         <v>1001317277</v>
       </c>
       <c r="B140" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C140">
         <v>3780</v>
@@ -17404,10 +17435,10 @@
         <v>359</v>
       </c>
       <c r="H140" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I140" s="10" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="141" spans="1:9">
@@ -17415,7 +17446,7 @@
         <v>5118059</v>
       </c>
       <c r="B141" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C141">
         <v>2720</v>
@@ -17430,10 +17461,10 @@
         <v>999</v>
       </c>
       <c r="H141" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I141" s="10" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="142" spans="1:9">
@@ -17456,7 +17487,7 @@
         <v>999</v>
       </c>
       <c r="H142" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I142" s="10" t="s">
         <v>45</v>
@@ -17467,7 +17498,7 @@
         <v>1001861625</v>
       </c>
       <c r="B143" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C143">
         <v>6000</v>
@@ -17482,10 +17513,10 @@
         <v>613</v>
       </c>
       <c r="H143" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I143" s="10" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="144" spans="1:9">
@@ -17493,7 +17524,7 @@
         <v>1002108866</v>
       </c>
       <c r="B144" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C144">
         <v>8900</v>
@@ -17508,10 +17539,10 @@
         <v>87</v>
       </c>
       <c r="H144" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I144" s="10" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="145" spans="1:9">
@@ -17519,7 +17550,7 @@
         <v>1002221130</v>
       </c>
       <c r="B145" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C145">
         <v>3480</v>
@@ -17534,10 +17565,10 @@
         <v>304</v>
       </c>
       <c r="H145" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I145" s="10" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="146" spans="1:9">
@@ -17545,7 +17576,7 @@
         <v>5049808</v>
       </c>
       <c r="B146" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C146">
         <v>2500</v>
@@ -17560,10 +17591,10 @@
         <v>9999</v>
       </c>
       <c r="H146" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I146" s="10" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="147" spans="1:9">
@@ -17571,7 +17602,7 @@
         <v>1000528989</v>
       </c>
       <c r="B147" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C147">
         <v>3980</v>
@@ -17586,10 +17617,10 @@
         <v>999</v>
       </c>
       <c r="H147" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I147" s="10" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="148" spans="1:9">
@@ -17597,7 +17628,7 @@
         <v>1000739633</v>
       </c>
       <c r="B148" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C148">
         <v>3900</v>
@@ -17612,10 +17643,10 @@
         <v>999</v>
       </c>
       <c r="H148" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I148" s="10" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="149" spans="1:9">
@@ -17623,7 +17654,7 @@
         <v>5121162</v>
       </c>
       <c r="B149" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C149">
         <v>2380</v>
@@ -17638,10 +17669,10 @@
         <v>999</v>
       </c>
       <c r="H149" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I149" s="10" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="150" spans="1:9">
@@ -17649,7 +17680,7 @@
         <v>1000891294</v>
       </c>
       <c r="B150" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C150">
         <v>11900</v>
@@ -17664,10 +17695,10 @@
         <v>826</v>
       </c>
       <c r="H150" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I150" s="10" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="151" spans="1:9">
@@ -17675,7 +17706,7 @@
         <v>1002280048</v>
       </c>
       <c r="B151" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C151">
         <v>2250</v>
@@ -17690,10 +17721,10 @@
         <v>622</v>
       </c>
       <c r="H151" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I151" s="10" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="152" spans="1:9">
@@ -17701,7 +17732,7 @@
         <v>1002003498</v>
       </c>
       <c r="B152" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C152">
         <v>3500</v>
@@ -17716,10 +17747,10 @@
         <v>866</v>
       </c>
       <c r="H152" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I152" s="10" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="153" spans="1:9">
@@ -17727,7 +17758,7 @@
         <v>1000485694</v>
       </c>
       <c r="B153" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C153">
         <v>4480</v>
@@ -17742,10 +17773,10 @@
         <v>999</v>
       </c>
       <c r="H153" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I153" s="10" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="154" spans="1:9">
@@ -17753,7 +17784,7 @@
         <v>1000612634</v>
       </c>
       <c r="B154" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C154">
         <v>6490</v>
@@ -17768,10 +17799,10 @@
         <v>416</v>
       </c>
       <c r="H154" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I154" s="10" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="155" spans="1:9">
@@ -17779,7 +17810,7 @@
         <v>1002475314</v>
       </c>
       <c r="B155" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C155">
         <v>4730</v>
@@ -17794,10 +17825,10 @@
         <v>181</v>
       </c>
       <c r="H155" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I155" s="10" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="156" spans="1:9">
@@ -17805,7 +17836,7 @@
         <v>1000198198</v>
       </c>
       <c r="B156" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C156">
         <v>3200</v>
@@ -17820,10 +17851,10 @@
         <v>999</v>
       </c>
       <c r="H156" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I156" s="10" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="157" spans="1:9">
@@ -17831,7 +17862,7 @@
         <v>1000147459</v>
       </c>
       <c r="B157" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C157">
         <v>3590</v>
@@ -17846,10 +17877,10 @@
         <v>999</v>
       </c>
       <c r="H157" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I157" s="10" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="158" spans="1:9">
@@ -17857,7 +17888,7 @@
         <v>1000030463</v>
       </c>
       <c r="B158" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C158">
         <v>8000</v>
@@ -17872,10 +17903,10 @@
         <v>533</v>
       </c>
       <c r="H158" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I158" s="10" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="159" spans="1:9">
@@ -17883,7 +17914,7 @@
         <v>1000525222</v>
       </c>
       <c r="B159" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C159">
         <v>4380</v>
@@ -17898,10 +17929,10 @@
         <v>718</v>
       </c>
       <c r="H159" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I159" s="10" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="160" spans="1:9">
@@ -17909,7 +17940,7 @@
         <v>1000330137</v>
       </c>
       <c r="B160" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C160">
         <v>7800</v>
@@ -17924,10 +17955,10 @@
         <v>999</v>
       </c>
       <c r="H160" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I160" s="10" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="161" spans="1:9">
@@ -17935,7 +17966,7 @@
         <v>5071375</v>
       </c>
       <c r="B161" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C161">
         <v>2700</v>
@@ -17950,10 +17981,10 @@
         <v>999</v>
       </c>
       <c r="H161" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I161" s="10" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="162" spans="1:9">
@@ -17961,7 +17992,7 @@
         <v>1001333045</v>
       </c>
       <c r="B162" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C162">
         <v>2880</v>
@@ -17976,10 +18007,10 @@
         <v>361</v>
       </c>
       <c r="H162" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I162" s="10" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="163" spans="1:9">
@@ -17987,7 +18018,7 @@
         <v>1001406908</v>
       </c>
       <c r="B163" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C163">
         <v>1280</v>
@@ -18002,10 +18033,10 @@
         <v>511</v>
       </c>
       <c r="H163" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I163" s="10" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="164" spans="1:9">
@@ -18013,7 +18044,7 @@
         <v>1002185327</v>
       </c>
       <c r="B164" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C164">
         <v>2280</v>
@@ -18028,10 +18059,10 @@
         <v>106</v>
       </c>
       <c r="H164" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I164" s="10" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="165" spans="1:9">
@@ -18039,7 +18070,7 @@
         <v>1002295305</v>
       </c>
       <c r="B165" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C165">
         <v>3300</v>
@@ -18054,10 +18085,10 @@
         <v>184</v>
       </c>
       <c r="H165" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I165" s="10" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="166" spans="1:9">
@@ -18065,7 +18096,7 @@
         <v>1000506290</v>
       </c>
       <c r="B166" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C166">
         <v>4180</v>
@@ -18080,10 +18111,10 @@
         <v>509</v>
       </c>
       <c r="H166" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I166" s="10" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="167" spans="1:9">
@@ -18091,7 +18122,7 @@
         <v>1001701315</v>
       </c>
       <c r="B167" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C167">
         <v>4980</v>
@@ -18106,10 +18137,10 @@
         <v>255</v>
       </c>
       <c r="H167" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I167" s="10" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="168" spans="1:9">
@@ -18117,7 +18148,7 @@
         <v>1001171286</v>
       </c>
       <c r="B168" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C168">
         <v>2720</v>
@@ -18132,10 +18163,10 @@
         <v>999</v>
       </c>
       <c r="H168" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I168" s="10" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="169" spans="1:9">
@@ -18143,7 +18174,7 @@
         <v>1002129045</v>
       </c>
       <c r="B169" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C169">
         <v>1440</v>
@@ -18158,10 +18189,10 @@
         <v>637</v>
       </c>
       <c r="H169" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I169" s="10" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="170" spans="1:9">
@@ -18169,7 +18200,7 @@
         <v>1000263120</v>
       </c>
       <c r="B170" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C170">
         <v>3980</v>
@@ -18184,10 +18215,10 @@
         <v>999</v>
       </c>
       <c r="H170" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I170" s="10" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="171" spans="1:9">
@@ -18195,7 +18226,7 @@
         <v>1002131257</v>
       </c>
       <c r="B171" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C171">
         <v>4780</v>
@@ -18210,10 +18241,10 @@
         <v>216</v>
       </c>
       <c r="H171" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I171" s="10" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="172" spans="1:9">
@@ -18221,7 +18252,7 @@
         <v>1000679265</v>
       </c>
       <c r="B172" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C172">
         <v>2780</v>
@@ -18236,10 +18267,10 @@
         <v>732</v>
       </c>
       <c r="H172" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I172" s="10" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="173" spans="1:9">
@@ -18262,7 +18293,7 @@
         <v>999</v>
       </c>
       <c r="H173" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I173" s="10" t="s">
         <v>28</v>
@@ -18273,7 +18304,7 @@
         <v>5086556</v>
       </c>
       <c r="B174" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C174">
         <v>5900</v>
@@ -18288,10 +18319,10 @@
         <v>999</v>
       </c>
       <c r="H174" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I174" s="10" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="175" spans="1:9">
@@ -18299,7 +18330,7 @@
         <v>1000608510</v>
       </c>
       <c r="B175" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C175">
         <v>2520</v>
@@ -18314,10 +18345,10 @@
         <v>999</v>
       </c>
       <c r="H175" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I175" s="10" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="176" spans="1:9">
@@ -18325,7 +18356,7 @@
         <v>1000648498</v>
       </c>
       <c r="B176" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C176">
         <v>3390</v>
@@ -18340,10 +18371,10 @@
         <v>9999</v>
       </c>
       <c r="H176" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I176" s="10" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="177" spans="1:9">
@@ -18351,7 +18382,7 @@
         <v>1001740103</v>
       </c>
       <c r="B177" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C177">
         <v>7200</v>
@@ -18366,10 +18397,10 @@
         <v>384</v>
       </c>
       <c r="H177" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I177" s="10" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="178" spans="1:9">
@@ -18377,7 +18408,7 @@
         <v>5004416</v>
       </c>
       <c r="B178" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C178">
         <v>2600</v>
@@ -18392,10 +18423,10 @@
         <v>9999</v>
       </c>
       <c r="H178" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I178" s="10" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="179" spans="1:9">
@@ -18403,7 +18434,7 @@
         <v>1001241376</v>
       </c>
       <c r="B179" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C179">
         <v>8980</v>
@@ -18418,10 +18449,10 @@
         <v>477</v>
       </c>
       <c r="H179" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I179" s="10" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="180" spans="1:9">
@@ -18429,7 +18460,7 @@
         <v>1000957506</v>
       </c>
       <c r="B180" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C180">
         <v>2500</v>
@@ -18444,10 +18475,10 @@
         <v>284</v>
       </c>
       <c r="H180" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I180" s="10" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="181" spans="1:9">
@@ -18455,7 +18486,7 @@
         <v>1001391101</v>
       </c>
       <c r="B181" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C181">
         <v>5280</v>
@@ -18470,10 +18501,10 @@
         <v>585</v>
       </c>
       <c r="H181" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I181" s="10" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="182" spans="1:9">
@@ -18481,7 +18512,7 @@
         <v>5009519</v>
       </c>
       <c r="B182" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C182">
         <v>6280</v>
@@ -18496,10 +18527,10 @@
         <v>999</v>
       </c>
       <c r="H182" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I182" s="10" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="183" spans="1:9">
@@ -18507,7 +18538,7 @@
         <v>1001399104</v>
       </c>
       <c r="B183" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C183">
         <v>1100</v>
@@ -18522,10 +18553,10 @@
         <v>623</v>
       </c>
       <c r="H183" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I183" s="10" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="184" spans="1:9">
@@ -18533,7 +18564,7 @@
         <v>1000215789</v>
       </c>
       <c r="B184" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C184">
         <v>1440</v>
@@ -18548,10 +18579,10 @@
         <v>999</v>
       </c>
       <c r="H184" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I184" s="10" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="185" spans="1:9">
@@ -18574,7 +18605,7 @@
         <v>999</v>
       </c>
       <c r="H185" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I185" s="10" t="s">
         <v>34</v>
@@ -18585,7 +18616,7 @@
         <v>5042489</v>
       </c>
       <c r="B186" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C186">
         <v>4980</v>
@@ -18600,10 +18631,10 @@
         <v>999</v>
       </c>
       <c r="H186" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I186" s="10" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="187" spans="1:9">
@@ -18611,7 +18642,7 @@
         <v>1002214154</v>
       </c>
       <c r="B187" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C187">
         <v>4380</v>
@@ -18626,10 +18657,10 @@
         <v>92</v>
       </c>
       <c r="H187" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I187" s="10" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="188" spans="1:9">
@@ -18637,7 +18668,7 @@
         <v>1002130774</v>
       </c>
       <c r="B188" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C188">
         <v>1700</v>
@@ -18652,10 +18683,10 @@
         <v>100</v>
       </c>
       <c r="H188" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I188" s="10" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="189" spans="1:9">
@@ -18663,7 +18694,7 @@
         <v>1000757615</v>
       </c>
       <c r="B189" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C189">
         <v>3820</v>
@@ -18678,10 +18709,10 @@
         <v>999</v>
       </c>
       <c r="H189" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I189" s="10" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="190" spans="1:9">
@@ -18689,7 +18720,7 @@
         <v>1002049283</v>
       </c>
       <c r="B190" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C190">
         <v>5980</v>
@@ -18704,10 +18735,10 @@
         <v>220</v>
       </c>
       <c r="H190" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I190" s="10" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="191" spans="1:9">
@@ -18715,7 +18746,7 @@
         <v>1001100806</v>
       </c>
       <c r="B191" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C191">
         <v>4490</v>
@@ -18730,10 +18761,10 @@
         <v>418</v>
       </c>
       <c r="H191" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I191" s="10" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="192" spans="1:9">
@@ -18741,7 +18772,7 @@
         <v>1001397633</v>
       </c>
       <c r="B192" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C192">
         <v>1360</v>
@@ -18756,10 +18787,10 @@
         <v>999</v>
       </c>
       <c r="H192" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I192" s="10" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="193" spans="1:9">
@@ -18767,7 +18798,7 @@
         <v>1000033205</v>
       </c>
       <c r="B193" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C193">
         <v>3280</v>
@@ -18782,10 +18813,10 @@
         <v>999</v>
       </c>
       <c r="H193" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I193" s="10" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="194" spans="1:9">
@@ -18793,7 +18824,7 @@
         <v>1002014584</v>
       </c>
       <c r="B194" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C194">
         <v>4950</v>
@@ -18808,10 +18839,10 @@
         <v>999</v>
       </c>
       <c r="H194" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I194" s="10" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="195" spans="1:9">
@@ -18819,7 +18850,7 @@
         <v>1001985656</v>
       </c>
       <c r="B195" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C195">
         <v>1980</v>
@@ -18834,10 +18865,10 @@
         <v>143</v>
       </c>
       <c r="H195" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I195" s="10" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="196" spans="1:9">
@@ -18845,7 +18876,7 @@
         <v>1002129012</v>
       </c>
       <c r="B196" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C196">
         <v>1440</v>
@@ -18860,10 +18891,10 @@
         <v>389</v>
       </c>
       <c r="H196" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I196" s="10" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="197" spans="1:9">
@@ -18871,7 +18902,7 @@
         <v>1001421090</v>
       </c>
       <c r="B197" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C197">
         <v>4000</v>
@@ -18883,10 +18914,10 @@
         <v>14</v>
       </c>
       <c r="H197" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I197" s="10" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="198" spans="1:9">
@@ -18894,7 +18925,7 @@
         <v>1001170989</v>
       </c>
       <c r="B198" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C198">
         <v>2720</v>
@@ -18909,10 +18940,10 @@
         <v>494</v>
       </c>
       <c r="H198" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I198" s="10" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="199" spans="1:9">
@@ -18920,7 +18951,7 @@
         <v>5134076</v>
       </c>
       <c r="B199" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C199">
         <v>4540</v>
@@ -18935,10 +18966,10 @@
         <v>999</v>
       </c>
       <c r="H199" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I199" s="10" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="200" spans="1:9">
@@ -18946,7 +18977,7 @@
         <v>1000640848</v>
       </c>
       <c r="B200" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C200">
         <v>2720</v>
@@ -18961,10 +18992,10 @@
         <v>953</v>
       </c>
       <c r="H200" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I200" s="10" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="201" spans="1:9">
@@ -18972,7 +19003,7 @@
         <v>1001318650</v>
       </c>
       <c r="B201" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C201">
         <v>28670</v>
@@ -18987,10 +19018,10 @@
         <v>22</v>
       </c>
       <c r="H201" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I201" s="10" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="202" spans="1:9">
@@ -18998,7 +19029,7 @@
         <v>1001937064</v>
       </c>
       <c r="B202" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C202">
         <v>2480</v>
@@ -19013,10 +19044,10 @@
         <v>534</v>
       </c>
       <c r="H202" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I202" s="10" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="203" spans="1:9">
@@ -19024,7 +19055,7 @@
         <v>1000612631</v>
       </c>
       <c r="B203" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C203">
         <v>6490</v>
@@ -19039,10 +19070,10 @@
         <v>168</v>
       </c>
       <c r="H203" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I203" s="10" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="204" spans="1:9">
@@ -19050,7 +19081,7 @@
         <v>1000891279</v>
       </c>
       <c r="B204" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C204">
         <v>3900</v>
@@ -19065,10 +19096,10 @@
         <v>999</v>
       </c>
       <c r="H204" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I204" s="10" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="205" spans="1:9">
@@ -19076,7 +19107,7 @@
         <v>1002380802</v>
       </c>
       <c r="B205" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C205">
         <v>2800</v>
@@ -19091,10 +19122,10 @@
         <v>240</v>
       </c>
       <c r="H205" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I205" s="10" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="206" spans="1:9">
@@ -19102,7 +19133,7 @@
         <v>1000584460</v>
       </c>
       <c r="B206" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C206">
         <v>5584</v>
@@ -19117,10 +19148,10 @@
         <v>347</v>
       </c>
       <c r="H206" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I206" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="207" spans="1:9">
@@ -19128,7 +19159,7 @@
         <v>1000179453</v>
       </c>
       <c r="B207" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C207">
         <v>13900</v>
@@ -19143,10 +19174,10 @@
         <v>999</v>
       </c>
       <c r="H207" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I207" s="10" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="208" spans="1:9">
@@ -19154,7 +19185,7 @@
         <v>1000570013</v>
       </c>
       <c r="B208" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C208">
         <v>3500</v>
@@ -19169,10 +19200,10 @@
         <v>404</v>
       </c>
       <c r="H208" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I208" s="10" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="209" spans="1:9">
@@ -19180,7 +19211,7 @@
         <v>1002247128</v>
       </c>
       <c r="B209" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="C209">
         <v>1380</v>
@@ -19195,10 +19226,10 @@
         <v>292</v>
       </c>
       <c r="H209" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I209" s="10" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="210" spans="1:9">
@@ -19206,7 +19237,7 @@
         <v>1002129077</v>
       </c>
       <c r="B210" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C210">
         <v>3450</v>
@@ -19221,10 +19252,10 @@
         <v>194</v>
       </c>
       <c r="H210" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I210" s="10" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="211" spans="1:9">
@@ -19232,7 +19263,7 @@
         <v>1002129075</v>
       </c>
       <c r="B211" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C211">
         <v>2340</v>
@@ -19247,10 +19278,10 @@
         <v>127</v>
       </c>
       <c r="H211" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I211" s="10" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="212" spans="1:9">
@@ -19258,7 +19289,7 @@
         <v>1001212964</v>
       </c>
       <c r="B212" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C212">
         <v>3780</v>
@@ -19273,10 +19304,10 @@
         <v>999</v>
       </c>
       <c r="H212" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I212" s="10" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="213" spans="1:9">
@@ -19284,7 +19315,7 @@
         <v>5073031</v>
       </c>
       <c r="B213" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C213">
         <v>3500</v>
@@ -19299,10 +19330,10 @@
         <v>999</v>
       </c>
       <c r="H213" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I213" s="10" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="214" spans="1:9">
@@ -19310,7 +19341,7 @@
         <v>1002129073</v>
       </c>
       <c r="B214" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C214">
         <v>1440</v>
@@ -19325,10 +19356,10 @@
         <v>148</v>
       </c>
       <c r="H214" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I214" s="10" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="215" spans="1:9">
@@ -19336,7 +19367,7 @@
         <v>1002129047</v>
       </c>
       <c r="B215" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C215">
         <v>2250</v>
@@ -19351,10 +19382,10 @@
         <v>60</v>
       </c>
       <c r="H215" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I215" s="10" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="216" spans="1:9">
@@ -19362,7 +19393,7 @@
         <v>1001098485</v>
       </c>
       <c r="B216" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C216">
         <v>3500</v>
@@ -19377,10 +19408,10 @@
         <v>401</v>
       </c>
       <c r="H216" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I216" s="10" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="217" spans="1:9">
@@ -19388,7 +19419,7 @@
         <v>1000205257</v>
       </c>
       <c r="B217" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C217">
         <v>2660</v>
@@ -19403,10 +19434,10 @@
         <v>9999</v>
       </c>
       <c r="H217" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I217" s="10" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="218" spans="1:9">
@@ -19414,7 +19445,7 @@
         <v>1002242483</v>
       </c>
       <c r="B218" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C218">
         <v>2400</v>
@@ -19429,10 +19460,10 @@
         <v>504</v>
       </c>
       <c r="H218" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I218" s="10" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="219" spans="1:9">
@@ -19440,7 +19471,7 @@
         <v>5155641</v>
       </c>
       <c r="B219" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C219">
         <v>5200</v>
@@ -19455,10 +19486,10 @@
         <v>999</v>
       </c>
       <c r="H219" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I219" s="10" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="220" spans="1:9">
@@ -19466,7 +19497,7 @@
         <v>1002326317</v>
       </c>
       <c r="B220" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="C220">
         <v>2720</v>
@@ -19481,10 +19512,10 @@
         <v>346</v>
       </c>
       <c r="H220" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I220" s="10" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="221" spans="1:9">
@@ -19492,7 +19523,7 @@
         <v>1000391076</v>
       </c>
       <c r="B221" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C221">
         <v>7980</v>
@@ -19507,10 +19538,10 @@
         <v>654</v>
       </c>
       <c r="H221" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I221" s="10" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="222" spans="1:9">
@@ -19518,7 +19549,7 @@
         <v>1001391095</v>
       </c>
       <c r="B222" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C222">
         <v>1600</v>
@@ -19533,10 +19564,10 @@
         <v>999</v>
       </c>
       <c r="H222" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I222" s="10" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="223" spans="1:9">
@@ -19544,7 +19575,7 @@
         <v>1002064464</v>
       </c>
       <c r="B223" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C223">
         <v>1440</v>
@@ -19559,10 +19590,10 @@
         <v>894</v>
       </c>
       <c r="H223" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I223" s="10" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="224" spans="1:9">
@@ -19570,7 +19601,7 @@
         <v>1000198131</v>
       </c>
       <c r="B224" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C224">
         <v>2580</v>
@@ -19585,10 +19616,10 @@
         <v>9999</v>
       </c>
       <c r="H224" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I224" s="10" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="225" spans="1:9">
@@ -19596,7 +19627,7 @@
         <v>5061325</v>
       </c>
       <c r="B225" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C225">
         <v>1260</v>
@@ -19611,10 +19642,10 @@
         <v>9999</v>
       </c>
       <c r="H225" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I225" s="10" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="226" spans="1:9">
@@ -19622,7 +19653,7 @@
         <v>1002129079</v>
       </c>
       <c r="B226" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="C226">
         <v>1440</v>
@@ -19637,10 +19668,10 @@
         <v>64</v>
       </c>
       <c r="H226" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I226" s="10" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="227" spans="1:9">
@@ -19648,7 +19679,7 @@
         <v>1001228129</v>
       </c>
       <c r="B227" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C227">
         <v>9900</v>
@@ -19663,10 +19694,10 @@
         <v>232</v>
       </c>
       <c r="H227" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I227" s="10" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="228" spans="1:9">
@@ -19674,7 +19705,7 @@
         <v>1002324004</v>
       </c>
       <c r="B228" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C228">
         <v>4490</v>
@@ -19689,10 +19720,10 @@
         <v>35</v>
       </c>
       <c r="H228" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I228" s="10" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="229" spans="1:9">
@@ -19700,7 +19731,7 @@
         <v>1000570015</v>
       </c>
       <c r="B229" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C229">
         <v>3500</v>
@@ -19715,10 +19746,10 @@
         <v>330</v>
       </c>
       <c r="H229" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I229" s="10" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="230" spans="1:9">
@@ -19726,7 +19757,7 @@
         <v>1000584474</v>
       </c>
       <c r="B230" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C230">
         <v>5584</v>
@@ -19741,10 +19772,10 @@
         <v>289</v>
       </c>
       <c r="H230" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I230" s="10" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="231" spans="1:9">
@@ -19752,7 +19783,7 @@
         <v>1000570032</v>
       </c>
       <c r="B231" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C231">
         <v>3500</v>
@@ -19767,10 +19798,10 @@
         <v>752</v>
       </c>
       <c r="H231" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I231" s="10" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="232" spans="1:9">
@@ -19778,7 +19809,7 @@
         <v>1002129009</v>
       </c>
       <c r="B232" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="C232">
         <v>1440</v>
@@ -19793,10 +19824,10 @@
         <v>170</v>
       </c>
       <c r="H232" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I232" s="10" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="233" spans="1:9">
@@ -19804,7 +19835,7 @@
         <v>1001384411</v>
       </c>
       <c r="B233" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C233">
         <v>1600</v>
@@ -19819,10 +19850,10 @@
         <v>999</v>
       </c>
       <c r="H233" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I233" s="10" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="234" spans="1:9">
@@ -19830,7 +19861,7 @@
         <v>5161381</v>
       </c>
       <c r="B234" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="C234">
         <v>6000</v>
@@ -19845,10 +19876,10 @@
         <v>999</v>
       </c>
       <c r="H234" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I234" s="10" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="235" spans="1:9">
@@ -19856,7 +19887,7 @@
         <v>1001406961</v>
       </c>
       <c r="B235" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="C235">
         <v>1280</v>
@@ -19871,10 +19902,10 @@
         <v>205</v>
       </c>
       <c r="H235" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I235" s="10" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="236" spans="1:9">
@@ -19882,7 +19913,7 @@
         <v>1000952281</v>
       </c>
       <c r="B236" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C236">
         <v>1260</v>
@@ -19897,10 +19928,10 @@
         <v>999</v>
       </c>
       <c r="H236" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I236" s="10" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="237" spans="1:9">
@@ -19908,7 +19939,7 @@
         <v>1000927098</v>
       </c>
       <c r="B237" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="C237">
         <v>4980</v>
@@ -19923,10 +19954,10 @@
         <v>392</v>
       </c>
       <c r="H237" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I237" s="10" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="238" spans="1:9">
@@ -19934,7 +19965,7 @@
         <v>1001388382</v>
       </c>
       <c r="B238" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="C238">
         <v>3500</v>
@@ -19949,10 +19980,10 @@
         <v>142</v>
       </c>
       <c r="H238" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I238" s="10" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="239" spans="1:9">
@@ -19960,7 +19991,7 @@
         <v>1002207194</v>
       </c>
       <c r="B239" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C239">
         <v>10800</v>
@@ -19975,10 +20006,10 @@
         <v>32</v>
       </c>
       <c r="H239" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I239" s="10" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="240" spans="1:9">
@@ -19986,7 +20017,7 @@
         <v>1002129049</v>
       </c>
       <c r="B240" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="C240">
         <v>1440</v>
@@ -20001,10 +20032,10 @@
         <v>229</v>
       </c>
       <c r="H240" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I240" s="10" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="241" spans="1:9">
@@ -20012,7 +20043,7 @@
         <v>1002129039</v>
       </c>
       <c r="B241" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="C241">
         <v>1440</v>
@@ -20027,10 +20058,10 @@
         <v>511</v>
       </c>
       <c r="H241" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I241" s="10" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="242" spans="1:9">
@@ -20038,7 +20069,7 @@
         <v>1001397641</v>
       </c>
       <c r="B242" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="C242">
         <v>1360</v>
@@ -20053,10 +20084,10 @@
         <v>169</v>
       </c>
       <c r="H242" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I242" s="10" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="243" spans="1:9">
@@ -20064,7 +20095,7 @@
         <v>1002185329</v>
       </c>
       <c r="B243" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C243">
         <v>5580</v>
@@ -20079,10 +20110,10 @@
         <v>231</v>
       </c>
       <c r="H243" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I243" s="10" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="244" spans="1:9">
@@ -20090,7 +20121,7 @@
         <v>1001434820</v>
       </c>
       <c r="B244" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="C244">
         <v>2660</v>
@@ -20105,10 +20136,10 @@
         <v>999</v>
       </c>
       <c r="H244" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I244" s="10" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="245" spans="1:9">
@@ -20116,7 +20147,7 @@
         <v>1002296291</v>
       </c>
       <c r="B245" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="C245">
         <v>1440</v>
@@ -20131,10 +20162,10 @@
         <v>251</v>
       </c>
       <c r="H245" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I245" s="10" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="246" spans="1:9">
@@ -20142,7 +20173,7 @@
         <v>1000365877</v>
       </c>
       <c r="B246" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C246">
         <v>3840</v>
@@ -20157,10 +20188,10 @@
         <v>999</v>
       </c>
       <c r="H246" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I246" s="10" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="247" spans="1:9">
@@ -20168,7 +20199,7 @@
         <v>5073060</v>
       </c>
       <c r="B247" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="C247">
         <v>4680</v>
@@ -20183,10 +20214,10 @@
         <v>999</v>
       </c>
       <c r="H247" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I247" s="10" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="248" spans="1:9">
@@ -20194,7 +20225,7 @@
         <v>1002327637</v>
       </c>
       <c r="B248" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="C248">
         <v>3500</v>
@@ -20209,10 +20240,10 @@
         <v>59</v>
       </c>
       <c r="H248" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I248" s="10" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="249" spans="1:9">
@@ -20220,7 +20251,7 @@
         <v>1001065190</v>
       </c>
       <c r="B249" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C249">
         <v>2400</v>
@@ -20235,10 +20266,10 @@
         <v>336</v>
       </c>
       <c r="H249" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I249" s="10" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="250" spans="1:9">
@@ -20246,7 +20277,7 @@
         <v>5136204</v>
       </c>
       <c r="B250" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C250">
         <v>1680</v>
@@ -20261,10 +20292,10 @@
         <v>999</v>
       </c>
       <c r="H250" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I250" s="10" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="251" spans="1:9">
@@ -20272,7 +20303,7 @@
         <v>5077459</v>
       </c>
       <c r="B251" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="C251">
         <v>2880</v>
@@ -20287,10 +20318,10 @@
         <v>999</v>
       </c>
       <c r="H251" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I251" s="10" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="252" spans="1:9">
@@ -20298,7 +20329,7 @@
         <v>1000858865</v>
       </c>
       <c r="B252" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="C252">
         <v>4480</v>
@@ -20313,10 +20344,10 @@
         <v>234</v>
       </c>
       <c r="H252" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I252" s="10" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="253" spans="1:9">
@@ -20324,7 +20355,7 @@
         <v>1002492970</v>
       </c>
       <c r="B253" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C253">
         <v>4180</v>
@@ -20339,10 +20370,10 @@
         <v>23</v>
       </c>
       <c r="H253" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I253" s="10" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="254" spans="1:9">
@@ -20350,7 +20381,7 @@
         <v>1002326631</v>
       </c>
       <c r="B254" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="C254">
         <v>2580</v>
@@ -20365,10 +20396,10 @@
         <v>123</v>
       </c>
       <c r="H254" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I254" s="10" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="255" spans="1:9">
@@ -20376,7 +20407,7 @@
         <v>1002134600</v>
       </c>
       <c r="B255" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="C255">
         <v>4980</v>
@@ -20391,10 +20422,10 @@
         <v>87</v>
       </c>
       <c r="H255" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I255" s="10" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="256" spans="1:9">
@@ -20402,7 +20433,7 @@
         <v>1001485461</v>
       </c>
       <c r="B256" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C256">
         <v>2180</v>
@@ -20417,10 +20448,10 @@
         <v>273</v>
       </c>
       <c r="H256" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I256" s="10" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="257" spans="1:9">
@@ -20428,7 +20459,7 @@
         <v>1002058181</v>
       </c>
       <c r="B257" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C257">
         <v>5000</v>
@@ -20443,10 +20474,10 @@
         <v>30</v>
       </c>
       <c r="H257" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I257" s="10" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="258" spans="1:9">
@@ -20454,7 +20485,7 @@
         <v>1002313083</v>
       </c>
       <c r="B258" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C258">
         <v>4980</v>
@@ -20469,10 +20500,10 @@
         <v>28</v>
       </c>
       <c r="H258" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I258" s="10" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="259" spans="1:9">
@@ -20480,7 +20511,7 @@
         <v>5118755</v>
       </c>
       <c r="B259" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="C259">
         <v>4500</v>
@@ -20495,10 +20526,10 @@
         <v>999</v>
       </c>
       <c r="H259" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I259" s="10" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="260" spans="1:9">
@@ -20506,7 +20537,7 @@
         <v>1002015596</v>
       </c>
       <c r="B260" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="C260">
         <v>1440</v>
@@ -20521,10 +20552,10 @@
         <v>205</v>
       </c>
       <c r="H260" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I260" s="10" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="261" spans="1:9">
@@ -20532,7 +20563,7 @@
         <v>1000472716</v>
       </c>
       <c r="B261" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="C261">
         <v>3080</v>
@@ -20547,10 +20578,10 @@
         <v>999</v>
       </c>
       <c r="H261" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I261" s="10" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="262" spans="1:9">
@@ -20558,7 +20589,7 @@
         <v>5155683</v>
       </c>
       <c r="B262" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="C262">
         <v>7300</v>
@@ -20573,10 +20604,10 @@
         <v>999</v>
       </c>
       <c r="H262" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I262" s="10" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="263" spans="1:9">
@@ -20584,7 +20615,7 @@
         <v>5114891</v>
       </c>
       <c r="B263" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="C263">
         <v>9980</v>
@@ -20599,10 +20630,10 @@
         <v>999</v>
       </c>
       <c r="H263" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I263" s="10" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="264" spans="1:9">
@@ -20610,7 +20641,7 @@
         <v>1000942888</v>
       </c>
       <c r="B264" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C264">
         <v>1490</v>
@@ -20625,10 +20656,10 @@
         <v>999</v>
       </c>
       <c r="H264" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I264" s="10" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="265" spans="1:9">
@@ -20636,7 +20667,7 @@
         <v>1001092106</v>
       </c>
       <c r="B265" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="C265">
         <v>12700</v>
@@ -20651,10 +20682,10 @@
         <v>731</v>
       </c>
       <c r="H265" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I265" s="10" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="266" spans="1:9">
@@ -20662,7 +20693,7 @@
         <v>1001803388</v>
       </c>
       <c r="B266" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="C266">
         <v>5400</v>
@@ -20677,10 +20708,10 @@
         <v>97</v>
       </c>
       <c r="H266" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I266" s="10" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="267" spans="1:9">
@@ -20688,7 +20719,7 @@
         <v>1000472613</v>
       </c>
       <c r="B267" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="C267">
         <v>2680</v>
@@ -20703,10 +20734,10 @@
         <v>690</v>
       </c>
       <c r="H267" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I267" s="10" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="268" spans="1:9">
@@ -20714,7 +20745,7 @@
         <v>1002369661</v>
       </c>
       <c r="B268" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="C268">
         <v>2130</v>
@@ -20729,10 +20760,10 @@
         <v>185</v>
       </c>
       <c r="H268" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I268" s="10" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="269" spans="1:9">
@@ -20740,7 +20771,7 @@
         <v>1000605483</v>
       </c>
       <c r="B269" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="C269">
         <v>1980</v>
@@ -20755,10 +20786,10 @@
         <v>999</v>
       </c>
       <c r="H269" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I269" s="10" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="270" spans="1:9">
@@ -20766,7 +20797,7 @@
         <v>1002303054</v>
       </c>
       <c r="B270" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="C270">
         <v>6300</v>
@@ -20781,10 +20812,10 @@
         <v>77</v>
       </c>
       <c r="H270" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I270" s="10" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="271" spans="1:9">
@@ -20792,7 +20823,7 @@
         <v>1001397542</v>
       </c>
       <c r="B271" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="C271">
         <v>3980</v>
@@ -20807,10 +20838,10 @@
         <v>57</v>
       </c>
       <c r="H271" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I271" s="10" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="272" spans="1:9">
@@ -20818,7 +20849,7 @@
         <v>1000960167</v>
       </c>
       <c r="B272" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="C272">
         <v>1490</v>
@@ -20833,10 +20864,10 @@
         <v>348</v>
       </c>
       <c r="H272" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I272" s="10" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="273" spans="1:9">
@@ -20844,7 +20875,7 @@
         <v>1002099803</v>
       </c>
       <c r="B273" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C273">
         <v>1990</v>
@@ -20859,10 +20890,10 @@
         <v>43</v>
       </c>
       <c r="H273" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I273" s="10" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="274" spans="1:9">
@@ -20870,7 +20901,7 @@
         <v>1002104217</v>
       </c>
       <c r="B274" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="C274">
         <v>1280</v>
@@ -20885,10 +20916,10 @@
         <v>62</v>
       </c>
       <c r="H274" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I274" s="10" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="275" spans="1:9">
@@ -20896,7 +20927,7 @@
         <v>1001942437</v>
       </c>
       <c r="B275" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="C275">
         <v>2500</v>
@@ -20911,10 +20942,10 @@
         <v>652</v>
       </c>
       <c r="H275" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I275" s="10" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
     </row>
     <row r="276" spans="1:9">
@@ -20922,7 +20953,7 @@
         <v>5038276</v>
       </c>
       <c r="B276" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="C276">
         <v>13500</v>
@@ -20937,10 +20968,10 @@
         <v>9999</v>
       </c>
       <c r="H276" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I276" s="10" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
     </row>
     <row r="277" spans="1:9">
@@ -20948,7 +20979,7 @@
         <v>5043922</v>
       </c>
       <c r="B277" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="C277">
         <v>13500</v>
@@ -20963,10 +20994,10 @@
         <v>999</v>
       </c>
       <c r="H277" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I277" s="10" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="278" spans="1:9">
@@ -20974,7 +21005,7 @@
         <v>1000639928</v>
       </c>
       <c r="B278" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="C278">
         <v>13500</v>
@@ -20989,10 +21020,10 @@
         <v>654</v>
       </c>
       <c r="H278" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I278" s="10" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="279" spans="1:9">
@@ -21000,7 +21031,7 @@
         <v>5061562</v>
       </c>
       <c r="B279" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="C279">
         <v>3690</v>
@@ -21015,10 +21046,10 @@
         <v>9999</v>
       </c>
       <c r="H279" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I279" s="10" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
     </row>
     <row r="280" spans="1:9">
@@ -21026,7 +21057,7 @@
         <v>5050887</v>
       </c>
       <c r="B280" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="C280">
         <v>3980</v>
@@ -21041,10 +21072,10 @@
         <v>999</v>
       </c>
       <c r="H280" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I280" s="10" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
     </row>
     <row r="281" spans="1:9">
@@ -21052,7 +21083,7 @@
         <v>5066715</v>
       </c>
       <c r="B281" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C281">
         <v>3600</v>
@@ -21067,10 +21098,10 @@
         <v>999</v>
       </c>
       <c r="H281" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I281" s="10" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="282" spans="1:9">
@@ -21078,7 +21109,7 @@
         <v>1000330130</v>
       </c>
       <c r="B282" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="C282">
         <v>8400</v>
@@ -21093,10 +21124,10 @@
         <v>999</v>
       </c>
       <c r="H282" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I282" s="10" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="283" spans="1:9">
@@ -21104,7 +21135,7 @@
         <v>1002478152</v>
       </c>
       <c r="B283" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="C283">
         <v>8550</v>
@@ -21119,10 +21150,10 @@
         <v>24</v>
       </c>
       <c r="H283" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I283" s="10" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
     </row>
     <row r="284" spans="1:9">
@@ -21130,7 +21161,7 @@
         <v>5034131</v>
       </c>
       <c r="B284" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="C284">
         <v>3980</v>
@@ -21145,10 +21176,10 @@
         <v>999</v>
       </c>
       <c r="H284" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I284" s="10" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
     </row>
     <row r="285" spans="1:9">
@@ -21156,7 +21187,7 @@
         <v>1000567683</v>
       </c>
       <c r="B285" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="C285">
         <v>5780</v>
@@ -21171,10 +21202,10 @@
         <v>458</v>
       </c>
       <c r="H285" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I285" s="10" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
     </row>
     <row r="286" spans="1:9">
@@ -21182,7 +21213,7 @@
         <v>1000339499</v>
       </c>
       <c r="B286" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="C286">
         <v>10800</v>
@@ -21197,10 +21228,10 @@
         <v>865</v>
       </c>
       <c r="H286" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I286" s="10" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
     </row>
     <row r="287" spans="1:9">
@@ -21208,7 +21239,7 @@
         <v>5055895</v>
       </c>
       <c r="B287" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C287">
         <v>5280</v>
@@ -21223,10 +21254,10 @@
         <v>999</v>
       </c>
       <c r="H287" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I287" s="10" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="288" spans="1:9">
@@ -21234,7 +21265,7 @@
         <v>5048316</v>
       </c>
       <c r="B288" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="C288">
         <v>3980</v>
@@ -21249,10 +21280,10 @@
         <v>999</v>
       </c>
       <c r="H288" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I288" s="10" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="289" spans="1:9">
@@ -21260,7 +21291,7 @@
         <v>5054690</v>
       </c>
       <c r="B289" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="C289">
         <v>4950</v>
@@ -21275,10 +21306,10 @@
         <v>999</v>
       </c>
       <c r="H289" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I289" s="10" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="290" spans="1:9">
@@ -21286,7 +21317,7 @@
         <v>1001018961</v>
       </c>
       <c r="B290" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="C290">
         <v>19350</v>
@@ -21301,10 +21332,10 @@
         <v>327</v>
       </c>
       <c r="H290" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I290" s="10" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
     </row>
     <row r="291" spans="1:9">
@@ -21312,7 +21343,7 @@
         <v>1000362713</v>
       </c>
       <c r="B291" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="C291">
         <v>9790</v>
@@ -21327,10 +21358,10 @@
         <v>557</v>
       </c>
       <c r="H291" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I291" s="10" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
     </row>
     <row r="292" spans="1:9">
@@ -21338,7 +21369,7 @@
         <v>1002422233</v>
       </c>
       <c r="B292" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="C292">
         <v>4480</v>
@@ -21353,10 +21384,10 @@
         <v>287</v>
       </c>
       <c r="H292" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I292" s="10" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="293" spans="1:9">
@@ -21364,7 +21395,7 @@
         <v>1000490132</v>
       </c>
       <c r="B293" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="C293">
         <v>3500</v>
@@ -21379,10 +21410,10 @@
         <v>999</v>
       </c>
       <c r="H293" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I293" s="10" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="294" spans="1:9">
@@ -21390,7 +21421,7 @@
         <v>1001900401</v>
       </c>
       <c r="B294" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="C294">
         <v>13980</v>
@@ -21405,10 +21436,10 @@
         <v>999</v>
       </c>
       <c r="H294" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I294" s="10" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="295" spans="1:9">
@@ -21416,7 +21447,7 @@
         <v>1002492960</v>
       </c>
       <c r="B295" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="C295">
         <v>6500</v>
@@ -21431,10 +21462,10 @@
         <v>13</v>
       </c>
       <c r="H295" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I295" s="10" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
     </row>
     <row r="296" spans="1:9">
@@ -21442,7 +21473,7 @@
         <v>5054901</v>
       </c>
       <c r="B296" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="C296">
         <v>4950</v>
@@ -21457,10 +21488,10 @@
         <v>999</v>
       </c>
       <c r="H296" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I296" s="10" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="297" spans="1:9">
@@ -21468,7 +21499,7 @@
         <v>1000958551</v>
       </c>
       <c r="B297" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="C297">
         <v>5280</v>
@@ -21483,10 +21514,10 @@
         <v>999</v>
       </c>
       <c r="H297" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I297" s="10" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="298" spans="1:9">
@@ -21494,7 +21525,7 @@
         <v>1000400060</v>
       </c>
       <c r="B298" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="C298">
         <v>12000</v>
@@ -21509,10 +21540,10 @@
         <v>775</v>
       </c>
       <c r="H298" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I298" s="10" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="299" spans="1:9">
@@ -21520,7 +21551,7 @@
         <v>5054167</v>
       </c>
       <c r="B299" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="C299">
         <v>5980</v>
@@ -21535,10 +21566,10 @@
         <v>999</v>
       </c>
       <c r="H299" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I299" s="10" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="300" spans="1:9">
@@ -21546,7 +21577,7 @@
         <v>1001049824</v>
       </c>
       <c r="B300" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="C300">
         <v>5980</v>
@@ -21561,10 +21592,10 @@
         <v>989</v>
       </c>
       <c r="H300" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I300" s="10" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="301" spans="1:9">
@@ -21572,7 +21603,7 @@
         <v>5104102</v>
       </c>
       <c r="B301" t="s">
-        <v>667</v>
+        <v>77</v>
       </c>
       <c r="C301">
         <v>2990</v>
@@ -21587,10 +21618,10 @@
         <v>999</v>
       </c>
       <c r="H301" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I301" s="10" t="s">
-        <v>668</v>
+        <v>78</v>
       </c>
     </row>
     <row r="302" spans="1:9">
@@ -21613,7 +21644,7 @@
         <v>231</v>
       </c>
       <c r="H302" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I302" s="10" t="s">
         <v>670</v>
@@ -21639,7 +21670,7 @@
         <v>59</v>
       </c>
       <c r="H303" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I303" s="10" t="s">
         <v>672</v>
@@ -21650,7 +21681,7 @@
         <v>5061291</v>
       </c>
       <c r="B304" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C304">
         <v>4780</v>
@@ -21665,10 +21696,10 @@
         <v>999</v>
       </c>
       <c r="H304" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I304" s="10" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="305" spans="1:9">
@@ -21691,7 +21722,7 @@
         <v>999</v>
       </c>
       <c r="H305" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I305" s="10" t="s">
         <v>674</v>
@@ -21717,7 +21748,7 @@
         <v>240</v>
       </c>
       <c r="H306" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I306" s="10" t="s">
         <v>676</v>
@@ -21743,7 +21774,7 @@
         <v>180</v>
       </c>
       <c r="H307" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I307" s="10" t="s">
         <v>678</v>
@@ -21769,7 +21800,7 @@
         <v>277</v>
       </c>
       <c r="H308" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I308" s="10" t="s">
         <v>680</v>
@@ -21795,7 +21826,7 @@
         <v>999</v>
       </c>
       <c r="H309" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I309" s="10" t="s">
         <v>682</v>
@@ -21821,7 +21852,7 @@
         <v>41</v>
       </c>
       <c r="H310" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I310" s="10" t="s">
         <v>684</v>
@@ -21847,7 +21878,7 @@
         <v>999</v>
       </c>
       <c r="H311" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I311" s="10" t="s">
         <v>686</v>
@@ -21873,7 +21904,7 @@
         <v>247</v>
       </c>
       <c r="H312" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I312" s="10" t="s">
         <v>688</v>
@@ -21899,7 +21930,7 @@
         <v>173</v>
       </c>
       <c r="H313" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I313" s="10" t="s">
         <v>690</v>
@@ -21925,7 +21956,7 @@
         <v>9999</v>
       </c>
       <c r="H314" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I314" s="10" t="s">
         <v>692</v>
@@ -21936,7 +21967,7 @@
         <v>1000175874</v>
       </c>
       <c r="B315" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C315">
         <v>5600</v>
@@ -21951,10 +21982,10 @@
         <v>999</v>
       </c>
       <c r="H315" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I315" s="10" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="316" spans="1:9">
@@ -21977,7 +22008,7 @@
         <v>999</v>
       </c>
       <c r="H316" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I316" s="10" t="s">
         <v>694</v>
@@ -22003,7 +22034,7 @@
         <v>67</v>
       </c>
       <c r="H317" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I317" s="10" t="s">
         <v>696</v>
@@ -22029,7 +22060,7 @@
         <v>999</v>
       </c>
       <c r="H318" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I318" s="10" t="s">
         <v>698</v>
@@ -22055,7 +22086,7 @@
         <v>9999</v>
       </c>
       <c r="H319" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I319" s="10" t="s">
         <v>700</v>
@@ -22081,7 +22112,7 @@
         <v>80</v>
       </c>
       <c r="H320" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I320" s="10" t="s">
         <v>702</v>
@@ -22107,7 +22138,7 @@
         <v>607</v>
       </c>
       <c r="H321" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I321" s="10" t="s">
         <v>704</v>
@@ -22133,7 +22164,7 @@
         <v>999</v>
       </c>
       <c r="H322" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I322" s="10" t="s">
         <v>706</v>
@@ -22159,7 +22190,7 @@
         <v>999</v>
       </c>
       <c r="H323" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I323" s="10" t="s">
         <v>76</v>
@@ -22170,7 +22201,7 @@
         <v>1000875718</v>
       </c>
       <c r="B324" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C324">
         <v>4320</v>
@@ -22185,10 +22216,10 @@
         <v>745</v>
       </c>
       <c r="H324" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I324" s="10" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="325" spans="1:9">
@@ -22211,7 +22242,7 @@
         <v>480</v>
       </c>
       <c r="H325" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I325" s="10" t="s">
         <v>708</v>
@@ -22237,7 +22268,7 @@
         <v>130</v>
       </c>
       <c r="H326" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I326" s="10" t="s">
         <v>710</v>
@@ -22263,7 +22294,7 @@
         <v>999</v>
       </c>
       <c r="H327" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I327" s="10" t="s">
         <v>712</v>
@@ -22274,7 +22305,7 @@
         <v>5070774</v>
       </c>
       <c r="B328" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C328">
         <v>3840</v>
@@ -22289,10 +22320,10 @@
         <v>999</v>
       </c>
       <c r="H328" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I328" s="10" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="329" spans="1:9">
@@ -22315,7 +22346,7 @@
         <v>202</v>
       </c>
       <c r="H329" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I329" s="10" t="s">
         <v>714</v>
@@ -22341,7 +22372,7 @@
         <v>999</v>
       </c>
       <c r="H330" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I330" s="10" t="s">
         <v>716</v>
@@ -22367,7 +22398,7 @@
         <v>76</v>
       </c>
       <c r="H331" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I331" s="10" t="s">
         <v>718</v>
@@ -22393,7 +22424,7 @@
         <v>31</v>
       </c>
       <c r="H332" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I332" s="10" t="s">
         <v>720</v>
@@ -22419,7 +22450,7 @@
         <v>618</v>
       </c>
       <c r="H333" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I333" s="10" t="s">
         <v>722</v>
@@ -22445,7 +22476,7 @@
         <v>121</v>
       </c>
       <c r="H334" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I334" s="10" t="s">
         <v>724</v>
@@ -22471,7 +22502,7 @@
         <v>107</v>
       </c>
       <c r="H335" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I335" s="10" t="s">
         <v>726</v>
@@ -22497,7 +22528,7 @@
         <v>78</v>
       </c>
       <c r="H336" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I336" s="10" t="s">
         <v>728</v>
@@ -22523,7 +22554,7 @@
         <v>116</v>
       </c>
       <c r="H337" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I337" s="10" t="s">
         <v>730</v>
@@ -22549,7 +22580,7 @@
         <v>45</v>
       </c>
       <c r="H338" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I338" s="10" t="s">
         <v>732</v>
@@ -22575,7 +22606,7 @@
         <v>999</v>
       </c>
       <c r="H339" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I339" s="10" t="s">
         <v>734</v>
@@ -22601,7 +22632,7 @@
         <v>84</v>
       </c>
       <c r="H340" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I340" s="10" t="s">
         <v>736</v>
@@ -22627,7 +22658,7 @@
         <v>661</v>
       </c>
       <c r="H341" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I341" s="10" t="s">
         <v>738</v>
@@ -22653,7 +22684,7 @@
         <v>999</v>
       </c>
       <c r="H342" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I342" s="10" t="s">
         <v>740</v>
@@ -22679,7 +22710,7 @@
         <v>999</v>
       </c>
       <c r="H343" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I343" s="10" t="s">
         <v>742</v>
@@ -22705,7 +22736,7 @@
         <v>999</v>
       </c>
       <c r="H344" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I344" s="10" t="s">
         <v>744</v>
@@ -22731,7 +22762,7 @@
         <v>42</v>
       </c>
       <c r="H345" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I345" s="10" t="s">
         <v>746</v>
@@ -22757,7 +22788,7 @@
         <v>999</v>
       </c>
       <c r="H346" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I346" s="10" t="s">
         <v>748</v>
@@ -22783,7 +22814,7 @@
         <v>877</v>
       </c>
       <c r="H347" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I347" s="10" t="s">
         <v>750</v>
@@ -22809,7 +22840,7 @@
         <v>260</v>
       </c>
       <c r="H348" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I348" s="10" t="s">
         <v>752</v>
@@ -22835,7 +22866,7 @@
         <v>999</v>
       </c>
       <c r="H349" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I349" s="10" t="s">
         <v>754</v>
@@ -22861,7 +22892,7 @@
         <v>999</v>
       </c>
       <c r="H350" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I350" s="10" t="s">
         <v>756</v>
@@ -22887,7 +22918,7 @@
         <v>269</v>
       </c>
       <c r="H351" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I351" s="10" t="s">
         <v>758</v>
@@ -22913,7 +22944,7 @@
         <v>140</v>
       </c>
       <c r="H352" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I352" s="10" t="s">
         <v>760</v>
@@ -22939,7 +22970,7 @@
         <v>999</v>
       </c>
       <c r="H353" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I353" s="10" t="s">
         <v>762</v>
@@ -22965,7 +22996,7 @@
         <v>675</v>
       </c>
       <c r="H354" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I354" s="10" t="s">
         <v>764</v>
@@ -22991,7 +23022,7 @@
         <v>357</v>
       </c>
       <c r="H355" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I355" s="10" t="s">
         <v>766</v>
@@ -23017,7 +23048,7 @@
         <v>12</v>
       </c>
       <c r="H356" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I356" s="10" t="s">
         <v>768</v>
@@ -23043,7 +23074,7 @@
         <v>463</v>
       </c>
       <c r="H357" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I357" s="10" t="s">
         <v>770</v>
@@ -23069,7 +23100,7 @@
         <v>231</v>
       </c>
       <c r="H358" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I358" s="10" t="s">
         <v>772</v>
@@ -23095,7 +23126,7 @@
         <v>220</v>
       </c>
       <c r="H359" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I359" s="10" t="s">
         <v>774</v>
@@ -23121,7 +23152,7 @@
         <v>9999</v>
       </c>
       <c r="H360" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I360" s="10" t="s">
         <v>776</v>
@@ -23147,7 +23178,7 @@
         <v>999</v>
       </c>
       <c r="H361" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I361" s="10" t="s">
         <v>778</v>
@@ -23170,7 +23201,7 @@
         <v>0</v>
       </c>
       <c r="H362" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I362" s="10" t="s">
         <v>780</v>
@@ -23196,7 +23227,7 @@
         <v>860</v>
       </c>
       <c r="H363" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I363" s="10" t="s">
         <v>782</v>
@@ -23222,7 +23253,7 @@
         <v>967</v>
       </c>
       <c r="H364" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I364" s="10" t="s">
         <v>784</v>
@@ -23245,7 +23276,7 @@
         <v>0</v>
       </c>
       <c r="H365" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I365" s="10" t="s">
         <v>786</v>
@@ -23271,7 +23302,7 @@
         <v>303</v>
       </c>
       <c r="H366" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I366" s="10" t="s">
         <v>788</v>
@@ -23297,7 +23328,7 @@
         <v>141</v>
       </c>
       <c r="H367" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I367" s="10" t="s">
         <v>790</v>
@@ -23323,7 +23354,7 @@
         <v>9999</v>
       </c>
       <c r="H368" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I368" s="10" t="s">
         <v>792</v>
@@ -23349,7 +23380,7 @@
         <v>314</v>
       </c>
       <c r="H369" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I369" s="10" t="s">
         <v>794</v>
@@ -23375,7 +23406,7 @@
         <v>162</v>
       </c>
       <c r="H370" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I370" s="10" t="s">
         <v>796</v>
@@ -23401,7 +23432,7 @@
         <v>879</v>
       </c>
       <c r="H371" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I371" s="10" t="s">
         <v>798</v>
@@ -23427,7 +23458,7 @@
         <v>19</v>
       </c>
       <c r="H372" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I372" s="10" t="s">
         <v>800</v>
@@ -23453,7 +23484,7 @@
         <v>55</v>
       </c>
       <c r="H373" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I373" s="10" t="s">
         <v>802</v>
@@ -23479,7 +23510,7 @@
         <v>999</v>
       </c>
       <c r="H374" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I374" s="10" t="s">
         <v>804</v>
@@ -23505,7 +23536,7 @@
         <v>117</v>
       </c>
       <c r="H375" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I375" s="10" t="s">
         <v>806</v>
@@ -23531,7 +23562,7 @@
         <v>10</v>
       </c>
       <c r="H376" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I376" s="10" t="s">
         <v>808</v>
@@ -23557,7 +23588,7 @@
         <v>90</v>
       </c>
       <c r="H377" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I377" s="10" t="s">
         <v>810</v>
@@ -23583,7 +23614,7 @@
         <v>428</v>
       </c>
       <c r="H378" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I378" s="10" t="s">
         <v>812</v>
@@ -23609,7 +23640,7 @@
         <v>273</v>
       </c>
       <c r="H379" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I379" s="10" t="s">
         <v>814</v>
@@ -23635,7 +23666,7 @@
         <v>893</v>
       </c>
       <c r="H380" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I380" s="10" t="s">
         <v>816</v>
@@ -23661,7 +23692,7 @@
         <v>23</v>
       </c>
       <c r="H381" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I381" s="10" t="s">
         <v>818</v>
@@ -23687,7 +23718,7 @@
         <v>801</v>
       </c>
       <c r="H382" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I382" s="10" t="s">
         <v>820</v>
@@ -23713,7 +23744,7 @@
         <v>126</v>
       </c>
       <c r="H383" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I383" s="10" t="s">
         <v>822</v>
@@ -23739,7 +23770,7 @@
         <v>194</v>
       </c>
       <c r="H384" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I384" s="10" t="s">
         <v>824</v>
@@ -23765,7 +23796,7 @@
         <v>40</v>
       </c>
       <c r="H385" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I385" s="10" t="s">
         <v>826</v>
@@ -23791,7 +23822,7 @@
         <v>13</v>
       </c>
       <c r="H386" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I386" s="10" t="s">
         <v>828</v>
@@ -23817,7 +23848,7 @@
         <v>217</v>
       </c>
       <c r="H387" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I387" s="10" t="s">
         <v>830</v>
@@ -23843,7 +23874,7 @@
         <v>983</v>
       </c>
       <c r="H388" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I388" s="10" t="s">
         <v>832</v>
@@ -23869,7 +23900,7 @@
         <v>56</v>
       </c>
       <c r="H389" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I389" s="10" t="s">
         <v>834</v>
@@ -23895,7 +23926,7 @@
         <v>999</v>
       </c>
       <c r="H390" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I390" s="10" t="s">
         <v>836</v>
@@ -23921,7 +23952,7 @@
         <v>254</v>
       </c>
       <c r="H391" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I391" s="10" t="s">
         <v>838</v>
@@ -23947,7 +23978,7 @@
         <v>857</v>
       </c>
       <c r="H392" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I392" s="10" t="s">
         <v>840</v>
@@ -23973,7 +24004,7 @@
         <v>999</v>
       </c>
       <c r="H393" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I393" s="10" t="s">
         <v>842</v>
@@ -23999,7 +24030,7 @@
         <v>999</v>
       </c>
       <c r="H394" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I394" s="10" t="s">
         <v>844</v>
@@ -24025,7 +24056,7 @@
         <v>749</v>
       </c>
       <c r="H395" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I395" s="10" t="s">
         <v>846</v>
@@ -24051,7 +24082,7 @@
         <v>384</v>
       </c>
       <c r="H396" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I396" s="10" t="s">
         <v>848</v>
@@ -24077,7 +24108,7 @@
         <v>73</v>
       </c>
       <c r="H397" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I397" s="10" t="s">
         <v>850</v>
@@ -24103,7 +24134,7 @@
         <v>999</v>
       </c>
       <c r="H398" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I398" s="10" t="s">
         <v>852</v>
@@ -24129,7 +24160,7 @@
         <v>167</v>
       </c>
       <c r="H399" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I399" s="10" t="s">
         <v>854</v>
@@ -24155,7 +24186,7 @@
         <v>27</v>
       </c>
       <c r="H400" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I400" s="10" t="s">
         <v>856</v>
@@ -24181,7 +24212,7 @@
         <v>103</v>
       </c>
       <c r="H401" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I401" s="10" t="s">
         <v>858</v>
@@ -24207,7 +24238,7 @@
         <v>61</v>
       </c>
       <c r="H402" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I402" s="10" t="s">
         <v>860</v>
@@ -24233,7 +24264,7 @@
         <v>41</v>
       </c>
       <c r="H403" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I403" s="10" t="s">
         <v>862</v>
@@ -24259,7 +24290,7 @@
         <v>16</v>
       </c>
       <c r="H404" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I404" s="10" t="s">
         <v>864</v>
@@ -24285,7 +24316,7 @@
         <v>15</v>
       </c>
       <c r="H405" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I405" s="10" t="s">
         <v>866</v>
@@ -24311,7 +24342,7 @@
         <v>190</v>
       </c>
       <c r="H406" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I406" s="10" t="s">
         <v>868</v>
@@ -24337,7 +24368,7 @@
         <v>999</v>
       </c>
       <c r="H407" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I407" s="10" t="s">
         <v>870</v>
@@ -24363,7 +24394,7 @@
         <v>101</v>
       </c>
       <c r="H408" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I408" s="10" t="s">
         <v>872</v>
@@ -24389,7 +24420,7 @@
         <v>626</v>
       </c>
       <c r="H409" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I409" s="10" t="s">
         <v>874</v>
@@ -24415,7 +24446,7 @@
         <v>150</v>
       </c>
       <c r="H410" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I410" s="10" t="s">
         <v>876</v>
@@ -24441,7 +24472,7 @@
         <v>432</v>
       </c>
       <c r="H411" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I411" s="10" t="s">
         <v>878</v>
@@ -24467,7 +24498,7 @@
         <v>71</v>
       </c>
       <c r="H412" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I412" s="10" t="s">
         <v>880</v>
@@ -24493,7 +24524,7 @@
         <v>524</v>
       </c>
       <c r="H413" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I413" s="10" t="s">
         <v>882</v>
@@ -24519,7 +24550,7 @@
         <v>24</v>
       </c>
       <c r="H414" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I414" s="10" t="s">
         <v>884</v>
@@ -24545,7 +24576,7 @@
         <v>999</v>
       </c>
       <c r="H415" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I415" s="10" t="s">
         <v>886</v>
@@ -24571,7 +24602,7 @@
         <v>999</v>
       </c>
       <c r="H416" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I416" s="10" t="s">
         <v>888</v>
@@ -24597,7 +24628,7 @@
         <v>999</v>
       </c>
       <c r="H417" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I417" s="10" t="s">
         <v>890</v>
@@ -24623,7 +24654,7 @@
         <v>999</v>
       </c>
       <c r="H418" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I418" s="10" t="s">
         <v>892</v>
@@ -24649,7 +24680,7 @@
         <v>999</v>
       </c>
       <c r="H419" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I419" s="10" t="s">
         <v>894</v>
@@ -24675,7 +24706,7 @@
         <v>102</v>
       </c>
       <c r="H420" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I420" s="10" t="s">
         <v>896</v>
@@ -24701,7 +24732,7 @@
         <v>23</v>
       </c>
       <c r="H421" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I421" s="10" t="s">
         <v>898</v>
@@ -45151,7 +45182,7 @@
         <v>1000204271</v>
       </c>
       <c r="B1193" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C1193">
         <v>3580</v>
@@ -45169,7 +45200,7 @@
         <v>2430</v>
       </c>
       <c r="I1193" s="10" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="1194" spans="1:9">
@@ -45385,7 +45416,7 @@
         <v>5061296</v>
       </c>
       <c r="B1202" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C1202">
         <v>4320</v>
@@ -45403,7 +45434,7 @@
         <v>2430</v>
       </c>
       <c r="I1202" s="10" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="1203" spans="1:9">
@@ -47069,7 +47100,7 @@
         <v>1000548850</v>
       </c>
       <c r="B1267" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="C1267">
         <v>4380</v>
@@ -47087,7 +47118,7 @@
         <v>2477</v>
       </c>
       <c r="I1267" s="10" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
     </row>
     <row r="1268" spans="1:9">
@@ -52846,7 +52877,7 @@
         <v>1000201444</v>
       </c>
       <c r="B1484" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C1484">
         <v>5280</v>
@@ -52864,7 +52895,7 @@
         <v>3014</v>
       </c>
       <c r="I1484" s="10" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="1485" spans="1:9">

--- a/다과_구매목록.xlsx
+++ b/다과_구매목록.xlsx
@@ -198,216 +198,222 @@
     <t>https://www.kurly.com/goods/5067311</t>
   </si>
   <si>
+    <t>[오리온] 다이제 쏙쏙포장 5종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000198198</t>
+  </si>
+  <si>
+    <t>[크라운] 쿠크다스 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5121160</t>
+  </si>
+  <si>
+    <t>[롯데] 마가렛트 오리지널 352g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000339526</t>
+  </si>
+  <si>
+    <t>[롯데] 칙촉 오리지널 벌크 180g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5132978</t>
+  </si>
+  <si>
+    <t>[롯데] 빈츠 204g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5079340</t>
+  </si>
+  <si>
+    <t>[리치] 버터 와플 270g (15g x 18입)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5066715</t>
+  </si>
+  <si>
+    <t>[청우] 쫀득 초코칩 240g (12입)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5061291</t>
+  </si>
+  <si>
+    <t>[마켓오] 리얼 브라우니 240g (20g x 12개입)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5055895</t>
+  </si>
+  <si>
+    <t>[오레오] 씬즈 84g 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000321594</t>
+  </si>
+  <si>
+    <t>[폴트] 프랑스 타르트 비스킷 2종</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5104102</t>
+  </si>
+  <si>
+    <t>[임페리얼] 데니쉬 버터쿠키 200g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5038004</t>
+  </si>
+  <si>
+    <t>[로투스] 비스코프 4종, 택1</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5071375</t>
+  </si>
+  <si>
+    <t>파이/케이크(개별포장)</t>
+  </si>
+  <si>
+    <t>[오리온] 초코파이 12입</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5061296</t>
+  </si>
+  <si>
+    <t>[오리온] 카스타드 12개입 276g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000875718</t>
+  </si>
+  <si>
+    <t>[롯데] 몽쉘 생크림케이크 오리지널 408g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000175874</t>
+  </si>
+  <si>
+    <t>[해태] 오예스 360g 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000201444</t>
+  </si>
+  <si>
+    <t>[크라운] 빅파이 딸기 324g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5070774</t>
+  </si>
+  <si>
+    <t>[해태] 후렌치파이 192g 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000204271</t>
+  </si>
+  <si>
+    <t>품목수</t>
+  </si>
+  <si>
+    <t>비중</t>
+  </si>
+  <si>
+    <t>상품번호</t>
+  </si>
+  <si>
+    <t>가격</t>
+  </si>
+  <si>
+    <t>정가</t>
+  </si>
+  <si>
+    <t>할인율</t>
+  </si>
+  <si>
+    <t>품절</t>
+  </si>
+  <si>
+    <t>검색어</t>
+  </si>
+  <si>
+    <t>[마요라] 아페티토 스틱 스낵 2종, 택1</t>
+  </si>
+  <si>
+    <t>가성비 과자</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1002110052</t>
+  </si>
+  <si>
+    <t>[해태] 아이비 309g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000747182</t>
+  </si>
+  <si>
+    <t>[해태] 자가비 소포장 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000343575</t>
+  </si>
+  <si>
+    <t>대만 누가크래커 대용량 32개입 448g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000862247</t>
+  </si>
+  <si>
+    <t>[비타비고] 이탈리안 브레드 스틱 4종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000178183</t>
+  </si>
+  <si>
+    <t>[밤부] 누가 크래커 140g</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5031072</t>
+  </si>
+  <si>
+    <t>[무직타이거] 옛날과자 골라담기 5종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000875821</t>
+  </si>
+  <si>
+    <t>[포테이토 크리스프] 감자칩 2종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000651310</t>
+  </si>
+  <si>
+    <t>[리츠] 크래커 3종 (택1)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/1000321598</t>
+  </si>
+  <si>
+    <t>[해태] 에이스 364g (24g x 15봉지)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5077465</t>
+  </si>
+  <si>
+    <t>[롯데] 꼬깔콘 스낵(소) 4번들</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5079319</t>
+  </si>
+  <si>
+    <t>[해태] 맛동산 304g (38g x 8팩)</t>
+  </si>
+  <si>
+    <t>https://www.kurly.com/goods/5077461</t>
+  </si>
+  <si>
     <t>[맥비티] 다이제스티브 비스킷 2종 (택1)</t>
   </si>
   <si>
     <t>https://www.kurly.com/goods/1000975389</t>
   </si>
   <si>
-    <t>[크라운] 쿠크다스 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5121160</t>
-  </si>
-  <si>
-    <t>[롯데] 마가렛트 오리지널 352g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000339526</t>
-  </si>
-  <si>
-    <t>[롯데] 칙촉 오리지널 벌크 180g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5132978</t>
-  </si>
-  <si>
-    <t>[롯데] 빈츠 204g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5079340</t>
-  </si>
-  <si>
-    <t>[리치] 버터 와플 270g (15g x 18입)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5066715</t>
-  </si>
-  <si>
-    <t>[청우] 쫀득 초코칩 240g (12입)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5061291</t>
-  </si>
-  <si>
-    <t>[마켓오] 리얼 브라우니 240g (20g x 12개입)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5055895</t>
-  </si>
-  <si>
-    <t>[오레오] 씬즈 84g 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000321594</t>
-  </si>
-  <si>
-    <t>[폴트] 프랑스 타르트 비스킷 2종</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5104102</t>
-  </si>
-  <si>
-    <t>[임페리얼] 데니쉬 버터쿠키 200g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5038004</t>
-  </si>
-  <si>
-    <t>[로투스] 비스코프 4종, 택1</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5071375</t>
-  </si>
-  <si>
-    <t>파이/케이크(개별포장)</t>
-  </si>
-  <si>
-    <t>[오리온] 초코파이 12입</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5061296</t>
-  </si>
-  <si>
-    <t>[오리온] 카스타드 12개입 276g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000875718</t>
-  </si>
-  <si>
-    <t>[롯데] 몽쉘 생크림케이크 오리지널 408g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000175874</t>
-  </si>
-  <si>
-    <t>[해태] 오예스 360g 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000201444</t>
-  </si>
-  <si>
-    <t>[크라운] 빅파이 딸기 324g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5070774</t>
-  </si>
-  <si>
-    <t>[해태] 후렌치파이 192g 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000204271</t>
-  </si>
-  <si>
-    <t>품목수</t>
-  </si>
-  <si>
-    <t>비중</t>
-  </si>
-  <si>
-    <t>상품번호</t>
-  </si>
-  <si>
-    <t>가격</t>
-  </si>
-  <si>
-    <t>정가</t>
-  </si>
-  <si>
-    <t>할인율</t>
-  </si>
-  <si>
-    <t>품절</t>
-  </si>
-  <si>
-    <t>검색어</t>
-  </si>
-  <si>
-    <t>[마요라] 아페티토 스틱 스낵 2종, 택1</t>
-  </si>
-  <si>
-    <t>가성비 과자</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1002110052</t>
-  </si>
-  <si>
-    <t>[해태] 아이비 309g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000747182</t>
-  </si>
-  <si>
-    <t>[해태] 자가비 소포장 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000343575</t>
-  </si>
-  <si>
-    <t>대만 누가크래커 대용량 32개입 448g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000862247</t>
-  </si>
-  <si>
-    <t>[비타비고] 이탈리안 브레드 스틱 4종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000178183</t>
-  </si>
-  <si>
-    <t>[밤부] 누가 크래커 140g</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5031072</t>
-  </si>
-  <si>
-    <t>[무직타이거] 옛날과자 골라담기 5종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000875821</t>
-  </si>
-  <si>
-    <t>[포테이토 크리스프] 감자칩 2종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000651310</t>
-  </si>
-  <si>
-    <t>[리츠] 크래커 3종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000321598</t>
-  </si>
-  <si>
-    <t>[해태] 에이스 364g (24g x 15봉지)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5077465</t>
-  </si>
-  <si>
-    <t>[롯데] 꼬깔콘 스낵(소) 4번들</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5079319</t>
-  </si>
-  <si>
-    <t>[해태] 맛동산 304g (38g x 8팩)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/5077461</t>
-  </si>
-  <si>
     <t xml:space="preserve">[농심] 인기 봉지 과자 7종 (택1) </t>
   </si>
   <si>
@@ -1180,12 +1186,6 @@
   </si>
   <si>
     <t>https://www.kurly.com/goods/1002475314</t>
-  </si>
-  <si>
-    <t>[오리온] 다이제 쏙쏙포장 5종 (택1)</t>
-  </si>
-  <si>
-    <t>https://www.kurly.com/goods/1000198198</t>
   </si>
   <si>
     <t>[HBAF] 넛츠앤스낵스 땅콩 120g 5종 (택1)</t>
@@ -12499,14 +12499,14 @@
       </c>
       <c r="D2" s="3">
         <f>SUM(F5:F41)</f>
-        <v>489810</v>
+        <v>490440</v>
       </c>
       <c r="E2" t="s">
         <v>3</v>
       </c>
       <c r="F2" s="3">
         <f>B2-D2</f>
-        <v>10190</v>
+        <v>9560</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -13124,14 +13124,14 @@
         <v>59</v>
       </c>
       <c r="D24" s="2">
-        <v>2990</v>
+        <v>3200</v>
       </c>
       <c r="E24">
         <v>3</v>
       </c>
       <c r="F24" s="2">
         <f>D24*E24</f>
-        <v>8970</v>
+        <v>9600</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -13736,7 +13736,7 @@
       </c>
       <c r="D2" s="9">
         <f>C2/SUM($C$2:$C$8)</f>
-        <v>0.0855025418019232</v>
+        <v>0.08539270858820651</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -13753,7 +13753,7 @@
       </c>
       <c r="D3" s="9">
         <f>C3/SUM($C$2:$C$8)</f>
-        <v>0.09015740797452074</v>
+        <v>0.09004159530217763</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -13770,7 +13770,7 @@
       </c>
       <c r="D4" s="9">
         <f>C4/SUM($C$2:$C$8)</f>
-        <v>0.1650027561707601</v>
+        <v>0.1647908000978713</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -13783,11 +13783,11 @@
       </c>
       <c r="C5" s="2">
         <f>SUMIF(구매목록!B5:B41,A5,구매목록!F5:F41)</f>
-        <v>156000</v>
+        <v>156630</v>
       </c>
       <c r="D5" s="9">
         <f>C5/SUM($C$2:$C$8)</f>
-        <v>0.31849084338825256</v>
+        <v>0.3193662833374113</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -13804,7 +13804,7 @@
       </c>
       <c r="D6" s="9">
         <f>C6/SUM($C$2:$C$8)</f>
-        <v>0.21247014148343235</v>
+        <v>0.21219721066797162</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -13821,7 +13821,7 @@
       </c>
       <c r="D7" s="9">
         <f>C7/SUM($C$2:$C$8)</f>
-        <v>0.07264041158816684</v>
+        <v>0.07254710056275997</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -13838,7 +13838,7 @@
       </c>
       <c r="D8" s="9">
         <f>C8/SUM($C$2:$C$8)</f>
-        <v>0.0557358975929442</v>
+        <v>0.05566430144360166</v>
       </c>
     </row>
   </sheetData>
@@ -14232,7 +14232,7 @@
         <v>1000975389</v>
       </c>
       <c r="B15" t="s">
-        <v>59</v>
+        <v>129</v>
       </c>
       <c r="C15">
         <v>2990</v>
@@ -14250,7 +14250,7 @@
         <v>105</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -14284,7 +14284,7 @@
         <v>1000198192</v>
       </c>
       <c r="B17" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C17">
         <v>4540</v>
@@ -14302,7 +14302,7 @@
         <v>105</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -14310,7 +14310,7 @@
         <v>5151421</v>
       </c>
       <c r="B18" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C18">
         <v>5940</v>
@@ -14328,7 +14328,7 @@
         <v>105</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -14336,7 +14336,7 @@
         <v>1001272797</v>
       </c>
       <c r="B19" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C19">
         <v>2980</v>
@@ -14354,7 +14354,7 @@
         <v>105</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -14362,7 +14362,7 @@
         <v>1001029494</v>
       </c>
       <c r="B20" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C20">
         <v>2280</v>
@@ -14380,7 +14380,7 @@
         <v>105</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -14388,7 +14388,7 @@
         <v>5030780</v>
       </c>
       <c r="B21" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C21">
         <v>5800</v>
@@ -14406,7 +14406,7 @@
         <v>105</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -14414,7 +14414,7 @@
         <v>1000339529</v>
       </c>
       <c r="B22" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C22">
         <v>3980</v>
@@ -14432,7 +14432,7 @@
         <v>105</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -14440,7 +14440,7 @@
         <v>5036524</v>
       </c>
       <c r="B23" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C23">
         <v>2520</v>
@@ -14458,7 +14458,7 @@
         <v>105</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -14466,7 +14466,7 @@
         <v>1000356676</v>
       </c>
       <c r="B24" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C24">
         <v>3800</v>
@@ -14484,7 +14484,7 @@
         <v>105</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -14492,7 +14492,7 @@
         <v>1000963099</v>
       </c>
       <c r="B25" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C25">
         <v>4780</v>
@@ -14510,7 +14510,7 @@
         <v>105</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -14518,7 +14518,7 @@
         <v>5088236</v>
       </c>
       <c r="B26" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C26">
         <v>8980</v>
@@ -14536,7 +14536,7 @@
         <v>105</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -14544,7 +14544,7 @@
         <v>1000617577</v>
       </c>
       <c r="B27" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C27">
         <v>1360</v>
@@ -14562,7 +14562,7 @@
         <v>105</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -14570,7 +14570,7 @@
         <v>1000455773</v>
       </c>
       <c r="B28" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C28">
         <v>4500</v>
@@ -14588,7 +14588,7 @@
         <v>105</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -14596,7 +14596,7 @@
         <v>1000137075</v>
       </c>
       <c r="B29" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C29">
         <v>4480</v>
@@ -14614,7 +14614,7 @@
         <v>105</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -14622,7 +14622,7 @@
         <v>1002134596</v>
       </c>
       <c r="B30" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C30">
         <v>5980</v>
@@ -14640,7 +14640,7 @@
         <v>105</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -14648,7 +14648,7 @@
         <v>1001447521</v>
       </c>
       <c r="B31" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C31">
         <v>1440</v>
@@ -14666,7 +14666,7 @@
         <v>105</v>
       </c>
       <c r="I31" s="10" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -14674,7 +14674,7 @@
         <v>1001421531</v>
       </c>
       <c r="B32" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C32">
         <v>4980</v>
@@ -14692,7 +14692,7 @@
         <v>105</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -14700,7 +14700,7 @@
         <v>1000269917</v>
       </c>
       <c r="B33" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C33">
         <v>12800</v>
@@ -14718,7 +14718,7 @@
         <v>105</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -14726,7 +14726,7 @@
         <v>1001592465</v>
       </c>
       <c r="B34" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C34">
         <v>3880</v>
@@ -14744,7 +14744,7 @@
         <v>105</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -14752,7 +14752,7 @@
         <v>5054491</v>
       </c>
       <c r="B35" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C35">
         <v>6590</v>
@@ -14770,7 +14770,7 @@
         <v>105</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -14778,7 +14778,7 @@
         <v>1001919935</v>
       </c>
       <c r="B36" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C36">
         <v>3800</v>
@@ -14796,7 +14796,7 @@
         <v>105</v>
       </c>
       <c r="I36" s="10" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="37" spans="1:9">
@@ -14804,7 +14804,7 @@
         <v>5062899</v>
       </c>
       <c r="B37" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C37">
         <v>4580</v>
@@ -14822,7 +14822,7 @@
         <v>105</v>
       </c>
       <c r="I37" s="10" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -14830,7 +14830,7 @@
         <v>1000875710</v>
       </c>
       <c r="B38" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C38">
         <v>4580</v>
@@ -14848,7 +14848,7 @@
         <v>105</v>
       </c>
       <c r="I38" s="10" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -14856,7 +14856,7 @@
         <v>5006818</v>
       </c>
       <c r="B39" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C39">
         <v>8500</v>
@@ -14874,7 +14874,7 @@
         <v>105</v>
       </c>
       <c r="I39" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -14882,7 +14882,7 @@
         <v>1000582944</v>
       </c>
       <c r="B40" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C40">
         <v>2780</v>
@@ -14900,7 +14900,7 @@
         <v>105</v>
       </c>
       <c r="I40" s="10" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -14908,7 +14908,7 @@
         <v>1000206111</v>
       </c>
       <c r="B41" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C41">
         <v>5900</v>
@@ -14926,7 +14926,7 @@
         <v>105</v>
       </c>
       <c r="I41" s="10" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="42" spans="1:9">
@@ -14934,7 +14934,7 @@
         <v>1000643389</v>
       </c>
       <c r="B42" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C42">
         <v>5480</v>
@@ -14952,7 +14952,7 @@
         <v>105</v>
       </c>
       <c r="I42" s="10" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="43" spans="1:9">
@@ -14960,7 +14960,7 @@
         <v>1000439362</v>
       </c>
       <c r="B43" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C43">
         <v>2250</v>
@@ -14978,7 +14978,7 @@
         <v>105</v>
       </c>
       <c r="I43" s="10" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="44" spans="1:9">
@@ -14986,7 +14986,7 @@
         <v>1000166566</v>
       </c>
       <c r="B44" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C44">
         <v>12000</v>
@@ -15004,7 +15004,7 @@
         <v>105</v>
       </c>
       <c r="I44" s="10" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="45" spans="1:9">
@@ -15012,7 +15012,7 @@
         <v>1000526145</v>
       </c>
       <c r="B45" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C45">
         <v>8900</v>
@@ -15030,7 +15030,7 @@
         <v>105</v>
       </c>
       <c r="I45" s="10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="46" spans="1:9">
@@ -15038,7 +15038,7 @@
         <v>1000789439</v>
       </c>
       <c r="B46" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C46">
         <v>3590</v>
@@ -15056,7 +15056,7 @@
         <v>105</v>
       </c>
       <c r="I46" s="10" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="47" spans="1:9">
@@ -15064,7 +15064,7 @@
         <v>1000356687</v>
       </c>
       <c r="B47" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C47">
         <v>4400</v>
@@ -15082,7 +15082,7 @@
         <v>105</v>
       </c>
       <c r="I47" s="10" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="48" spans="1:9">
@@ -15090,7 +15090,7 @@
         <v>5153242</v>
       </c>
       <c r="B48" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C48">
         <v>9980</v>
@@ -15108,7 +15108,7 @@
         <v>105</v>
       </c>
       <c r="I48" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="49" spans="1:9">
@@ -15116,7 +15116,7 @@
         <v>1000033235</v>
       </c>
       <c r="B49" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C49">
         <v>2600</v>
@@ -15134,7 +15134,7 @@
         <v>105</v>
       </c>
       <c r="I49" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -15142,7 +15142,7 @@
         <v>1001570087</v>
       </c>
       <c r="B50" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C50">
         <v>6080</v>
@@ -15160,7 +15160,7 @@
         <v>105</v>
       </c>
       <c r="I50" s="10" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -15194,7 +15194,7 @@
         <v>1000942359</v>
       </c>
       <c r="B52" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C52">
         <v>1440</v>
@@ -15212,7 +15212,7 @@
         <v>105</v>
       </c>
       <c r="I52" s="10" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="53" spans="1:9">
@@ -15220,7 +15220,7 @@
         <v>1001397540</v>
       </c>
       <c r="B53" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C53">
         <v>1080</v>
@@ -15238,7 +15238,7 @@
         <v>105</v>
       </c>
       <c r="I53" s="10" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="54" spans="1:9">
@@ -15246,7 +15246,7 @@
         <v>1000927112</v>
       </c>
       <c r="B54" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C54">
         <v>3325</v>
@@ -15264,7 +15264,7 @@
         <v>105</v>
       </c>
       <c r="I54" s="10" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="55" spans="1:9">
@@ -15272,7 +15272,7 @@
         <v>5103484</v>
       </c>
       <c r="B55" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C55">
         <v>11980</v>
@@ -15290,7 +15290,7 @@
         <v>105</v>
       </c>
       <c r="I55" s="10" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="56" spans="1:9">
@@ -15298,7 +15298,7 @@
         <v>1000605988</v>
       </c>
       <c r="B56" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C56">
         <v>4180</v>
@@ -15316,7 +15316,7 @@
         <v>105</v>
       </c>
       <c r="I56" s="10" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="57" spans="1:9">
@@ -15324,7 +15324,7 @@
         <v>5060050</v>
       </c>
       <c r="B57" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C57">
         <v>5980</v>
@@ -15342,7 +15342,7 @@
         <v>105</v>
       </c>
       <c r="I57" s="10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="58" spans="1:9">
@@ -15350,7 +15350,7 @@
         <v>1002324203</v>
       </c>
       <c r="B58" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C58">
         <v>6980</v>
@@ -15368,7 +15368,7 @@
         <v>105</v>
       </c>
       <c r="I58" s="10" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="59" spans="1:9">
@@ -15376,7 +15376,7 @@
         <v>5095165</v>
       </c>
       <c r="B59" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C59">
         <v>3580</v>
@@ -15394,7 +15394,7 @@
         <v>105</v>
       </c>
       <c r="I59" s="10" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="60" spans="1:9">
@@ -15402,7 +15402,7 @@
         <v>1000178191</v>
       </c>
       <c r="B60" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C60">
         <v>4150</v>
@@ -15420,7 +15420,7 @@
         <v>105</v>
       </c>
       <c r="I60" s="10" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="61" spans="1:9">
@@ -15428,7 +15428,7 @@
         <v>1000914382</v>
       </c>
       <c r="B61" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C61">
         <v>15500</v>
@@ -15446,7 +15446,7 @@
         <v>105</v>
       </c>
       <c r="I61" s="10" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="62" spans="1:9">
@@ -15454,7 +15454,7 @@
         <v>1002014581</v>
       </c>
       <c r="B62" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C62">
         <v>4950</v>
@@ -15472,7 +15472,7 @@
         <v>105</v>
       </c>
       <c r="I62" s="10" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="63" spans="1:9">
@@ -15480,7 +15480,7 @@
         <v>5052362</v>
       </c>
       <c r="B63" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C63">
         <v>13900</v>
@@ -15498,7 +15498,7 @@
         <v>105</v>
       </c>
       <c r="I63" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="64" spans="1:9">
@@ -15532,7 +15532,7 @@
         <v>1000958549</v>
       </c>
       <c r="B65" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C65">
         <v>3380</v>
@@ -15550,7 +15550,7 @@
         <v>105</v>
       </c>
       <c r="I65" s="10" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="66" spans="1:9">
@@ -15558,7 +15558,7 @@
         <v>1002010936</v>
       </c>
       <c r="B66" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C66">
         <v>2800</v>
@@ -15576,7 +15576,7 @@
         <v>105</v>
       </c>
       <c r="I66" s="10" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="67" spans="1:9">
@@ -15584,7 +15584,7 @@
         <v>1000242960</v>
       </c>
       <c r="B67" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C67">
         <v>7000</v>
@@ -15602,7 +15602,7 @@
         <v>105</v>
       </c>
       <c r="I67" s="10" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="68" spans="1:9">
@@ -15610,7 +15610,7 @@
         <v>1002482468</v>
       </c>
       <c r="B68" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C68">
         <v>2130</v>
@@ -15628,7 +15628,7 @@
         <v>105</v>
       </c>
       <c r="I68" s="10" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="69" spans="1:9">
@@ -15636,7 +15636,7 @@
         <v>5058855</v>
       </c>
       <c r="B69" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C69">
         <v>8500</v>
@@ -15654,7 +15654,7 @@
         <v>105</v>
       </c>
       <c r="I69" s="10" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="70" spans="1:9">
@@ -15662,7 +15662,7 @@
         <v>1000783621</v>
       </c>
       <c r="B70" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C70">
         <v>10960</v>
@@ -15680,7 +15680,7 @@
         <v>105</v>
       </c>
       <c r="I70" s="10" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="71" spans="1:9">
@@ -15688,7 +15688,7 @@
         <v>1000525224</v>
       </c>
       <c r="B71" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C71">
         <v>12980</v>
@@ -15706,7 +15706,7 @@
         <v>105</v>
       </c>
       <c r="I71" s="10" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="72" spans="1:9">
@@ -15714,7 +15714,7 @@
         <v>1000365879</v>
       </c>
       <c r="B72" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C72">
         <v>3380</v>
@@ -15732,7 +15732,7 @@
         <v>105</v>
       </c>
       <c r="I72" s="10" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="73" spans="1:9">
@@ -15740,7 +15740,7 @@
         <v>1002133624</v>
       </c>
       <c r="B73" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C73">
         <v>6300</v>
@@ -15758,7 +15758,7 @@
         <v>105</v>
       </c>
       <c r="I73" s="10" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="74" spans="1:9">
@@ -15766,7 +15766,7 @@
         <v>1000339558</v>
       </c>
       <c r="B74" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C74">
         <v>2720</v>
@@ -15784,7 +15784,7 @@
         <v>105</v>
       </c>
       <c r="I74" s="10" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="75" spans="1:9">
@@ -15792,7 +15792,7 @@
         <v>5081478</v>
       </c>
       <c r="B75" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C75">
         <v>3360</v>
@@ -15810,7 +15810,7 @@
         <v>105</v>
       </c>
       <c r="I75" s="10" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="76" spans="1:9">
@@ -15818,7 +15818,7 @@
         <v>5005540</v>
       </c>
       <c r="B76" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C76">
         <v>8000</v>
@@ -15836,7 +15836,7 @@
         <v>105</v>
       </c>
       <c r="I76" s="10" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="77" spans="1:9">
@@ -15844,7 +15844,7 @@
         <v>1000526148</v>
       </c>
       <c r="B77" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C77">
         <v>8900</v>
@@ -15862,7 +15862,7 @@
         <v>105</v>
       </c>
       <c r="I77" s="10" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="78" spans="1:9">
@@ -15870,7 +15870,7 @@
         <v>1000677312</v>
       </c>
       <c r="B78" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C78">
         <v>1480</v>
@@ -15888,7 +15888,7 @@
         <v>105</v>
       </c>
       <c r="I78" s="10" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="79" spans="1:9">
@@ -15896,7 +15896,7 @@
         <v>1001407039</v>
       </c>
       <c r="B79" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C79">
         <v>3980</v>
@@ -15914,7 +15914,7 @@
         <v>105</v>
       </c>
       <c r="I79" s="10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="80" spans="1:9">
@@ -15922,7 +15922,7 @@
         <v>1000248448</v>
       </c>
       <c r="B80" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C80">
         <v>5200</v>
@@ -15940,7 +15940,7 @@
         <v>105</v>
       </c>
       <c r="I80" s="10" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="81" spans="1:9">
@@ -15948,7 +15948,7 @@
         <v>1001027192</v>
       </c>
       <c r="B81" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C81">
         <v>9000</v>
@@ -15966,7 +15966,7 @@
         <v>105</v>
       </c>
       <c r="I81" s="10" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="82" spans="1:9">
@@ -15974,7 +15974,7 @@
         <v>5067308</v>
       </c>
       <c r="B82" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C82">
         <v>2880</v>
@@ -15992,7 +15992,7 @@
         <v>105</v>
       </c>
       <c r="I82" s="10" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="83" spans="1:9">
@@ -16000,7 +16000,7 @@
         <v>1000942860</v>
       </c>
       <c r="B83" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C83">
         <v>1390</v>
@@ -16018,7 +16018,7 @@
         <v>105</v>
       </c>
       <c r="I83" s="10" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="84" spans="1:9">
@@ -16026,7 +16026,7 @@
         <v>1001991119</v>
       </c>
       <c r="B84" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C84">
         <v>3480</v>
@@ -16044,7 +16044,7 @@
         <v>105</v>
       </c>
       <c r="I84" s="10" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="85" spans="1:9">
@@ -16052,7 +16052,7 @@
         <v>5132664</v>
       </c>
       <c r="B85" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C85">
         <v>3800</v>
@@ -16070,7 +16070,7 @@
         <v>105</v>
       </c>
       <c r="I85" s="10" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="86" spans="1:9">
@@ -16078,7 +16078,7 @@
         <v>1000640854</v>
       </c>
       <c r="B86" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C86">
         <v>2720</v>
@@ -16096,7 +16096,7 @@
         <v>105</v>
       </c>
       <c r="I86" s="10" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="87" spans="1:9">
@@ -16104,7 +16104,7 @@
         <v>1000045935</v>
       </c>
       <c r="B87" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C87">
         <v>5990</v>
@@ -16122,7 +16122,7 @@
         <v>105</v>
       </c>
       <c r="I87" s="10" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="88" spans="1:9">
@@ -16130,7 +16130,7 @@
         <v>1000349505</v>
       </c>
       <c r="B88" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C88">
         <v>1440</v>
@@ -16148,7 +16148,7 @@
         <v>105</v>
       </c>
       <c r="I88" s="10" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="89" spans="1:9">
@@ -16156,7 +16156,7 @@
         <v>5060582</v>
       </c>
       <c r="B89" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C89">
         <v>10000</v>
@@ -16174,7 +16174,7 @@
         <v>105</v>
       </c>
       <c r="I89" s="10" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="90" spans="1:9">
@@ -16182,7 +16182,7 @@
         <v>1001363953</v>
       </c>
       <c r="B90" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C90">
         <v>2180</v>
@@ -16200,7 +16200,7 @@
         <v>105</v>
       </c>
       <c r="I90" s="10" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="91" spans="1:9">
@@ -16208,7 +16208,7 @@
         <v>5103372</v>
       </c>
       <c r="B91" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C91">
         <v>11980</v>
@@ -16226,7 +16226,7 @@
         <v>105</v>
       </c>
       <c r="I91" s="10" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="92" spans="1:9">
@@ -16234,7 +16234,7 @@
         <v>1001501063</v>
       </c>
       <c r="B92" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C92">
         <v>1260</v>
@@ -16252,7 +16252,7 @@
         <v>105</v>
       </c>
       <c r="I92" s="10" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="93" spans="1:9">
@@ -16260,7 +16260,7 @@
         <v>1000443353</v>
       </c>
       <c r="B93" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C93">
         <v>4040</v>
@@ -16278,7 +16278,7 @@
         <v>105</v>
       </c>
       <c r="I93" s="10" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="94" spans="1:9">
@@ -16286,7 +16286,7 @@
         <v>1002221133</v>
       </c>
       <c r="B94" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C94">
         <v>4980</v>
@@ -16304,7 +16304,7 @@
         <v>105</v>
       </c>
       <c r="I94" s="10" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="95" spans="1:9">
@@ -16312,7 +16312,7 @@
         <v>1000136966</v>
       </c>
       <c r="B95" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C95">
         <v>9000</v>
@@ -16330,7 +16330,7 @@
         <v>105</v>
       </c>
       <c r="I95" s="10" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="96" spans="1:9">
@@ -16338,7 +16338,7 @@
         <v>1000799985</v>
       </c>
       <c r="B96" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C96">
         <v>4980</v>
@@ -16356,7 +16356,7 @@
         <v>105</v>
       </c>
       <c r="I96" s="10" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="97" spans="1:9">
@@ -16364,7 +16364,7 @@
         <v>1000960165</v>
       </c>
       <c r="B97" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C97">
         <v>1390</v>
@@ -16382,7 +16382,7 @@
         <v>105</v>
       </c>
       <c r="I97" s="10" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="98" spans="1:9">
@@ -16390,7 +16390,7 @@
         <v>1001337989</v>
       </c>
       <c r="B98" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C98">
         <v>5280</v>
@@ -16408,7 +16408,7 @@
         <v>105</v>
       </c>
       <c r="I98" s="10" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="99" spans="1:9">
@@ -16468,7 +16468,7 @@
         <v>1002104225</v>
       </c>
       <c r="B101" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C101">
         <v>1280</v>
@@ -16486,7 +16486,7 @@
         <v>105</v>
       </c>
       <c r="I101" s="10" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="102" spans="1:9">
@@ -16494,7 +16494,7 @@
         <v>1002020133</v>
       </c>
       <c r="B102" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C102">
         <v>9030</v>
@@ -16512,7 +16512,7 @@
         <v>105</v>
       </c>
       <c r="I102" s="10" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="103" spans="1:9">
@@ -16520,7 +16520,7 @@
         <v>1000360436</v>
       </c>
       <c r="B103" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C103">
         <v>4480</v>
@@ -16538,7 +16538,7 @@
         <v>105</v>
       </c>
       <c r="I103" s="10" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="104" spans="1:9">
@@ -16546,7 +16546,7 @@
         <v>1001042362</v>
       </c>
       <c r="B104" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C104">
         <v>3980</v>
@@ -16564,7 +16564,7 @@
         <v>105</v>
       </c>
       <c r="I104" s="10" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="105" spans="1:9">
@@ -16572,7 +16572,7 @@
         <v>1002340554</v>
       </c>
       <c r="B105" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C105">
         <v>4250</v>
@@ -16590,7 +16590,7 @@
         <v>105</v>
       </c>
       <c r="I105" s="10" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="106" spans="1:9">
@@ -16598,7 +16598,7 @@
         <v>1000490099</v>
       </c>
       <c r="B106" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C106">
         <v>3980</v>
@@ -16616,7 +16616,7 @@
         <v>105</v>
       </c>
       <c r="I106" s="10" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="107" spans="1:9">
@@ -16624,7 +16624,7 @@
         <v>5077641</v>
       </c>
       <c r="B107" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C107">
         <v>7080</v>
@@ -16642,7 +16642,7 @@
         <v>105</v>
       </c>
       <c r="I107" s="10" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="108" spans="1:9">
@@ -16650,7 +16650,7 @@
         <v>1001397631</v>
       </c>
       <c r="B108" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C108">
         <v>1360</v>
@@ -16668,7 +16668,7 @@
         <v>105</v>
       </c>
       <c r="I108" s="10" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="109" spans="1:9">
@@ -16676,7 +16676,7 @@
         <v>1001942440</v>
       </c>
       <c r="B109" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C109">
         <v>2500</v>
@@ -16694,7 +16694,7 @@
         <v>105</v>
       </c>
       <c r="I109" s="10" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="110" spans="1:9">
@@ -16702,7 +16702,7 @@
         <v>1000958603</v>
       </c>
       <c r="B110" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C110">
         <v>3480</v>
@@ -16720,7 +16720,7 @@
         <v>105</v>
       </c>
       <c r="I110" s="10" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="111" spans="1:9">
@@ -16754,7 +16754,7 @@
         <v>1002221138</v>
       </c>
       <c r="B112" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C112">
         <v>4480</v>
@@ -16772,7 +16772,7 @@
         <v>105</v>
       </c>
       <c r="I112" s="10" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="113" spans="1:9">
@@ -16780,7 +16780,7 @@
         <v>1000216544</v>
       </c>
       <c r="B113" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C113">
         <v>4380</v>
@@ -16798,7 +16798,7 @@
         <v>105</v>
       </c>
       <c r="I113" s="10" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="114" spans="1:9">
@@ -16806,7 +16806,7 @@
         <v>5118057</v>
       </c>
       <c r="B114" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C114">
         <v>2720</v>
@@ -16824,7 +16824,7 @@
         <v>105</v>
       </c>
       <c r="I114" s="10" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="115" spans="1:9">
@@ -16832,7 +16832,7 @@
         <v>1000656471</v>
       </c>
       <c r="B115" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C115">
         <v>5850</v>
@@ -16850,7 +16850,7 @@
         <v>105</v>
       </c>
       <c r="I115" s="10" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="116" spans="1:9">
@@ -16858,7 +16858,7 @@
         <v>1001073370</v>
       </c>
       <c r="B116" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C116">
         <v>3500</v>
@@ -16876,7 +16876,7 @@
         <v>105</v>
       </c>
       <c r="I116" s="10" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="117" spans="1:9">
@@ -16884,7 +16884,7 @@
         <v>1000365868</v>
       </c>
       <c r="B117" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C117">
         <v>4380</v>
@@ -16902,7 +16902,7 @@
         <v>105</v>
       </c>
       <c r="I117" s="10" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="118" spans="1:9">
@@ -16910,7 +16910,7 @@
         <v>1001740101</v>
       </c>
       <c r="B118" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C118">
         <v>4200</v>
@@ -16928,7 +16928,7 @@
         <v>105</v>
       </c>
       <c r="I118" s="10" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="119" spans="1:9">
@@ -16962,7 +16962,7 @@
         <v>1000125337</v>
       </c>
       <c r="B120" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C120">
         <v>6280</v>
@@ -16980,7 +16980,7 @@
         <v>105</v>
       </c>
       <c r="I120" s="10" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="121" spans="1:9">
@@ -16988,7 +16988,7 @@
         <v>5013230</v>
       </c>
       <c r="B121" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C121">
         <v>4780</v>
@@ -17006,7 +17006,7 @@
         <v>105</v>
       </c>
       <c r="I121" s="10" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="122" spans="1:9">
@@ -17014,7 +17014,7 @@
         <v>5043538</v>
       </c>
       <c r="B122" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C122">
         <v>11500</v>
@@ -17032,7 +17032,7 @@
         <v>105</v>
       </c>
       <c r="I122" s="10" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="123" spans="1:9">
@@ -17040,7 +17040,7 @@
         <v>1001382381</v>
       </c>
       <c r="B123" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C123">
         <v>8990</v>
@@ -17058,7 +17058,7 @@
         <v>105</v>
       </c>
       <c r="I123" s="10" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="124" spans="1:9">
@@ -17066,7 +17066,7 @@
         <v>1002159262</v>
       </c>
       <c r="B124" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C124">
         <v>2500</v>
@@ -17084,7 +17084,7 @@
         <v>105</v>
       </c>
       <c r="I124" s="10" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="125" spans="1:9">
@@ -17092,7 +17092,7 @@
         <v>1002286852</v>
       </c>
       <c r="B125" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C125">
         <v>3540</v>
@@ -17110,7 +17110,7 @@
         <v>105</v>
       </c>
       <c r="I125" s="10" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="126" spans="1:9">
@@ -17118,7 +17118,7 @@
         <v>5052356</v>
       </c>
       <c r="B126" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C126">
         <v>12300</v>
@@ -17136,7 +17136,7 @@
         <v>105</v>
       </c>
       <c r="I126" s="10" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="127" spans="1:9">
@@ -17144,7 +17144,7 @@
         <v>1000499057</v>
       </c>
       <c r="B127" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C127">
         <v>11980</v>
@@ -17162,7 +17162,7 @@
         <v>105</v>
       </c>
       <c r="I127" s="10" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="128" spans="1:9">
@@ -17170,7 +17170,7 @@
         <v>1000791609</v>
       </c>
       <c r="B128" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C128">
         <v>1520</v>
@@ -17188,7 +17188,7 @@
         <v>105</v>
       </c>
       <c r="I128" s="10" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="129" spans="1:9">
@@ -17196,7 +17196,7 @@
         <v>1000074625</v>
       </c>
       <c r="B129" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C129">
         <v>20900</v>
@@ -17214,7 +17214,7 @@
         <v>105</v>
       </c>
       <c r="I129" s="10" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="130" spans="1:9">
@@ -17222,7 +17222,7 @@
         <v>5077457</v>
       </c>
       <c r="B130" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C130">
         <v>4320</v>
@@ -17240,7 +17240,7 @@
         <v>105</v>
       </c>
       <c r="I130" s="10" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="131" spans="1:9">
@@ -17248,7 +17248,7 @@
         <v>1000349503</v>
       </c>
       <c r="B131" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C131">
         <v>2250</v>
@@ -17266,7 +17266,7 @@
         <v>105</v>
       </c>
       <c r="I131" s="10" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="132" spans="1:9">
@@ -17300,7 +17300,7 @@
         <v>5054219</v>
       </c>
       <c r="B133" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C133">
         <v>2490</v>
@@ -17318,7 +17318,7 @@
         <v>105</v>
       </c>
       <c r="I133" s="10" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="134" spans="1:9">
@@ -17326,7 +17326,7 @@
         <v>1001959559</v>
       </c>
       <c r="B134" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C134">
         <v>2400</v>
@@ -17344,7 +17344,7 @@
         <v>105</v>
       </c>
       <c r="I134" s="10" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="135" spans="1:9">
@@ -17378,7 +17378,7 @@
         <v>1000777595</v>
       </c>
       <c r="B136" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C136">
         <v>2980</v>
@@ -17396,7 +17396,7 @@
         <v>105</v>
       </c>
       <c r="I136" s="10" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="137" spans="1:9">
@@ -17430,7 +17430,7 @@
         <v>1002225093</v>
       </c>
       <c r="B138" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C138">
         <v>3980</v>
@@ -17448,7 +17448,7 @@
         <v>105</v>
       </c>
       <c r="I138" s="10" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="139" spans="1:9">
@@ -17456,7 +17456,7 @@
         <v>5030130</v>
       </c>
       <c r="B139" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C139">
         <v>3980</v>
@@ -17474,7 +17474,7 @@
         <v>105</v>
       </c>
       <c r="I139" s="10" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="140" spans="1:9">
@@ -17482,7 +17482,7 @@
         <v>1001317277</v>
       </c>
       <c r="B140" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C140">
         <v>3780</v>
@@ -17500,7 +17500,7 @@
         <v>105</v>
       </c>
       <c r="I140" s="10" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="141" spans="1:9">
@@ -17508,7 +17508,7 @@
         <v>5118059</v>
       </c>
       <c r="B141" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C141">
         <v>2720</v>
@@ -17526,7 +17526,7 @@
         <v>105</v>
       </c>
       <c r="I141" s="10" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="142" spans="1:9">
@@ -17560,7 +17560,7 @@
         <v>1001861625</v>
       </c>
       <c r="B143" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C143">
         <v>6000</v>
@@ -17578,7 +17578,7 @@
         <v>105</v>
       </c>
       <c r="I143" s="10" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="144" spans="1:9">
@@ -17586,7 +17586,7 @@
         <v>1002108866</v>
       </c>
       <c r="B144" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C144">
         <v>8900</v>
@@ -17604,7 +17604,7 @@
         <v>105</v>
       </c>
       <c r="I144" s="10" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="145" spans="1:9">
@@ -17612,7 +17612,7 @@
         <v>1002221130</v>
       </c>
       <c r="B145" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C145">
         <v>3480</v>
@@ -17630,7 +17630,7 @@
         <v>105</v>
       </c>
       <c r="I145" s="10" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="146" spans="1:9">
@@ -17638,7 +17638,7 @@
         <v>5049808</v>
       </c>
       <c r="B146" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C146">
         <v>2500</v>
@@ -17656,7 +17656,7 @@
         <v>105</v>
       </c>
       <c r="I146" s="10" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="147" spans="1:9">
@@ -17664,7 +17664,7 @@
         <v>1000528989</v>
       </c>
       <c r="B147" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C147">
         <v>3980</v>
@@ -17682,7 +17682,7 @@
         <v>105</v>
       </c>
       <c r="I147" s="10" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="148" spans="1:9">
@@ -17690,7 +17690,7 @@
         <v>1000739633</v>
       </c>
       <c r="B148" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C148">
         <v>3900</v>
@@ -17708,7 +17708,7 @@
         <v>105</v>
       </c>
       <c r="I148" s="10" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="149" spans="1:9">
@@ -17716,7 +17716,7 @@
         <v>5121162</v>
       </c>
       <c r="B149" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C149">
         <v>2380</v>
@@ -17734,7 +17734,7 @@
         <v>105</v>
       </c>
       <c r="I149" s="10" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="150" spans="1:9">
@@ -17742,7 +17742,7 @@
         <v>1000891294</v>
       </c>
       <c r="B150" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C150">
         <v>11900</v>
@@ -17760,7 +17760,7 @@
         <v>105</v>
       </c>
       <c r="I150" s="10" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="151" spans="1:9">
@@ -17768,7 +17768,7 @@
         <v>1002280048</v>
       </c>
       <c r="B151" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C151">
         <v>2250</v>
@@ -17786,7 +17786,7 @@
         <v>105</v>
       </c>
       <c r="I151" s="10" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="152" spans="1:9">
@@ -17794,7 +17794,7 @@
         <v>1002003498</v>
       </c>
       <c r="B152" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C152">
         <v>3500</v>
@@ -17812,7 +17812,7 @@
         <v>105</v>
       </c>
       <c r="I152" s="10" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="153" spans="1:9">
@@ -17820,7 +17820,7 @@
         <v>1000485694</v>
       </c>
       <c r="B153" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C153">
         <v>4480</v>
@@ -17838,7 +17838,7 @@
         <v>105</v>
       </c>
       <c r="I153" s="10" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="154" spans="1:9">
@@ -17846,7 +17846,7 @@
         <v>1000612634</v>
       </c>
       <c r="B154" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C154">
         <v>6490</v>
@@ -17864,7 +17864,7 @@
         <v>105</v>
       </c>
       <c r="I154" s="10" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="155" spans="1:9">
@@ -17872,7 +17872,7 @@
         <v>1002475314</v>
       </c>
       <c r="B155" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C155">
         <v>4730</v>
@@ -17890,7 +17890,7 @@
         <v>105</v>
       </c>
       <c r="I155" s="10" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="156" spans="1:9">
@@ -17898,7 +17898,7 @@
         <v>1000198198</v>
       </c>
       <c r="B156" t="s">
-        <v>387</v>
+        <v>59</v>
       </c>
       <c r="C156">
         <v>3200</v>
@@ -17916,7 +17916,7 @@
         <v>105</v>
       </c>
       <c r="I156" s="10" t="s">
-        <v>388</v>
+        <v>60</v>
       </c>
     </row>
     <row r="157" spans="1:9">
